--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -197,6 +197,153 @@
     <t xml:space="preserve">F-331</t>
   </si>
   <si>
+    <t xml:space="preserve">Diagnosticar e corrigir falha no sistema do motor: temperatura dos gases de escape (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adilton · Gabriel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reprogramada por conta de box bloqueado por conta de guindaste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem e sanar vazamento na bomba de direção hidráulica (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanar vazamento na mangueira da bomba de direção (serviço interno base Mossoró solicitar codigo do tubo original)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar limpeza nos bornes das baterias;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baixa de carteira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar lanterna corujinha do teto LE e revisar iluminação;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnosticar e corrigir falhas: ABS e caixa de marchas (embreagem);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir tacógrafo com dificuldade de visualização do display;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completar nível de óleo do motor e corrigir vazamentos no mesmo (OS ABRIR OS · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baixa de pendências backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frota não chegou na oficina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir junta da tampa de válvulas com vazamento (OS 7157 · 20804638 (junta motor D11))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor acabamento inferior frontal do parachoque (20711859)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor vidrala sanefa/carga e corrigir empeno no varão (1628953 peça adaptada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir iluminação interna da cabine (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir palhetas do limpador de para-brisas (LD não limpa) 8189631(2 UND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Júnior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar tubo de escapamento inferior;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar placa dianteira e traseira;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar retrovisor LD e inferior LE;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar extensão da porta e saia lateral LD;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor quebra-sol do motorista (está dentro da cabine);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir chave geral avariada (OS 7158 · 21243844)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor tampa de proteção das tomadas frontais (erraque) LD (OS 7159 · 20410141)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir amortecedor dianteiro da cabine LD com desgaste nas buchas, apresentando ruído "ferro com ferro" ao movimentar a mesma (OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7160</t>
+  </si>
+  <si>
     <t xml:space="preserve">Realizar alinhamento</t>
   </si>
   <si>
@@ -206,139 +353,25 @@
     <t xml:space="preserve">Alinhar pneus</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagnosticar e corrigir falha no sistema do motor: temperatura dos gases de escape (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adilton · Gabriel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preventiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reprogramada por conta de box bloqueado por conta de guindaste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar lavagem e sanar vazamento na bomba de direção hidráulica (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanar vazamento na mangueira da bomba de direção (serviço interno base Mossoró solicitar codigo do tubo original)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar limpeza nos bornes das baterias;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baixa de carteira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar lanterna corujinha do teto LE e revisar iluminação;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosticar e corrigir falhas: ABS e caixa de marchas (embreagem);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir tacógrafo com dificuldade de visualização do display;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir palhetas do limpador de para-brisas (LD não limpa) 8189631(2 UND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar nível de óleo do motor e corrigir vazamentos no mesmo (OS ABRIR OS · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heliton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baixa de pendências backlog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frota não chegou na oficina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir junta da tampa de válvulas com vazamento (OS 7157 · 20804638 (junta motor D11))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir chave geral avariada (OS 7158 · 21243844)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor acabamento inferior frontal do parachoque (20711859)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor vidrala sanefa/carga e corrigir empeno no varão (1628953 peça adaptada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir iluminação interna da cabine (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar tubo de escapamento inferior;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar placa dianteira e traseira;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar retrovisor LD e inferior LE;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar extensão da porta e saia lateral LD;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor quebra-sol do motorista (está dentro da cabine);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21322</t>
+    <t xml:space="preserve">Motor esguicho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peça não chegou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mola gás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina d'agua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mola do pedal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interruptor</t>
   </si>
   <si>
     <t xml:space="preserve">Substituir junta da tampa de válvulas com vazamento;20538793</t>
@@ -347,16 +380,28 @@
     <t xml:space="preserve">21334</t>
   </si>
   <si>
-    <t xml:space="preserve">Repor tampa de proteção das tomadas frontais (erraque) LD (OS 7159 · 20410141)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir amortecedor dianteiro da cabine LD com desgaste nas buchas, apresentando ruído "ferro com ferro" ao movimentar a mesma (OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7160</t>
+    <t xml:space="preserve">Corrigir vazamento na mangueira de arrefecimento do compressor;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completar óleo hidráulico da direção;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir lanterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir chicote eletrico</t>
   </si>
   <si>
     <t xml:space="preserve">Substituir vedação da tampa do cubo de roda dianteiro LD (OS 7161 · 3986189)</t>
@@ -365,51 +410,6 @@
     <t xml:space="preserve">7161</t>
   </si>
   <si>
-    <t xml:space="preserve">Motor esguicho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peça não chegou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mola gás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lamina d'agua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mola do pedal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interruptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir vazamento na mangueira de arrefecimento do compressor;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar óleo hidráulico da direção;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir lanterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir chicote eletrico</t>
-  </si>
-  <si>
     <t xml:space="preserve">Substituir flexível do escapamento avariado, evitando danificar mangueiras e chicotes (OS 7162 · 20442244)</t>
   </si>
   <si>
@@ -845,187 +845,187 @@
     <t xml:space="preserve">FIXAR CHICOTE ELETRICO SOLTO</t>
   </si>
   <si>
+    <t xml:space="preserve">F-326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar troca de pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema: Pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem e corrigir vazamento na bomba de direção (serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Substituir lanterna do pisca dianteiro LD avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Substituir extensão da porta LE avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Substituir saia lateral da cabine LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Programar recuperação da barra de direção curta com início de folga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar a substituição das juntas do coletor de escapamento (20855371 (6 unidades))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21341</t>
+  </si>
+  <si>
     <t xml:space="preserve">FICAR CHICOTE ELETRICO SOLTO NO BLOCO DE COMANDO</t>
   </si>
   <si>
-    <t xml:space="preserve">F-326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar troca de pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema: Pneus</t>
+    <t xml:space="preserve">FIXAR GRADE FRONTAL SOLTA</t>
   </si>
   <si>
     <t xml:space="preserve">Substituir batentes dos eixos traseiros LE e LD gastos (serviço empresa especializada/20390836 (4 unidades))</t>
   </si>
   <si>
-    <t xml:space="preserve">Realizar lavagem e corrigir vazamento na bomba de direção (serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19784</t>
-  </si>
-  <si>
     <t xml:space="preserve">Realizar regulagem do travamento das portas, motorista relata que as mesmas estão abrindo em movimento (serviço interno Matriz)</t>
   </si>
   <si>
-    <t xml:space="preserve">6. Substituir lanterna do pisca dianteiro LD avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Substituir extensão da porta LE avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Substituir saia lateral da cabine LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Programar recuperação da barra de direção curta com início de folga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar a substituição das juntas do coletor de escapamento (20855371 (6 unidades))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21341</t>
+    <t xml:space="preserve">Programar recuperação das barras de direção curta e longa (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição da lona de freio terceiro eixo LD avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21343</t>
   </si>
   <si>
     <t xml:space="preserve">F-789</t>
   </si>
   <si>
-    <t xml:space="preserve">FIXAR GRADE FRONTAL SOLTA</t>
+    <t xml:space="preserve">F-938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar palhetas do climatizador</t>
   </si>
   <si>
     <t xml:space="preserve">CORRIGIR MARCAÇÃO DE NICEL DE COMBUSTIVEL</t>
   </si>
   <si>
+    <t xml:space="preserve">ARLA CONTAMINADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSOR DE NICEL DE AGUA COM FALHA</t>
+  </si>
+  <si>
     <t xml:space="preserve">F-1064</t>
   </si>
   <si>
     <t xml:space="preserve">Trocar e calibrar pneus</t>
   </si>
   <si>
+    <t xml:space="preserve">Soldar base do paralama dianteiro LD avariada (20453900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor tampa da caixa de fusíveis LD (OS 20352 · 20398773)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir para-sol avariado (82245535)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar válvula de freio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema: Freios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROCAR PNEUS E FERRAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROCAR E FERRAR PNEUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIORIDADE DO KAIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Substituir paralama dianteiro LD avariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Substituir lente da lanterna traseira LD avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Corujinha lateral: Avaria no lado direito (LD).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpeza do climatizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir acabamento do retrovisor inferior LD (item em aplicação direta ou realizar pedido 21169971)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARCAÇA INTERNA DO FAROL (20453627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir bomba d'água com princípio de vazamento pelo selo lateral (20538820)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Vidros: Revisar a visibilidade dos vidros frontal e laterais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Grade frontal: Apresenta avaria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Corote: Verificar fixação, pois está batendo no para-lama.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Lameira: Avaria no lado esquerdo (LE).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Para-lama: Parafuso do lado direito (LD) folgado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição lona de freio dianteira LD avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição da lona de freio dianteiro LE avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alinhar</t>
+  </si>
+  <si>
     <t xml:space="preserve">F-1065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soldar base do paralama dianteiro LD avariada (20453900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor tampa da caixa de fusíveis LD (OS 20352 · 20398773)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar válvula de freio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema: Freios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar recuperação das barras de direção curta e longa (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição da lona de freio terceiro eixo LD avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar palhetas do climatizador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARLA CONTAMINADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENSOR DE NICEL DE AGUA COM FALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir acabamento do retrovisor inferior LD (item em aplicação direta ou realizar pedido 21169971)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir para-sol avariado (82245535)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir bomba d'água com princípio de vazamento pelo selo lateral (20538820)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TROCAR PNEUS E FERRAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TROCAR E FERRAR PNEUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRIORIDADE DO KAIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Substituir paralama dianteiro LD avariado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Substituir lente da lanterna traseira LD avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Corujinha lateral: Avaria no lado direito (LD).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limpeza do climatizador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARCAÇA INTERNA DO FAROL (20453627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Vidros: Revisar a visibilidade dos vidros frontal e laterais.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Grade frontal: Apresenta avaria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Corote: Verificar fixação, pois está batendo no para-lama.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Lameira: Avaria no lado esquerdo (LE).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Para-lama: Parafuso do lado direito (LD) folgado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição lona de freio dianteira LD avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição da lona de freio dianteiro LE avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alinhar</t>
   </si>
   <si>
     <t xml:space="preserve">Realizar troca de óleo e filtro</t>
@@ -1889,11 +1889,11 @@
       </c>
       <c r="B3" s="4" t="n">
         <f aca="true">TODAY()</f>
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C3" s="5" t="str">
         <f aca="false">IF($B$3="","",TEXT($B$3,"[$-416]dddd"))</f>
-        <v>segunda-feira</v>
+        <v>terça-feira</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>3</v>
@@ -1912,7 +1912,7 @@
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D4" s="7" t="n">
         <f aca="false">COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G4" s="9" t="n">
         <f aca="false">IF($D$4=0,"",$F$4/$D$4)</f>
-        <v>0.133333333333333</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="H4" s="10" t="n">
         <f aca="false">COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;")-COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;",$E$7:$E$706,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="str">
         <f aca="false">"Atrasadas, de dias anteriores:  "&amp;(COUNTIFS($A$7:$A$706,"&lt;"&amp;$B$3,$C$7:$C$706,"&lt;&gt;")-COUNTIFS($A$7:$A$706,"&lt;"&amp;$B$3,$C$7:$C$706,"&lt;&gt;",$D$7:$D$706,"Sim"))&amp;"        |        Sem data, esperando entrar na programação:  "&amp;(COUNTIFS($C$7:$C$706,"&lt;&gt;")-COUNTIFS($C$7:$C$706,"&lt;&gt;",$A$7:$A$706,"&lt;&gt;"))</f>
-        <v>Atrasadas, de dias anteriores:  0        |        Sem data, esperando entrar na programação:  79</v>
+        <v>Atrasadas, de dias anteriores:  10        |        Sem data, esperando entrar na programação:  79</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1978,14 +1978,18 @@
         <v>16</v>
       </c>
       <c r="D7" s="14"/>
-      <c r="E7" s="16"/>
+      <c r="E7" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="F7" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="15"/>
+        <v>19</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
@@ -1995,20 +1999,20 @@
         <v>15</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>20</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2019,17 +2023,17 @@
         <v>15</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>23</v>
@@ -2040,44 +2044,42 @@
         <v>46265</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>26</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H11" s="15"/>
     </row>
@@ -2086,20 +2088,20 @@
         <v>46265</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H12" s="15"/>
     </row>
@@ -2108,20 +2110,20 @@
         <v>46265</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H13" s="15"/>
     </row>
@@ -2130,20 +2132,20 @@
         <v>46265</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H14" s="15"/>
     </row>
@@ -2152,7 +2154,7 @@
         <v>46265</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>37</v>
@@ -2162,105 +2164,109 @@
         <v>38</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="H16" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="16" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="16" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="16" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2268,92 +2274,86 @@
         <v>46266</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="16" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>23</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="16" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>23</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="16" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>26</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15"/>
     </row>
@@ -2362,20 +2362,20 @@
         <v>46266</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H24" s="15"/>
     </row>
@@ -2384,20 +2384,20 @@
         <v>46266</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H25" s="15"/>
     </row>
@@ -2406,97 +2406,99 @@
         <v>46266</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F27" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F28" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G28" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="16" t="s">
+      <c r="G29" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>47</v>
-      </c>
+      <c r="H29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>68</v>
@@ -2506,37 +2508,37 @@
         <v>69</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2551,16 +2553,16 @@
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2571,20 +2573,20 @@
         <v>15</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2595,20 +2597,20 @@
         <v>15</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2616,68 +2618,64 @@
         <v>46267</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="16" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H37" s="15"/>
     </row>
@@ -2686,7 +2684,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>80</v>
@@ -2696,10 +2694,10 @@
         <v>81</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H38" s="15"/>
     </row>
@@ -2708,7 +2706,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>82</v>
@@ -2718,10 +2716,10 @@
         <v>83</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H39" s="15"/>
     </row>
@@ -2730,20 +2728,20 @@
         <v>46267</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="16" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H40" s="15"/>
     </row>
@@ -2752,29 +2750,31 @@
         <v>46267</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="16" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>87</v>
@@ -2784,13 +2784,13 @@
         <v>88</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2798,7 +2798,7 @@
         <v>46267</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>89</v>
@@ -2808,13 +2808,13 @@
         <v>90</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2830,7 +2830,7 @@
       <c r="D44" s="14"/>
       <c r="E44" s="16"/>
       <c r="F44" s="15" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="G44" s="15" t="s">
         <v>93</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>95</v>
@@ -2854,7 +2854,7 @@
         <v>97</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="G45" s="15" t="s">
         <v>93</v>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>99</v>
@@ -2876,7 +2876,7 @@
       <c r="D46" s="14"/>
       <c r="E46" s="16"/>
       <c r="F46" s="15" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="G46" s="15" t="s">
         <v>93</v>
@@ -2966,7 +2966,7 @@
         <v>107</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3324,7 +3324,7 @@
     <row r="72" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="13"/>
       <c r="B72" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>143</v>
@@ -3333,14 +3333,14 @@
       <c r="E72" s="16"/>
       <c r="F72" s="15"/>
       <c r="G72" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H72" s="15"/>
     </row>
     <row r="73" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="13"/>
       <c r="B73" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>144</v>
@@ -3349,14 +3349,14 @@
       <c r="E73" s="16"/>
       <c r="F73" s="15"/>
       <c r="G73" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H73" s="15"/>
     </row>
     <row r="74" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="13"/>
       <c r="B74" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>145</v>
@@ -3365,14 +3365,14 @@
       <c r="E74" s="16"/>
       <c r="F74" s="15"/>
       <c r="G74" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="13"/>
       <c r="B75" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>146</v>
@@ -3381,14 +3381,14 @@
       <c r="E75" s="16"/>
       <c r="F75" s="15"/>
       <c r="G75" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H75" s="15"/>
     </row>
     <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="13"/>
       <c r="B76" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>147</v>
@@ -3397,14 +3397,14 @@
       <c r="E76" s="16"/>
       <c r="F76" s="15"/>
       <c r="G76" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H76" s="15"/>
     </row>
     <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="13"/>
       <c r="B77" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>148</v>
@@ -3413,14 +3413,14 @@
       <c r="E77" s="16"/>
       <c r="F77" s="15"/>
       <c r="G77" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H77" s="15"/>
     </row>
     <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="13"/>
       <c r="B78" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>149</v>
@@ -3429,14 +3429,14 @@
       <c r="E78" s="16"/>
       <c r="F78" s="15"/>
       <c r="G78" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H78" s="15"/>
     </row>
     <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="13"/>
       <c r="B79" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>150</v>
@@ -3445,14 +3445,14 @@
       <c r="E79" s="16"/>
       <c r="F79" s="15"/>
       <c r="G79" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H79" s="15"/>
     </row>
     <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="13"/>
       <c r="B80" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>151</v>
@@ -3461,14 +3461,14 @@
       <c r="E80" s="16"/>
       <c r="F80" s="15"/>
       <c r="G80" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H80" s="15"/>
     </row>
     <row r="81" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="13"/>
       <c r="B81" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>152</v>
@@ -3477,14 +3477,14 @@
       <c r="E81" s="16"/>
       <c r="F81" s="15"/>
       <c r="G81" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H81" s="15"/>
     </row>
     <row r="82" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="13"/>
       <c r="B82" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>153</v>
@@ -3493,14 +3493,14 @@
       <c r="E82" s="16"/>
       <c r="F82" s="15"/>
       <c r="G82" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H82" s="15"/>
     </row>
     <row r="83" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="13"/>
       <c r="B83" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>154</v>
@@ -3509,14 +3509,14 @@
       <c r="E83" s="16"/>
       <c r="F83" s="15"/>
       <c r="G83" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H83" s="15"/>
     </row>
     <row r="84" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="13"/>
       <c r="B84" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>155</v>
@@ -3525,14 +3525,14 @@
       <c r="E84" s="16"/>
       <c r="F84" s="15"/>
       <c r="G84" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H84" s="15"/>
     </row>
     <row r="85" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="13"/>
       <c r="B85" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>156</v>
@@ -3541,14 +3541,14 @@
       <c r="E85" s="16"/>
       <c r="F85" s="15"/>
       <c r="G85" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H85" s="15"/>
     </row>
     <row r="86" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="13"/>
       <c r="B86" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>157</v>
@@ -3557,14 +3557,14 @@
       <c r="E86" s="16"/>
       <c r="F86" s="15"/>
       <c r="G86" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H86" s="15"/>
     </row>
     <row r="87" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="13"/>
       <c r="B87" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>158</v>
@@ -3573,14 +3573,14 @@
       <c r="E87" s="16"/>
       <c r="F87" s="15"/>
       <c r="G87" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H87" s="15"/>
     </row>
     <row r="88" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="13"/>
       <c r="B88" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>159</v>
@@ -3589,14 +3589,14 @@
       <c r="E88" s="16"/>
       <c r="F88" s="15"/>
       <c r="G88" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H88" s="15"/>
     </row>
     <row r="89" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="13"/>
       <c r="B89" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>160</v>
@@ -3605,14 +3605,14 @@
       <c r="E89" s="16"/>
       <c r="F89" s="15"/>
       <c r="G89" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H89" s="15"/>
     </row>
     <row r="90" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="13"/>
       <c r="B90" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>161</v>
@@ -3621,14 +3621,14 @@
       <c r="E90" s="16"/>
       <c r="F90" s="15"/>
       <c r="G90" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H90" s="15"/>
     </row>
     <row r="91" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="13"/>
       <c r="B91" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>162</v>
@@ -3637,14 +3637,14 @@
       <c r="E91" s="16"/>
       <c r="F91" s="15"/>
       <c r="G91" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H91" s="15"/>
     </row>
     <row r="92" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="13"/>
       <c r="B92" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>163</v>
@@ -3653,14 +3653,14 @@
       <c r="E92" s="16"/>
       <c r="F92" s="15"/>
       <c r="G92" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H92" s="15"/>
     </row>
     <row r="93" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="13"/>
       <c r="B93" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>164</v>
@@ -3669,14 +3669,14 @@
       <c r="E93" s="16"/>
       <c r="F93" s="15"/>
       <c r="G93" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H93" s="15"/>
     </row>
     <row r="94" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="13"/>
       <c r="B94" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>165</v>
@@ -3685,14 +3685,14 @@
       <c r="E94" s="16"/>
       <c r="F94" s="15"/>
       <c r="G94" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H94" s="15"/>
     </row>
     <row r="95" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="13"/>
       <c r="B95" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>166</v>
@@ -3701,14 +3701,14 @@
       <c r="E95" s="16"/>
       <c r="F95" s="15"/>
       <c r="G95" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H95" s="15"/>
     </row>
     <row r="96" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="13"/>
       <c r="B96" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>167</v>
@@ -3717,14 +3717,14 @@
       <c r="E96" s="16"/>
       <c r="F96" s="15"/>
       <c r="G96" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H96" s="15"/>
     </row>
     <row r="97" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="13"/>
       <c r="B97" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>168</v>
@@ -3733,7 +3733,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="15"/>
       <c r="G97" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H97" s="15"/>
     </row>
@@ -4395,7 +4395,7 @@
         <v>219</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H137" s="15" t="s">
         <v>220</v>
@@ -4421,7 +4421,7 @@
         <v>219</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H138" s="15" t="s">
         <v>220</v>
@@ -4445,7 +4445,7 @@
         <v>219</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H139" s="15" t="s">
         <v>220</v>
@@ -4469,7 +4469,7 @@
         <v>219</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H140" s="15" t="s">
         <v>220</v>
@@ -4493,7 +4493,7 @@
         <v>219</v>
       </c>
       <c r="G141" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H141" s="15" t="s">
         <v>220</v>
@@ -4544,7 +4544,7 @@
         <v>122</v>
       </c>
       <c r="H143" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4568,31 +4568,33 @@
         <v>122</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="13" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D145" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E145" s="16"/>
+      <c r="E145" s="16" t="s">
+        <v>234</v>
+      </c>
       <c r="F145" s="15" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="H145" s="15" t="s">
-        <v>74</v>
+        <v>235</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4600,51 +4602,47 @@
         <v>46260</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>233</v>
+        <v>105</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D146" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E146" s="16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H146" s="15" t="s">
-        <v>236</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="H146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D147" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E147" s="16" t="s">
-        <v>235</v>
-      </c>
+      <c r="E147" s="16"/>
       <c r="F147" s="15" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="H147" s="15" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4652,31 +4650,31 @@
         <v>46260</v>
       </c>
       <c r="B148" s="14" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D148" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E148" s="16" t="s">
-        <v>239</v>
-      </c>
+      <c r="E148" s="16"/>
       <c r="F148" s="15" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H148" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="H148" s="15" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>240</v>
@@ -4684,16 +4682,16 @@
       <c r="D149" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E149" s="16" t="s">
-        <v>239</v>
-      </c>
+      <c r="E149" s="16"/>
       <c r="F149" s="15" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H149" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="H149" s="15" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="13" t="n">
@@ -4713,7 +4711,7 @@
         <v>219</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H150" s="15" t="s">
         <v>220</v>
@@ -4737,7 +4735,7 @@
         <v>219</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H151" s="15" t="s">
         <v>220</v>
@@ -4748,7 +4746,7 @@
         <v>46260</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>243</v>
@@ -4756,39 +4754,39 @@
       <c r="D152" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E152" s="16"/>
+      <c r="E152" s="16" t="s">
+        <v>244</v>
+      </c>
       <c r="F152" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H152" s="15" t="s">
-        <v>220</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D153" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E153" s="16"/>
       <c r="F153" s="15" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>220</v>
+        <v>70</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4796,77 +4794,81 @@
         <v>46260</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D154" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E154" s="16"/>
       <c r="F154" s="15" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>220</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="13" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D155" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E155" s="16" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F155" s="15" t="s">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G155" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="H155" s="15"/>
+        <v>93</v>
+      </c>
+      <c r="H155" s="15" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="13" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B156" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C156" s="15" t="s">
         <v>248</v>
-      </c>
-      <c r="C156" s="15" t="s">
-        <v>92</v>
       </c>
       <c r="D156" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E156" s="16"/>
+      <c r="E156" s="16" t="s">
+        <v>237</v>
+      </c>
       <c r="F156" s="15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="H156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="13" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>249</v>
@@ -4874,57 +4876,57 @@
       <c r="D157" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E157" s="16"/>
+      <c r="E157" s="16" t="s">
+        <v>250</v>
+      </c>
       <c r="F157" s="15" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="H157" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="13" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D158" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E158" s="16"/>
+      <c r="E158" s="16" t="s">
+        <v>252</v>
+      </c>
       <c r="F158" s="15" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="H158" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>252</v>
+        <v>92</v>
       </c>
       <c r="D159" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E159" s="16"/>
       <c r="F159" s="15" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="G159" s="15" t="s">
         <v>93</v>
@@ -4936,20 +4938,20 @@
         <v>46261</v>
       </c>
       <c r="B160" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D160" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E160" s="16"/>
       <c r="F160" s="15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>93</v>
+        <v>255</v>
       </c>
       <c r="H160" s="15"/>
     </row>
@@ -4958,25 +4960,23 @@
         <v>46261</v>
       </c>
       <c r="B161" s="14" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D161" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E161" s="16" t="s">
-        <v>235</v>
-      </c>
+      <c r="E161" s="16"/>
       <c r="F161" s="15" t="s">
-        <v>41</v>
+        <v>230</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>236</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4984,103 +4984,103 @@
         <v>46261</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D162" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E162" s="16" t="s">
-        <v>239</v>
-      </c>
+      <c r="E162" s="16"/>
       <c r="F162" s="15" t="s">
-        <v>41</v>
+        <v>230</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H162" s="15"/>
+        <v>122</v>
+      </c>
+      <c r="H162" s="15" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D163" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E163" s="16"/>
       <c r="F163" s="15" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="H163" s="15" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B164" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C164" s="15" t="s">
         <v>260</v>
-      </c>
-      <c r="C164" s="15" t="s">
-        <v>257</v>
       </c>
       <c r="D164" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E164" s="16"/>
       <c r="F164" s="15" t="s">
-        <v>258</v>
+        <v>66</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="H164" s="15" t="s">
-        <v>259</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="H164" s="15"/>
     </row>
     <row r="165" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B165" s="14" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>96</v>
+        <v>261</v>
       </c>
       <c r="D165" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="F165" s="15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G165" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H165" s="15"/>
+      <c r="H165" s="15" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>262</v>
@@ -5089,108 +5089,110 @@
         <v>210</v>
       </c>
       <c r="E166" s="16" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="H166" s="15"/>
     </row>
     <row r="167" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D167" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F167" s="15" t="s">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="H167" s="15"/>
     </row>
     <row r="168" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B168" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C168" s="15" t="s">
         <v>266</v>
-      </c>
-      <c r="C168" s="15" t="s">
-        <v>267</v>
       </c>
       <c r="D168" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E168" s="16"/>
       <c r="F168" s="15" t="s">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H168" s="15"/>
+        <v>266</v>
+      </c>
+      <c r="H168" s="15" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D169" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E169" s="16"/>
       <c r="F169" s="15" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="G169" s="15" t="s">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="H169" s="15" t="s">
-        <v>74</v>
+        <v>268</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D170" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E170" s="16"/>
       <c r="F170" s="15" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>122</v>
+        <v>272</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5198,75 +5200,71 @@
         <v>46262</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>233</v>
+        <v>24</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>270</v>
+        <v>96</v>
       </c>
       <c r="D171" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="F171" s="15" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H171" s="15" t="s">
-        <v>236</v>
-      </c>
+      <c r="H171" s="15"/>
     </row>
     <row r="172" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D172" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E172" s="16" t="s">
-        <v>272</v>
-      </c>
+      <c r="E172" s="16"/>
       <c r="F172" s="15" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H172" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="H172" s="15" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>15</v>
+        <v>216</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D173" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E173" s="16" t="s">
-        <v>20</v>
-      </c>
+      <c r="E173" s="16"/>
       <c r="F173" s="15" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="G173" s="15" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H173" s="15" t="s">
-        <v>23</v>
+        <v>220</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5274,23 +5272,23 @@
         <v>46262</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D174" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E174" s="16"/>
       <c r="F174" s="15" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5311,7 +5309,7 @@
         <v>219</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H175" s="15" t="s">
         <v>220</v>
@@ -5335,7 +5333,7 @@
         <v>219</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H176" s="15" t="s">
         <v>220</v>
@@ -5346,7 +5344,7 @@
         <v>46262</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>280</v>
@@ -5356,21 +5354,19 @@
       </c>
       <c r="E177" s="16"/>
       <c r="F177" s="15" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H177" s="15" t="s">
-        <v>220</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="H177" s="15"/>
     </row>
     <row r="178" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="13" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>281</v>
@@ -5378,23 +5374,25 @@
       <c r="D178" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E178" s="16"/>
+      <c r="E178" s="16" t="s">
+        <v>234</v>
+      </c>
       <c r="F178" s="15" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="H178" s="15" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="13" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>282</v>
@@ -5402,23 +5400,25 @@
       <c r="D179" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E179" s="16"/>
+      <c r="E179" s="16" t="s">
+        <v>234</v>
+      </c>
       <c r="F179" s="15" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="H179" s="15" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="13" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>266</v>
+        <v>15</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>283</v>
@@ -5426,21 +5426,25 @@
       <c r="D180" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E180" s="16"/>
+      <c r="E180" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="F180" s="15" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H180" s="15"/>
+        <v>19</v>
+      </c>
+      <c r="H180" s="15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>284</v>
@@ -5448,17 +5452,15 @@
       <c r="D181" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E181" s="16" t="s">
-        <v>235</v>
-      </c>
+      <c r="E181" s="16"/>
       <c r="F181" s="15" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="G181" s="15" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="H181" s="15" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5479,7 +5481,7 @@
         <v>219</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H182" s="15" t="s">
         <v>220</v>
@@ -5503,7 +5505,7 @@
         <v>219</v>
       </c>
       <c r="G183" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H183" s="15" t="s">
         <v>220</v>
@@ -5527,7 +5529,7 @@
         <v>219</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H184" s="15" t="s">
         <v>220</v>
@@ -5551,7 +5553,7 @@
         <v>219</v>
       </c>
       <c r="G185" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H185" s="15" t="s">
         <v>220</v>
@@ -5562,7 +5564,7 @@
         <v>46263</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>289</v>
@@ -5570,16 +5572,16 @@
       <c r="D186" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E186" s="16"/>
+      <c r="E186" s="16" t="s">
+        <v>252</v>
+      </c>
       <c r="F186" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H186" s="15" t="s">
-        <v>220</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H186" s="15"/>
     </row>
     <row r="187" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="13" t="n">
@@ -5595,7 +5597,7 @@
         <v>210</v>
       </c>
       <c r="E187" s="16" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="F187" s="15" t="s">
         <v>212</v>
@@ -5610,7 +5612,7 @@
         <v>46263</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="C188" s="15" t="s">
         <v>291</v>
@@ -5618,36 +5620,34 @@
       <c r="D188" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E188" s="16" t="s">
-        <v>265</v>
-      </c>
+      <c r="E188" s="16"/>
       <c r="F188" s="15" t="s">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="H188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="13" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="D189" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E189" s="16"/>
       <c r="F189" s="15" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>267</v>
+        <v>93</v>
       </c>
       <c r="H189" s="15"/>
     </row>
@@ -5665,16 +5665,16 @@
         <v>210</v>
       </c>
       <c r="E190" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5691,16 +5691,16 @@
         <v>210</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F191" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G191" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H191" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5717,16 +5717,16 @@
         <v>210</v>
       </c>
       <c r="E192" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H192" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5743,21 +5743,21 @@
         <v>210</v>
       </c>
       <c r="E193" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F193" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G193" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H193" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="13" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>297</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E194" s="16"/>
       <c r="F194" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G194" s="15" t="s">
         <v>299</v>
@@ -10984,7 +10984,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>302</v>
@@ -11001,10 +11001,10 @@
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>304</v>
@@ -11012,7 +11012,7 @@
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>305</v>
@@ -11026,7 +11026,7 @@
         <v>307</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>308</v>
@@ -11037,7 +11037,7 @@
         <v>91</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>309</v>
@@ -11045,7 +11045,7 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>310</v>
@@ -11109,14 +11109,14 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B14" s="19"/>
       <c r="D14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B15" s="19"/>
       <c r="D15" s="20" t="s">
@@ -11140,13 +11140,13 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B19" s="19"/>
     </row>
@@ -11188,7 +11188,7 @@
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B26" s="19"/>
     </row>
@@ -11200,7 +11200,7 @@
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B28" s="19"/>
     </row>
@@ -11230,7 +11230,7 @@
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B33" s="19"/>
     </row>

--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Listas" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$244</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$248</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Dia a dia'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Dia a dia'!$A$6:$H$706</definedName>
   </definedNames>
@@ -147,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="455">
   <si>
     <t xml:space="preserve">PROGRAMAÇÃO DIÁRIA  ·  MAKRO TRANSPORTES</t>
   </si>
@@ -593,6 +593,9 @@
     <t xml:space="preserve">Substituir pneu 1º eixo LE devido desgaste</t>
   </si>
   <si>
+    <t xml:space="preserve">007305</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pendências de inspeção</t>
   </si>
   <si>
@@ -602,60 +605,114 @@
     <t xml:space="preserve">Lubrificar graxeiros da quinta roda entre os bitrens</t>
   </si>
   <si>
+    <t xml:space="preserve">007306</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corrigir trinca no lastro</t>
   </si>
   <si>
+    <t xml:space="preserve">007307</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reapertar parafusos da tampa do cubo 1º eixo LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007308</t>
+  </si>
+  <si>
     <t xml:space="preserve">Regular freios 1º eixo LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007310</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixar grade de proteção do ciclista LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007313</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixar para-lamas folgados 2º eixo LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007317</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixar para-lamas folgados LE</t>
   </si>
   <si>
+    <t xml:space="preserve">007318</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reposicionar pinos da balança 2º e 3º eixo LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007316</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corrigir travessa avariada ao lado direito da quinta roda</t>
   </si>
   <si>
+    <t xml:space="preserve">007319</t>
+  </si>
+  <si>
     <t xml:space="preserve">F-1039</t>
   </si>
   <si>
     <t xml:space="preserve">Repor estepe faltante da carreta</t>
   </si>
   <si>
+    <t xml:space="preserve">007320</t>
+  </si>
+  <si>
     <t xml:space="preserve">Repor porca de roda faltante 2º eixo LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007321</t>
+  </si>
+  <si>
     <t xml:space="preserve">Substituir tampa do cubo 3º eixo LE</t>
   </si>
   <si>
+    <t xml:space="preserve">007322</t>
+  </si>
+  <si>
     <t xml:space="preserve">Substituir grade traseira com apoio faltante no LE</t>
   </si>
   <si>
+    <t xml:space="preserve">007323</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corrigir trincas no lastro da carreta</t>
   </si>
   <si>
+    <t xml:space="preserve">007324</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corrigir iluminação meia-luz dianteira LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007325</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corrigir parafusos do para-choque traseiro LD</t>
   </si>
   <si>
+    <t xml:space="preserve">007326</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixar para-lamas folgados LD e LE</t>
   </si>
   <si>
+    <t xml:space="preserve">007328</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reapertar tirante folgado 3º eixo LE</t>
   </si>
   <si>
+    <t xml:space="preserve">007330</t>
+  </si>
+  <si>
     <t xml:space="preserve">Repor acabamento do cinto do banco do motorista (0586501)</t>
   </si>
   <si>
@@ -695,72 +752,135 @@
     <t xml:space="preserve">Substituir vareta de nível de óleo avariada</t>
   </si>
   <si>
+    <t xml:space="preserve">021400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir junta da tampa de válvulas devido vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir válvula termostática e tampa do reservatório contaminado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir amortecedores do 3º eixo LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir amortecedores da cabine (horizontais traseiros e verticais dianteiros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir joystick de mudanças</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanar vazamento no tubo de enchimento / vedação do cárter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar retrovisor inferior LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolar fiação exposta do sensor de temperatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar caixa do chicote das unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar módulo do motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios 3º eixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios 1º eixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir fixação da lameira traseira LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar cabo do varão da válvula sensível à carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar tampa superior do catalisador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar mangueira do dreno do AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir iluminação interna da cabine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir faixa refletiva do para-choque traseiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar barra V dianteira e traseira devido folga</t>
+  </si>
+  <si>
     <t xml:space="preserve">21378</t>
   </si>
   <si>
-    <t xml:space="preserve">Substituir junta da tampa de válvulas devido vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir válvula termostática e tampa do reservatório contaminado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir amortecedores do 3º eixo LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir amortecedores da cabine (horizontais traseiros e verticais dianteiros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir joystick de mudanças</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanar vazamento no tubo de enchimento / vedação do cárter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar retrovisor inferior LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolar fiação exposta do sensor de temperatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar caixa do chicote das unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar módulo do motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios 3º eixo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios 1º eixo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir fixação da lameira traseira LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar cabo do varão da válvula sensível à carga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar tampa superior do catalisador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar mangueira do dreno do AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir iluminação interna da cabine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir faixa refletiva do para-choque traseiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar barra V dianteira e traseira devido folga</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cardan Nordeste (externo)</t>
   </si>
   <si>
@@ -785,6 +905,33 @@
     <t xml:space="preserve">Terceirizada — Rodo Ceará</t>
   </si>
   <si>
+    <t xml:space="preserve">F-938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desobstruir esguichos dos limpadores de para-brisas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar lameiras dianteiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar indicadores de porcas folgadas nas rodas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios do terceiro eixo LE e LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021397</t>
+  </si>
+  <si>
     <t xml:space="preserve">F-964</t>
   </si>
   <si>
@@ -1047,9 +1194,6 @@
   </si>
   <si>
     <t xml:space="preserve">Calibrar e trocar pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-938</t>
   </si>
   <si>
     <t xml:space="preserve">Trocar palhetas do climatizador</t>
@@ -2171,7 +2315,7 @@
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="str">
         <f aca="false">"Atrasadas, de dias anteriores:  "&amp;(COUNTIFS($A$7:$A$706,"&lt;"&amp;$B$3,$C$7:$C$706,"&lt;&gt;")-COUNTIFS($A$7:$A$706,"&lt;"&amp;$B$3,$C$7:$C$706,"&lt;&gt;",$D$7:$D$706,"Sim"))&amp;"        |        Sem data, esperando entrar na programação:  "&amp;(COUNTIFS($C$7:$C$706,"&lt;&gt;")-COUNTIFS($C$7:$C$706,"&lt;&gt;",$A$7:$A$706,"&lt;&gt;"))</f>
-        <v>Atrasadas, de dias anteriores:  16        |        Sem data, esperando entrar na programação:  87</v>
+        <v>Atrasadas, de dias anteriores:  16        |        Sem data, esperando entrar na programação:  91</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -3672,13 +3816,15 @@
         <v>147</v>
       </c>
       <c r="D75" s="14"/>
-      <c r="E75" s="16"/>
+      <c r="E75" s="16" t="s">
+        <v>148</v>
+      </c>
       <c r="F75" s="15"/>
       <c r="G75" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3687,16 +3833,18 @@
         <v>146</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D76" s="14"/>
-      <c r="E76" s="16"/>
+      <c r="E76" s="16" t="s">
+        <v>152</v>
+      </c>
       <c r="F76" s="15"/>
       <c r="G76" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3705,16 +3853,18 @@
         <v>146</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D77" s="14"/>
-      <c r="E77" s="16"/>
+      <c r="E77" s="16" t="s">
+        <v>154</v>
+      </c>
       <c r="F77" s="15"/>
       <c r="G77" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3723,16 +3873,18 @@
         <v>146</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D78" s="14"/>
-      <c r="E78" s="16"/>
+      <c r="E78" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="F78" s="15"/>
       <c r="G78" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3741,16 +3893,18 @@
         <v>146</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D79" s="14"/>
-      <c r="E79" s="16"/>
+      <c r="E79" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="F79" s="15"/>
       <c r="G79" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3759,16 +3913,18 @@
         <v>146</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D80" s="14"/>
-      <c r="E80" s="16"/>
+      <c r="E80" s="16" t="s">
+        <v>160</v>
+      </c>
       <c r="F80" s="15"/>
       <c r="G80" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3777,16 +3933,18 @@
         <v>146</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D81" s="14"/>
-      <c r="E81" s="16"/>
+      <c r="E81" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="F81" s="15"/>
       <c r="G81" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3795,16 +3953,18 @@
         <v>146</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D82" s="14"/>
-      <c r="E82" s="16"/>
+      <c r="E82" s="16" t="s">
+        <v>164</v>
+      </c>
       <c r="F82" s="15"/>
       <c r="G82" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3813,16 +3973,18 @@
         <v>146</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D83" s="14"/>
-      <c r="E83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>166</v>
+      </c>
       <c r="F83" s="15"/>
       <c r="G83" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,178 +3993,198 @@
         <v>146</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D84" s="14"/>
-      <c r="E84" s="16"/>
+      <c r="E84" s="16" t="s">
+        <v>168</v>
+      </c>
       <c r="F84" s="15"/>
       <c r="G84" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="13"/>
       <c r="B85" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D85" s="14"/>
-      <c r="E85" s="16"/>
+      <c r="E85" s="16" t="s">
+        <v>171</v>
+      </c>
       <c r="F85" s="15"/>
       <c r="G85" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="13"/>
       <c r="B86" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D86" s="14"/>
-      <c r="E86" s="16"/>
+      <c r="E86" s="16" t="s">
+        <v>173</v>
+      </c>
       <c r="F86" s="15"/>
       <c r="G86" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="13"/>
       <c r="B87" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D87" s="14"/>
-      <c r="E87" s="16"/>
+      <c r="E87" s="16" t="s">
+        <v>175</v>
+      </c>
       <c r="F87" s="15"/>
       <c r="G87" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="13"/>
       <c r="B88" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D88" s="14"/>
-      <c r="E88" s="16"/>
+      <c r="E88" s="16" t="s">
+        <v>177</v>
+      </c>
       <c r="F88" s="15"/>
       <c r="G88" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="13"/>
       <c r="B89" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D89" s="14"/>
-      <c r="E89" s="16"/>
+      <c r="E89" s="16" t="s">
+        <v>179</v>
+      </c>
       <c r="F89" s="15"/>
       <c r="G89" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="13"/>
       <c r="B90" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D90" s="14"/>
-      <c r="E90" s="16"/>
+      <c r="E90" s="16" t="s">
+        <v>181</v>
+      </c>
       <c r="F90" s="15"/>
       <c r="G90" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="13"/>
       <c r="B91" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D91" s="14"/>
-      <c r="E91" s="16"/>
+      <c r="E91" s="16" t="s">
+        <v>183</v>
+      </c>
       <c r="F91" s="15"/>
       <c r="G91" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="13"/>
       <c r="B92" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D92" s="14"/>
-      <c r="E92" s="16"/>
+      <c r="E92" s="16" t="s">
+        <v>185</v>
+      </c>
       <c r="F92" s="15"/>
       <c r="G92" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="13"/>
       <c r="B93" s="14" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D93" s="14"/>
-      <c r="E93" s="16"/>
+      <c r="E93" s="16" t="s">
+        <v>187</v>
+      </c>
       <c r="F93" s="15"/>
       <c r="G93" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H93" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4011,7 +4193,7 @@
         <v>15</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="D94" s="14"/>
       <c r="E94" s="16"/>
@@ -4020,7 +4202,7 @@
         <v>19</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4029,7 +4211,7 @@
         <v>15</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="16"/>
@@ -4038,1359 +4220,1333 @@
         <v>19</v>
       </c>
       <c r="H95" s="15" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="13"/>
       <c r="B96" s="14" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="16"/>
       <c r="F96" s="15"/>
       <c r="G96" s="15" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="13"/>
       <c r="B97" s="14" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D97" s="14"/>
       <c r="E97" s="16"/>
       <c r="F97" s="15"/>
       <c r="G97" s="15" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="13"/>
       <c r="B98" s="14" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="16"/>
       <c r="F98" s="15"/>
       <c r="G98" s="15" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H98" s="15" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="13"/>
       <c r="B99" s="14" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D99" s="14"/>
       <c r="E99" s="16"/>
       <c r="F99" s="15"/>
       <c r="G99" s="15" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H99" s="15" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="13"/>
       <c r="B100" s="14" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D100" s="14"/>
       <c r="E100" s="16"/>
       <c r="F100" s="15"/>
       <c r="G100" s="15" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="13"/>
       <c r="B101" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="D101" s="14"/>
       <c r="E101" s="16" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="F101" s="15"/>
       <c r="G101" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H101" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="13"/>
       <c r="B102" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="16" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F102" s="15"/>
       <c r="G102" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="13"/>
       <c r="B103" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="D103" s="14"/>
       <c r="E103" s="16" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F103" s="15"/>
       <c r="G103" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H103" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="13"/>
       <c r="B104" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="16" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="F104" s="15"/>
       <c r="G104" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="13"/>
       <c r="B105" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D105" s="14"/>
       <c r="E105" s="16" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="F105" s="15"/>
       <c r="G105" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="13"/>
       <c r="B106" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="D106" s="14"/>
       <c r="E106" s="16" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="F106" s="15"/>
       <c r="G106" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="13"/>
       <c r="B107" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D107" s="14"/>
       <c r="E107" s="16" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="F107" s="15"/>
       <c r="G107" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="13"/>
       <c r="B108" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="16" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="F108" s="15"/>
       <c r="G108" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="13"/>
       <c r="B109" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="16" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="F109" s="15"/>
       <c r="G109" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="13"/>
       <c r="B110" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="D110" s="14"/>
       <c r="E110" s="16" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F110" s="15"/>
       <c r="G110" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
       <c r="B111" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D111" s="14"/>
       <c r="E111" s="16" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="F111" s="15"/>
       <c r="G111" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H111" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="13"/>
       <c r="B112" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="D112" s="14"/>
       <c r="E112" s="16" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="F112" s="15"/>
       <c r="G112" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="13"/>
       <c r="B113" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="D113" s="14"/>
       <c r="E113" s="16" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="F113" s="15"/>
       <c r="G113" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H113" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="13"/>
       <c r="B114" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D114" s="14"/>
       <c r="E114" s="16" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="F114" s="15"/>
       <c r="G114" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="13"/>
       <c r="B115" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D115" s="14"/>
       <c r="E115" s="16" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="F115" s="15"/>
       <c r="G115" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="13"/>
       <c r="B116" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="D116" s="14"/>
       <c r="E116" s="16" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="F116" s="15"/>
       <c r="G116" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="13"/>
       <c r="B117" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="D117" s="14"/>
       <c r="E117" s="16" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="F117" s="15"/>
       <c r="G117" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="13"/>
       <c r="B118" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="D118" s="14"/>
       <c r="E118" s="16" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="F118" s="15"/>
       <c r="G118" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="13"/>
       <c r="B119" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D119" s="14"/>
       <c r="E119" s="16" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="F119" s="15"/>
       <c r="G119" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="13"/>
       <c r="B120" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="D120" s="14"/>
       <c r="E120" s="16" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="F120" s="15"/>
       <c r="G120" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="13"/>
       <c r="B121" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="D121" s="14"/>
       <c r="E121" s="16" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="F121" s="15"/>
       <c r="G121" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H121" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="13"/>
       <c r="B122" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="16" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="13"/>
       <c r="B123" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="D123" s="14"/>
       <c r="E123" s="16" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="G123" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="13"/>
       <c r="B124" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="16" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="13"/>
       <c r="B125" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="D125" s="14"/>
       <c r="E125" s="16" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="G125" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H125" s="15" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="13"/>
       <c r="B126" s="14" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="D126" s="14"/>
       <c r="E126" s="16" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="13"/>
       <c r="B127" s="14" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="D127" s="14"/>
-      <c r="E127" s="16"/>
+      <c r="E127" s="16" t="s">
+        <v>254</v>
+      </c>
       <c r="F127" s="15"/>
       <c r="G127" s="15" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="H127" s="15"/>
     </row>
     <row r="128" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="13"/>
       <c r="B128" s="14" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="D128" s="14"/>
-      <c r="E128" s="16"/>
+      <c r="E128" s="16" t="s">
+        <v>256</v>
+      </c>
       <c r="F128" s="15"/>
       <c r="G128" s="15" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="H128" s="15"/>
     </row>
     <row r="129" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="13"/>
       <c r="B129" s="14" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="D129" s="14"/>
-      <c r="E129" s="16"/>
+      <c r="E129" s="16" t="s">
+        <v>258</v>
+      </c>
       <c r="F129" s="15"/>
       <c r="G129" s="15" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="H129" s="15"/>
     </row>
     <row r="130" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="13"/>
       <c r="B130" s="14" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="D130" s="14"/>
-      <c r="E130" s="16"/>
+      <c r="E130" s="16" t="s">
+        <v>260</v>
+      </c>
       <c r="F130" s="15"/>
       <c r="G130" s="15" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="H130" s="15"/>
     </row>
     <row r="131" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="13"/>
       <c r="B131" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="D131" s="14"/>
       <c r="E131" s="16"/>
       <c r="F131" s="15"/>
       <c r="G131" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H131" s="15"/>
     </row>
     <row r="132" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="13"/>
       <c r="B132" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="D132" s="14"/>
       <c r="E132" s="16"/>
       <c r="F132" s="15"/>
       <c r="G132" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H132" s="15"/>
     </row>
     <row r="133" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="13"/>
       <c r="B133" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="D133" s="14"/>
       <c r="E133" s="16"/>
       <c r="F133" s="15"/>
       <c r="G133" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H133" s="15"/>
     </row>
     <row r="134" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="13"/>
       <c r="B134" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="D134" s="14"/>
       <c r="E134" s="16"/>
       <c r="F134" s="15"/>
       <c r="G134" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H134" s="15"/>
     </row>
     <row r="135" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="13"/>
       <c r="B135" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="D135" s="14"/>
       <c r="E135" s="16"/>
       <c r="F135" s="15"/>
       <c r="G135" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H135" s="15"/>
     </row>
     <row r="136" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="13"/>
       <c r="B136" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="D136" s="14"/>
       <c r="E136" s="16"/>
       <c r="F136" s="15"/>
       <c r="G136" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H136" s="15"/>
     </row>
     <row r="137" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="13"/>
       <c r="B137" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D137" s="14"/>
       <c r="E137" s="16"/>
       <c r="F137" s="15"/>
       <c r="G137" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H137" s="15"/>
     </row>
     <row r="138" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="13"/>
       <c r="B138" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="16"/>
       <c r="F138" s="15"/>
       <c r="G138" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H138" s="15"/>
     </row>
     <row r="139" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="13"/>
       <c r="B139" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="D139" s="14"/>
       <c r="E139" s="16"/>
       <c r="F139" s="15"/>
       <c r="G139" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H139" s="15"/>
     </row>
     <row r="140" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="13"/>
       <c r="B140" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="16"/>
       <c r="F140" s="15"/>
       <c r="G140" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H140" s="15"/>
     </row>
     <row r="141" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="13"/>
       <c r="B141" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>228</v>
+        <v>273</v>
       </c>
       <c r="D141" s="14"/>
       <c r="E141" s="16"/>
       <c r="F141" s="15"/>
       <c r="G141" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H141" s="15"/>
     </row>
     <row r="142" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="13"/>
       <c r="B142" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>229</v>
+        <v>274</v>
       </c>
       <c r="D142" s="14"/>
       <c r="E142" s="16"/>
       <c r="F142" s="15"/>
       <c r="G142" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H142" s="15"/>
     </row>
     <row r="143" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="13"/>
       <c r="B143" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="D143" s="14"/>
       <c r="E143" s="16"/>
       <c r="F143" s="15"/>
       <c r="G143" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H143" s="15"/>
     </row>
     <row r="144" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="13"/>
       <c r="B144" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="D144" s="14"/>
       <c r="E144" s="16"/>
       <c r="F144" s="15"/>
       <c r="G144" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H144" s="15"/>
     </row>
     <row r="145" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="13"/>
       <c r="B145" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="D145" s="14"/>
       <c r="E145" s="16"/>
       <c r="F145" s="15"/>
       <c r="G145" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H145" s="15"/>
     </row>
     <row r="146" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="13"/>
       <c r="B146" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="D146" s="14"/>
       <c r="E146" s="16"/>
       <c r="F146" s="15"/>
       <c r="G146" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="13"/>
       <c r="B147" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="D147" s="14"/>
       <c r="E147" s="16"/>
       <c r="F147" s="15"/>
       <c r="G147" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H147" s="15"/>
     </row>
     <row r="148" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="13"/>
       <c r="B148" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="D148" s="14"/>
       <c r="E148" s="16"/>
       <c r="F148" s="15"/>
       <c r="G148" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H148" s="15"/>
     </row>
     <row r="149" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="13"/>
       <c r="B149" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="D149" s="14"/>
       <c r="E149" s="16"/>
       <c r="F149" s="15"/>
       <c r="G149" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H149" s="15"/>
     </row>
     <row r="150" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="13"/>
       <c r="B150" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="D150" s="14"/>
       <c r="E150" s="16"/>
       <c r="F150" s="15"/>
       <c r="G150" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H150" s="15"/>
     </row>
     <row r="151" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="13"/>
       <c r="B151" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="D151" s="14"/>
       <c r="E151" s="16"/>
       <c r="F151" s="15"/>
       <c r="G151" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H151" s="15"/>
     </row>
     <row r="152" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="13"/>
       <c r="B152" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="D152" s="14"/>
       <c r="E152" s="16"/>
       <c r="F152" s="15"/>
       <c r="G152" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="13"/>
       <c r="B153" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="D153" s="14"/>
       <c r="E153" s="16"/>
       <c r="F153" s="15"/>
       <c r="G153" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="13"/>
       <c r="B154" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D154" s="14"/>
       <c r="E154" s="16"/>
       <c r="F154" s="15"/>
       <c r="G154" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="13"/>
       <c r="B155" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="D155" s="14"/>
       <c r="E155" s="16"/>
       <c r="F155" s="15"/>
       <c r="G155" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="13"/>
       <c r="B156" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="16"/>
       <c r="F156" s="15"/>
       <c r="G156" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="13"/>
       <c r="B157" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="D157" s="14"/>
       <c r="E157" s="16"/>
       <c r="F157" s="15"/>
       <c r="G157" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="13"/>
       <c r="B158" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="D158" s="14"/>
       <c r="E158" s="16"/>
       <c r="F158" s="15"/>
       <c r="G158" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="13"/>
       <c r="B159" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="D159" s="14"/>
       <c r="E159" s="16"/>
       <c r="F159" s="15"/>
       <c r="G159" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H159" s="15"/>
     </row>
     <row r="160" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="13"/>
       <c r="B160" s="14" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="D160" s="14"/>
       <c r="E160" s="16"/>
       <c r="F160" s="15"/>
       <c r="G160" s="15" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="H160" s="15"/>
     </row>
     <row r="161" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="13"/>
       <c r="B161" s="14" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="D161" s="14"/>
       <c r="E161" s="16"/>
       <c r="F161" s="15"/>
       <c r="G161" s="15" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="H161" s="15"/>
     </row>
     <row r="162" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="13" t="n">
-        <v>46258</v>
-      </c>
+      <c r="A162" s="13"/>
       <c r="B162" s="14" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D162" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E162" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F162" s="15" t="s">
-        <v>255</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="D162" s="14"/>
+      <c r="E162" s="16"/>
+      <c r="F162" s="15"/>
       <c r="G162" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H162" s="15"/>
     </row>
     <row r="163" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="13" t="n">
-        <v>46258</v>
-      </c>
+      <c r="A163" s="13"/>
       <c r="B163" s="14" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="D163" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E163" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F163" s="15" t="s">
-        <v>255</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="D163" s="14"/>
+      <c r="E163" s="16"/>
+      <c r="F163" s="15"/>
       <c r="G163" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H163" s="15"/>
     </row>
     <row r="164" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="13" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A164" s="13"/>
       <c r="B164" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D164" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E164" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="F164" s="15" t="s">
-        <v>262</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="D164" s="14"/>
+      <c r="E164" s="16"/>
+      <c r="F164" s="15"/>
       <c r="G164" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H164" s="15" t="s">
         <v>263</v>
       </c>
+      <c r="H164" s="15"/>
     </row>
     <row r="165" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="13" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A165" s="13"/>
       <c r="B165" s="14" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="D165" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E165" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="F165" s="15" t="s">
-        <v>262</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="D165" s="14"/>
+      <c r="E165" s="16"/>
+      <c r="F165" s="15"/>
       <c r="G165" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H165" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="H165" s="15"/>
     </row>
     <row r="166" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="13" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E166" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E166" s="16" t="s">
+        <v>303</v>
+      </c>
       <c r="F166" s="15" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H166" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H166" s="15"/>
     </row>
     <row r="167" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="13" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E167" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E167" s="16" t="s">
+        <v>307</v>
+      </c>
       <c r="F167" s="15" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H167" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H167" s="15"/>
     </row>
     <row r="168" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="13" t="n">
         <v>46259</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E168" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E168" s="16" t="s">
+        <v>310</v>
+      </c>
       <c r="F168" s="15" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>43</v>
       </c>
       <c r="H168" s="15" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5398,47 +5554,49 @@
         <v>46259</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="F169" s="15" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G169" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H169" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="13" t="n">
         <v>46259</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E170" s="16"/>
       <c r="F170" s="15" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5446,121 +5604,119 @@
         <v>46259</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E171" s="16"/>
       <c r="F171" s="15" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="G171" s="15" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="H171" s="15" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="13" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E172" s="16" t="s">
-        <v>277</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E172" s="16"/>
       <c r="F172" s="15" t="s">
-        <v>109</v>
+        <v>311</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="H172" s="15" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="13" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="F173" s="15" t="s">
-        <v>72</v>
+        <v>304</v>
       </c>
       <c r="G173" s="15" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="H173" s="15"/>
     </row>
     <row r="174" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="13" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E174" s="16"/>
       <c r="F174" s="15" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>263</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="13" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E175" s="16"/>
       <c r="F175" s="15" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H175" s="15" t="s">
-        <v>263</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5568,23 +5724,25 @@
         <v>46260</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E176" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E176" s="16" t="s">
+        <v>326</v>
+      </c>
       <c r="F176" s="15" t="s">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>43</v>
+        <v>327</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5592,47 +5750,47 @@
         <v>46260</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>259</v>
+        <v>15</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E177" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E177" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="F177" s="15" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H177" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="H177" s="15"/>
     </row>
     <row r="178" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E178" s="16"/>
       <c r="F178" s="15" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="G178" s="15" t="s">
         <v>43</v>
       </c>
       <c r="H178" s="15" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5640,47 +5798,47 @@
         <v>46260</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E179" s="16" t="s">
-        <v>289</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E179" s="16"/>
       <c r="F179" s="15" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H179" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H179" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E180" s="16"/>
       <c r="F180" s="15" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5688,164 +5846,168 @@
         <v>46260</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E181" s="16"/>
       <c r="F181" s="15" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="G181" s="15" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="H181" s="15" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="13" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E182" s="16" t="s">
-        <v>277</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E182" s="16"/>
       <c r="F182" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="H182" s="15" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="13" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E183" s="16" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="F183" s="15" t="s">
-        <v>72</v>
+        <v>304</v>
       </c>
       <c r="G183" s="15" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="H183" s="15"/>
     </row>
     <row r="184" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="13" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B184" s="14" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E184" s="16" t="s">
-        <v>295</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E184" s="16"/>
       <c r="F184" s="15" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H184" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="H184" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="13" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B185" s="14" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E185" s="16" t="s">
-        <v>297</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E185" s="16"/>
       <c r="F185" s="15" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="G185" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H185" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="H185" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E186" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E186" s="16" t="s">
+        <v>326</v>
+      </c>
       <c r="F186" s="15" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="H186" s="15"/>
+        <v>327</v>
+      </c>
+      <c r="H186" s="15" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E187" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E187" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="F187" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G187" s="15" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="H187" s="15"/>
     </row>
@@ -5854,215 +6016,211 @@
         <v>46261</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="C188" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="D188" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="D188" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E188" s="16"/>
+      <c r="E188" s="16" t="s">
+        <v>344</v>
+      </c>
       <c r="F188" s="15" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H188" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E189" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E189" s="16" t="s">
+        <v>346</v>
+      </c>
       <c r="F189" s="15" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H189" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H189" s="15"/>
     </row>
     <row r="190" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E190" s="16"/>
       <c r="F190" s="15" t="s">
-        <v>273</v>
+        <v>109</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H190" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="H190" s="15"/>
     </row>
     <row r="191" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="13" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E191" s="16"/>
       <c r="F191" s="15" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G191" s="15" t="s">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="H191" s="15"/>
     </row>
     <row r="192" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="13" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="D192" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E192" s="16" t="s">
-        <v>277</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E192" s="16"/>
       <c r="F192" s="15" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="H192" s="15" t="s">
-        <v>279</v>
+        <v>25</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="13" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E193" s="16" t="s">
-        <v>281</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E193" s="16"/>
       <c r="F193" s="15" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="G193" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="H193" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="H193" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="13" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E194" s="16" t="s">
-        <v>310</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E194" s="16"/>
       <c r="F194" s="15" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="H194" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="H194" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B195" s="14" t="s">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E195" s="16"/>
       <c r="F195" s="15" t="s">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="G195" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="H195" s="15" t="s">
-        <v>314</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="H195" s="15"/>
     </row>
     <row r="196" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B196" s="14" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E196" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E196" s="16" t="s">
+        <v>326</v>
+      </c>
       <c r="F196" s="15" t="s">
-        <v>313</v>
+        <v>72</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6070,46 +6228,46 @@
         <v>46262</v>
       </c>
       <c r="B197" s="14" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E197" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E197" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="F197" s="15" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G197" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="H197" s="15" t="s">
-        <v>319</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="H197" s="15"/>
     </row>
     <row r="198" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="H198" s="15"/>
     </row>
@@ -6118,23 +6276,23 @@
         <v>46262</v>
       </c>
       <c r="B199" s="14" t="s">
-        <v>259</v>
+        <v>359</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="D199" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E199" s="16"/>
       <c r="F199" s="15" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="G199" s="15" t="s">
-        <v>43</v>
+        <v>360</v>
       </c>
       <c r="H199" s="15" t="s">
-        <v>263</v>
+        <v>362</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6142,23 +6300,23 @@
         <v>46262</v>
       </c>
       <c r="B200" s="14" t="s">
-        <v>259</v>
+        <v>363</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="D200" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E200" s="16"/>
       <c r="F200" s="15" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>43</v>
+        <v>360</v>
       </c>
       <c r="H200" s="15" t="s">
-        <v>263</v>
+        <v>362</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6166,23 +6324,23 @@
         <v>46262</v>
       </c>
       <c r="B201" s="14" t="s">
-        <v>259</v>
+        <v>364</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E201" s="16"/>
       <c r="F201" s="15" t="s">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="G201" s="15" t="s">
-        <v>43</v>
+        <v>366</v>
       </c>
       <c r="H201" s="15" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6190,47 +6348,47 @@
         <v>46262</v>
       </c>
       <c r="B202" s="14" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>325</v>
+        <v>368</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E202" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E202" s="16" t="s">
+        <v>369</v>
+      </c>
       <c r="F202" s="15" t="s">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H202" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="H202" s="15"/>
     </row>
     <row r="203" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B203" s="14" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E203" s="16"/>
       <c r="F203" s="15" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>43</v>
       </c>
       <c r="H203" s="15" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6238,169 +6396,165 @@
         <v>46262</v>
       </c>
       <c r="B204" s="14" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="D204" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E204" s="16"/>
       <c r="F204" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="H204" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H204" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E205" s="16"/>
       <c r="F205" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G205" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="H205" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H205" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="13" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B206" s="14" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E206" s="16" t="s">
-        <v>277</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E206" s="16"/>
       <c r="F206" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="H206" s="15" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="13" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B207" s="14" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E207" s="16" t="s">
-        <v>277</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E207" s="16"/>
       <c r="F207" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G207" s="15" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="H207" s="15" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="13" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B208" s="14" t="s">
-        <v>26</v>
+        <v>375</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E208" s="16" t="s">
-        <v>28</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E208" s="16"/>
       <c r="F208" s="15" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H208" s="15" t="s">
-        <v>30</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="H208" s="15"/>
     </row>
     <row r="209" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="13" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B209" s="14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E209" s="16"/>
       <c r="F209" s="15" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="G209" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H209" s="15" t="s">
-        <v>263</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="H209" s="15"/>
     </row>
     <row r="210" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B210" s="14" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E210" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E210" s="16" t="s">
+        <v>326</v>
+      </c>
       <c r="F210" s="15" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>43</v>
+        <v>327</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6408,23 +6562,25 @@
         <v>46263</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E211" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E211" s="16" t="s">
+        <v>326</v>
+      </c>
       <c r="F211" s="15" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="G211" s="15" t="s">
-        <v>43</v>
+        <v>327</v>
       </c>
       <c r="H211" s="15" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6432,23 +6588,25 @@
         <v>46263</v>
       </c>
       <c r="B212" s="14" t="s">
-        <v>259</v>
+        <v>26</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E212" s="16"/>
+        <v>302</v>
+      </c>
+      <c r="E212" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="F212" s="15" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H212" s="15" t="s">
-        <v>263</v>
+        <v>30</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6456,23 +6614,23 @@
         <v>46263</v>
       </c>
       <c r="B213" s="14" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="D213" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E213" s="16"/>
       <c r="F213" s="15" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="G213" s="15" t="s">
         <v>43</v>
       </c>
       <c r="H213" s="15" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6480,190 +6638,186 @@
         <v>46263</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E214" s="16" t="s">
-        <v>297</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E214" s="16"/>
       <c r="F214" s="15" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H214" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H214" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="215" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B215" s="14" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="D215" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E215" s="16" t="s">
-        <v>297</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E215" s="16"/>
       <c r="F215" s="15" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G215" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H215" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H215" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="216" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B216" s="14" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D216" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E216" s="16"/>
       <c r="F216" s="15" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="H216" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H216" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="217" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="13" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B217" s="14" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>306</v>
+        <v>386</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E217" s="16"/>
       <c r="F217" s="15" t="s">
-        <v>109</v>
+        <v>311</v>
       </c>
       <c r="G217" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="H217" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H217" s="15" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="218" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="13" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E218" s="16" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="F218" s="15" t="s">
-        <v>18</v>
+        <v>304</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H218" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H218" s="15"/>
     </row>
     <row r="219" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="13" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E219" s="16" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="F219" s="15" t="s">
-        <v>18</v>
+        <v>304</v>
       </c>
       <c r="G219" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H219" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="H219" s="15"/>
     </row>
     <row r="220" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="13" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>69</v>
+        <v>252</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E220" s="16" t="s">
-        <v>346</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E220" s="16"/>
       <c r="F220" s="15" t="s">
-        <v>347</v>
+        <v>72</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>73</v>
+        <v>349</v>
       </c>
       <c r="H220" s="15"/>
     </row>
     <row r="221" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="13" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>69</v>
+        <v>390</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E221" s="16" t="s">
-        <v>349</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E221" s="16"/>
       <c r="F221" s="15" t="s">
-        <v>347</v>
+        <v>109</v>
       </c>
       <c r="G221" s="15" t="s">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="H221" s="15"/>
     </row>
@@ -6672,48 +6826,52 @@
         <v>46265</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>349</v>
+        <v>28</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H222" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H222" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="223" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E223" s="16" t="s">
-        <v>352</v>
+        <v>28</v>
       </c>
       <c r="F223" s="15" t="s">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="G223" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H223" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H223" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="224" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="13" t="n">
@@ -6723,16 +6881,16 @@
         <v>69</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E224" s="16" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>72</v>
+        <v>395</v>
       </c>
       <c r="G224" s="15" t="s">
         <v>73</v>
@@ -6747,16 +6905,16 @@
         <v>69</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="D225" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E225" s="16" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="F225" s="15" t="s">
-        <v>72</v>
+        <v>395</v>
       </c>
       <c r="G225" s="15" t="s">
         <v>73</v>
@@ -6771,16 +6929,16 @@
         <v>69</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="D226" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E226" s="16" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>72</v>
+        <v>395</v>
       </c>
       <c r="G226" s="15" t="s">
         <v>73</v>
@@ -6795,16 +6953,16 @@
         <v>69</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E227" s="16" t="s">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>72</v>
+        <v>395</v>
       </c>
       <c r="G227" s="15" t="s">
         <v>73</v>
@@ -6819,13 +6977,13 @@
         <v>69</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E228" s="16" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="F228" s="15" t="s">
         <v>72</v>
@@ -6843,13 +7001,13 @@
         <v>69</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="F229" s="15" t="s">
         <v>72</v>
@@ -6867,13 +7025,13 @@
         <v>69</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="D230" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E230" s="16" t="s">
-        <v>71</v>
+        <v>406</v>
       </c>
       <c r="F230" s="15" t="s">
         <v>72</v>
@@ -6885,71 +7043,67 @@
     </row>
     <row r="231" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="13" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E231" s="16" t="s">
-        <v>28</v>
+        <v>408</v>
       </c>
       <c r="F231" s="15" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G231" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H231" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H231" s="15"/>
     </row>
     <row r="232" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="13" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B232" s="14" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C232" s="15" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E232" s="16" t="s">
-        <v>28</v>
+        <v>410</v>
       </c>
       <c r="F232" s="15" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H232" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H232" s="15"/>
     </row>
     <row r="233" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="13" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B233" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C233" s="15" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E233" s="16" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="F233" s="15" t="s">
         <v>72</v>
@@ -6961,19 +7115,19 @@
     </row>
     <row r="234" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="13" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>371</v>
+        <v>71</v>
       </c>
       <c r="F234" s="15" t="s">
         <v>72</v>
@@ -6988,48 +7142,52 @@
         <v>46266</v>
       </c>
       <c r="B235" s="14" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C235" s="15" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>373</v>
+        <v>28</v>
       </c>
       <c r="F235" s="15" t="s">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="G235" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H235" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H235" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="236" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C236" s="15" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E236" s="16" t="s">
-        <v>375</v>
+        <v>28</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H236" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H236" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="13" t="n">
@@ -7039,13 +7197,13 @@
         <v>69</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E237" s="16" t="s">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>72</v>
@@ -7063,13 +7221,13 @@
         <v>69</v>
       </c>
       <c r="C238" s="15" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E238" s="16" t="s">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="F238" s="15" t="s">
         <v>72</v>
@@ -7087,16 +7245,16 @@
         <v>69</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="E239" s="16" t="s">
-        <v>321</v>
+        <v>421</v>
       </c>
       <c r="F239" s="15" t="s">
-        <v>109</v>
+        <v>395</v>
       </c>
       <c r="G239" s="15" t="s">
         <v>73</v>
@@ -7104,43 +7262,99 @@
       <c r="H239" s="15"/>
     </row>
     <row r="240" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="13"/>
-      <c r="B240" s="14"/>
-      <c r="C240" s="15"/>
-      <c r="D240" s="14"/>
-      <c r="E240" s="16"/>
-      <c r="F240" s="15"/>
-      <c r="G240" s="15"/>
+      <c r="A240" s="13" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B240" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C240" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D240" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E240" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="F240" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="G240" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="H240" s="15"/>
     </row>
     <row r="241" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="13"/>
-      <c r="B241" s="14"/>
-      <c r="C241" s="15"/>
-      <c r="D241" s="14"/>
-      <c r="E241" s="16"/>
-      <c r="F241" s="15"/>
-      <c r="G241" s="15"/>
+      <c r="A241" s="13" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C241" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D241" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E241" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F241" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G241" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="H241" s="15"/>
     </row>
     <row r="242" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="13"/>
-      <c r="B242" s="14"/>
-      <c r="C242" s="15"/>
-      <c r="D242" s="14"/>
-      <c r="E242" s="16"/>
-      <c r="F242" s="15"/>
-      <c r="G242" s="15"/>
+      <c r="A242" s="13" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B242" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C242" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="D242" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E242" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F242" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G242" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="H242" s="15"/>
     </row>
     <row r="243" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="13"/>
-      <c r="B243" s="14"/>
-      <c r="C243" s="15"/>
-      <c r="D243" s="14"/>
-      <c r="E243" s="16"/>
-      <c r="F243" s="15"/>
-      <c r="G243" s="15"/>
+      <c r="A243" s="13" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B243" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C243" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="D243" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E243" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="F243" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G243" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="H243" s="15"/>
     </row>
     <row r="244" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11846,13 +12060,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>380</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11860,74 +12074,74 @@
         <v>146</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>381</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="D3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11935,18 +12149,18 @@
         <v>15</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>392</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="D10" s="20"/>
     </row>
@@ -11955,70 +12169,70 @@
         <v>26</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>395</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>399</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="D14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="B15" s="19"/>
       <c r="D15" s="20" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="B16" s="19"/>
       <c r="D16" s="20" t="s">
-        <v>402</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="B17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="B18" s="19"/>
     </row>
@@ -12030,25 +12244,25 @@
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="B21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
       <c r="B22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="B23" s="19"/>
     </row>
@@ -12060,19 +12274,19 @@
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="B26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="B27" s="19"/>
     </row>
@@ -12090,49 +12304,49 @@
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="B32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="B33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>300</v>
+        <v>252</v>
       </c>
       <c r="B34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="B35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="B37" s="19"/>
     </row>

--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -10,11 +10,15 @@
   <sheets>
     <sheet name="Dia a dia" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Listas" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Movimentações" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$265</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Dia a dia'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Dia a dia'!$A$6:$H$706</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Movimentações!$A$1:$I$37</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Movimentações!$8:$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Movimentações!$A$8:$I$308</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -146,8 +150,150 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">tudo que foi pedido à operação</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">já chegaram</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">O dia em que você pediu a movimentação à operação.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">chegaram até a data prometida</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A data que a operação SE COMPROMETEU a entregar. É contra ela que o atraso é medido — sem essa data não há o que cobrar.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">no prazo ÷ entregues. É este o número para levar à reunião</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">O dia em que a frota chegou de verdade. Enquanto estiver vazio, a movimentação está em aberto.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sai sozinho: chegou menos prometida, em dias. Chegar antes conta zero.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">dias, contando só as que atrasaram</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">a soma de todos os atrasos: o tamanho do prejuízo em dias de oficina</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Quem, na operação, deu a data. Sem nome, a cobrança vira conversa.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="539">
   <si>
     <t xml:space="preserve">PROGRAMAÇÃO DIÁRIA  ·  MAKRO TRANSPORTES</t>
   </si>
@@ -1704,20 +1850,81 @@
   </si>
   <si>
     <t xml:space="preserve">F-871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOVIMENTAÇÃO DE FROTAS  ·  o que a operação prometeu e quando entregou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoje — não apague</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peça a movimentação, anote a data que a operação prometeu, e marque quando a frota chegou. O atraso e os números saem sozinhos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOVIMENTAÇÕES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTREGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO PRAZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTUALIDADE DA OPERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATRASO MÉDIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAS PERDIDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atraso = quando chegou menos quando foi prometida. Chegar antes conta como zero, não como crédito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destino / fornecedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedida em</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometida para</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chegou em</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atraso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para quê</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem prometeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ informar o fornecedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ informar para que serviço</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$-416]dd/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0%"/>
     <numFmt numFmtId="168" formatCode="@"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1861,6 +2068,37 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FFB00020"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4A5464"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FFB00020"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF4A5464"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1884,13 +2122,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF1F7"/>
-        <bgColor rgb="FFDCF3E4"/>
+        <bgColor rgb="FFEDF2FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A3170"/>
-        <bgColor rgb="FF333333"/>
+        <bgColor rgb="FF2C4272"/>
       </patternFill>
     </fill>
   </fills>
@@ -1958,7 +2196,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2047,6 +2285,26 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2056,7 +2314,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2173,6 +2431,64 @@
         <color rgb="FF98A1B2"/>
       </font>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDF2FC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2C4272"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF116B3E"/>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFB00020"/>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF2C4272"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEDF2FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF8A5A05"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF6E8CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -2187,15 +2503,15 @@
       <rgbColor rgb="FFB00020"/>
       <rgbColor rgb="FF116B3E"/>
       <rgbColor rgb="FF13164E"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF8A5A05"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFFDE4E7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF3CF"/>
-      <rgbColor rgb="FFEEF1F7"/>
+      <rgbColor rgb="FFEDF2FC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -2209,13 +2525,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFEEF1F7"/>
       <rgbColor rgb="FFDCF3E4"/>
       <rgbColor rgb="FFFFE9CC"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFDE4E7"/>
+      <rgbColor rgb="FFF6E8CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2231,13 +2547,17 @@
       <rgbColor rgb="FF9A4C00"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2A3170"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF2C4272"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -13041,4 +13361,5334 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF13164E"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:L308"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="K1" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="L1" s="23" t="n">
+        <f aca="true">TODAY()</f>
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8" t="n">
+        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;",$E$9:$E$308,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;",$E$9:$E$308,"&lt;&gt;")-COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f aca="false">IF($C$4=0,"",$D$4/$C$4)</f>
+        <v/>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="24" t="str">
+        <f aca="false">IF(COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0")=0,"",SUMIFS($F$9:$F$308,$A$9:$A$308,"&lt;&gt;")/COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25" t="n">
+        <f aca="false">SUMIFS($F$9:$F$308,$A$9:$A$308,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>528</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14" t="str">
+        <f aca="false">IF(OR($A9="",$D9="",$E9=""),"",MAX(0,$E9-$D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="14" t="str">
+        <f aca="false">IF($A9="","",IF($E9&lt;&gt;"",IF(N($F9)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D9="","Sem data prometida",IF($D9&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v>Aguardando</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14" t="str">
+        <f aca="false">IF(OR($A10="",$D10="",$E10=""),"",MAX(0,$E10-$D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="14" t="str">
+        <f aca="false">IF($A10="","",IF($E10&lt;&gt;"",IF(N($F10)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D10="","Sem data prometida",IF($D10&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14" t="str">
+        <f aca="false">IF(OR($A11="",$D11="",$E11=""),"",MAX(0,$E11-$D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="14" t="str">
+        <f aca="false">IF($A11="","",IF($E11&lt;&gt;"",IF(N($F11)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D11="","Sem data prometida",IF($D11&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14" t="str">
+        <f aca="false">IF(OR($A12="",$D12="",$E12=""),"",MAX(0,$E12-$D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="14" t="str">
+        <f aca="false">IF($A12="","",IF($E12&lt;&gt;"",IF(N($F12)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D12="","Sem data prometida",IF($D12&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14" t="str">
+        <f aca="false">IF(OR($A13="",$D13="",$E13=""),"",MAX(0,$E13-$D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="14" t="str">
+        <f aca="false">IF($A13="","",IF($E13&lt;&gt;"",IF(N($F13)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D13="","Sem data prometida",IF($D13&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14" t="str">
+        <f aca="false">IF(OR($A14="",$D14="",$E14=""),"",MAX(0,$E14-$D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="14" t="str">
+        <f aca="false">IF($A14="","",IF($E14&lt;&gt;"",IF(N($F14)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D14="","Sem data prometida",IF($D14&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="14" t="str">
+        <f aca="false">IF(OR($A15="",$D15="",$E15=""),"",MAX(0,$E15-$D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="14" t="str">
+        <f aca="false">IF($A15="","",IF($E15&lt;&gt;"",IF(N($F15)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D15="","Sem data prometida",IF($D15&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14" t="str">
+        <f aca="false">IF(OR($A16="",$D16="",$E16=""),"",MAX(0,$E16-$D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="14" t="str">
+        <f aca="false">IF($A16="","",IF($E16&lt;&gt;"",IF(N($F16)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D16="","Sem data prometida",IF($D16&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14" t="str">
+        <f aca="false">IF(OR($A17="",$D17="",$E17=""),"",MAX(0,$E17-$D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="14" t="str">
+        <f aca="false">IF($A17="","",IF($E17&lt;&gt;"",IF(N($F17)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D17="","Sem data prometida",IF($D17&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14" t="str">
+        <f aca="false">IF(OR($A18="",$D18="",$E18=""),"",MAX(0,$E18-$D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="14" t="str">
+        <f aca="false">IF($A18="","",IF($E18&lt;&gt;"",IF(N($F18)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D18="","Sem data prometida",IF($D18&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="14" t="str">
+        <f aca="false">IF(OR($A19="",$D19="",$E19=""),"",MAX(0,$E19-$D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="14" t="str">
+        <f aca="false">IF($A19="","",IF($E19&lt;&gt;"",IF(N($F19)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D19="","Sem data prometida",IF($D19&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14" t="str">
+        <f aca="false">IF(OR($A20="",$D20="",$E20=""),"",MAX(0,$E20-$D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="14" t="str">
+        <f aca="false">IF($A20="","",IF($E20&lt;&gt;"",IF(N($F20)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D20="","Sem data prometida",IF($D20&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="14" t="str">
+        <f aca="false">IF(OR($A21="",$D21="",$E21=""),"",MAX(0,$E21-$D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="14" t="str">
+        <f aca="false">IF($A21="","",IF($E21&lt;&gt;"",IF(N($F21)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D21="","Sem data prometida",IF($D21&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14" t="str">
+        <f aca="false">IF(OR($A22="",$D22="",$E22=""),"",MAX(0,$E22-$D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="14" t="str">
+        <f aca="false">IF($A22="","",IF($E22&lt;&gt;"",IF(N($F22)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D22="","Sem data prometida",IF($D22&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="14" t="str">
+        <f aca="false">IF(OR($A23="",$D23="",$E23=""),"",MAX(0,$E23-$D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="14" t="str">
+        <f aca="false">IF($A23="","",IF($E23&lt;&gt;"",IF(N($F23)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D23="","Sem data prometida",IF($D23&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14" t="str">
+        <f aca="false">IF(OR($A24="",$D24="",$E24=""),"",MAX(0,$E24-$D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="14" t="str">
+        <f aca="false">IF($A24="","",IF($E24&lt;&gt;"",IF(N($F24)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D24="","Sem data prometida",IF($D24&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14" t="str">
+        <f aca="false">IF(OR($A25="",$D25="",$E25=""),"",MAX(0,$E25-$D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="14" t="str">
+        <f aca="false">IF($A25="","",IF($E25&lt;&gt;"",IF(N($F25)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D25="","Sem data prometida",IF($D25&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="14" t="str">
+        <f aca="false">IF(OR($A26="",$D26="",$E26=""),"",MAX(0,$E26-$D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="14" t="str">
+        <f aca="false">IF($A26="","",IF($E26&lt;&gt;"",IF(N($F26)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D26="","Sem data prometida",IF($D26&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="14" t="str">
+        <f aca="false">IF(OR($A27="",$D27="",$E27=""),"",MAX(0,$E27-$D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="14" t="str">
+        <f aca="false">IF($A27="","",IF($E27&lt;&gt;"",IF(N($F27)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D27="","Sem data prometida",IF($D27&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14" t="str">
+        <f aca="false">IF(OR($A28="",$D28="",$E28=""),"",MAX(0,$E28-$D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="14" t="str">
+        <f aca="false">IF($A28="","",IF($E28&lt;&gt;"",IF(N($F28)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D28="","Sem data prometida",IF($D28&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="14" t="str">
+        <f aca="false">IF(OR($A29="",$D29="",$E29=""),"",MAX(0,$E29-$D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="14" t="str">
+        <f aca="false">IF($A29="","",IF($E29&lt;&gt;"",IF(N($F29)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D29="","Sem data prometida",IF($D29&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14" t="str">
+        <f aca="false">IF(OR($A30="",$D30="",$E30=""),"",MAX(0,$E30-$D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="14" t="str">
+        <f aca="false">IF($A30="","",IF($E30&lt;&gt;"",IF(N($F30)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D30="","Sem data prometida",IF($D30&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="14" t="str">
+        <f aca="false">IF(OR($A31="",$D31="",$E31=""),"",MAX(0,$E31-$D31))</f>
+        <v/>
+      </c>
+      <c r="G31" s="14" t="str">
+        <f aca="false">IF($A31="","",IF($E31&lt;&gt;"",IF(N($F31)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D31="","Sem data prometida",IF($D31&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="14" t="str">
+        <f aca="false">IF(OR($A32="",$D32="",$E32=""),"",MAX(0,$E32-$D32))</f>
+        <v/>
+      </c>
+      <c r="G32" s="14" t="str">
+        <f aca="false">IF($A32="","",IF($E32&lt;&gt;"",IF(N($F32)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D32="","Sem data prometida",IF($D32&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="14" t="str">
+        <f aca="false">IF(OR($A33="",$D33="",$E33=""),"",MAX(0,$E33-$D33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="14" t="str">
+        <f aca="false">IF($A33="","",IF($E33&lt;&gt;"",IF(N($F33)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D33="","Sem data prometida",IF($D33&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="14" t="str">
+        <f aca="false">IF(OR($A34="",$D34="",$E34=""),"",MAX(0,$E34-$D34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="14" t="str">
+        <f aca="false">IF($A34="","",IF($E34&lt;&gt;"",IF(N($F34)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D34="","Sem data prometida",IF($D34&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="14" t="str">
+        <f aca="false">IF(OR($A35="",$D35="",$E35=""),"",MAX(0,$E35-$D35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="14" t="str">
+        <f aca="false">IF($A35="","",IF($E35&lt;&gt;"",IF(N($F35)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D35="","Sem data prometida",IF($D35&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="14" t="str">
+        <f aca="false">IF(OR($A36="",$D36="",$E36=""),"",MAX(0,$E36-$D36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="14" t="str">
+        <f aca="false">IF($A36="","",IF($E36&lt;&gt;"",IF(N($F36)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D36="","Sem data prometida",IF($D36&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="14" t="str">
+        <f aca="false">IF(OR($A37="",$D37="",$E37=""),"",MAX(0,$E37-$D37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="14" t="str">
+        <f aca="false">IF($A37="","",IF($E37&lt;&gt;"",IF(N($F37)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D37="","Sem data prometida",IF($D37&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="14" t="str">
+        <f aca="false">IF(OR($A38="",$D38="",$E38=""),"",MAX(0,$E38-$D38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="14" t="str">
+        <f aca="false">IF($A38="","",IF($E38&lt;&gt;"",IF(N($F38)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D38="","Sem data prometida",IF($D38&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="14" t="str">
+        <f aca="false">IF(OR($A39="",$D39="",$E39=""),"",MAX(0,$E39-$D39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="14" t="str">
+        <f aca="false">IF($A39="","",IF($E39&lt;&gt;"",IF(N($F39)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D39="","Sem data prometida",IF($D39&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+    </row>
+    <row r="40" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="14" t="str">
+        <f aca="false">IF(OR($A40="",$D40="",$E40=""),"",MAX(0,$E40-$D40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="14" t="str">
+        <f aca="false">IF($A40="","",IF($E40&lt;&gt;"",IF(N($F40)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D40="","Sem data prometida",IF($D40&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+    </row>
+    <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="14" t="str">
+        <f aca="false">IF(OR($A41="",$D41="",$E41=""),"",MAX(0,$E41-$D41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="14" t="str">
+        <f aca="false">IF($A41="","",IF($E41&lt;&gt;"",IF(N($F41)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D41="","Sem data prometida",IF($D41&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+    </row>
+    <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="14" t="str">
+        <f aca="false">IF(OR($A42="",$D42="",$E42=""),"",MAX(0,$E42-$D42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="14" t="str">
+        <f aca="false">IF($A42="","",IF($E42&lt;&gt;"",IF(N($F42)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D42="","Sem data prometida",IF($D42&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+    </row>
+    <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="14" t="str">
+        <f aca="false">IF(OR($A43="",$D43="",$E43=""),"",MAX(0,$E43-$D43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="14" t="str">
+        <f aca="false">IF($A43="","",IF($E43&lt;&gt;"",IF(N($F43)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D43="","Sem data prometida",IF($D43&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+    </row>
+    <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="14" t="str">
+        <f aca="false">IF(OR($A44="",$D44="",$E44=""),"",MAX(0,$E44-$D44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="14" t="str">
+        <f aca="false">IF($A44="","",IF($E44&lt;&gt;"",IF(N($F44)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D44="","Sem data prometida",IF($D44&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+    </row>
+    <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="14" t="str">
+        <f aca="false">IF(OR($A45="",$D45="",$E45=""),"",MAX(0,$E45-$D45))</f>
+        <v/>
+      </c>
+      <c r="G45" s="14" t="str">
+        <f aca="false">IF($A45="","",IF($E45&lt;&gt;"",IF(N($F45)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D45="","Sem data prometida",IF($D45&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+    </row>
+    <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="14" t="str">
+        <f aca="false">IF(OR($A46="",$D46="",$E46=""),"",MAX(0,$E46-$D46))</f>
+        <v/>
+      </c>
+      <c r="G46" s="14" t="str">
+        <f aca="false">IF($A46="","",IF($E46&lt;&gt;"",IF(N($F46)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D46="","Sem data prometida",IF($D46&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+    </row>
+    <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="14" t="str">
+        <f aca="false">IF(OR($A47="",$D47="",$E47=""),"",MAX(0,$E47-$D47))</f>
+        <v/>
+      </c>
+      <c r="G47" s="14" t="str">
+        <f aca="false">IF($A47="","",IF($E47&lt;&gt;"",IF(N($F47)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D47="","Sem data prometida",IF($D47&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+    </row>
+    <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="14" t="str">
+        <f aca="false">IF(OR($A48="",$D48="",$E48=""),"",MAX(0,$E48-$D48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="14" t="str">
+        <f aca="false">IF($A48="","",IF($E48&lt;&gt;"",IF(N($F48)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D48="","Sem data prometida",IF($D48&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+    </row>
+    <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="14" t="str">
+        <f aca="false">IF(OR($A49="",$D49="",$E49=""),"",MAX(0,$E49-$D49))</f>
+        <v/>
+      </c>
+      <c r="G49" s="14" t="str">
+        <f aca="false">IF($A49="","",IF($E49&lt;&gt;"",IF(N($F49)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D49="","Sem data prometida",IF($D49&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+    </row>
+    <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="14" t="str">
+        <f aca="false">IF(OR($A50="",$D50="",$E50=""),"",MAX(0,$E50-$D50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="14" t="str">
+        <f aca="false">IF($A50="","",IF($E50&lt;&gt;"",IF(N($F50)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D50="","Sem data prometida",IF($D50&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+    </row>
+    <row r="51" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="14" t="str">
+        <f aca="false">IF(OR($A51="",$D51="",$E51=""),"",MAX(0,$E51-$D51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="14" t="str">
+        <f aca="false">IF($A51="","",IF($E51&lt;&gt;"",IF(N($F51)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D51="","Sem data prometida",IF($D51&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+    </row>
+    <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="14" t="str">
+        <f aca="false">IF(OR($A52="",$D52="",$E52=""),"",MAX(0,$E52-$D52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="14" t="str">
+        <f aca="false">IF($A52="","",IF($E52&lt;&gt;"",IF(N($F52)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D52="","Sem data prometida",IF($D52&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+    </row>
+    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14" t="str">
+        <f aca="false">IF(OR($A53="",$D53="",$E53=""),"",MAX(0,$E53-$D53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="14" t="str">
+        <f aca="false">IF($A53="","",IF($E53&lt;&gt;"",IF(N($F53)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D53="","Sem data prometida",IF($D53&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+    </row>
+    <row r="54" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="14" t="str">
+        <f aca="false">IF(OR($A54="",$D54="",$E54=""),"",MAX(0,$E54-$D54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="14" t="str">
+        <f aca="false">IF($A54="","",IF($E54&lt;&gt;"",IF(N($F54)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D54="","Sem data prometida",IF($D54&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+    </row>
+    <row r="55" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="14" t="str">
+        <f aca="false">IF(OR($A55="",$D55="",$E55=""),"",MAX(0,$E55-$D55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="14" t="str">
+        <f aca="false">IF($A55="","",IF($E55&lt;&gt;"",IF(N($F55)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D55="","Sem data prometida",IF($D55&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+    </row>
+    <row r="56" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="14" t="str">
+        <f aca="false">IF(OR($A56="",$D56="",$E56=""),"",MAX(0,$E56-$D56))</f>
+        <v/>
+      </c>
+      <c r="G56" s="14" t="str">
+        <f aca="false">IF($A56="","",IF($E56&lt;&gt;"",IF(N($F56)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D56="","Sem data prometida",IF($D56&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+    </row>
+    <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="14" t="str">
+        <f aca="false">IF(OR($A57="",$D57="",$E57=""),"",MAX(0,$E57-$D57))</f>
+        <v/>
+      </c>
+      <c r="G57" s="14" t="str">
+        <f aca="false">IF($A57="","",IF($E57&lt;&gt;"",IF(N($F57)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D57="","Sem data prometida",IF($D57&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+    </row>
+    <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="14" t="str">
+        <f aca="false">IF(OR($A58="",$D58="",$E58=""),"",MAX(0,$E58-$D58))</f>
+        <v/>
+      </c>
+      <c r="G58" s="14" t="str">
+        <f aca="false">IF($A58="","",IF($E58&lt;&gt;"",IF(N($F58)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D58="","Sem data prometida",IF($D58&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+    </row>
+    <row r="59" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="14" t="str">
+        <f aca="false">IF(OR($A59="",$D59="",$E59=""),"",MAX(0,$E59-$D59))</f>
+        <v/>
+      </c>
+      <c r="G59" s="14" t="str">
+        <f aca="false">IF($A59="","",IF($E59&lt;&gt;"",IF(N($F59)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D59="","Sem data prometida",IF($D59&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+    </row>
+    <row r="60" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="14" t="str">
+        <f aca="false">IF(OR($A60="",$D60="",$E60=""),"",MAX(0,$E60-$D60))</f>
+        <v/>
+      </c>
+      <c r="G60" s="14" t="str">
+        <f aca="false">IF($A60="","",IF($E60&lt;&gt;"",IF(N($F60)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D60="","Sem data prometida",IF($D60&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+    </row>
+    <row r="61" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="14"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="14" t="str">
+        <f aca="false">IF(OR($A61="",$D61="",$E61=""),"",MAX(0,$E61-$D61))</f>
+        <v/>
+      </c>
+      <c r="G61" s="14" t="str">
+        <f aca="false">IF($A61="","",IF($E61&lt;&gt;"",IF(N($F61)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D61="","Sem data prometida",IF($D61&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+    </row>
+    <row r="62" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="14"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="14" t="str">
+        <f aca="false">IF(OR($A62="",$D62="",$E62=""),"",MAX(0,$E62-$D62))</f>
+        <v/>
+      </c>
+      <c r="G62" s="14" t="str">
+        <f aca="false">IF($A62="","",IF($E62&lt;&gt;"",IF(N($F62)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D62="","Sem data prometida",IF($D62&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+    </row>
+    <row r="63" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="14"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="14" t="str">
+        <f aca="false">IF(OR($A63="",$D63="",$E63=""),"",MAX(0,$E63-$D63))</f>
+        <v/>
+      </c>
+      <c r="G63" s="14" t="str">
+        <f aca="false">IF($A63="","",IF($E63&lt;&gt;"",IF(N($F63)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D63="","Sem data prometida",IF($D63&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+    </row>
+    <row r="64" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="14"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="14" t="str">
+        <f aca="false">IF(OR($A64="",$D64="",$E64=""),"",MAX(0,$E64-$D64))</f>
+        <v/>
+      </c>
+      <c r="G64" s="14" t="str">
+        <f aca="false">IF($A64="","",IF($E64&lt;&gt;"",IF(N($F64)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D64="","Sem data prometida",IF($D64&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+    </row>
+    <row r="65" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="14" t="str">
+        <f aca="false">IF(OR($A65="",$D65="",$E65=""),"",MAX(0,$E65-$D65))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14" t="str">
+        <f aca="false">IF($A65="","",IF($E65&lt;&gt;"",IF(N($F65)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D65="","Sem data prometida",IF($D65&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+    </row>
+    <row r="66" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="14"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="14" t="str">
+        <f aca="false">IF(OR($A66="",$D66="",$E66=""),"",MAX(0,$E66-$D66))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14" t="str">
+        <f aca="false">IF($A66="","",IF($E66&lt;&gt;"",IF(N($F66)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D66="","Sem data prometida",IF($D66&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+    </row>
+    <row r="67" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="14"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="14" t="str">
+        <f aca="false">IF(OR($A67="",$D67="",$E67=""),"",MAX(0,$E67-$D67))</f>
+        <v/>
+      </c>
+      <c r="G67" s="14" t="str">
+        <f aca="false">IF($A67="","",IF($E67&lt;&gt;"",IF(N($F67)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D67="","Sem data prometida",IF($D67&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+    </row>
+    <row r="68" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="14" t="str">
+        <f aca="false">IF(OR($A68="",$D68="",$E68=""),"",MAX(0,$E68-$D68))</f>
+        <v/>
+      </c>
+      <c r="G68" s="14" t="str">
+        <f aca="false">IF($A68="","",IF($E68&lt;&gt;"",IF(N($F68)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D68="","Sem data prometida",IF($D68&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+    </row>
+    <row r="69" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="14"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="14" t="str">
+        <f aca="false">IF(OR($A69="",$D69="",$E69=""),"",MAX(0,$E69-$D69))</f>
+        <v/>
+      </c>
+      <c r="G69" s="14" t="str">
+        <f aca="false">IF($A69="","",IF($E69&lt;&gt;"",IF(N($F69)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D69="","Sem data prometida",IF($D69&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+    </row>
+    <row r="70" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="14"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="14" t="str">
+        <f aca="false">IF(OR($A70="",$D70="",$E70=""),"",MAX(0,$E70-$D70))</f>
+        <v/>
+      </c>
+      <c r="G70" s="14" t="str">
+        <f aca="false">IF($A70="","",IF($E70&lt;&gt;"",IF(N($F70)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D70="","Sem data prometida",IF($D70&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+    </row>
+    <row r="71" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="14"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14" t="str">
+        <f aca="false">IF(OR($A71="",$D71="",$E71=""),"",MAX(0,$E71-$D71))</f>
+        <v/>
+      </c>
+      <c r="G71" s="14" t="str">
+        <f aca="false">IF($A71="","",IF($E71&lt;&gt;"",IF(N($F71)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D71="","Sem data prometida",IF($D71&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+    </row>
+    <row r="72" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="14"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="14" t="str">
+        <f aca="false">IF(OR($A72="",$D72="",$E72=""),"",MAX(0,$E72-$D72))</f>
+        <v/>
+      </c>
+      <c r="G72" s="14" t="str">
+        <f aca="false">IF($A72="","",IF($E72&lt;&gt;"",IF(N($F72)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D72="","Sem data prometida",IF($D72&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+    </row>
+    <row r="73" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="14"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="14" t="str">
+        <f aca="false">IF(OR($A73="",$D73="",$E73=""),"",MAX(0,$E73-$D73))</f>
+        <v/>
+      </c>
+      <c r="G73" s="14" t="str">
+        <f aca="false">IF($A73="","",IF($E73&lt;&gt;"",IF(N($F73)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D73="","Sem data prometida",IF($D73&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+    </row>
+    <row r="74" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="14"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="14" t="str">
+        <f aca="false">IF(OR($A74="",$D74="",$E74=""),"",MAX(0,$E74-$D74))</f>
+        <v/>
+      </c>
+      <c r="G74" s="14" t="str">
+        <f aca="false">IF($A74="","",IF($E74&lt;&gt;"",IF(N($F74)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D74="","Sem data prometida",IF($D74&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+    </row>
+    <row r="75" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="14"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="14" t="str">
+        <f aca="false">IF(OR($A75="",$D75="",$E75=""),"",MAX(0,$E75-$D75))</f>
+        <v/>
+      </c>
+      <c r="G75" s="14" t="str">
+        <f aca="false">IF($A75="","",IF($E75&lt;&gt;"",IF(N($F75)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D75="","Sem data prometida",IF($D75&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+    </row>
+    <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="14"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="14" t="str">
+        <f aca="false">IF(OR($A76="",$D76="",$E76=""),"",MAX(0,$E76-$D76))</f>
+        <v/>
+      </c>
+      <c r="G76" s="14" t="str">
+        <f aca="false">IF($A76="","",IF($E76&lt;&gt;"",IF(N($F76)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D76="","Sem data prometida",IF($D76&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+    </row>
+    <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="14"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="14" t="str">
+        <f aca="false">IF(OR($A77="",$D77="",$E77=""),"",MAX(0,$E77-$D77))</f>
+        <v/>
+      </c>
+      <c r="G77" s="14" t="str">
+        <f aca="false">IF($A77="","",IF($E77&lt;&gt;"",IF(N($F77)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D77="","Sem data prometida",IF($D77&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+    </row>
+    <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="14"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="14" t="str">
+        <f aca="false">IF(OR($A78="",$D78="",$E78=""),"",MAX(0,$E78-$D78))</f>
+        <v/>
+      </c>
+      <c r="G78" s="14" t="str">
+        <f aca="false">IF($A78="","",IF($E78&lt;&gt;"",IF(N($F78)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D78="","Sem data prometida",IF($D78&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+    </row>
+    <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="14"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="14" t="str">
+        <f aca="false">IF(OR($A79="",$D79="",$E79=""),"",MAX(0,$E79-$D79))</f>
+        <v/>
+      </c>
+      <c r="G79" s="14" t="str">
+        <f aca="false">IF($A79="","",IF($E79&lt;&gt;"",IF(N($F79)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D79="","Sem data prometida",IF($D79&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+    </row>
+    <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="14"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="14" t="str">
+        <f aca="false">IF(OR($A80="",$D80="",$E80=""),"",MAX(0,$E80-$D80))</f>
+        <v/>
+      </c>
+      <c r="G80" s="14" t="str">
+        <f aca="false">IF($A80="","",IF($E80&lt;&gt;"",IF(N($F80)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D80="","Sem data prometida",IF($D80&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+    </row>
+    <row r="81" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="14"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="14" t="str">
+        <f aca="false">IF(OR($A81="",$D81="",$E81=""),"",MAX(0,$E81-$D81))</f>
+        <v/>
+      </c>
+      <c r="G81" s="14" t="str">
+        <f aca="false">IF($A81="","",IF($E81&lt;&gt;"",IF(N($F81)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D81="","Sem data prometida",IF($D81&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+    </row>
+    <row r="82" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="14"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="14" t="str">
+        <f aca="false">IF(OR($A82="",$D82="",$E82=""),"",MAX(0,$E82-$D82))</f>
+        <v/>
+      </c>
+      <c r="G82" s="14" t="str">
+        <f aca="false">IF($A82="","",IF($E82&lt;&gt;"",IF(N($F82)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D82="","Sem data prometida",IF($D82&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+    </row>
+    <row r="83" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="14"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="14" t="str">
+        <f aca="false">IF(OR($A83="",$D83="",$E83=""),"",MAX(0,$E83-$D83))</f>
+        <v/>
+      </c>
+      <c r="G83" s="14" t="str">
+        <f aca="false">IF($A83="","",IF($E83&lt;&gt;"",IF(N($F83)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D83="","Sem data prometida",IF($D83&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+    </row>
+    <row r="84" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="14"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="14" t="str">
+        <f aca="false">IF(OR($A84="",$D84="",$E84=""),"",MAX(0,$E84-$D84))</f>
+        <v/>
+      </c>
+      <c r="G84" s="14" t="str">
+        <f aca="false">IF($A84="","",IF($E84&lt;&gt;"",IF(N($F84)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D84="","Sem data prometida",IF($D84&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+    </row>
+    <row r="85" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="14"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="14" t="str">
+        <f aca="false">IF(OR($A85="",$D85="",$E85=""),"",MAX(0,$E85-$D85))</f>
+        <v/>
+      </c>
+      <c r="G85" s="14" t="str">
+        <f aca="false">IF($A85="","",IF($E85&lt;&gt;"",IF(N($F85)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D85="","Sem data prometida",IF($D85&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+    </row>
+    <row r="86" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="14"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="14" t="str">
+        <f aca="false">IF(OR($A86="",$D86="",$E86=""),"",MAX(0,$E86-$D86))</f>
+        <v/>
+      </c>
+      <c r="G86" s="14" t="str">
+        <f aca="false">IF($A86="","",IF($E86&lt;&gt;"",IF(N($F86)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D86="","Sem data prometida",IF($D86&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+    </row>
+    <row r="87" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="14"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="14" t="str">
+        <f aca="false">IF(OR($A87="",$D87="",$E87=""),"",MAX(0,$E87-$D87))</f>
+        <v/>
+      </c>
+      <c r="G87" s="14" t="str">
+        <f aca="false">IF($A87="","",IF($E87&lt;&gt;"",IF(N($F87)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D87="","Sem data prometida",IF($D87&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+    </row>
+    <row r="88" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="14"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="14" t="str">
+        <f aca="false">IF(OR($A88="",$D88="",$E88=""),"",MAX(0,$E88-$D88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="14" t="str">
+        <f aca="false">IF($A88="","",IF($E88&lt;&gt;"",IF(N($F88)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D88="","Sem data prometida",IF($D88&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+    </row>
+    <row r="89" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="14"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="14" t="str">
+        <f aca="false">IF(OR($A89="",$D89="",$E89=""),"",MAX(0,$E89-$D89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="14" t="str">
+        <f aca="false">IF($A89="","",IF($E89&lt;&gt;"",IF(N($F89)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D89="","Sem data prometida",IF($D89&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+    </row>
+    <row r="90" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="14"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="14" t="str">
+        <f aca="false">IF(OR($A90="",$D90="",$E90=""),"",MAX(0,$E90-$D90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="14" t="str">
+        <f aca="false">IF($A90="","",IF($E90&lt;&gt;"",IF(N($F90)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D90="","Sem data prometida",IF($D90&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+    </row>
+    <row r="91" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="14"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="14" t="str">
+        <f aca="false">IF(OR($A91="",$D91="",$E91=""),"",MAX(0,$E91-$D91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="14" t="str">
+        <f aca="false">IF($A91="","",IF($E91&lt;&gt;"",IF(N($F91)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D91="","Sem data prometida",IF($D91&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+    </row>
+    <row r="92" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="14"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="14" t="str">
+        <f aca="false">IF(OR($A92="",$D92="",$E92=""),"",MAX(0,$E92-$D92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="14" t="str">
+        <f aca="false">IF($A92="","",IF($E92&lt;&gt;"",IF(N($F92)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D92="","Sem data prometida",IF($D92&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+    </row>
+    <row r="93" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="14"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="14" t="str">
+        <f aca="false">IF(OR($A93="",$D93="",$E93=""),"",MAX(0,$E93-$D93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="14" t="str">
+        <f aca="false">IF($A93="","",IF($E93&lt;&gt;"",IF(N($F93)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D93="","Sem data prometida",IF($D93&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+    </row>
+    <row r="94" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="14"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="14" t="str">
+        <f aca="false">IF(OR($A94="",$D94="",$E94=""),"",MAX(0,$E94-$D94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="14" t="str">
+        <f aca="false">IF($A94="","",IF($E94&lt;&gt;"",IF(N($F94)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D94="","Sem data prometida",IF($D94&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+    </row>
+    <row r="95" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="14"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="14" t="str">
+        <f aca="false">IF(OR($A95="",$D95="",$E95=""),"",MAX(0,$E95-$D95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="14" t="str">
+        <f aca="false">IF($A95="","",IF($E95&lt;&gt;"",IF(N($F95)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D95="","Sem data prometida",IF($D95&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+    </row>
+    <row r="96" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="14"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="14" t="str">
+        <f aca="false">IF(OR($A96="",$D96="",$E96=""),"",MAX(0,$E96-$D96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="14" t="str">
+        <f aca="false">IF($A96="","",IF($E96&lt;&gt;"",IF(N($F96)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D96="","Sem data prometida",IF($D96&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+    </row>
+    <row r="97" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="14"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="14" t="str">
+        <f aca="false">IF(OR($A97="",$D97="",$E97=""),"",MAX(0,$E97-$D97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="14" t="str">
+        <f aca="false">IF($A97="","",IF($E97&lt;&gt;"",IF(N($F97)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D97="","Sem data prometida",IF($D97&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+    </row>
+    <row r="98" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="14"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="14" t="str">
+        <f aca="false">IF(OR($A98="",$D98="",$E98=""),"",MAX(0,$E98-$D98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="14" t="str">
+        <f aca="false">IF($A98="","",IF($E98&lt;&gt;"",IF(N($F98)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D98="","Sem data prometida",IF($D98&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+    </row>
+    <row r="99" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="14"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="14" t="str">
+        <f aca="false">IF(OR($A99="",$D99="",$E99=""),"",MAX(0,$E99-$D99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="14" t="str">
+        <f aca="false">IF($A99="","",IF($E99&lt;&gt;"",IF(N($F99)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D99="","Sem data prometida",IF($D99&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+    </row>
+    <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="14"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="14" t="str">
+        <f aca="false">IF(OR($A100="",$D100="",$E100=""),"",MAX(0,$E100-$D100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="14" t="str">
+        <f aca="false">IF($A100="","",IF($E100&lt;&gt;"",IF(N($F100)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D100="","Sem data prometida",IF($D100&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H100" s="15"/>
+      <c r="I100" s="15"/>
+    </row>
+    <row r="101" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="14"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="14" t="str">
+        <f aca="false">IF(OR($A101="",$D101="",$E101=""),"",MAX(0,$E101-$D101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="14" t="str">
+        <f aca="false">IF($A101="","",IF($E101&lt;&gt;"",IF(N($F101)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D101="","Sem data prometida",IF($D101&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
+    </row>
+    <row r="102" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="14"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="14" t="str">
+        <f aca="false">IF(OR($A102="",$D102="",$E102=""),"",MAX(0,$E102-$D102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="14" t="str">
+        <f aca="false">IF($A102="","",IF($E102&lt;&gt;"",IF(N($F102)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D102="","Sem data prometida",IF($D102&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+    </row>
+    <row r="103" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="14"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="14" t="str">
+        <f aca="false">IF(OR($A103="",$D103="",$E103=""),"",MAX(0,$E103-$D103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="14" t="str">
+        <f aca="false">IF($A103="","",IF($E103&lt;&gt;"",IF(N($F103)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D103="","Sem data prometida",IF($D103&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H103" s="15"/>
+      <c r="I103" s="15"/>
+    </row>
+    <row r="104" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="14"/>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="14" t="str">
+        <f aca="false">IF(OR($A104="",$D104="",$E104=""),"",MAX(0,$E104-$D104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="14" t="str">
+        <f aca="false">IF($A104="","",IF($E104&lt;&gt;"",IF(N($F104)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D104="","Sem data prometida",IF($D104&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H104" s="15"/>
+      <c r="I104" s="15"/>
+    </row>
+    <row r="105" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="14"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="14" t="str">
+        <f aca="false">IF(OR($A105="",$D105="",$E105=""),"",MAX(0,$E105-$D105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="14" t="str">
+        <f aca="false">IF($A105="","",IF($E105&lt;&gt;"",IF(N($F105)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D105="","Sem data prometida",IF($D105&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H105" s="15"/>
+      <c r="I105" s="15"/>
+    </row>
+    <row r="106" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="14"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="14" t="str">
+        <f aca="false">IF(OR($A106="",$D106="",$E106=""),"",MAX(0,$E106-$D106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="14" t="str">
+        <f aca="false">IF($A106="","",IF($E106&lt;&gt;"",IF(N($F106)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D106="","Sem data prometida",IF($D106&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+    </row>
+    <row r="107" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="14"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="14" t="str">
+        <f aca="false">IF(OR($A107="",$D107="",$E107=""),"",MAX(0,$E107-$D107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="14" t="str">
+        <f aca="false">IF($A107="","",IF($E107&lt;&gt;"",IF(N($F107)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D107="","Sem data prometida",IF($D107&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H107" s="15"/>
+      <c r="I107" s="15"/>
+    </row>
+    <row r="108" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="14"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="14" t="str">
+        <f aca="false">IF(OR($A108="",$D108="",$E108=""),"",MAX(0,$E108-$D108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="14" t="str">
+        <f aca="false">IF($A108="","",IF($E108&lt;&gt;"",IF(N($F108)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D108="","Sem data prometida",IF($D108&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H108" s="15"/>
+      <c r="I108" s="15"/>
+    </row>
+    <row r="109" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="14"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="14" t="str">
+        <f aca="false">IF(OR($A109="",$D109="",$E109=""),"",MAX(0,$E109-$D109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="14" t="str">
+        <f aca="false">IF($A109="","",IF($E109&lt;&gt;"",IF(N($F109)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D109="","Sem data prometida",IF($D109&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H109" s="15"/>
+      <c r="I109" s="15"/>
+    </row>
+    <row r="110" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="14"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="14" t="str">
+        <f aca="false">IF(OR($A110="",$D110="",$E110=""),"",MAX(0,$E110-$D110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="14" t="str">
+        <f aca="false">IF($A110="","",IF($E110&lt;&gt;"",IF(N($F110)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D110="","Sem data prometida",IF($D110&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
+    </row>
+    <row r="111" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="14"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="14" t="str">
+        <f aca="false">IF(OR($A111="",$D111="",$E111=""),"",MAX(0,$E111-$D111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="14" t="str">
+        <f aca="false">IF($A111="","",IF($E111&lt;&gt;"",IF(N($F111)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D111="","Sem data prometida",IF($D111&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
+    </row>
+    <row r="112" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="14"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="14" t="str">
+        <f aca="false">IF(OR($A112="",$D112="",$E112=""),"",MAX(0,$E112-$D112))</f>
+        <v/>
+      </c>
+      <c r="G112" s="14" t="str">
+        <f aca="false">IF($A112="","",IF($E112&lt;&gt;"",IF(N($F112)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D112="","Sem data prometida",IF($D112&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+    </row>
+    <row r="113" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="14"/>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="14" t="str">
+        <f aca="false">IF(OR($A113="",$D113="",$E113=""),"",MAX(0,$E113-$D113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="14" t="str">
+        <f aca="false">IF($A113="","",IF($E113&lt;&gt;"",IF(N($F113)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D113="","Sem data prometida",IF($D113&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+    </row>
+    <row r="114" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="14"/>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="14" t="str">
+        <f aca="false">IF(OR($A114="",$D114="",$E114=""),"",MAX(0,$E114-$D114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="14" t="str">
+        <f aca="false">IF($A114="","",IF($E114&lt;&gt;"",IF(N($F114)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D114="","Sem data prometida",IF($D114&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+    </row>
+    <row r="115" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="14"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="14" t="str">
+        <f aca="false">IF(OR($A115="",$D115="",$E115=""),"",MAX(0,$E115-$D115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="14" t="str">
+        <f aca="false">IF($A115="","",IF($E115&lt;&gt;"",IF(N($F115)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D115="","Sem data prometida",IF($D115&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+    </row>
+    <row r="116" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="14"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="14" t="str">
+        <f aca="false">IF(OR($A116="",$D116="",$E116=""),"",MAX(0,$E116-$D116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="14" t="str">
+        <f aca="false">IF($A116="","",IF($E116&lt;&gt;"",IF(N($F116)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D116="","Sem data prometida",IF($D116&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+    </row>
+    <row r="117" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="14"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="14" t="str">
+        <f aca="false">IF(OR($A117="",$D117="",$E117=""),"",MAX(0,$E117-$D117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="14" t="str">
+        <f aca="false">IF($A117="","",IF($E117&lt;&gt;"",IF(N($F117)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D117="","Sem data prometida",IF($D117&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
+    </row>
+    <row r="118" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="14"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="14" t="str">
+        <f aca="false">IF(OR($A118="",$D118="",$E118=""),"",MAX(0,$E118-$D118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="14" t="str">
+        <f aca="false">IF($A118="","",IF($E118&lt;&gt;"",IF(N($F118)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D118="","Sem data prometida",IF($D118&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
+    </row>
+    <row r="119" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="14"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="14" t="str">
+        <f aca="false">IF(OR($A119="",$D119="",$E119=""),"",MAX(0,$E119-$D119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="14" t="str">
+        <f aca="false">IF($A119="","",IF($E119&lt;&gt;"",IF(N($F119)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D119="","Sem data prometida",IF($D119&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+    </row>
+    <row r="120" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="14"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="14" t="str">
+        <f aca="false">IF(OR($A120="",$D120="",$E120=""),"",MAX(0,$E120-$D120))</f>
+        <v/>
+      </c>
+      <c r="G120" s="14" t="str">
+        <f aca="false">IF($A120="","",IF($E120&lt;&gt;"",IF(N($F120)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D120="","Sem data prometida",IF($D120&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+    </row>
+    <row r="121" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="14"/>
+      <c r="B121" s="15"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="14" t="str">
+        <f aca="false">IF(OR($A121="",$D121="",$E121=""),"",MAX(0,$E121-$D121))</f>
+        <v/>
+      </c>
+      <c r="G121" s="14" t="str">
+        <f aca="false">IF($A121="","",IF($E121&lt;&gt;"",IF(N($F121)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D121="","Sem data prometida",IF($D121&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
+    </row>
+    <row r="122" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="14"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="13"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="14" t="str">
+        <f aca="false">IF(OR($A122="",$D122="",$E122=""),"",MAX(0,$E122-$D122))</f>
+        <v/>
+      </c>
+      <c r="G122" s="14" t="str">
+        <f aca="false">IF($A122="","",IF($E122&lt;&gt;"",IF(N($F122)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D122="","Sem data prometida",IF($D122&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+    </row>
+    <row r="123" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="14"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="13"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="14" t="str">
+        <f aca="false">IF(OR($A123="",$D123="",$E123=""),"",MAX(0,$E123-$D123))</f>
+        <v/>
+      </c>
+      <c r="G123" s="14" t="str">
+        <f aca="false">IF($A123="","",IF($E123&lt;&gt;"",IF(N($F123)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D123="","Sem data prometida",IF($D123&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+    </row>
+    <row r="124" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="14"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="14" t="str">
+        <f aca="false">IF(OR($A124="",$D124="",$E124=""),"",MAX(0,$E124-$D124))</f>
+        <v/>
+      </c>
+      <c r="G124" s="14" t="str">
+        <f aca="false">IF($A124="","",IF($E124&lt;&gt;"",IF(N($F124)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D124="","Sem data prometida",IF($D124&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+    </row>
+    <row r="125" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="14"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="13"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="14" t="str">
+        <f aca="false">IF(OR($A125="",$D125="",$E125=""),"",MAX(0,$E125-$D125))</f>
+        <v/>
+      </c>
+      <c r="G125" s="14" t="str">
+        <f aca="false">IF($A125="","",IF($E125&lt;&gt;"",IF(N($F125)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D125="","Sem data prometida",IF($D125&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+    </row>
+    <row r="126" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="14"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="14" t="str">
+        <f aca="false">IF(OR($A126="",$D126="",$E126=""),"",MAX(0,$E126-$D126))</f>
+        <v/>
+      </c>
+      <c r="G126" s="14" t="str">
+        <f aca="false">IF($A126="","",IF($E126&lt;&gt;"",IF(N($F126)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D126="","Sem data prometida",IF($D126&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+    </row>
+    <row r="127" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="14"/>
+      <c r="B127" s="15"/>
+      <c r="C127" s="13"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="14" t="str">
+        <f aca="false">IF(OR($A127="",$D127="",$E127=""),"",MAX(0,$E127-$D127))</f>
+        <v/>
+      </c>
+      <c r="G127" s="14" t="str">
+        <f aca="false">IF($A127="","",IF($E127&lt;&gt;"",IF(N($F127)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D127="","Sem data prometida",IF($D127&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
+    </row>
+    <row r="128" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="14"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="14" t="str">
+        <f aca="false">IF(OR($A128="",$D128="",$E128=""),"",MAX(0,$E128-$D128))</f>
+        <v/>
+      </c>
+      <c r="G128" s="14" t="str">
+        <f aca="false">IF($A128="","",IF($E128&lt;&gt;"",IF(N($F128)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D128="","Sem data prometida",IF($D128&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
+    </row>
+    <row r="129" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="14"/>
+      <c r="B129" s="15"/>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="14" t="str">
+        <f aca="false">IF(OR($A129="",$D129="",$E129=""),"",MAX(0,$E129-$D129))</f>
+        <v/>
+      </c>
+      <c r="G129" s="14" t="str">
+        <f aca="false">IF($A129="","",IF($E129&lt;&gt;"",IF(N($F129)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D129="","Sem data prometida",IF($D129&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
+    </row>
+    <row r="130" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="14"/>
+      <c r="B130" s="15"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="14" t="str">
+        <f aca="false">IF(OR($A130="",$D130="",$E130=""),"",MAX(0,$E130-$D130))</f>
+        <v/>
+      </c>
+      <c r="G130" s="14" t="str">
+        <f aca="false">IF($A130="","",IF($E130&lt;&gt;"",IF(N($F130)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D130="","Sem data prometida",IF($D130&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
+    </row>
+    <row r="131" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="14"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="13"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="14" t="str">
+        <f aca="false">IF(OR($A131="",$D131="",$E131=""),"",MAX(0,$E131-$D131))</f>
+        <v/>
+      </c>
+      <c r="G131" s="14" t="str">
+        <f aca="false">IF($A131="","",IF($E131&lt;&gt;"",IF(N($F131)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D131="","Sem data prometida",IF($D131&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
+    </row>
+    <row r="132" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="14"/>
+      <c r="B132" s="15"/>
+      <c r="C132" s="13"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="14" t="str">
+        <f aca="false">IF(OR($A132="",$D132="",$E132=""),"",MAX(0,$E132-$D132))</f>
+        <v/>
+      </c>
+      <c r="G132" s="14" t="str">
+        <f aca="false">IF($A132="","",IF($E132&lt;&gt;"",IF(N($F132)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D132="","Sem data prometida",IF($D132&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
+    </row>
+    <row r="133" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="14"/>
+      <c r="B133" s="15"/>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="14" t="str">
+        <f aca="false">IF(OR($A133="",$D133="",$E133=""),"",MAX(0,$E133-$D133))</f>
+        <v/>
+      </c>
+      <c r="G133" s="14" t="str">
+        <f aca="false">IF($A133="","",IF($E133&lt;&gt;"",IF(N($F133)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D133="","Sem data prometida",IF($D133&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+    </row>
+    <row r="134" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="14"/>
+      <c r="B134" s="15"/>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="14" t="str">
+        <f aca="false">IF(OR($A134="",$D134="",$E134=""),"",MAX(0,$E134-$D134))</f>
+        <v/>
+      </c>
+      <c r="G134" s="14" t="str">
+        <f aca="false">IF($A134="","",IF($E134&lt;&gt;"",IF(N($F134)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D134="","Sem data prometida",IF($D134&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H134" s="15"/>
+      <c r="I134" s="15"/>
+    </row>
+    <row r="135" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="14"/>
+      <c r="B135" s="15"/>
+      <c r="C135" s="13"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="13"/>
+      <c r="F135" s="14" t="str">
+        <f aca="false">IF(OR($A135="",$D135="",$E135=""),"",MAX(0,$E135-$D135))</f>
+        <v/>
+      </c>
+      <c r="G135" s="14" t="str">
+        <f aca="false">IF($A135="","",IF($E135&lt;&gt;"",IF(N($F135)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D135="","Sem data prometida",IF($D135&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H135" s="15"/>
+      <c r="I135" s="15"/>
+    </row>
+    <row r="136" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="14"/>
+      <c r="B136" s="15"/>
+      <c r="C136" s="13"/>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
+      <c r="F136" s="14" t="str">
+        <f aca="false">IF(OR($A136="",$D136="",$E136=""),"",MAX(0,$E136-$D136))</f>
+        <v/>
+      </c>
+      <c r="G136" s="14" t="str">
+        <f aca="false">IF($A136="","",IF($E136&lt;&gt;"",IF(N($F136)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D136="","Sem data prometida",IF($D136&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
+    </row>
+    <row r="137" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="14"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
+      <c r="F137" s="14" t="str">
+        <f aca="false">IF(OR($A137="",$D137="",$E137=""),"",MAX(0,$E137-$D137))</f>
+        <v/>
+      </c>
+      <c r="G137" s="14" t="str">
+        <f aca="false">IF($A137="","",IF($E137&lt;&gt;"",IF(N($F137)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D137="","Sem data prometida",IF($D137&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
+    </row>
+    <row r="138" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="14"/>
+      <c r="B138" s="15"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="14" t="str">
+        <f aca="false">IF(OR($A138="",$D138="",$E138=""),"",MAX(0,$E138-$D138))</f>
+        <v/>
+      </c>
+      <c r="G138" s="14" t="str">
+        <f aca="false">IF($A138="","",IF($E138&lt;&gt;"",IF(N($F138)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D138="","Sem data prometida",IF($D138&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H138" s="15"/>
+      <c r="I138" s="15"/>
+    </row>
+    <row r="139" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="14"/>
+      <c r="B139" s="15"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="14" t="str">
+        <f aca="false">IF(OR($A139="",$D139="",$E139=""),"",MAX(0,$E139-$D139))</f>
+        <v/>
+      </c>
+      <c r="G139" s="14" t="str">
+        <f aca="false">IF($A139="","",IF($E139&lt;&gt;"",IF(N($F139)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D139="","Sem data prometida",IF($D139&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H139" s="15"/>
+      <c r="I139" s="15"/>
+    </row>
+    <row r="140" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="14"/>
+      <c r="B140" s="15"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="14" t="str">
+        <f aca="false">IF(OR($A140="",$D140="",$E140=""),"",MAX(0,$E140-$D140))</f>
+        <v/>
+      </c>
+      <c r="G140" s="14" t="str">
+        <f aca="false">IF($A140="","",IF($E140&lt;&gt;"",IF(N($F140)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D140="","Sem data prometida",IF($D140&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
+    </row>
+    <row r="141" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="14"/>
+      <c r="B141" s="15"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="14" t="str">
+        <f aca="false">IF(OR($A141="",$D141="",$E141=""),"",MAX(0,$E141-$D141))</f>
+        <v/>
+      </c>
+      <c r="G141" s="14" t="str">
+        <f aca="false">IF($A141="","",IF($E141&lt;&gt;"",IF(N($F141)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D141="","Sem data prometida",IF($D141&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+    </row>
+    <row r="142" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="14"/>
+      <c r="B142" s="15"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="14" t="str">
+        <f aca="false">IF(OR($A142="",$D142="",$E142=""),"",MAX(0,$E142-$D142))</f>
+        <v/>
+      </c>
+      <c r="G142" s="14" t="str">
+        <f aca="false">IF($A142="","",IF($E142&lt;&gt;"",IF(N($F142)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D142="","Sem data prometida",IF($D142&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+    </row>
+    <row r="143" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="14"/>
+      <c r="B143" s="15"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="14" t="str">
+        <f aca="false">IF(OR($A143="",$D143="",$E143=""),"",MAX(0,$E143-$D143))</f>
+        <v/>
+      </c>
+      <c r="G143" s="14" t="str">
+        <f aca="false">IF($A143="","",IF($E143&lt;&gt;"",IF(N($F143)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D143="","Sem data prometida",IF($D143&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
+    </row>
+    <row r="144" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="14"/>
+      <c r="B144" s="15"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
+      <c r="F144" s="14" t="str">
+        <f aca="false">IF(OR($A144="",$D144="",$E144=""),"",MAX(0,$E144-$D144))</f>
+        <v/>
+      </c>
+      <c r="G144" s="14" t="str">
+        <f aca="false">IF($A144="","",IF($E144&lt;&gt;"",IF(N($F144)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D144="","Sem data prometida",IF($D144&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H144" s="15"/>
+      <c r="I144" s="15"/>
+    </row>
+    <row r="145" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="14"/>
+      <c r="B145" s="15"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="14" t="str">
+        <f aca="false">IF(OR($A145="",$D145="",$E145=""),"",MAX(0,$E145-$D145))</f>
+        <v/>
+      </c>
+      <c r="G145" s="14" t="str">
+        <f aca="false">IF($A145="","",IF($E145&lt;&gt;"",IF(N($F145)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D145="","Sem data prometida",IF($D145&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
+    </row>
+    <row r="146" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="14"/>
+      <c r="B146" s="15"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="14" t="str">
+        <f aca="false">IF(OR($A146="",$D146="",$E146=""),"",MAX(0,$E146-$D146))</f>
+        <v/>
+      </c>
+      <c r="G146" s="14" t="str">
+        <f aca="false">IF($A146="","",IF($E146&lt;&gt;"",IF(N($F146)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D146="","Sem data prometida",IF($D146&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H146" s="15"/>
+      <c r="I146" s="15"/>
+    </row>
+    <row r="147" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="14"/>
+      <c r="B147" s="15"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="14" t="str">
+        <f aca="false">IF(OR($A147="",$D147="",$E147=""),"",MAX(0,$E147-$D147))</f>
+        <v/>
+      </c>
+      <c r="G147" s="14" t="str">
+        <f aca="false">IF($A147="","",IF($E147&lt;&gt;"",IF(N($F147)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D147="","Sem data prometida",IF($D147&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H147" s="15"/>
+      <c r="I147" s="15"/>
+    </row>
+    <row r="148" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="14"/>
+      <c r="B148" s="15"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="14" t="str">
+        <f aca="false">IF(OR($A148="",$D148="",$E148=""),"",MAX(0,$E148-$D148))</f>
+        <v/>
+      </c>
+      <c r="G148" s="14" t="str">
+        <f aca="false">IF($A148="","",IF($E148&lt;&gt;"",IF(N($F148)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D148="","Sem data prometida",IF($D148&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H148" s="15"/>
+      <c r="I148" s="15"/>
+    </row>
+    <row r="149" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="14"/>
+      <c r="B149" s="15"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="14" t="str">
+        <f aca="false">IF(OR($A149="",$D149="",$E149=""),"",MAX(0,$E149-$D149))</f>
+        <v/>
+      </c>
+      <c r="G149" s="14" t="str">
+        <f aca="false">IF($A149="","",IF($E149&lt;&gt;"",IF(N($F149)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D149="","Sem data prometida",IF($D149&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H149" s="15"/>
+      <c r="I149" s="15"/>
+    </row>
+    <row r="150" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="14"/>
+      <c r="B150" s="15"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="14" t="str">
+        <f aca="false">IF(OR($A150="",$D150="",$E150=""),"",MAX(0,$E150-$D150))</f>
+        <v/>
+      </c>
+      <c r="G150" s="14" t="str">
+        <f aca="false">IF($A150="","",IF($E150&lt;&gt;"",IF(N($F150)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D150="","Sem data prometida",IF($D150&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H150" s="15"/>
+      <c r="I150" s="15"/>
+    </row>
+    <row r="151" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="14"/>
+      <c r="B151" s="15"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="14" t="str">
+        <f aca="false">IF(OR($A151="",$D151="",$E151=""),"",MAX(0,$E151-$D151))</f>
+        <v/>
+      </c>
+      <c r="G151" s="14" t="str">
+        <f aca="false">IF($A151="","",IF($E151&lt;&gt;"",IF(N($F151)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D151="","Sem data prometida",IF($D151&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
+    </row>
+    <row r="152" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="14"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="14" t="str">
+        <f aca="false">IF(OR($A152="",$D152="",$E152=""),"",MAX(0,$E152-$D152))</f>
+        <v/>
+      </c>
+      <c r="G152" s="14" t="str">
+        <f aca="false">IF($A152="","",IF($E152&lt;&gt;"",IF(N($F152)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D152="","Sem data prometida",IF($D152&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+    </row>
+    <row r="153" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="14"/>
+      <c r="B153" s="15"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="14" t="str">
+        <f aca="false">IF(OR($A153="",$D153="",$E153=""),"",MAX(0,$E153-$D153))</f>
+        <v/>
+      </c>
+      <c r="G153" s="14" t="str">
+        <f aca="false">IF($A153="","",IF($E153&lt;&gt;"",IF(N($F153)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D153="","Sem data prometida",IF($D153&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H153" s="15"/>
+      <c r="I153" s="15"/>
+    </row>
+    <row r="154" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="14"/>
+      <c r="B154" s="15"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="14" t="str">
+        <f aca="false">IF(OR($A154="",$D154="",$E154=""),"",MAX(0,$E154-$D154))</f>
+        <v/>
+      </c>
+      <c r="G154" s="14" t="str">
+        <f aca="false">IF($A154="","",IF($E154&lt;&gt;"",IF(N($F154)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D154="","Sem data prometida",IF($D154&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H154" s="15"/>
+      <c r="I154" s="15"/>
+    </row>
+    <row r="155" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="14"/>
+      <c r="B155" s="15"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="14" t="str">
+        <f aca="false">IF(OR($A155="",$D155="",$E155=""),"",MAX(0,$E155-$D155))</f>
+        <v/>
+      </c>
+      <c r="G155" s="14" t="str">
+        <f aca="false">IF($A155="","",IF($E155&lt;&gt;"",IF(N($F155)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D155="","Sem data prometida",IF($D155&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
+    </row>
+    <row r="156" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="14"/>
+      <c r="B156" s="15"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="14" t="str">
+        <f aca="false">IF(OR($A156="",$D156="",$E156=""),"",MAX(0,$E156-$D156))</f>
+        <v/>
+      </c>
+      <c r="G156" s="14" t="str">
+        <f aca="false">IF($A156="","",IF($E156&lt;&gt;"",IF(N($F156)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D156="","Sem data prometida",IF($D156&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H156" s="15"/>
+      <c r="I156" s="15"/>
+    </row>
+    <row r="157" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="14"/>
+      <c r="B157" s="15"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
+      <c r="F157" s="14" t="str">
+        <f aca="false">IF(OR($A157="",$D157="",$E157=""),"",MAX(0,$E157-$D157))</f>
+        <v/>
+      </c>
+      <c r="G157" s="14" t="str">
+        <f aca="false">IF($A157="","",IF($E157&lt;&gt;"",IF(N($F157)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D157="","Sem data prometida",IF($D157&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
+    </row>
+    <row r="158" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="14"/>
+      <c r="B158" s="15"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
+      <c r="F158" s="14" t="str">
+        <f aca="false">IF(OR($A158="",$D158="",$E158=""),"",MAX(0,$E158-$D158))</f>
+        <v/>
+      </c>
+      <c r="G158" s="14" t="str">
+        <f aca="false">IF($A158="","",IF($E158&lt;&gt;"",IF(N($F158)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D158="","Sem data prometida",IF($D158&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H158" s="15"/>
+      <c r="I158" s="15"/>
+    </row>
+    <row r="159" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="14"/>
+      <c r="B159" s="15"/>
+      <c r="C159" s="13"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="13"/>
+      <c r="F159" s="14" t="str">
+        <f aca="false">IF(OR($A159="",$D159="",$E159=""),"",MAX(0,$E159-$D159))</f>
+        <v/>
+      </c>
+      <c r="G159" s="14" t="str">
+        <f aca="false">IF($A159="","",IF($E159&lt;&gt;"",IF(N($F159)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D159="","Sem data prometida",IF($D159&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H159" s="15"/>
+      <c r="I159" s="15"/>
+    </row>
+    <row r="160" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="14"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="14" t="str">
+        <f aca="false">IF(OR($A160="",$D160="",$E160=""),"",MAX(0,$E160-$D160))</f>
+        <v/>
+      </c>
+      <c r="G160" s="14" t="str">
+        <f aca="false">IF($A160="","",IF($E160&lt;&gt;"",IF(N($F160)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D160="","Sem data prometida",IF($D160&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H160" s="15"/>
+      <c r="I160" s="15"/>
+    </row>
+    <row r="161" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="14"/>
+      <c r="B161" s="15"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="14" t="str">
+        <f aca="false">IF(OR($A161="",$D161="",$E161=""),"",MAX(0,$E161-$D161))</f>
+        <v/>
+      </c>
+      <c r="G161" s="14" t="str">
+        <f aca="false">IF($A161="","",IF($E161&lt;&gt;"",IF(N($F161)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D161="","Sem data prometida",IF($D161&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H161" s="15"/>
+      <c r="I161" s="15"/>
+    </row>
+    <row r="162" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="14"/>
+      <c r="B162" s="15"/>
+      <c r="C162" s="13"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="13"/>
+      <c r="F162" s="14" t="str">
+        <f aca="false">IF(OR($A162="",$D162="",$E162=""),"",MAX(0,$E162-$D162))</f>
+        <v/>
+      </c>
+      <c r="G162" s="14" t="str">
+        <f aca="false">IF($A162="","",IF($E162&lt;&gt;"",IF(N($F162)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D162="","Sem data prometida",IF($D162&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H162" s="15"/>
+      <c r="I162" s="15"/>
+    </row>
+    <row r="163" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="14"/>
+      <c r="B163" s="15"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="13"/>
+      <c r="F163" s="14" t="str">
+        <f aca="false">IF(OR($A163="",$D163="",$E163=""),"",MAX(0,$E163-$D163))</f>
+        <v/>
+      </c>
+      <c r="G163" s="14" t="str">
+        <f aca="false">IF($A163="","",IF($E163&lt;&gt;"",IF(N($F163)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D163="","Sem data prometida",IF($D163&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H163" s="15"/>
+      <c r="I163" s="15"/>
+    </row>
+    <row r="164" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="14"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="13"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="13"/>
+      <c r="F164" s="14" t="str">
+        <f aca="false">IF(OR($A164="",$D164="",$E164=""),"",MAX(0,$E164-$D164))</f>
+        <v/>
+      </c>
+      <c r="G164" s="14" t="str">
+        <f aca="false">IF($A164="","",IF($E164&lt;&gt;"",IF(N($F164)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D164="","Sem data prometida",IF($D164&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H164" s="15"/>
+      <c r="I164" s="15"/>
+    </row>
+    <row r="165" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="14"/>
+      <c r="B165" s="15"/>
+      <c r="C165" s="13"/>
+      <c r="D165" s="13"/>
+      <c r="E165" s="13"/>
+      <c r="F165" s="14" t="str">
+        <f aca="false">IF(OR($A165="",$D165="",$E165=""),"",MAX(0,$E165-$D165))</f>
+        <v/>
+      </c>
+      <c r="G165" s="14" t="str">
+        <f aca="false">IF($A165="","",IF($E165&lt;&gt;"",IF(N($F165)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D165="","Sem data prometida",IF($D165&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
+    </row>
+    <row r="166" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="14"/>
+      <c r="B166" s="15"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="13"/>
+      <c r="F166" s="14" t="str">
+        <f aca="false">IF(OR($A166="",$D166="",$E166=""),"",MAX(0,$E166-$D166))</f>
+        <v/>
+      </c>
+      <c r="G166" s="14" t="str">
+        <f aca="false">IF($A166="","",IF($E166&lt;&gt;"",IF(N($F166)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D166="","Sem data prometida",IF($D166&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H166" s="15"/>
+      <c r="I166" s="15"/>
+    </row>
+    <row r="167" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="14"/>
+      <c r="B167" s="15"/>
+      <c r="C167" s="13"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="13"/>
+      <c r="F167" s="14" t="str">
+        <f aca="false">IF(OR($A167="",$D167="",$E167=""),"",MAX(0,$E167-$D167))</f>
+        <v/>
+      </c>
+      <c r="G167" s="14" t="str">
+        <f aca="false">IF($A167="","",IF($E167&lt;&gt;"",IF(N($F167)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D167="","Sem data prometida",IF($D167&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H167" s="15"/>
+      <c r="I167" s="15"/>
+    </row>
+    <row r="168" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="14"/>
+      <c r="B168" s="15"/>
+      <c r="C168" s="13"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="13"/>
+      <c r="F168" s="14" t="str">
+        <f aca="false">IF(OR($A168="",$D168="",$E168=""),"",MAX(0,$E168-$D168))</f>
+        <v/>
+      </c>
+      <c r="G168" s="14" t="str">
+        <f aca="false">IF($A168="","",IF($E168&lt;&gt;"",IF(N($F168)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D168="","Sem data prometida",IF($D168&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H168" s="15"/>
+      <c r="I168" s="15"/>
+    </row>
+    <row r="169" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="14"/>
+      <c r="B169" s="15"/>
+      <c r="C169" s="13"/>
+      <c r="D169" s="13"/>
+      <c r="E169" s="13"/>
+      <c r="F169" s="14" t="str">
+        <f aca="false">IF(OR($A169="",$D169="",$E169=""),"",MAX(0,$E169-$D169))</f>
+        <v/>
+      </c>
+      <c r="G169" s="14" t="str">
+        <f aca="false">IF($A169="","",IF($E169&lt;&gt;"",IF(N($F169)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D169="","Sem data prometida",IF($D169&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H169" s="15"/>
+      <c r="I169" s="15"/>
+    </row>
+    <row r="170" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="14"/>
+      <c r="B170" s="15"/>
+      <c r="C170" s="13"/>
+      <c r="D170" s="13"/>
+      <c r="E170" s="13"/>
+      <c r="F170" s="14" t="str">
+        <f aca="false">IF(OR($A170="",$D170="",$E170=""),"",MAX(0,$E170-$D170))</f>
+        <v/>
+      </c>
+      <c r="G170" s="14" t="str">
+        <f aca="false">IF($A170="","",IF($E170&lt;&gt;"",IF(N($F170)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D170="","Sem data prometida",IF($D170&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H170" s="15"/>
+      <c r="I170" s="15"/>
+    </row>
+    <row r="171" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="14"/>
+      <c r="B171" s="15"/>
+      <c r="C171" s="13"/>
+      <c r="D171" s="13"/>
+      <c r="E171" s="13"/>
+      <c r="F171" s="14" t="str">
+        <f aca="false">IF(OR($A171="",$D171="",$E171=""),"",MAX(0,$E171-$D171))</f>
+        <v/>
+      </c>
+      <c r="G171" s="14" t="str">
+        <f aca="false">IF($A171="","",IF($E171&lt;&gt;"",IF(N($F171)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D171="","Sem data prometida",IF($D171&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H171" s="15"/>
+      <c r="I171" s="15"/>
+    </row>
+    <row r="172" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="14"/>
+      <c r="B172" s="15"/>
+      <c r="C172" s="13"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="13"/>
+      <c r="F172" s="14" t="str">
+        <f aca="false">IF(OR($A172="",$D172="",$E172=""),"",MAX(0,$E172-$D172))</f>
+        <v/>
+      </c>
+      <c r="G172" s="14" t="str">
+        <f aca="false">IF($A172="","",IF($E172&lt;&gt;"",IF(N($F172)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D172="","Sem data prometida",IF($D172&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H172" s="15"/>
+      <c r="I172" s="15"/>
+    </row>
+    <row r="173" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="14"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="13"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="13"/>
+      <c r="F173" s="14" t="str">
+        <f aca="false">IF(OR($A173="",$D173="",$E173=""),"",MAX(0,$E173-$D173))</f>
+        <v/>
+      </c>
+      <c r="G173" s="14" t="str">
+        <f aca="false">IF($A173="","",IF($E173&lt;&gt;"",IF(N($F173)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D173="","Sem data prometida",IF($D173&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+    </row>
+    <row r="174" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="14"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="13"/>
+      <c r="F174" s="14" t="str">
+        <f aca="false">IF(OR($A174="",$D174="",$E174=""),"",MAX(0,$E174-$D174))</f>
+        <v/>
+      </c>
+      <c r="G174" s="14" t="str">
+        <f aca="false">IF($A174="","",IF($E174&lt;&gt;"",IF(N($F174)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D174="","Sem data prometida",IF($D174&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
+    </row>
+    <row r="175" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="14"/>
+      <c r="B175" s="15"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="14" t="str">
+        <f aca="false">IF(OR($A175="",$D175="",$E175=""),"",MAX(0,$E175-$D175))</f>
+        <v/>
+      </c>
+      <c r="G175" s="14" t="str">
+        <f aca="false">IF($A175="","",IF($E175&lt;&gt;"",IF(N($F175)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D175="","Sem data prometida",IF($D175&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H175" s="15"/>
+      <c r="I175" s="15"/>
+    </row>
+    <row r="176" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="14"/>
+      <c r="B176" s="15"/>
+      <c r="C176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="13"/>
+      <c r="F176" s="14" t="str">
+        <f aca="false">IF(OR($A176="",$D176="",$E176=""),"",MAX(0,$E176-$D176))</f>
+        <v/>
+      </c>
+      <c r="G176" s="14" t="str">
+        <f aca="false">IF($A176="","",IF($E176&lt;&gt;"",IF(N($F176)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D176="","Sem data prometida",IF($D176&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H176" s="15"/>
+      <c r="I176" s="15"/>
+    </row>
+    <row r="177" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="14"/>
+      <c r="B177" s="15"/>
+      <c r="C177" s="13"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="13"/>
+      <c r="F177" s="14" t="str">
+        <f aca="false">IF(OR($A177="",$D177="",$E177=""),"",MAX(0,$E177-$D177))</f>
+        <v/>
+      </c>
+      <c r="G177" s="14" t="str">
+        <f aca="false">IF($A177="","",IF($E177&lt;&gt;"",IF(N($F177)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D177="","Sem data prometida",IF($D177&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
+    </row>
+    <row r="178" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="14"/>
+      <c r="B178" s="15"/>
+      <c r="C178" s="13"/>
+      <c r="D178" s="13"/>
+      <c r="E178" s="13"/>
+      <c r="F178" s="14" t="str">
+        <f aca="false">IF(OR($A178="",$D178="",$E178=""),"",MAX(0,$E178-$D178))</f>
+        <v/>
+      </c>
+      <c r="G178" s="14" t="str">
+        <f aca="false">IF($A178="","",IF($E178&lt;&gt;"",IF(N($F178)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D178="","Sem data prometida",IF($D178&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
+    </row>
+    <row r="179" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="14"/>
+      <c r="B179" s="15"/>
+      <c r="C179" s="13"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="14" t="str">
+        <f aca="false">IF(OR($A179="",$D179="",$E179=""),"",MAX(0,$E179-$D179))</f>
+        <v/>
+      </c>
+      <c r="G179" s="14" t="str">
+        <f aca="false">IF($A179="","",IF($E179&lt;&gt;"",IF(N($F179)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D179="","Sem data prometida",IF($D179&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H179" s="15"/>
+      <c r="I179" s="15"/>
+    </row>
+    <row r="180" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="14"/>
+      <c r="B180" s="15"/>
+      <c r="C180" s="13"/>
+      <c r="D180" s="13"/>
+      <c r="E180" s="13"/>
+      <c r="F180" s="14" t="str">
+        <f aca="false">IF(OR($A180="",$D180="",$E180=""),"",MAX(0,$E180-$D180))</f>
+        <v/>
+      </c>
+      <c r="G180" s="14" t="str">
+        <f aca="false">IF($A180="","",IF($E180&lt;&gt;"",IF(N($F180)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D180="","Sem data prometida",IF($D180&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H180" s="15"/>
+      <c r="I180" s="15"/>
+    </row>
+    <row r="181" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="14"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="13"/>
+      <c r="D181" s="13"/>
+      <c r="E181" s="13"/>
+      <c r="F181" s="14" t="str">
+        <f aca="false">IF(OR($A181="",$D181="",$E181=""),"",MAX(0,$E181-$D181))</f>
+        <v/>
+      </c>
+      <c r="G181" s="14" t="str">
+        <f aca="false">IF($A181="","",IF($E181&lt;&gt;"",IF(N($F181)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D181="","Sem data prometida",IF($D181&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H181" s="15"/>
+      <c r="I181" s="15"/>
+    </row>
+    <row r="182" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="14"/>
+      <c r="B182" s="15"/>
+      <c r="C182" s="13"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="13"/>
+      <c r="F182" s="14" t="str">
+        <f aca="false">IF(OR($A182="",$D182="",$E182=""),"",MAX(0,$E182-$D182))</f>
+        <v/>
+      </c>
+      <c r="G182" s="14" t="str">
+        <f aca="false">IF($A182="","",IF($E182&lt;&gt;"",IF(N($F182)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D182="","Sem data prometida",IF($D182&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H182" s="15"/>
+      <c r="I182" s="15"/>
+    </row>
+    <row r="183" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="14"/>
+      <c r="B183" s="15"/>
+      <c r="C183" s="13"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="13"/>
+      <c r="F183" s="14" t="str">
+        <f aca="false">IF(OR($A183="",$D183="",$E183=""),"",MAX(0,$E183-$D183))</f>
+        <v/>
+      </c>
+      <c r="G183" s="14" t="str">
+        <f aca="false">IF($A183="","",IF($E183&lt;&gt;"",IF(N($F183)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D183="","Sem data prometida",IF($D183&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H183" s="15"/>
+      <c r="I183" s="15"/>
+    </row>
+    <row r="184" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="14"/>
+      <c r="B184" s="15"/>
+      <c r="C184" s="13"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="13"/>
+      <c r="F184" s="14" t="str">
+        <f aca="false">IF(OR($A184="",$D184="",$E184=""),"",MAX(0,$E184-$D184))</f>
+        <v/>
+      </c>
+      <c r="G184" s="14" t="str">
+        <f aca="false">IF($A184="","",IF($E184&lt;&gt;"",IF(N($F184)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D184="","Sem data prometida",IF($D184&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
+    </row>
+    <row r="185" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="14"/>
+      <c r="B185" s="15"/>
+      <c r="C185" s="13"/>
+      <c r="D185" s="13"/>
+      <c r="E185" s="13"/>
+      <c r="F185" s="14" t="str">
+        <f aca="false">IF(OR($A185="",$D185="",$E185=""),"",MAX(0,$E185-$D185))</f>
+        <v/>
+      </c>
+      <c r="G185" s="14" t="str">
+        <f aca="false">IF($A185="","",IF($E185&lt;&gt;"",IF(N($F185)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D185="","Sem data prometida",IF($D185&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H185" s="15"/>
+      <c r="I185" s="15"/>
+    </row>
+    <row r="186" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="14"/>
+      <c r="B186" s="15"/>
+      <c r="C186" s="13"/>
+      <c r="D186" s="13"/>
+      <c r="E186" s="13"/>
+      <c r="F186" s="14" t="str">
+        <f aca="false">IF(OR($A186="",$D186="",$E186=""),"",MAX(0,$E186-$D186))</f>
+        <v/>
+      </c>
+      <c r="G186" s="14" t="str">
+        <f aca="false">IF($A186="","",IF($E186&lt;&gt;"",IF(N($F186)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D186="","Sem data prometida",IF($D186&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
+    </row>
+    <row r="187" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="14"/>
+      <c r="B187" s="15"/>
+      <c r="C187" s="13"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="14" t="str">
+        <f aca="false">IF(OR($A187="",$D187="",$E187=""),"",MAX(0,$E187-$D187))</f>
+        <v/>
+      </c>
+      <c r="G187" s="14" t="str">
+        <f aca="false">IF($A187="","",IF($E187&lt;&gt;"",IF(N($F187)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D187="","Sem data prometida",IF($D187&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H187" s="15"/>
+      <c r="I187" s="15"/>
+    </row>
+    <row r="188" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="14"/>
+      <c r="B188" s="15"/>
+      <c r="C188" s="13"/>
+      <c r="D188" s="13"/>
+      <c r="E188" s="13"/>
+      <c r="F188" s="14" t="str">
+        <f aca="false">IF(OR($A188="",$D188="",$E188=""),"",MAX(0,$E188-$D188))</f>
+        <v/>
+      </c>
+      <c r="G188" s="14" t="str">
+        <f aca="false">IF($A188="","",IF($E188&lt;&gt;"",IF(N($F188)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D188="","Sem data prometida",IF($D188&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H188" s="15"/>
+      <c r="I188" s="15"/>
+    </row>
+    <row r="189" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="14"/>
+      <c r="B189" s="15"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="14" t="str">
+        <f aca="false">IF(OR($A189="",$D189="",$E189=""),"",MAX(0,$E189-$D189))</f>
+        <v/>
+      </c>
+      <c r="G189" s="14" t="str">
+        <f aca="false">IF($A189="","",IF($E189&lt;&gt;"",IF(N($F189)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D189="","Sem data prometida",IF($D189&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H189" s="15"/>
+      <c r="I189" s="15"/>
+    </row>
+    <row r="190" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="14"/>
+      <c r="B190" s="15"/>
+      <c r="C190" s="13"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="13"/>
+      <c r="F190" s="14" t="str">
+        <f aca="false">IF(OR($A190="",$D190="",$E190=""),"",MAX(0,$E190-$D190))</f>
+        <v/>
+      </c>
+      <c r="G190" s="14" t="str">
+        <f aca="false">IF($A190="","",IF($E190&lt;&gt;"",IF(N($F190)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D190="","Sem data prometida",IF($D190&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H190" s="15"/>
+      <c r="I190" s="15"/>
+    </row>
+    <row r="191" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="14"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="13"/>
+      <c r="D191" s="13"/>
+      <c r="E191" s="13"/>
+      <c r="F191" s="14" t="str">
+        <f aca="false">IF(OR($A191="",$D191="",$E191=""),"",MAX(0,$E191-$D191))</f>
+        <v/>
+      </c>
+      <c r="G191" s="14" t="str">
+        <f aca="false">IF($A191="","",IF($E191&lt;&gt;"",IF(N($F191)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D191="","Sem data prometida",IF($D191&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H191" s="15"/>
+      <c r="I191" s="15"/>
+    </row>
+    <row r="192" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="14"/>
+      <c r="B192" s="15"/>
+      <c r="C192" s="13"/>
+      <c r="D192" s="13"/>
+      <c r="E192" s="13"/>
+      <c r="F192" s="14" t="str">
+        <f aca="false">IF(OR($A192="",$D192="",$E192=""),"",MAX(0,$E192-$D192))</f>
+        <v/>
+      </c>
+      <c r="G192" s="14" t="str">
+        <f aca="false">IF($A192="","",IF($E192&lt;&gt;"",IF(N($F192)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D192="","Sem data prometida",IF($D192&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H192" s="15"/>
+      <c r="I192" s="15"/>
+    </row>
+    <row r="193" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="14"/>
+      <c r="B193" s="15"/>
+      <c r="C193" s="13"/>
+      <c r="D193" s="13"/>
+      <c r="E193" s="13"/>
+      <c r="F193" s="14" t="str">
+        <f aca="false">IF(OR($A193="",$D193="",$E193=""),"",MAX(0,$E193-$D193))</f>
+        <v/>
+      </c>
+      <c r="G193" s="14" t="str">
+        <f aca="false">IF($A193="","",IF($E193&lt;&gt;"",IF(N($F193)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D193="","Sem data prometida",IF($D193&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H193" s="15"/>
+      <c r="I193" s="15"/>
+    </row>
+    <row r="194" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="14"/>
+      <c r="B194" s="15"/>
+      <c r="C194" s="13"/>
+      <c r="D194" s="13"/>
+      <c r="E194" s="13"/>
+      <c r="F194" s="14" t="str">
+        <f aca="false">IF(OR($A194="",$D194="",$E194=""),"",MAX(0,$E194-$D194))</f>
+        <v/>
+      </c>
+      <c r="G194" s="14" t="str">
+        <f aca="false">IF($A194="","",IF($E194&lt;&gt;"",IF(N($F194)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D194="","Sem data prometida",IF($D194&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H194" s="15"/>
+      <c r="I194" s="15"/>
+    </row>
+    <row r="195" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="14"/>
+      <c r="B195" s="15"/>
+      <c r="C195" s="13"/>
+      <c r="D195" s="13"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="14" t="str">
+        <f aca="false">IF(OR($A195="",$D195="",$E195=""),"",MAX(0,$E195-$D195))</f>
+        <v/>
+      </c>
+      <c r="G195" s="14" t="str">
+        <f aca="false">IF($A195="","",IF($E195&lt;&gt;"",IF(N($F195)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D195="","Sem data prometida",IF($D195&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H195" s="15"/>
+      <c r="I195" s="15"/>
+    </row>
+    <row r="196" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="14"/>
+      <c r="B196" s="15"/>
+      <c r="C196" s="13"/>
+      <c r="D196" s="13"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="14" t="str">
+        <f aca="false">IF(OR($A196="",$D196="",$E196=""),"",MAX(0,$E196-$D196))</f>
+        <v/>
+      </c>
+      <c r="G196" s="14" t="str">
+        <f aca="false">IF($A196="","",IF($E196&lt;&gt;"",IF(N($F196)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D196="","Sem data prometida",IF($D196&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H196" s="15"/>
+      <c r="I196" s="15"/>
+    </row>
+    <row r="197" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="14"/>
+      <c r="B197" s="15"/>
+      <c r="C197" s="13"/>
+      <c r="D197" s="13"/>
+      <c r="E197" s="13"/>
+      <c r="F197" s="14" t="str">
+        <f aca="false">IF(OR($A197="",$D197="",$E197=""),"",MAX(0,$E197-$D197))</f>
+        <v/>
+      </c>
+      <c r="G197" s="14" t="str">
+        <f aca="false">IF($A197="","",IF($E197&lt;&gt;"",IF(N($F197)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D197="","Sem data prometida",IF($D197&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H197" s="15"/>
+      <c r="I197" s="15"/>
+    </row>
+    <row r="198" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="14"/>
+      <c r="B198" s="15"/>
+      <c r="C198" s="13"/>
+      <c r="D198" s="13"/>
+      <c r="E198" s="13"/>
+      <c r="F198" s="14" t="str">
+        <f aca="false">IF(OR($A198="",$D198="",$E198=""),"",MAX(0,$E198-$D198))</f>
+        <v/>
+      </c>
+      <c r="G198" s="14" t="str">
+        <f aca="false">IF($A198="","",IF($E198&lt;&gt;"",IF(N($F198)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D198="","Sem data prometida",IF($D198&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H198" s="15"/>
+      <c r="I198" s="15"/>
+    </row>
+    <row r="199" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="14"/>
+      <c r="B199" s="15"/>
+      <c r="C199" s="13"/>
+      <c r="D199" s="13"/>
+      <c r="E199" s="13"/>
+      <c r="F199" s="14" t="str">
+        <f aca="false">IF(OR($A199="",$D199="",$E199=""),"",MAX(0,$E199-$D199))</f>
+        <v/>
+      </c>
+      <c r="G199" s="14" t="str">
+        <f aca="false">IF($A199="","",IF($E199&lt;&gt;"",IF(N($F199)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D199="","Sem data prometida",IF($D199&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H199" s="15"/>
+      <c r="I199" s="15"/>
+    </row>
+    <row r="200" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="14"/>
+      <c r="B200" s="15"/>
+      <c r="C200" s="13"/>
+      <c r="D200" s="13"/>
+      <c r="E200" s="13"/>
+      <c r="F200" s="14" t="str">
+        <f aca="false">IF(OR($A200="",$D200="",$E200=""),"",MAX(0,$E200-$D200))</f>
+        <v/>
+      </c>
+      <c r="G200" s="14" t="str">
+        <f aca="false">IF($A200="","",IF($E200&lt;&gt;"",IF(N($F200)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D200="","Sem data prometida",IF($D200&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H200" s="15"/>
+      <c r="I200" s="15"/>
+    </row>
+    <row r="201" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="14"/>
+      <c r="B201" s="15"/>
+      <c r="C201" s="13"/>
+      <c r="D201" s="13"/>
+      <c r="E201" s="13"/>
+      <c r="F201" s="14" t="str">
+        <f aca="false">IF(OR($A201="",$D201="",$E201=""),"",MAX(0,$E201-$D201))</f>
+        <v/>
+      </c>
+      <c r="G201" s="14" t="str">
+        <f aca="false">IF($A201="","",IF($E201&lt;&gt;"",IF(N($F201)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D201="","Sem data prometida",IF($D201&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H201" s="15"/>
+      <c r="I201" s="15"/>
+    </row>
+    <row r="202" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="14"/>
+      <c r="B202" s="15"/>
+      <c r="C202" s="13"/>
+      <c r="D202" s="13"/>
+      <c r="E202" s="13"/>
+      <c r="F202" s="14" t="str">
+        <f aca="false">IF(OR($A202="",$D202="",$E202=""),"",MAX(0,$E202-$D202))</f>
+        <v/>
+      </c>
+      <c r="G202" s="14" t="str">
+        <f aca="false">IF($A202="","",IF($E202&lt;&gt;"",IF(N($F202)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D202="","Sem data prometida",IF($D202&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H202" s="15"/>
+      <c r="I202" s="15"/>
+    </row>
+    <row r="203" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="14"/>
+      <c r="B203" s="15"/>
+      <c r="C203" s="13"/>
+      <c r="D203" s="13"/>
+      <c r="E203" s="13"/>
+      <c r="F203" s="14" t="str">
+        <f aca="false">IF(OR($A203="",$D203="",$E203=""),"",MAX(0,$E203-$D203))</f>
+        <v/>
+      </c>
+      <c r="G203" s="14" t="str">
+        <f aca="false">IF($A203="","",IF($E203&lt;&gt;"",IF(N($F203)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D203="","Sem data prometida",IF($D203&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H203" s="15"/>
+      <c r="I203" s="15"/>
+    </row>
+    <row r="204" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="14"/>
+      <c r="B204" s="15"/>
+      <c r="C204" s="13"/>
+      <c r="D204" s="13"/>
+      <c r="E204" s="13"/>
+      <c r="F204" s="14" t="str">
+        <f aca="false">IF(OR($A204="",$D204="",$E204=""),"",MAX(0,$E204-$D204))</f>
+        <v/>
+      </c>
+      <c r="G204" s="14" t="str">
+        <f aca="false">IF($A204="","",IF($E204&lt;&gt;"",IF(N($F204)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D204="","Sem data prometida",IF($D204&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H204" s="15"/>
+      <c r="I204" s="15"/>
+    </row>
+    <row r="205" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="14"/>
+      <c r="B205" s="15"/>
+      <c r="C205" s="13"/>
+      <c r="D205" s="13"/>
+      <c r="E205" s="13"/>
+      <c r="F205" s="14" t="str">
+        <f aca="false">IF(OR($A205="",$D205="",$E205=""),"",MAX(0,$E205-$D205))</f>
+        <v/>
+      </c>
+      <c r="G205" s="14" t="str">
+        <f aca="false">IF($A205="","",IF($E205&lt;&gt;"",IF(N($F205)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D205="","Sem data prometida",IF($D205&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H205" s="15"/>
+      <c r="I205" s="15"/>
+    </row>
+    <row r="206" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="14"/>
+      <c r="B206" s="15"/>
+      <c r="C206" s="13"/>
+      <c r="D206" s="13"/>
+      <c r="E206" s="13"/>
+      <c r="F206" s="14" t="str">
+        <f aca="false">IF(OR($A206="",$D206="",$E206=""),"",MAX(0,$E206-$D206))</f>
+        <v/>
+      </c>
+      <c r="G206" s="14" t="str">
+        <f aca="false">IF($A206="","",IF($E206&lt;&gt;"",IF(N($F206)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D206="","Sem data prometida",IF($D206&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H206" s="15"/>
+      <c r="I206" s="15"/>
+    </row>
+    <row r="207" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="14"/>
+      <c r="B207" s="15"/>
+      <c r="C207" s="13"/>
+      <c r="D207" s="13"/>
+      <c r="E207" s="13"/>
+      <c r="F207" s="14" t="str">
+        <f aca="false">IF(OR($A207="",$D207="",$E207=""),"",MAX(0,$E207-$D207))</f>
+        <v/>
+      </c>
+      <c r="G207" s="14" t="str">
+        <f aca="false">IF($A207="","",IF($E207&lt;&gt;"",IF(N($F207)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D207="","Sem data prometida",IF($D207&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H207" s="15"/>
+      <c r="I207" s="15"/>
+    </row>
+    <row r="208" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="14"/>
+      <c r="B208" s="15"/>
+      <c r="C208" s="13"/>
+      <c r="D208" s="13"/>
+      <c r="E208" s="13"/>
+      <c r="F208" s="14" t="str">
+        <f aca="false">IF(OR($A208="",$D208="",$E208=""),"",MAX(0,$E208-$D208))</f>
+        <v/>
+      </c>
+      <c r="G208" s="14" t="str">
+        <f aca="false">IF($A208="","",IF($E208&lt;&gt;"",IF(N($F208)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D208="","Sem data prometida",IF($D208&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H208" s="15"/>
+      <c r="I208" s="15"/>
+    </row>
+    <row r="209" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="14"/>
+      <c r="B209" s="15"/>
+      <c r="C209" s="13"/>
+      <c r="D209" s="13"/>
+      <c r="E209" s="13"/>
+      <c r="F209" s="14" t="str">
+        <f aca="false">IF(OR($A209="",$D209="",$E209=""),"",MAX(0,$E209-$D209))</f>
+        <v/>
+      </c>
+      <c r="G209" s="14" t="str">
+        <f aca="false">IF($A209="","",IF($E209&lt;&gt;"",IF(N($F209)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D209="","Sem data prometida",IF($D209&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H209" s="15"/>
+      <c r="I209" s="15"/>
+    </row>
+    <row r="210" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="14"/>
+      <c r="B210" s="15"/>
+      <c r="C210" s="13"/>
+      <c r="D210" s="13"/>
+      <c r="E210" s="13"/>
+      <c r="F210" s="14" t="str">
+        <f aca="false">IF(OR($A210="",$D210="",$E210=""),"",MAX(0,$E210-$D210))</f>
+        <v/>
+      </c>
+      <c r="G210" s="14" t="str">
+        <f aca="false">IF($A210="","",IF($E210&lt;&gt;"",IF(N($F210)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D210="","Sem data prometida",IF($D210&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H210" s="15"/>
+      <c r="I210" s="15"/>
+    </row>
+    <row r="211" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="14"/>
+      <c r="B211" s="15"/>
+      <c r="C211" s="13"/>
+      <c r="D211" s="13"/>
+      <c r="E211" s="13"/>
+      <c r="F211" s="14" t="str">
+        <f aca="false">IF(OR($A211="",$D211="",$E211=""),"",MAX(0,$E211-$D211))</f>
+        <v/>
+      </c>
+      <c r="G211" s="14" t="str">
+        <f aca="false">IF($A211="","",IF($E211&lt;&gt;"",IF(N($F211)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D211="","Sem data prometida",IF($D211&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H211" s="15"/>
+      <c r="I211" s="15"/>
+    </row>
+    <row r="212" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="14"/>
+      <c r="B212" s="15"/>
+      <c r="C212" s="13"/>
+      <c r="D212" s="13"/>
+      <c r="E212" s="13"/>
+      <c r="F212" s="14" t="str">
+        <f aca="false">IF(OR($A212="",$D212="",$E212=""),"",MAX(0,$E212-$D212))</f>
+        <v/>
+      </c>
+      <c r="G212" s="14" t="str">
+        <f aca="false">IF($A212="","",IF($E212&lt;&gt;"",IF(N($F212)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D212="","Sem data prometida",IF($D212&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H212" s="15"/>
+      <c r="I212" s="15"/>
+    </row>
+    <row r="213" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="14"/>
+      <c r="B213" s="15"/>
+      <c r="C213" s="13"/>
+      <c r="D213" s="13"/>
+      <c r="E213" s="13"/>
+      <c r="F213" s="14" t="str">
+        <f aca="false">IF(OR($A213="",$D213="",$E213=""),"",MAX(0,$E213-$D213))</f>
+        <v/>
+      </c>
+      <c r="G213" s="14" t="str">
+        <f aca="false">IF($A213="","",IF($E213&lt;&gt;"",IF(N($F213)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D213="","Sem data prometida",IF($D213&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H213" s="15"/>
+      <c r="I213" s="15"/>
+    </row>
+    <row r="214" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="14"/>
+      <c r="B214" s="15"/>
+      <c r="C214" s="13"/>
+      <c r="D214" s="13"/>
+      <c r="E214" s="13"/>
+      <c r="F214" s="14" t="str">
+        <f aca="false">IF(OR($A214="",$D214="",$E214=""),"",MAX(0,$E214-$D214))</f>
+        <v/>
+      </c>
+      <c r="G214" s="14" t="str">
+        <f aca="false">IF($A214="","",IF($E214&lt;&gt;"",IF(N($F214)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D214="","Sem data prometida",IF($D214&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H214" s="15"/>
+      <c r="I214" s="15"/>
+    </row>
+    <row r="215" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="14"/>
+      <c r="B215" s="15"/>
+      <c r="C215" s="13"/>
+      <c r="D215" s="13"/>
+      <c r="E215" s="13"/>
+      <c r="F215" s="14" t="str">
+        <f aca="false">IF(OR($A215="",$D215="",$E215=""),"",MAX(0,$E215-$D215))</f>
+        <v/>
+      </c>
+      <c r="G215" s="14" t="str">
+        <f aca="false">IF($A215="","",IF($E215&lt;&gt;"",IF(N($F215)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D215="","Sem data prometida",IF($D215&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H215" s="15"/>
+      <c r="I215" s="15"/>
+    </row>
+    <row r="216" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="14"/>
+      <c r="B216" s="15"/>
+      <c r="C216" s="13"/>
+      <c r="D216" s="13"/>
+      <c r="E216" s="13"/>
+      <c r="F216" s="14" t="str">
+        <f aca="false">IF(OR($A216="",$D216="",$E216=""),"",MAX(0,$E216-$D216))</f>
+        <v/>
+      </c>
+      <c r="G216" s="14" t="str">
+        <f aca="false">IF($A216="","",IF($E216&lt;&gt;"",IF(N($F216)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D216="","Sem data prometida",IF($D216&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H216" s="15"/>
+      <c r="I216" s="15"/>
+    </row>
+    <row r="217" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="14"/>
+      <c r="B217" s="15"/>
+      <c r="C217" s="13"/>
+      <c r="D217" s="13"/>
+      <c r="E217" s="13"/>
+      <c r="F217" s="14" t="str">
+        <f aca="false">IF(OR($A217="",$D217="",$E217=""),"",MAX(0,$E217-$D217))</f>
+        <v/>
+      </c>
+      <c r="G217" s="14" t="str">
+        <f aca="false">IF($A217="","",IF($E217&lt;&gt;"",IF(N($F217)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D217="","Sem data prometida",IF($D217&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+    </row>
+    <row r="218" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="14"/>
+      <c r="B218" s="15"/>
+      <c r="C218" s="13"/>
+      <c r="D218" s="13"/>
+      <c r="E218" s="13"/>
+      <c r="F218" s="14" t="str">
+        <f aca="false">IF(OR($A218="",$D218="",$E218=""),"",MAX(0,$E218-$D218))</f>
+        <v/>
+      </c>
+      <c r="G218" s="14" t="str">
+        <f aca="false">IF($A218="","",IF($E218&lt;&gt;"",IF(N($F218)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D218="","Sem data prometida",IF($D218&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H218" s="15"/>
+      <c r="I218" s="15"/>
+    </row>
+    <row r="219" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="14"/>
+      <c r="B219" s="15"/>
+      <c r="C219" s="13"/>
+      <c r="D219" s="13"/>
+      <c r="E219" s="13"/>
+      <c r="F219" s="14" t="str">
+        <f aca="false">IF(OR($A219="",$D219="",$E219=""),"",MAX(0,$E219-$D219))</f>
+        <v/>
+      </c>
+      <c r="G219" s="14" t="str">
+        <f aca="false">IF($A219="","",IF($E219&lt;&gt;"",IF(N($F219)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D219="","Sem data prometida",IF($D219&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H219" s="15"/>
+      <c r="I219" s="15"/>
+    </row>
+    <row r="220" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="14"/>
+      <c r="B220" s="15"/>
+      <c r="C220" s="13"/>
+      <c r="D220" s="13"/>
+      <c r="E220" s="13"/>
+      <c r="F220" s="14" t="str">
+        <f aca="false">IF(OR($A220="",$D220="",$E220=""),"",MAX(0,$E220-$D220))</f>
+        <v/>
+      </c>
+      <c r="G220" s="14" t="str">
+        <f aca="false">IF($A220="","",IF($E220&lt;&gt;"",IF(N($F220)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D220="","Sem data prometida",IF($D220&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H220" s="15"/>
+      <c r="I220" s="15"/>
+    </row>
+    <row r="221" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="14"/>
+      <c r="B221" s="15"/>
+      <c r="C221" s="13"/>
+      <c r="D221" s="13"/>
+      <c r="E221" s="13"/>
+      <c r="F221" s="14" t="str">
+        <f aca="false">IF(OR($A221="",$D221="",$E221=""),"",MAX(0,$E221-$D221))</f>
+        <v/>
+      </c>
+      <c r="G221" s="14" t="str">
+        <f aca="false">IF($A221="","",IF($E221&lt;&gt;"",IF(N($F221)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D221="","Sem data prometida",IF($D221&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H221" s="15"/>
+      <c r="I221" s="15"/>
+    </row>
+    <row r="222" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A222" s="14"/>
+      <c r="B222" s="15"/>
+      <c r="C222" s="13"/>
+      <c r="D222" s="13"/>
+      <c r="E222" s="13"/>
+      <c r="F222" s="14" t="str">
+        <f aca="false">IF(OR($A222="",$D222="",$E222=""),"",MAX(0,$E222-$D222))</f>
+        <v/>
+      </c>
+      <c r="G222" s="14" t="str">
+        <f aca="false">IF($A222="","",IF($E222&lt;&gt;"",IF(N($F222)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D222="","Sem data prometida",IF($D222&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H222" s="15"/>
+      <c r="I222" s="15"/>
+    </row>
+    <row r="223" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="14"/>
+      <c r="B223" s="15"/>
+      <c r="C223" s="13"/>
+      <c r="D223" s="13"/>
+      <c r="E223" s="13"/>
+      <c r="F223" s="14" t="str">
+        <f aca="false">IF(OR($A223="",$D223="",$E223=""),"",MAX(0,$E223-$D223))</f>
+        <v/>
+      </c>
+      <c r="G223" s="14" t="str">
+        <f aca="false">IF($A223="","",IF($E223&lt;&gt;"",IF(N($F223)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D223="","Sem data prometida",IF($D223&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H223" s="15"/>
+      <c r="I223" s="15"/>
+    </row>
+    <row r="224" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="14"/>
+      <c r="B224" s="15"/>
+      <c r="C224" s="13"/>
+      <c r="D224" s="13"/>
+      <c r="E224" s="13"/>
+      <c r="F224" s="14" t="str">
+        <f aca="false">IF(OR($A224="",$D224="",$E224=""),"",MAX(0,$E224-$D224))</f>
+        <v/>
+      </c>
+      <c r="G224" s="14" t="str">
+        <f aca="false">IF($A224="","",IF($E224&lt;&gt;"",IF(N($F224)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D224="","Sem data prometida",IF($D224&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H224" s="15"/>
+      <c r="I224" s="15"/>
+    </row>
+    <row r="225" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A225" s="14"/>
+      <c r="B225" s="15"/>
+      <c r="C225" s="13"/>
+      <c r="D225" s="13"/>
+      <c r="E225" s="13"/>
+      <c r="F225" s="14" t="str">
+        <f aca="false">IF(OR($A225="",$D225="",$E225=""),"",MAX(0,$E225-$D225))</f>
+        <v/>
+      </c>
+      <c r="G225" s="14" t="str">
+        <f aca="false">IF($A225="","",IF($E225&lt;&gt;"",IF(N($F225)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D225="","Sem data prometida",IF($D225&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H225" s="15"/>
+      <c r="I225" s="15"/>
+    </row>
+    <row r="226" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="14"/>
+      <c r="B226" s="15"/>
+      <c r="C226" s="13"/>
+      <c r="D226" s="13"/>
+      <c r="E226" s="13"/>
+      <c r="F226" s="14" t="str">
+        <f aca="false">IF(OR($A226="",$D226="",$E226=""),"",MAX(0,$E226-$D226))</f>
+        <v/>
+      </c>
+      <c r="G226" s="14" t="str">
+        <f aca="false">IF($A226="","",IF($E226&lt;&gt;"",IF(N($F226)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D226="","Sem data prometida",IF($D226&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H226" s="15"/>
+      <c r="I226" s="15"/>
+    </row>
+    <row r="227" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A227" s="14"/>
+      <c r="B227" s="15"/>
+      <c r="C227" s="13"/>
+      <c r="D227" s="13"/>
+      <c r="E227" s="13"/>
+      <c r="F227" s="14" t="str">
+        <f aca="false">IF(OR($A227="",$D227="",$E227=""),"",MAX(0,$E227-$D227))</f>
+        <v/>
+      </c>
+      <c r="G227" s="14" t="str">
+        <f aca="false">IF($A227="","",IF($E227&lt;&gt;"",IF(N($F227)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D227="","Sem data prometida",IF($D227&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H227" s="15"/>
+      <c r="I227" s="15"/>
+    </row>
+    <row r="228" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="14"/>
+      <c r="B228" s="15"/>
+      <c r="C228" s="13"/>
+      <c r="D228" s="13"/>
+      <c r="E228" s="13"/>
+      <c r="F228" s="14" t="str">
+        <f aca="false">IF(OR($A228="",$D228="",$E228=""),"",MAX(0,$E228-$D228))</f>
+        <v/>
+      </c>
+      <c r="G228" s="14" t="str">
+        <f aca="false">IF($A228="","",IF($E228&lt;&gt;"",IF(N($F228)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D228="","Sem data prometida",IF($D228&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H228" s="15"/>
+      <c r="I228" s="15"/>
+    </row>
+    <row r="229" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A229" s="14"/>
+      <c r="B229" s="15"/>
+      <c r="C229" s="13"/>
+      <c r="D229" s="13"/>
+      <c r="E229" s="13"/>
+      <c r="F229" s="14" t="str">
+        <f aca="false">IF(OR($A229="",$D229="",$E229=""),"",MAX(0,$E229-$D229))</f>
+        <v/>
+      </c>
+      <c r="G229" s="14" t="str">
+        <f aca="false">IF($A229="","",IF($E229&lt;&gt;"",IF(N($F229)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D229="","Sem data prometida",IF($D229&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H229" s="15"/>
+      <c r="I229" s="15"/>
+    </row>
+    <row r="230" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A230" s="14"/>
+      <c r="B230" s="15"/>
+      <c r="C230" s="13"/>
+      <c r="D230" s="13"/>
+      <c r="E230" s="13"/>
+      <c r="F230" s="14" t="str">
+        <f aca="false">IF(OR($A230="",$D230="",$E230=""),"",MAX(0,$E230-$D230))</f>
+        <v/>
+      </c>
+      <c r="G230" s="14" t="str">
+        <f aca="false">IF($A230="","",IF($E230&lt;&gt;"",IF(N($F230)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D230="","Sem data prometida",IF($D230&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H230" s="15"/>
+      <c r="I230" s="15"/>
+    </row>
+    <row r="231" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="14"/>
+      <c r="B231" s="15"/>
+      <c r="C231" s="13"/>
+      <c r="D231" s="13"/>
+      <c r="E231" s="13"/>
+      <c r="F231" s="14" t="str">
+        <f aca="false">IF(OR($A231="",$D231="",$E231=""),"",MAX(0,$E231-$D231))</f>
+        <v/>
+      </c>
+      <c r="G231" s="14" t="str">
+        <f aca="false">IF($A231="","",IF($E231&lt;&gt;"",IF(N($F231)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D231="","Sem data prometida",IF($D231&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H231" s="15"/>
+      <c r="I231" s="15"/>
+    </row>
+    <row r="232" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="14"/>
+      <c r="B232" s="15"/>
+      <c r="C232" s="13"/>
+      <c r="D232" s="13"/>
+      <c r="E232" s="13"/>
+      <c r="F232" s="14" t="str">
+        <f aca="false">IF(OR($A232="",$D232="",$E232=""),"",MAX(0,$E232-$D232))</f>
+        <v/>
+      </c>
+      <c r="G232" s="14" t="str">
+        <f aca="false">IF($A232="","",IF($E232&lt;&gt;"",IF(N($F232)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D232="","Sem data prometida",IF($D232&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H232" s="15"/>
+      <c r="I232" s="15"/>
+    </row>
+    <row r="233" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="14"/>
+      <c r="B233" s="15"/>
+      <c r="C233" s="13"/>
+      <c r="D233" s="13"/>
+      <c r="E233" s="13"/>
+      <c r="F233" s="14" t="str">
+        <f aca="false">IF(OR($A233="",$D233="",$E233=""),"",MAX(0,$E233-$D233))</f>
+        <v/>
+      </c>
+      <c r="G233" s="14" t="str">
+        <f aca="false">IF($A233="","",IF($E233&lt;&gt;"",IF(N($F233)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D233="","Sem data prometida",IF($D233&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H233" s="15"/>
+      <c r="I233" s="15"/>
+    </row>
+    <row r="234" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="14"/>
+      <c r="B234" s="15"/>
+      <c r="C234" s="13"/>
+      <c r="D234" s="13"/>
+      <c r="E234" s="13"/>
+      <c r="F234" s="14" t="str">
+        <f aca="false">IF(OR($A234="",$D234="",$E234=""),"",MAX(0,$E234-$D234))</f>
+        <v/>
+      </c>
+      <c r="G234" s="14" t="str">
+        <f aca="false">IF($A234="","",IF($E234&lt;&gt;"",IF(N($F234)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D234="","Sem data prometida",IF($D234&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H234" s="15"/>
+      <c r="I234" s="15"/>
+    </row>
+    <row r="235" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="14"/>
+      <c r="B235" s="15"/>
+      <c r="C235" s="13"/>
+      <c r="D235" s="13"/>
+      <c r="E235" s="13"/>
+      <c r="F235" s="14" t="str">
+        <f aca="false">IF(OR($A235="",$D235="",$E235=""),"",MAX(0,$E235-$D235))</f>
+        <v/>
+      </c>
+      <c r="G235" s="14" t="str">
+        <f aca="false">IF($A235="","",IF($E235&lt;&gt;"",IF(N($F235)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D235="","Sem data prometida",IF($D235&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H235" s="15"/>
+      <c r="I235" s="15"/>
+    </row>
+    <row r="236" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="14"/>
+      <c r="B236" s="15"/>
+      <c r="C236" s="13"/>
+      <c r="D236" s="13"/>
+      <c r="E236" s="13"/>
+      <c r="F236" s="14" t="str">
+        <f aca="false">IF(OR($A236="",$D236="",$E236=""),"",MAX(0,$E236-$D236))</f>
+        <v/>
+      </c>
+      <c r="G236" s="14" t="str">
+        <f aca="false">IF($A236="","",IF($E236&lt;&gt;"",IF(N($F236)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D236="","Sem data prometida",IF($D236&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H236" s="15"/>
+      <c r="I236" s="15"/>
+    </row>
+    <row r="237" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="14"/>
+      <c r="B237" s="15"/>
+      <c r="C237" s="13"/>
+      <c r="D237" s="13"/>
+      <c r="E237" s="13"/>
+      <c r="F237" s="14" t="str">
+        <f aca="false">IF(OR($A237="",$D237="",$E237=""),"",MAX(0,$E237-$D237))</f>
+        <v/>
+      </c>
+      <c r="G237" s="14" t="str">
+        <f aca="false">IF($A237="","",IF($E237&lt;&gt;"",IF(N($F237)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D237="","Sem data prometida",IF($D237&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H237" s="15"/>
+      <c r="I237" s="15"/>
+    </row>
+    <row r="238" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="14"/>
+      <c r="B238" s="15"/>
+      <c r="C238" s="13"/>
+      <c r="D238" s="13"/>
+      <c r="E238" s="13"/>
+      <c r="F238" s="14" t="str">
+        <f aca="false">IF(OR($A238="",$D238="",$E238=""),"",MAX(0,$E238-$D238))</f>
+        <v/>
+      </c>
+      <c r="G238" s="14" t="str">
+        <f aca="false">IF($A238="","",IF($E238&lt;&gt;"",IF(N($F238)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D238="","Sem data prometida",IF($D238&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H238" s="15"/>
+      <c r="I238" s="15"/>
+    </row>
+    <row r="239" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="14"/>
+      <c r="B239" s="15"/>
+      <c r="C239" s="13"/>
+      <c r="D239" s="13"/>
+      <c r="E239" s="13"/>
+      <c r="F239" s="14" t="str">
+        <f aca="false">IF(OR($A239="",$D239="",$E239=""),"",MAX(0,$E239-$D239))</f>
+        <v/>
+      </c>
+      <c r="G239" s="14" t="str">
+        <f aca="false">IF($A239="","",IF($E239&lt;&gt;"",IF(N($F239)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D239="","Sem data prometida",IF($D239&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H239" s="15"/>
+      <c r="I239" s="15"/>
+    </row>
+    <row r="240" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="14"/>
+      <c r="B240" s="15"/>
+      <c r="C240" s="13"/>
+      <c r="D240" s="13"/>
+      <c r="E240" s="13"/>
+      <c r="F240" s="14" t="str">
+        <f aca="false">IF(OR($A240="",$D240="",$E240=""),"",MAX(0,$E240-$D240))</f>
+        <v/>
+      </c>
+      <c r="G240" s="14" t="str">
+        <f aca="false">IF($A240="","",IF($E240&lt;&gt;"",IF(N($F240)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D240="","Sem data prometida",IF($D240&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H240" s="15"/>
+      <c r="I240" s="15"/>
+    </row>
+    <row r="241" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="14"/>
+      <c r="B241" s="15"/>
+      <c r="C241" s="13"/>
+      <c r="D241" s="13"/>
+      <c r="E241" s="13"/>
+      <c r="F241" s="14" t="str">
+        <f aca="false">IF(OR($A241="",$D241="",$E241=""),"",MAX(0,$E241-$D241))</f>
+        <v/>
+      </c>
+      <c r="G241" s="14" t="str">
+        <f aca="false">IF($A241="","",IF($E241&lt;&gt;"",IF(N($F241)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D241="","Sem data prometida",IF($D241&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H241" s="15"/>
+      <c r="I241" s="15"/>
+    </row>
+    <row r="242" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="14"/>
+      <c r="B242" s="15"/>
+      <c r="C242" s="13"/>
+      <c r="D242" s="13"/>
+      <c r="E242" s="13"/>
+      <c r="F242" s="14" t="str">
+        <f aca="false">IF(OR($A242="",$D242="",$E242=""),"",MAX(0,$E242-$D242))</f>
+        <v/>
+      </c>
+      <c r="G242" s="14" t="str">
+        <f aca="false">IF($A242="","",IF($E242&lt;&gt;"",IF(N($F242)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D242="","Sem data prometida",IF($D242&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H242" s="15"/>
+      <c r="I242" s="15"/>
+    </row>
+    <row r="243" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="14"/>
+      <c r="B243" s="15"/>
+      <c r="C243" s="13"/>
+      <c r="D243" s="13"/>
+      <c r="E243" s="13"/>
+      <c r="F243" s="14" t="str">
+        <f aca="false">IF(OR($A243="",$D243="",$E243=""),"",MAX(0,$E243-$D243))</f>
+        <v/>
+      </c>
+      <c r="G243" s="14" t="str">
+        <f aca="false">IF($A243="","",IF($E243&lt;&gt;"",IF(N($F243)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D243="","Sem data prometida",IF($D243&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H243" s="15"/>
+      <c r="I243" s="15"/>
+    </row>
+    <row r="244" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A244" s="14"/>
+      <c r="B244" s="15"/>
+      <c r="C244" s="13"/>
+      <c r="D244" s="13"/>
+      <c r="E244" s="13"/>
+      <c r="F244" s="14" t="str">
+        <f aca="false">IF(OR($A244="",$D244="",$E244=""),"",MAX(0,$E244-$D244))</f>
+        <v/>
+      </c>
+      <c r="G244" s="14" t="str">
+        <f aca="false">IF($A244="","",IF($E244&lt;&gt;"",IF(N($F244)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D244="","Sem data prometida",IF($D244&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H244" s="15"/>
+      <c r="I244" s="15"/>
+    </row>
+    <row r="245" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="14"/>
+      <c r="B245" s="15"/>
+      <c r="C245" s="13"/>
+      <c r="D245" s="13"/>
+      <c r="E245" s="13"/>
+      <c r="F245" s="14" t="str">
+        <f aca="false">IF(OR($A245="",$D245="",$E245=""),"",MAX(0,$E245-$D245))</f>
+        <v/>
+      </c>
+      <c r="G245" s="14" t="str">
+        <f aca="false">IF($A245="","",IF($E245&lt;&gt;"",IF(N($F245)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D245="","Sem data prometida",IF($D245&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H245" s="15"/>
+      <c r="I245" s="15"/>
+    </row>
+    <row r="246" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A246" s="14"/>
+      <c r="B246" s="15"/>
+      <c r="C246" s="13"/>
+      <c r="D246" s="13"/>
+      <c r="E246" s="13"/>
+      <c r="F246" s="14" t="str">
+        <f aca="false">IF(OR($A246="",$D246="",$E246=""),"",MAX(0,$E246-$D246))</f>
+        <v/>
+      </c>
+      <c r="G246" s="14" t="str">
+        <f aca="false">IF($A246="","",IF($E246&lt;&gt;"",IF(N($F246)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D246="","Sem data prometida",IF($D246&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H246" s="15"/>
+      <c r="I246" s="15"/>
+    </row>
+    <row r="247" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="14"/>
+      <c r="B247" s="15"/>
+      <c r="C247" s="13"/>
+      <c r="D247" s="13"/>
+      <c r="E247" s="13"/>
+      <c r="F247" s="14" t="str">
+        <f aca="false">IF(OR($A247="",$D247="",$E247=""),"",MAX(0,$E247-$D247))</f>
+        <v/>
+      </c>
+      <c r="G247" s="14" t="str">
+        <f aca="false">IF($A247="","",IF($E247&lt;&gt;"",IF(N($F247)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D247="","Sem data prometida",IF($D247&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H247" s="15"/>
+      <c r="I247" s="15"/>
+    </row>
+    <row r="248" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="14"/>
+      <c r="B248" s="15"/>
+      <c r="C248" s="13"/>
+      <c r="D248" s="13"/>
+      <c r="E248" s="13"/>
+      <c r="F248" s="14" t="str">
+        <f aca="false">IF(OR($A248="",$D248="",$E248=""),"",MAX(0,$E248-$D248))</f>
+        <v/>
+      </c>
+      <c r="G248" s="14" t="str">
+        <f aca="false">IF($A248="","",IF($E248&lt;&gt;"",IF(N($F248)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D248="","Sem data prometida",IF($D248&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H248" s="15"/>
+      <c r="I248" s="15"/>
+    </row>
+    <row r="249" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="14"/>
+      <c r="B249" s="15"/>
+      <c r="C249" s="13"/>
+      <c r="D249" s="13"/>
+      <c r="E249" s="13"/>
+      <c r="F249" s="14" t="str">
+        <f aca="false">IF(OR($A249="",$D249="",$E249=""),"",MAX(0,$E249-$D249))</f>
+        <v/>
+      </c>
+      <c r="G249" s="14" t="str">
+        <f aca="false">IF($A249="","",IF($E249&lt;&gt;"",IF(N($F249)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D249="","Sem data prometida",IF($D249&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H249" s="15"/>
+      <c r="I249" s="15"/>
+    </row>
+    <row r="250" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="14"/>
+      <c r="B250" s="15"/>
+      <c r="C250" s="13"/>
+      <c r="D250" s="13"/>
+      <c r="E250" s="13"/>
+      <c r="F250" s="14" t="str">
+        <f aca="false">IF(OR($A250="",$D250="",$E250=""),"",MAX(0,$E250-$D250))</f>
+        <v/>
+      </c>
+      <c r="G250" s="14" t="str">
+        <f aca="false">IF($A250="","",IF($E250&lt;&gt;"",IF(N($F250)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D250="","Sem data prometida",IF($D250&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H250" s="15"/>
+      <c r="I250" s="15"/>
+    </row>
+    <row r="251" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="14"/>
+      <c r="B251" s="15"/>
+      <c r="C251" s="13"/>
+      <c r="D251" s="13"/>
+      <c r="E251" s="13"/>
+      <c r="F251" s="14" t="str">
+        <f aca="false">IF(OR($A251="",$D251="",$E251=""),"",MAX(0,$E251-$D251))</f>
+        <v/>
+      </c>
+      <c r="G251" s="14" t="str">
+        <f aca="false">IF($A251="","",IF($E251&lt;&gt;"",IF(N($F251)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D251="","Sem data prometida",IF($D251&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H251" s="15"/>
+      <c r="I251" s="15"/>
+    </row>
+    <row r="252" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="14"/>
+      <c r="B252" s="15"/>
+      <c r="C252" s="13"/>
+      <c r="D252" s="13"/>
+      <c r="E252" s="13"/>
+      <c r="F252" s="14" t="str">
+        <f aca="false">IF(OR($A252="",$D252="",$E252=""),"",MAX(0,$E252-$D252))</f>
+        <v/>
+      </c>
+      <c r="G252" s="14" t="str">
+        <f aca="false">IF($A252="","",IF($E252&lt;&gt;"",IF(N($F252)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D252="","Sem data prometida",IF($D252&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H252" s="15"/>
+      <c r="I252" s="15"/>
+    </row>
+    <row r="253" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A253" s="14"/>
+      <c r="B253" s="15"/>
+      <c r="C253" s="13"/>
+      <c r="D253" s="13"/>
+      <c r="E253" s="13"/>
+      <c r="F253" s="14" t="str">
+        <f aca="false">IF(OR($A253="",$D253="",$E253=""),"",MAX(0,$E253-$D253))</f>
+        <v/>
+      </c>
+      <c r="G253" s="14" t="str">
+        <f aca="false">IF($A253="","",IF($E253&lt;&gt;"",IF(N($F253)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D253="","Sem data prometida",IF($D253&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H253" s="15"/>
+      <c r="I253" s="15"/>
+    </row>
+    <row r="254" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A254" s="14"/>
+      <c r="B254" s="15"/>
+      <c r="C254" s="13"/>
+      <c r="D254" s="13"/>
+      <c r="E254" s="13"/>
+      <c r="F254" s="14" t="str">
+        <f aca="false">IF(OR($A254="",$D254="",$E254=""),"",MAX(0,$E254-$D254))</f>
+        <v/>
+      </c>
+      <c r="G254" s="14" t="str">
+        <f aca="false">IF($A254="","",IF($E254&lt;&gt;"",IF(N($F254)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D254="","Sem data prometida",IF($D254&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H254" s="15"/>
+      <c r="I254" s="15"/>
+    </row>
+    <row r="255" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A255" s="14"/>
+      <c r="B255" s="15"/>
+      <c r="C255" s="13"/>
+      <c r="D255" s="13"/>
+      <c r="E255" s="13"/>
+      <c r="F255" s="14" t="str">
+        <f aca="false">IF(OR($A255="",$D255="",$E255=""),"",MAX(0,$E255-$D255))</f>
+        <v/>
+      </c>
+      <c r="G255" s="14" t="str">
+        <f aca="false">IF($A255="","",IF($E255&lt;&gt;"",IF(N($F255)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D255="","Sem data prometida",IF($D255&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H255" s="15"/>
+      <c r="I255" s="15"/>
+    </row>
+    <row r="256" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="14"/>
+      <c r="B256" s="15"/>
+      <c r="C256" s="13"/>
+      <c r="D256" s="13"/>
+      <c r="E256" s="13"/>
+      <c r="F256" s="14" t="str">
+        <f aca="false">IF(OR($A256="",$D256="",$E256=""),"",MAX(0,$E256-$D256))</f>
+        <v/>
+      </c>
+      <c r="G256" s="14" t="str">
+        <f aca="false">IF($A256="","",IF($E256&lt;&gt;"",IF(N($F256)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D256="","Sem data prometida",IF($D256&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H256" s="15"/>
+      <c r="I256" s="15"/>
+    </row>
+    <row r="257" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A257" s="14"/>
+      <c r="B257" s="15"/>
+      <c r="C257" s="13"/>
+      <c r="D257" s="13"/>
+      <c r="E257" s="13"/>
+      <c r="F257" s="14" t="str">
+        <f aca="false">IF(OR($A257="",$D257="",$E257=""),"",MAX(0,$E257-$D257))</f>
+        <v/>
+      </c>
+      <c r="G257" s="14" t="str">
+        <f aca="false">IF($A257="","",IF($E257&lt;&gt;"",IF(N($F257)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D257="","Sem data prometida",IF($D257&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H257" s="15"/>
+      <c r="I257" s="15"/>
+    </row>
+    <row r="258" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A258" s="14"/>
+      <c r="B258" s="15"/>
+      <c r="C258" s="13"/>
+      <c r="D258" s="13"/>
+      <c r="E258" s="13"/>
+      <c r="F258" s="14" t="str">
+        <f aca="false">IF(OR($A258="",$D258="",$E258=""),"",MAX(0,$E258-$D258))</f>
+        <v/>
+      </c>
+      <c r="G258" s="14" t="str">
+        <f aca="false">IF($A258="","",IF($E258&lt;&gt;"",IF(N($F258)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D258="","Sem data prometida",IF($D258&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H258" s="15"/>
+      <c r="I258" s="15"/>
+    </row>
+    <row r="259" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="14"/>
+      <c r="B259" s="15"/>
+      <c r="C259" s="13"/>
+      <c r="D259" s="13"/>
+      <c r="E259" s="13"/>
+      <c r="F259" s="14" t="str">
+        <f aca="false">IF(OR($A259="",$D259="",$E259=""),"",MAX(0,$E259-$D259))</f>
+        <v/>
+      </c>
+      <c r="G259" s="14" t="str">
+        <f aca="false">IF($A259="","",IF($E259&lt;&gt;"",IF(N($F259)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D259="","Sem data prometida",IF($D259&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H259" s="15"/>
+      <c r="I259" s="15"/>
+    </row>
+    <row r="260" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A260" s="14"/>
+      <c r="B260" s="15"/>
+      <c r="C260" s="13"/>
+      <c r="D260" s="13"/>
+      <c r="E260" s="13"/>
+      <c r="F260" s="14" t="str">
+        <f aca="false">IF(OR($A260="",$D260="",$E260=""),"",MAX(0,$E260-$D260))</f>
+        <v/>
+      </c>
+      <c r="G260" s="14" t="str">
+        <f aca="false">IF($A260="","",IF($E260&lt;&gt;"",IF(N($F260)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D260="","Sem data prometida",IF($D260&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H260" s="15"/>
+      <c r="I260" s="15"/>
+    </row>
+    <row r="261" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A261" s="14"/>
+      <c r="B261" s="15"/>
+      <c r="C261" s="13"/>
+      <c r="D261" s="13"/>
+      <c r="E261" s="13"/>
+      <c r="F261" s="14" t="str">
+        <f aca="false">IF(OR($A261="",$D261="",$E261=""),"",MAX(0,$E261-$D261))</f>
+        <v/>
+      </c>
+      <c r="G261" s="14" t="str">
+        <f aca="false">IF($A261="","",IF($E261&lt;&gt;"",IF(N($F261)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D261="","Sem data prometida",IF($D261&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H261" s="15"/>
+      <c r="I261" s="15"/>
+    </row>
+    <row r="262" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="14"/>
+      <c r="B262" s="15"/>
+      <c r="C262" s="13"/>
+      <c r="D262" s="13"/>
+      <c r="E262" s="13"/>
+      <c r="F262" s="14" t="str">
+        <f aca="false">IF(OR($A262="",$D262="",$E262=""),"",MAX(0,$E262-$D262))</f>
+        <v/>
+      </c>
+      <c r="G262" s="14" t="str">
+        <f aca="false">IF($A262="","",IF($E262&lt;&gt;"",IF(N($F262)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D262="","Sem data prometida",IF($D262&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H262" s="15"/>
+      <c r="I262" s="15"/>
+    </row>
+    <row r="263" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A263" s="14"/>
+      <c r="B263" s="15"/>
+      <c r="C263" s="13"/>
+      <c r="D263" s="13"/>
+      <c r="E263" s="13"/>
+      <c r="F263" s="14" t="str">
+        <f aca="false">IF(OR($A263="",$D263="",$E263=""),"",MAX(0,$E263-$D263))</f>
+        <v/>
+      </c>
+      <c r="G263" s="14" t="str">
+        <f aca="false">IF($A263="","",IF($E263&lt;&gt;"",IF(N($F263)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D263="","Sem data prometida",IF($D263&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H263" s="15"/>
+      <c r="I263" s="15"/>
+    </row>
+    <row r="264" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A264" s="14"/>
+      <c r="B264" s="15"/>
+      <c r="C264" s="13"/>
+      <c r="D264" s="13"/>
+      <c r="E264" s="13"/>
+      <c r="F264" s="14" t="str">
+        <f aca="false">IF(OR($A264="",$D264="",$E264=""),"",MAX(0,$E264-$D264))</f>
+        <v/>
+      </c>
+      <c r="G264" s="14" t="str">
+        <f aca="false">IF($A264="","",IF($E264&lt;&gt;"",IF(N($F264)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D264="","Sem data prometida",IF($D264&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H264" s="15"/>
+      <c r="I264" s="15"/>
+    </row>
+    <row r="265" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A265" s="14"/>
+      <c r="B265" s="15"/>
+      <c r="C265" s="13"/>
+      <c r="D265" s="13"/>
+      <c r="E265" s="13"/>
+      <c r="F265" s="14" t="str">
+        <f aca="false">IF(OR($A265="",$D265="",$E265=""),"",MAX(0,$E265-$D265))</f>
+        <v/>
+      </c>
+      <c r="G265" s="14" t="str">
+        <f aca="false">IF($A265="","",IF($E265&lt;&gt;"",IF(N($F265)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D265="","Sem data prometida",IF($D265&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H265" s="15"/>
+      <c r="I265" s="15"/>
+    </row>
+    <row r="266" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A266" s="14"/>
+      <c r="B266" s="15"/>
+      <c r="C266" s="13"/>
+      <c r="D266" s="13"/>
+      <c r="E266" s="13"/>
+      <c r="F266" s="14" t="str">
+        <f aca="false">IF(OR($A266="",$D266="",$E266=""),"",MAX(0,$E266-$D266))</f>
+        <v/>
+      </c>
+      <c r="G266" s="14" t="str">
+        <f aca="false">IF($A266="","",IF($E266&lt;&gt;"",IF(N($F266)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D266="","Sem data prometida",IF($D266&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H266" s="15"/>
+      <c r="I266" s="15"/>
+    </row>
+    <row r="267" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="14"/>
+      <c r="B267" s="15"/>
+      <c r="C267" s="13"/>
+      <c r="D267" s="13"/>
+      <c r="E267" s="13"/>
+      <c r="F267" s="14" t="str">
+        <f aca="false">IF(OR($A267="",$D267="",$E267=""),"",MAX(0,$E267-$D267))</f>
+        <v/>
+      </c>
+      <c r="G267" s="14" t="str">
+        <f aca="false">IF($A267="","",IF($E267&lt;&gt;"",IF(N($F267)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D267="","Sem data prometida",IF($D267&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H267" s="15"/>
+      <c r="I267" s="15"/>
+    </row>
+    <row r="268" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="14"/>
+      <c r="B268" s="15"/>
+      <c r="C268" s="13"/>
+      <c r="D268" s="13"/>
+      <c r="E268" s="13"/>
+      <c r="F268" s="14" t="str">
+        <f aca="false">IF(OR($A268="",$D268="",$E268=""),"",MAX(0,$E268-$D268))</f>
+        <v/>
+      </c>
+      <c r="G268" s="14" t="str">
+        <f aca="false">IF($A268="","",IF($E268&lt;&gt;"",IF(N($F268)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D268="","Sem data prometida",IF($D268&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H268" s="15"/>
+      <c r="I268" s="15"/>
+    </row>
+    <row r="269" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A269" s="14"/>
+      <c r="B269" s="15"/>
+      <c r="C269" s="13"/>
+      <c r="D269" s="13"/>
+      <c r="E269" s="13"/>
+      <c r="F269" s="14" t="str">
+        <f aca="false">IF(OR($A269="",$D269="",$E269=""),"",MAX(0,$E269-$D269))</f>
+        <v/>
+      </c>
+      <c r="G269" s="14" t="str">
+        <f aca="false">IF($A269="","",IF($E269&lt;&gt;"",IF(N($F269)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D269="","Sem data prometida",IF($D269&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H269" s="15"/>
+      <c r="I269" s="15"/>
+    </row>
+    <row r="270" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A270" s="14"/>
+      <c r="B270" s="15"/>
+      <c r="C270" s="13"/>
+      <c r="D270" s="13"/>
+      <c r="E270" s="13"/>
+      <c r="F270" s="14" t="str">
+        <f aca="false">IF(OR($A270="",$D270="",$E270=""),"",MAX(0,$E270-$D270))</f>
+        <v/>
+      </c>
+      <c r="G270" s="14" t="str">
+        <f aca="false">IF($A270="","",IF($E270&lt;&gt;"",IF(N($F270)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D270="","Sem data prometida",IF($D270&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H270" s="15"/>
+      <c r="I270" s="15"/>
+    </row>
+    <row r="271" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A271" s="14"/>
+      <c r="B271" s="15"/>
+      <c r="C271" s="13"/>
+      <c r="D271" s="13"/>
+      <c r="E271" s="13"/>
+      <c r="F271" s="14" t="str">
+        <f aca="false">IF(OR($A271="",$D271="",$E271=""),"",MAX(0,$E271-$D271))</f>
+        <v/>
+      </c>
+      <c r="G271" s="14" t="str">
+        <f aca="false">IF($A271="","",IF($E271&lt;&gt;"",IF(N($F271)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D271="","Sem data prometida",IF($D271&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H271" s="15"/>
+      <c r="I271" s="15"/>
+    </row>
+    <row r="272" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A272" s="14"/>
+      <c r="B272" s="15"/>
+      <c r="C272" s="13"/>
+      <c r="D272" s="13"/>
+      <c r="E272" s="13"/>
+      <c r="F272" s="14" t="str">
+        <f aca="false">IF(OR($A272="",$D272="",$E272=""),"",MAX(0,$E272-$D272))</f>
+        <v/>
+      </c>
+      <c r="G272" s="14" t="str">
+        <f aca="false">IF($A272="","",IF($E272&lt;&gt;"",IF(N($F272)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D272="","Sem data prometida",IF($D272&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H272" s="15"/>
+      <c r="I272" s="15"/>
+    </row>
+    <row r="273" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="14"/>
+      <c r="B273" s="15"/>
+      <c r="C273" s="13"/>
+      <c r="D273" s="13"/>
+      <c r="E273" s="13"/>
+      <c r="F273" s="14" t="str">
+        <f aca="false">IF(OR($A273="",$D273="",$E273=""),"",MAX(0,$E273-$D273))</f>
+        <v/>
+      </c>
+      <c r="G273" s="14" t="str">
+        <f aca="false">IF($A273="","",IF($E273&lt;&gt;"",IF(N($F273)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D273="","Sem data prometida",IF($D273&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H273" s="15"/>
+      <c r="I273" s="15"/>
+    </row>
+    <row r="274" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A274" s="14"/>
+      <c r="B274" s="15"/>
+      <c r="C274" s="13"/>
+      <c r="D274" s="13"/>
+      <c r="E274" s="13"/>
+      <c r="F274" s="14" t="str">
+        <f aca="false">IF(OR($A274="",$D274="",$E274=""),"",MAX(0,$E274-$D274))</f>
+        <v/>
+      </c>
+      <c r="G274" s="14" t="str">
+        <f aca="false">IF($A274="","",IF($E274&lt;&gt;"",IF(N($F274)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D274="","Sem data prometida",IF($D274&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H274" s="15"/>
+      <c r="I274" s="15"/>
+    </row>
+    <row r="275" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A275" s="14"/>
+      <c r="B275" s="15"/>
+      <c r="C275" s="13"/>
+      <c r="D275" s="13"/>
+      <c r="E275" s="13"/>
+      <c r="F275" s="14" t="str">
+        <f aca="false">IF(OR($A275="",$D275="",$E275=""),"",MAX(0,$E275-$D275))</f>
+        <v/>
+      </c>
+      <c r="G275" s="14" t="str">
+        <f aca="false">IF($A275="","",IF($E275&lt;&gt;"",IF(N($F275)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D275="","Sem data prometida",IF($D275&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H275" s="15"/>
+      <c r="I275" s="15"/>
+    </row>
+    <row r="276" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A276" s="14"/>
+      <c r="B276" s="15"/>
+      <c r="C276" s="13"/>
+      <c r="D276" s="13"/>
+      <c r="E276" s="13"/>
+      <c r="F276" s="14" t="str">
+        <f aca="false">IF(OR($A276="",$D276="",$E276=""),"",MAX(0,$E276-$D276))</f>
+        <v/>
+      </c>
+      <c r="G276" s="14" t="str">
+        <f aca="false">IF($A276="","",IF($E276&lt;&gt;"",IF(N($F276)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D276="","Sem data prometida",IF($D276&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H276" s="15"/>
+      <c r="I276" s="15"/>
+    </row>
+    <row r="277" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A277" s="14"/>
+      <c r="B277" s="15"/>
+      <c r="C277" s="13"/>
+      <c r="D277" s="13"/>
+      <c r="E277" s="13"/>
+      <c r="F277" s="14" t="str">
+        <f aca="false">IF(OR($A277="",$D277="",$E277=""),"",MAX(0,$E277-$D277))</f>
+        <v/>
+      </c>
+      <c r="G277" s="14" t="str">
+        <f aca="false">IF($A277="","",IF($E277&lt;&gt;"",IF(N($F277)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D277="","Sem data prometida",IF($D277&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H277" s="15"/>
+      <c r="I277" s="15"/>
+    </row>
+    <row r="278" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A278" s="14"/>
+      <c r="B278" s="15"/>
+      <c r="C278" s="13"/>
+      <c r="D278" s="13"/>
+      <c r="E278" s="13"/>
+      <c r="F278" s="14" t="str">
+        <f aca="false">IF(OR($A278="",$D278="",$E278=""),"",MAX(0,$E278-$D278))</f>
+        <v/>
+      </c>
+      <c r="G278" s="14" t="str">
+        <f aca="false">IF($A278="","",IF($E278&lt;&gt;"",IF(N($F278)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D278="","Sem data prometida",IF($D278&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H278" s="15"/>
+      <c r="I278" s="15"/>
+    </row>
+    <row r="279" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A279" s="14"/>
+      <c r="B279" s="15"/>
+      <c r="C279" s="13"/>
+      <c r="D279" s="13"/>
+      <c r="E279" s="13"/>
+      <c r="F279" s="14" t="str">
+        <f aca="false">IF(OR($A279="",$D279="",$E279=""),"",MAX(0,$E279-$D279))</f>
+        <v/>
+      </c>
+      <c r="G279" s="14" t="str">
+        <f aca="false">IF($A279="","",IF($E279&lt;&gt;"",IF(N($F279)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D279="","Sem data prometida",IF($D279&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H279" s="15"/>
+      <c r="I279" s="15"/>
+    </row>
+    <row r="280" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A280" s="14"/>
+      <c r="B280" s="15"/>
+      <c r="C280" s="13"/>
+      <c r="D280" s="13"/>
+      <c r="E280" s="13"/>
+      <c r="F280" s="14" t="str">
+        <f aca="false">IF(OR($A280="",$D280="",$E280=""),"",MAX(0,$E280-$D280))</f>
+        <v/>
+      </c>
+      <c r="G280" s="14" t="str">
+        <f aca="false">IF($A280="","",IF($E280&lt;&gt;"",IF(N($F280)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D280="","Sem data prometida",IF($D280&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H280" s="15"/>
+      <c r="I280" s="15"/>
+    </row>
+    <row r="281" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A281" s="14"/>
+      <c r="B281" s="15"/>
+      <c r="C281" s="13"/>
+      <c r="D281" s="13"/>
+      <c r="E281" s="13"/>
+      <c r="F281" s="14" t="str">
+        <f aca="false">IF(OR($A281="",$D281="",$E281=""),"",MAX(0,$E281-$D281))</f>
+        <v/>
+      </c>
+      <c r="G281" s="14" t="str">
+        <f aca="false">IF($A281="","",IF($E281&lt;&gt;"",IF(N($F281)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D281="","Sem data prometida",IF($D281&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H281" s="15"/>
+      <c r="I281" s="15"/>
+    </row>
+    <row r="282" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A282" s="14"/>
+      <c r="B282" s="15"/>
+      <c r="C282" s="13"/>
+      <c r="D282" s="13"/>
+      <c r="E282" s="13"/>
+      <c r="F282" s="14" t="str">
+        <f aca="false">IF(OR($A282="",$D282="",$E282=""),"",MAX(0,$E282-$D282))</f>
+        <v/>
+      </c>
+      <c r="G282" s="14" t="str">
+        <f aca="false">IF($A282="","",IF($E282&lt;&gt;"",IF(N($F282)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D282="","Sem data prometida",IF($D282&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H282" s="15"/>
+      <c r="I282" s="15"/>
+    </row>
+    <row r="283" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A283" s="14"/>
+      <c r="B283" s="15"/>
+      <c r="C283" s="13"/>
+      <c r="D283" s="13"/>
+      <c r="E283" s="13"/>
+      <c r="F283" s="14" t="str">
+        <f aca="false">IF(OR($A283="",$D283="",$E283=""),"",MAX(0,$E283-$D283))</f>
+        <v/>
+      </c>
+      <c r="G283" s="14" t="str">
+        <f aca="false">IF($A283="","",IF($E283&lt;&gt;"",IF(N($F283)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D283="","Sem data prometida",IF($D283&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H283" s="15"/>
+      <c r="I283" s="15"/>
+    </row>
+    <row r="284" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A284" s="14"/>
+      <c r="B284" s="15"/>
+      <c r="C284" s="13"/>
+      <c r="D284" s="13"/>
+      <c r="E284" s="13"/>
+      <c r="F284" s="14" t="str">
+        <f aca="false">IF(OR($A284="",$D284="",$E284=""),"",MAX(0,$E284-$D284))</f>
+        <v/>
+      </c>
+      <c r="G284" s="14" t="str">
+        <f aca="false">IF($A284="","",IF($E284&lt;&gt;"",IF(N($F284)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D284="","Sem data prometida",IF($D284&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H284" s="15"/>
+      <c r="I284" s="15"/>
+    </row>
+    <row r="285" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A285" s="14"/>
+      <c r="B285" s="15"/>
+      <c r="C285" s="13"/>
+      <c r="D285" s="13"/>
+      <c r="E285" s="13"/>
+      <c r="F285" s="14" t="str">
+        <f aca="false">IF(OR($A285="",$D285="",$E285=""),"",MAX(0,$E285-$D285))</f>
+        <v/>
+      </c>
+      <c r="G285" s="14" t="str">
+        <f aca="false">IF($A285="","",IF($E285&lt;&gt;"",IF(N($F285)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D285="","Sem data prometida",IF($D285&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H285" s="15"/>
+      <c r="I285" s="15"/>
+    </row>
+    <row r="286" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A286" s="14"/>
+      <c r="B286" s="15"/>
+      <c r="C286" s="13"/>
+      <c r="D286" s="13"/>
+      <c r="E286" s="13"/>
+      <c r="F286" s="14" t="str">
+        <f aca="false">IF(OR($A286="",$D286="",$E286=""),"",MAX(0,$E286-$D286))</f>
+        <v/>
+      </c>
+      <c r="G286" s="14" t="str">
+        <f aca="false">IF($A286="","",IF($E286&lt;&gt;"",IF(N($F286)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D286="","Sem data prometida",IF($D286&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H286" s="15"/>
+      <c r="I286" s="15"/>
+    </row>
+    <row r="287" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A287" s="14"/>
+      <c r="B287" s="15"/>
+      <c r="C287" s="13"/>
+      <c r="D287" s="13"/>
+      <c r="E287" s="13"/>
+      <c r="F287" s="14" t="str">
+        <f aca="false">IF(OR($A287="",$D287="",$E287=""),"",MAX(0,$E287-$D287))</f>
+        <v/>
+      </c>
+      <c r="G287" s="14" t="str">
+        <f aca="false">IF($A287="","",IF($E287&lt;&gt;"",IF(N($F287)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D287="","Sem data prometida",IF($D287&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H287" s="15"/>
+      <c r="I287" s="15"/>
+    </row>
+    <row r="288" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A288" s="14"/>
+      <c r="B288" s="15"/>
+      <c r="C288" s="13"/>
+      <c r="D288" s="13"/>
+      <c r="E288" s="13"/>
+      <c r="F288" s="14" t="str">
+        <f aca="false">IF(OR($A288="",$D288="",$E288=""),"",MAX(0,$E288-$D288))</f>
+        <v/>
+      </c>
+      <c r="G288" s="14" t="str">
+        <f aca="false">IF($A288="","",IF($E288&lt;&gt;"",IF(N($F288)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D288="","Sem data prometida",IF($D288&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H288" s="15"/>
+      <c r="I288" s="15"/>
+    </row>
+    <row r="289" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A289" s="14"/>
+      <c r="B289" s="15"/>
+      <c r="C289" s="13"/>
+      <c r="D289" s="13"/>
+      <c r="E289" s="13"/>
+      <c r="F289" s="14" t="str">
+        <f aca="false">IF(OR($A289="",$D289="",$E289=""),"",MAX(0,$E289-$D289))</f>
+        <v/>
+      </c>
+      <c r="G289" s="14" t="str">
+        <f aca="false">IF($A289="","",IF($E289&lt;&gt;"",IF(N($F289)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D289="","Sem data prometida",IF($D289&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H289" s="15"/>
+      <c r="I289" s="15"/>
+    </row>
+    <row r="290" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A290" s="14"/>
+      <c r="B290" s="15"/>
+      <c r="C290" s="13"/>
+      <c r="D290" s="13"/>
+      <c r="E290" s="13"/>
+      <c r="F290" s="14" t="str">
+        <f aca="false">IF(OR($A290="",$D290="",$E290=""),"",MAX(0,$E290-$D290))</f>
+        <v/>
+      </c>
+      <c r="G290" s="14" t="str">
+        <f aca="false">IF($A290="","",IF($E290&lt;&gt;"",IF(N($F290)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D290="","Sem data prometida",IF($D290&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H290" s="15"/>
+      <c r="I290" s="15"/>
+    </row>
+    <row r="291" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A291" s="14"/>
+      <c r="B291" s="15"/>
+      <c r="C291" s="13"/>
+      <c r="D291" s="13"/>
+      <c r="E291" s="13"/>
+      <c r="F291" s="14" t="str">
+        <f aca="false">IF(OR($A291="",$D291="",$E291=""),"",MAX(0,$E291-$D291))</f>
+        <v/>
+      </c>
+      <c r="G291" s="14" t="str">
+        <f aca="false">IF($A291="","",IF($E291&lt;&gt;"",IF(N($F291)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D291="","Sem data prometida",IF($D291&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H291" s="15"/>
+      <c r="I291" s="15"/>
+    </row>
+    <row r="292" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A292" s="14"/>
+      <c r="B292" s="15"/>
+      <c r="C292" s="13"/>
+      <c r="D292" s="13"/>
+      <c r="E292" s="13"/>
+      <c r="F292" s="14" t="str">
+        <f aca="false">IF(OR($A292="",$D292="",$E292=""),"",MAX(0,$E292-$D292))</f>
+        <v/>
+      </c>
+      <c r="G292" s="14" t="str">
+        <f aca="false">IF($A292="","",IF($E292&lt;&gt;"",IF(N($F292)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D292="","Sem data prometida",IF($D292&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H292" s="15"/>
+      <c r="I292" s="15"/>
+    </row>
+    <row r="293" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A293" s="14"/>
+      <c r="B293" s="15"/>
+      <c r="C293" s="13"/>
+      <c r="D293" s="13"/>
+      <c r="E293" s="13"/>
+      <c r="F293" s="14" t="str">
+        <f aca="false">IF(OR($A293="",$D293="",$E293=""),"",MAX(0,$E293-$D293))</f>
+        <v/>
+      </c>
+      <c r="G293" s="14" t="str">
+        <f aca="false">IF($A293="","",IF($E293&lt;&gt;"",IF(N($F293)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D293="","Sem data prometida",IF($D293&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H293" s="15"/>
+      <c r="I293" s="15"/>
+    </row>
+    <row r="294" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A294" s="14"/>
+      <c r="B294" s="15"/>
+      <c r="C294" s="13"/>
+      <c r="D294" s="13"/>
+      <c r="E294" s="13"/>
+      <c r="F294" s="14" t="str">
+        <f aca="false">IF(OR($A294="",$D294="",$E294=""),"",MAX(0,$E294-$D294))</f>
+        <v/>
+      </c>
+      <c r="G294" s="14" t="str">
+        <f aca="false">IF($A294="","",IF($E294&lt;&gt;"",IF(N($F294)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D294="","Sem data prometida",IF($D294&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H294" s="15"/>
+      <c r="I294" s="15"/>
+    </row>
+    <row r="295" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A295" s="14"/>
+      <c r="B295" s="15"/>
+      <c r="C295" s="13"/>
+      <c r="D295" s="13"/>
+      <c r="E295" s="13"/>
+      <c r="F295" s="14" t="str">
+        <f aca="false">IF(OR($A295="",$D295="",$E295=""),"",MAX(0,$E295-$D295))</f>
+        <v/>
+      </c>
+      <c r="G295" s="14" t="str">
+        <f aca="false">IF($A295="","",IF($E295&lt;&gt;"",IF(N($F295)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D295="","Sem data prometida",IF($D295&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H295" s="15"/>
+      <c r="I295" s="15"/>
+    </row>
+    <row r="296" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A296" s="14"/>
+      <c r="B296" s="15"/>
+      <c r="C296" s="13"/>
+      <c r="D296" s="13"/>
+      <c r="E296" s="13"/>
+      <c r="F296" s="14" t="str">
+        <f aca="false">IF(OR($A296="",$D296="",$E296=""),"",MAX(0,$E296-$D296))</f>
+        <v/>
+      </c>
+      <c r="G296" s="14" t="str">
+        <f aca="false">IF($A296="","",IF($E296&lt;&gt;"",IF(N($F296)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D296="","Sem data prometida",IF($D296&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H296" s="15"/>
+      <c r="I296" s="15"/>
+    </row>
+    <row r="297" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A297" s="14"/>
+      <c r="B297" s="15"/>
+      <c r="C297" s="13"/>
+      <c r="D297" s="13"/>
+      <c r="E297" s="13"/>
+      <c r="F297" s="14" t="str">
+        <f aca="false">IF(OR($A297="",$D297="",$E297=""),"",MAX(0,$E297-$D297))</f>
+        <v/>
+      </c>
+      <c r="G297" s="14" t="str">
+        <f aca="false">IF($A297="","",IF($E297&lt;&gt;"",IF(N($F297)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D297="","Sem data prometida",IF($D297&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H297" s="15"/>
+      <c r="I297" s="15"/>
+    </row>
+    <row r="298" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A298" s="14"/>
+      <c r="B298" s="15"/>
+      <c r="C298" s="13"/>
+      <c r="D298" s="13"/>
+      <c r="E298" s="13"/>
+      <c r="F298" s="14" t="str">
+        <f aca="false">IF(OR($A298="",$D298="",$E298=""),"",MAX(0,$E298-$D298))</f>
+        <v/>
+      </c>
+      <c r="G298" s="14" t="str">
+        <f aca="false">IF($A298="","",IF($E298&lt;&gt;"",IF(N($F298)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D298="","Sem data prometida",IF($D298&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H298" s="15"/>
+      <c r="I298" s="15"/>
+    </row>
+    <row r="299" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A299" s="14"/>
+      <c r="B299" s="15"/>
+      <c r="C299" s="13"/>
+      <c r="D299" s="13"/>
+      <c r="E299" s="13"/>
+      <c r="F299" s="14" t="str">
+        <f aca="false">IF(OR($A299="",$D299="",$E299=""),"",MAX(0,$E299-$D299))</f>
+        <v/>
+      </c>
+      <c r="G299" s="14" t="str">
+        <f aca="false">IF($A299="","",IF($E299&lt;&gt;"",IF(N($F299)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D299="","Sem data prometida",IF($D299&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H299" s="15"/>
+      <c r="I299" s="15"/>
+    </row>
+    <row r="300" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A300" s="14"/>
+      <c r="B300" s="15"/>
+      <c r="C300" s="13"/>
+      <c r="D300" s="13"/>
+      <c r="E300" s="13"/>
+      <c r="F300" s="14" t="str">
+        <f aca="false">IF(OR($A300="",$D300="",$E300=""),"",MAX(0,$E300-$D300))</f>
+        <v/>
+      </c>
+      <c r="G300" s="14" t="str">
+        <f aca="false">IF($A300="","",IF($E300&lt;&gt;"",IF(N($F300)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D300="","Sem data prometida",IF($D300&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H300" s="15"/>
+      <c r="I300" s="15"/>
+    </row>
+    <row r="301" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A301" s="14"/>
+      <c r="B301" s="15"/>
+      <c r="C301" s="13"/>
+      <c r="D301" s="13"/>
+      <c r="E301" s="13"/>
+      <c r="F301" s="14" t="str">
+        <f aca="false">IF(OR($A301="",$D301="",$E301=""),"",MAX(0,$E301-$D301))</f>
+        <v/>
+      </c>
+      <c r="G301" s="14" t="str">
+        <f aca="false">IF($A301="","",IF($E301&lt;&gt;"",IF(N($F301)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D301="","Sem data prometida",IF($D301&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H301" s="15"/>
+      <c r="I301" s="15"/>
+    </row>
+    <row r="302" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A302" s="14"/>
+      <c r="B302" s="15"/>
+      <c r="C302" s="13"/>
+      <c r="D302" s="13"/>
+      <c r="E302" s="13"/>
+      <c r="F302" s="14" t="str">
+        <f aca="false">IF(OR($A302="",$D302="",$E302=""),"",MAX(0,$E302-$D302))</f>
+        <v/>
+      </c>
+      <c r="G302" s="14" t="str">
+        <f aca="false">IF($A302="","",IF($E302&lt;&gt;"",IF(N($F302)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D302="","Sem data prometida",IF($D302&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H302" s="15"/>
+      <c r="I302" s="15"/>
+    </row>
+    <row r="303" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A303" s="14"/>
+      <c r="B303" s="15"/>
+      <c r="C303" s="13"/>
+      <c r="D303" s="13"/>
+      <c r="E303" s="13"/>
+      <c r="F303" s="14" t="str">
+        <f aca="false">IF(OR($A303="",$D303="",$E303=""),"",MAX(0,$E303-$D303))</f>
+        <v/>
+      </c>
+      <c r="G303" s="14" t="str">
+        <f aca="false">IF($A303="","",IF($E303&lt;&gt;"",IF(N($F303)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D303="","Sem data prometida",IF($D303&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H303" s="15"/>
+      <c r="I303" s="15"/>
+    </row>
+    <row r="304" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A304" s="14"/>
+      <c r="B304" s="15"/>
+      <c r="C304" s="13"/>
+      <c r="D304" s="13"/>
+      <c r="E304" s="13"/>
+      <c r="F304" s="14" t="str">
+        <f aca="false">IF(OR($A304="",$D304="",$E304=""),"",MAX(0,$E304-$D304))</f>
+        <v/>
+      </c>
+      <c r="G304" s="14" t="str">
+        <f aca="false">IF($A304="","",IF($E304&lt;&gt;"",IF(N($F304)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D304="","Sem data prometida",IF($D304&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H304" s="15"/>
+      <c r="I304" s="15"/>
+    </row>
+    <row r="305" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A305" s="14"/>
+      <c r="B305" s="15"/>
+      <c r="C305" s="13"/>
+      <c r="D305" s="13"/>
+      <c r="E305" s="13"/>
+      <c r="F305" s="14" t="str">
+        <f aca="false">IF(OR($A305="",$D305="",$E305=""),"",MAX(0,$E305-$D305))</f>
+        <v/>
+      </c>
+      <c r="G305" s="14" t="str">
+        <f aca="false">IF($A305="","",IF($E305&lt;&gt;"",IF(N($F305)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D305="","Sem data prometida",IF($D305&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H305" s="15"/>
+      <c r="I305" s="15"/>
+    </row>
+    <row r="306" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A306" s="14"/>
+      <c r="B306" s="15"/>
+      <c r="C306" s="13"/>
+      <c r="D306" s="13"/>
+      <c r="E306" s="13"/>
+      <c r="F306" s="14" t="str">
+        <f aca="false">IF(OR($A306="",$D306="",$E306=""),"",MAX(0,$E306-$D306))</f>
+        <v/>
+      </c>
+      <c r="G306" s="14" t="str">
+        <f aca="false">IF($A306="","",IF($E306&lt;&gt;"",IF(N($F306)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D306="","Sem data prometida",IF($D306&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H306" s="15"/>
+      <c r="I306" s="15"/>
+    </row>
+    <row r="307" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A307" s="14"/>
+      <c r="B307" s="15"/>
+      <c r="C307" s="13"/>
+      <c r="D307" s="13"/>
+      <c r="E307" s="13"/>
+      <c r="F307" s="14" t="str">
+        <f aca="false">IF(OR($A307="",$D307="",$E307=""),"",MAX(0,$E307-$D307))</f>
+        <v/>
+      </c>
+      <c r="G307" s="14" t="str">
+        <f aca="false">IF($A307="","",IF($E307&lt;&gt;"",IF(N($F307)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D307="","Sem data prometida",IF($D307&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H307" s="15"/>
+      <c r="I307" s="15"/>
+    </row>
+    <row r="308" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A308" s="14"/>
+      <c r="B308" s="15"/>
+      <c r="C308" s="13"/>
+      <c r="D308" s="13"/>
+      <c r="E308" s="13"/>
+      <c r="F308" s="14" t="str">
+        <f aca="false">IF(OR($A308="",$D308="",$E308=""),"",MAX(0,$E308-$D308))</f>
+        <v/>
+      </c>
+      <c r="G308" s="14" t="str">
+        <f aca="false">IF($A308="","",IF($E308&lt;&gt;"",IF(N($F308)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D308="","Sem data prometida",IF($D308&lt;$L$1,"ATRASADA","Aguardando"))))</f>
+        <v/>
+      </c>
+      <c r="H308" s="15"/>
+      <c r="I308" s="15"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:I308"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>0.85</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>0.6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:G308">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$G9="Entregue no prazo"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>$G9="Entregue com atraso"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$G9="ATRASADA"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>$G9="Aguardando"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>$G9="Sem data prometida"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F308">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>N($F9)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D308">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>AND($A9&lt;&gt;"",$D9&lt;&gt;"",$E9="",$D9&lt;$L$1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:I308">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>$E9&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Frota fora da lista — pode continuar." errorStyle="warning" errorTitle="Frota" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A9:A308" type="list">
+      <formula1>Listas!$A$2:$A$81</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Movimentações" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$265</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$264</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Dia a dia'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Dia a dia'!$A$6:$H$706</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Movimentações!$A$1:$I$37</definedName>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="537">
   <si>
     <t xml:space="preserve">PROGRAMAÇÃO DIÁRIA  ·  MAKRO TRANSPORTES</t>
   </si>
@@ -847,1009 +847,1003 @@
     <t xml:space="preserve">Airton · Luiz Paulo</t>
   </si>
   <si>
+    <t xml:space="preserve">Reapertar amortecedor segundo eixo LE;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freio terceiro eixo LE;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porta do passageiro não está abrindo por dentro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meia luz traseira com problema ( LD )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revisar pneus dianteiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lubrificar travas da cabine com dificuldade de liberar a mesma para bascular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-1038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir pneu 1º eixo LE devido desgaste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendências de inspeção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas HH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lubrificar graxeiros da quinta roda entre os bitrens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir trinca no lastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reapertar parafusos da tampa do cubo 1º eixo LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios 1º eixo LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar grade de proteção do ciclista LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar para-lamas folgados 2º eixo LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar para-lamas folgados LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar pinos da balança 2º e 3º eixo LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir travessa avariada ao lado direito da quinta roda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-1039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor estepe faltante da carreta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor porca de roda faltante 2º eixo LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir tampa do cubo 3º eixo LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir grade traseira com apoio faltante no LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir trincas no lastro da carreta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir iluminação meia-luz dianteira LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir parafusos do para-choque traseiro LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar para-lamas folgados LD e LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reapertar tirante folgado 3º eixo LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">007330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor acabamento do cinto do banco do motorista (0586501)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peça não chegou · Aguardando material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir para-sol avariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar pendências na rota de inspeção de setembro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspeção de setembro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar preventiva da frota F-425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local: Matriz · Para programar · OS informadas: 007011, 007012, 007013 · ⚠️ Aguardando identificação da OS correspondente · Origem: WhatsApp 02/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir vareta de nível de óleo avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir junta da tampa de válvulas devido vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir válvula termostática e tampa do reservatório contaminado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir amortecedores do 3º eixo LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir amortecedores da cabine (horizontais traseiros e verticais dianteiros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir joystick de mudanças</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanar vazamento no tubo de enchimento / vedação do cárter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar retrovisor inferior LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolar fiação exposta do sensor de temperatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar caixa do chicote das unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar módulo do motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios 3º eixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios 1º eixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir fixação da lameira traseira LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar cabo do varão da válvula sensível à carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar tampa superior do catalisador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar mangueira do dreno do AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir iluminação interna da cabine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir faixa refletiva do para-choque traseiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar barra V dianteira e traseira devido folga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardan Nordeste (externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terceirizada — Cardan Nordeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar recuperação da barra de direção longa (coifa rasgada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir espelho contrapoeira 2º eixo LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição das lonas de freio 1º eixo LD e LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar banco do motorista (fixação do assento e tapeçaria)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodo Ceará (externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terceirizada — Rodo Ceará</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desobstruir esguichos dos limpadores de para-brisas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar lameiras dianteiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar indicadores de porcas folgadas nas rodas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular freios do terceiro eixo LE e LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado vestígio de óleo no reservatório de ar, ficando em observação recuperar o compressor pneumático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAIXA DE CARTEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem para verificação de vazamento de óleo diesel na dianteira do motor LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir anéis de vedação das unidades devido vazamento nas mesmas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem e verificar vazamento nas juntas das tampas de válvulas, se é escorrido do vazamento de óleo diesel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir engate das marchas: substituir pino de bloqueio de marcha, realizar testes e concluir diagnóstico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir mangote superior do radiador ressecado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir farol LE avariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar lanterna do pisca LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar lanternas traseiras e placa de trânsito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar base do chicote elétrico e das mangueiras da carreta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar tubo de enchimento frontal evitando danificar o mesmo com atrito da ventoinha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar e instalar cardan do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir anéis de vedação das unidades devido vazamento nas mesmas (OS 7166 · A 023 997 64 48 (6 unidades)/A 023 997 65 48 (6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem do conjunto do filtro racor e verificar vazamento no mesmo (A 000 470 24 90 (realizar acompanhamento))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar barra de direção curta com desgaste (OS 7185 · serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar barra de direção longa com desgaste (OS 7185 · serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor espelho retrovisor inferior LE (OS 7168 · A 000 810 24 79/A 002 811 31 33 (retrovisor auxiliar completo))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor parafuso de fixação do painel frontal (OS 7189 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir instalação elétrica da tomada 12V e do acendedor de cigarros (OS 7171 · serviço interno Matriz/A 694 820 01 53/A 696 825 01 54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirar borracha inferior da cabine devido atrito com reservatório de arrefecimento, evitando danificar o mesmo (OS 7193 · serviço interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir feixes de molas dianteiros: LE com mais molas devido transporte da lança do munck (OS 7185 · serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirar espelhos das rodas traseiras, especialmente LE, para melhor visualização do desgaste das lonas de freio (OS 7190 · serviço interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar regulagem dos freios segundo eixo LD (OS 7205 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor parafuso da bieleta traseira LE (fixação com a barra estabilizadora) (OS 7192 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor acabamento das abraçadeiras do retrovisor LD (OS 7168 · A 000 811 36 07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir janela de inspeção frontal (A 940 888 11 23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor acabamento inferior do braço do retrovisor LD (OS 7168 · A 000 811 04 61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reapertar parafusos de fixação do paralama dianteiro LD (OS 7195 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor borracha de vedação da porta LD (OS 7168 · A 958 721 00 80 (2 unidades))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar acabamento da tomada OBD (OS 7196 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirar manta inferior da cabine (OS 7197 · serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição das buchas da barra estabilizadora dianteira (OS 7185 · serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir letreiro do modelo Axor "3344" (A 943 817 13 14 (certificar com fornecedor))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperar pisante do estribo LD avariado (serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bater e validar as pendências da inspeção realizada em Mossoró</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspeção Mossoró</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar cabeçote de combustível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adilton · Alexandre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar o cabeçote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba de combustível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Substituir reservatório do líquido de arrefecimento contaminado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adilton · Gabriel · Júnior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema: Estruturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Realizar lavagem e corrigir vazamento na bomba de direção hidráulica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Substituir tirante V traseiro empenado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Corrigir vazamento de ar no freio de estacionamento (maneco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Repor batedores dianteiros da cabine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar ajuste no velocímetro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REPOR PARAFUSO DE FIXAÇÃO DA GRADE DO FAROL LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre · Heliton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXAR CHICOTE ELETRICO SOLTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar troca de pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema: Pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar lavagem e corrigir vazamento na bomba de direção (serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montar adesivos e baixa de carteira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Substituir lanterna do pisca dianteiro LD avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Substituir extensão da porta LE avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Substituir saia lateral da cabine LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Programar recuperação da barra de direção curta com início de folga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar a substituição das juntas do coletor de escapamento (20855371 (6 unidades))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FICAR CHICOTE ELETRICO SOLTO NO BLOCO DE COMANDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXAR GRADE FRONTAL SOLTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir batentes dos eixos traseiros LE e LD gastos (serviço empresa especializada/20390836 (4 unidades))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar regulagem do travamento das portas, motorista relata que as mesmas estão abrindo em movimento (serviço interno Matriz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar recuperação das barras de direção curta e longa (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição da lona de freio terceiro eixo LD avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibrar e trocar pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBSTITUIR BARRA DE DIREÇÃO PEQUENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar palhetas do climatizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRIGIR MARCAÇÃO DE NICEL DE COMBUSTIVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARLA CONTAMINADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSOR DE NICEL DE AGUA COM FALHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-1064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar e calibrar pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soldar base do paralama dianteiro LD avariada (20453900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor tampa da caixa de fusíveis LD (OS 20352 · 20398773)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir para-sol avariado (82245535)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar válvula de freio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema: Freios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROCAR PNEUS E FERRAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROCAR E FERRAR PNEUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIORIDADE DO KAIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar troca ou calibração dos pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Substituir paralama dianteiro LD avariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Substituir lente da lanterna traseira LD avariada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Corujinha lateral: Avaria no lado direito (LD).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar faixa refletiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar faixas refletivas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpeza do climatizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir acabamento do retrovisor inferior LD (item em aplicação direta ou realizar pedido 21169971)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARCAÇA INTERNA DO FAROL (20453627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir bomba d'água com princípio de vazamento pelo selo lateral (20538820)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Vidros: Revisar a visibilidade dos vidros frontal e laterais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Grade frontal: Apresenta avaria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Corote: Verificar fixação, pois está batendo no para-lama.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Lameira: Avaria no lado esquerdo (LE).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Para-lama: Parafuso do lado direito (LD) folgado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição lona de freio dianteira LD avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar substituição da lona de freio dianteiro LE avariada (serviço empresa especializada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alinhar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-1065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar troca de óleo e filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir fixação elétrica solta na frente do intercooler (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar limpeza nos bornes das baterias;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposicionar lanterna corujinha do teto LE e revisar iluminação;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnosticar e corrigir falhas: ABS e caixa de marchas (embreagem);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir palhetas do limpador de para-brisas (LD não limpa) 8189631(2 UND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar tubo de escapamento inferior;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar placa dianteira e traseira;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar retrovisor LD e inferior LE;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar extensão da porta e saia lateral LD;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repor quebra-sol do motorista (está dentro da cabine);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir junta da tampa de válvulas com vazamento;20538793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir carcaça do filtro de ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar chicote elétrico solto na longarina LD (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixar mangueiras soltas na longarina LE (serviço interno base Mossoró)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completar óleo hidráulico da direção;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir lanterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vidro do passageira não aciona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presilha do farol LD e LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade do farol LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substituir pneu dianteiro LD com desgaste irregular e verificar demais - instalar indicadores de porca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferragem de pneus do bitrem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar TAG · Bitrem identificado pelo PCM como F-1065 (mensagem das 10:03) · Origem: WhatsApp 02/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar alinhamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alinhar pneus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar parabrisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terceirizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frotas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMO USAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acrescente nomes aqui e eles aparecem nas caixinhas da aba Dia a dia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIA A DIA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  A caixa amarela lá em cima é o DIA. Vem em hoje; troque para ver outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  Para achar o dia: toque na setinha da coluna Data e filtre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.  Fez? Toque em FEITO e escolha Sim. A linha apaga e o número sobe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.  Abriu a OS no Protheus? Escreva o número em OS PROTHEUS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Enquanto estiver vazia a célula fica laranja — é o que falta lançar lá.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASX (externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARA ACRESCENTAR ATIVIDADE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Escreva numa linha vazia no fim. Data, frota, atividade, e pronto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduardo da sticker (externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Sem data ela fica esperando, e entra na conta de “sem data”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molas Pinheiro (externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não há fórmula nenhuma nas linhas: pode apagar, inserir e arrastar à</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vontade que nada quebra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-871</t>
+  </si>
+  <si>
     <t xml:space="preserve">Não informada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrar pneus do bitrem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ VERIFICAR qual bitrem: a mensagem diz só 'Bitrem' · Origem: WhatsApp 02/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reapertar amortecedor segundo eixo LE;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freio terceiro eixo LE;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">porta do passageiro não está abrindo por dentro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meia luz traseira com problema ( LD )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">revisar pneus dianteiros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lubrificar travas da cabine com dificuldade de liberar a mesma para bascular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-1038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir pneu 1º eixo LE devido desgaste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendências de inspeção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apenas HH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lubrificar graxeiros da quinta roda entre os bitrens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir trinca no lastro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reapertar parafusos da tampa do cubo 1º eixo LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios 1º eixo LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar grade de proteção do ciclista LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar para-lamas folgados 2º eixo LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar para-lamas folgados LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar pinos da balança 2º e 3º eixo LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir travessa avariada ao lado direito da quinta roda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-1039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor estepe faltante da carreta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor porca de roda faltante 2º eixo LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir tampa do cubo 3º eixo LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir grade traseira com apoio faltante no LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir trincas no lastro da carreta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir iluminação meia-luz dianteira LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir parafusos do para-choque traseiro LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar para-lamas folgados LD e LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reapertar tirante folgado 3º eixo LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor acabamento do cinto do banco do motorista (0586501)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peça não chegou · Aguardando material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir para-sol avariado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar pendências na rota de inspeção de setembro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspeção de setembro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar preventiva da frota F-425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local: Matriz · Para programar · OS informadas: 007011, 007012, 007013 · ⚠️ Aguardando identificação da OS correspondente · Origem: WhatsApp 02/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir vareta de nível de óleo avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir junta da tampa de válvulas devido vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir válvula termostática e tampa do reservatório contaminado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir amortecedores do 3º eixo LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir amortecedores da cabine (horizontais traseiros e verticais dianteiros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir joystick de mudanças</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanar vazamento no tubo de enchimento / vedação do cárter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar retrovisor inferior LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolar fiação exposta do sensor de temperatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar caixa do chicote das unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar módulo do motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios 3º eixo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios 1º eixo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir fixação da lameira traseira LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar cabo do varão da válvula sensível à carga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar tampa superior do catalisador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar mangueira do dreno do AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir iluminação interna da cabine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir faixa refletiva do para-choque traseiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar barra V dianteira e traseira devido folga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardan Nordeste (externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terceirizada — Cardan Nordeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar recuperação da barra de direção longa (coifa rasgada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir espelho contrapoeira 2º eixo LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição das lonas de freio 1º eixo LD e LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar banco do motorista (fixação do assento e tapeçaria)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodo Ceará (externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terceirizada — Rodo Ceará</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desobstruir esguichos dos limpadores de para-brisas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalar lameiras dianteiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalar indicadores de porcas folgadas nas rodas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular freios do terceiro eixo LE e LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificado vestígio de óleo no reservatório de ar, ficando em observação recuperar o compressor pneumático</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAIXA DE CARTEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar lavagem para verificação de vazamento de óleo diesel na dianteira do motor LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir anéis de vedação das unidades devido vazamento nas mesmas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar lavagem e verificar vazamento nas juntas das tampas de válvulas, se é escorrido do vazamento de óleo diesel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir engate das marchas: substituir pino de bloqueio de marcha, realizar testes e concluir diagnóstico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir mangote superior do radiador ressecado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir farol LE avariado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar lanterna do pisca LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalar lanternas traseiras e placa de trânsito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar base do chicote elétrico e das mangueiras da carreta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar tubo de enchimento frontal evitando danificar o mesmo com atrito da ventoinha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar e instalar cardan do veículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir anéis de vedação das unidades devido vazamento nas mesmas (OS 7166 · A 023 997 64 48 (6 unidades)/A 023 997 65 48 (6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar lavagem do conjunto do filtro racor e verificar vazamento no mesmo (A 000 470 24 90 (realizar acompanhamento))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar barra de direção curta com desgaste (OS 7185 · serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar barra de direção longa com desgaste (OS 7185 · serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor espelho retrovisor inferior LE (OS 7168 · A 000 810 24 79/A 002 811 31 33 (retrovisor auxiliar completo))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor parafuso de fixação do painel frontal (OS 7189 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir instalação elétrica da tomada 12V e do acendedor de cigarros (OS 7171 · serviço interno Matriz/A 694 820 01 53/A 696 825 01 54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retirar borracha inferior da cabine devido atrito com reservatório de arrefecimento, evitando danificar o mesmo (OS 7193 · serviço interno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir feixes de molas dianteiros: LE com mais molas devido transporte da lança do munck (OS 7185 · serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retirar espelhos das rodas traseiras, especialmente LE, para melhor visualização do desgaste das lonas de freio (OS 7190 · serviço interno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar regulagem dos freios segundo eixo LD (OS 7205 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor parafuso da bieleta traseira LE (fixação com a barra estabilizadora) (OS 7192 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor acabamento das abraçadeiras do retrovisor LD (OS 7168 · A 000 811 36 07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir janela de inspeção frontal (A 940 888 11 23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor acabamento inferior do braço do retrovisor LD (OS 7168 · A 000 811 04 61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reapertar parafusos de fixação do paralama dianteiro LD (OS 7195 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor borracha de vedação da porta LD (OS 7168 · A 958 721 00 80 (2 unidades))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar acabamento da tomada OBD (OS 7196 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retirar manta inferior da cabine (OS 7197 · serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição das buchas da barra estabilizadora dianteira (OS 7185 · serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir letreiro do modelo Axor "3344" (A 943 817 13 14 (certificar com fornecedor))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperar pisante do estribo LD avariado (serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bater e validar as pendências da inspeção realizada em Mossoró</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspeção Mossoró</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar cabeçote de combustível</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adilton · Alexandre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar o cabeçote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomba de combustível</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Substituir reservatório do líquido de arrefecimento contaminado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adilton · Gabriel · Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema: Estruturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Realizar lavagem e corrigir vazamento na bomba de direção hidráulica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Substituir tirante V traseiro empenado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Corrigir vazamento de ar no freio de estacionamento (maneco)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Repor batedores dianteiros da cabine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar ajuste no velocímetro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPOR PARAFUSO DE FIXAÇÃO DA GRADE DO FAROL LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre · Heliton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXAR CHICOTE ELETRICO SOLTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar troca de pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema: Pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar lavagem e corrigir vazamento na bomba de direção (serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montar adesivos e baixa de carteira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Substituir lanterna do pisca dianteiro LD avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Substituir extensão da porta LE avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Substituir saia lateral da cabine LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Programar recuperação da barra de direção curta com início de folga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar a substituição das juntas do coletor de escapamento (20855371 (6 unidades))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FICAR CHICOTE ELETRICO SOLTO NO BLOCO DE COMANDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXAR GRADE FRONTAL SOLTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir batentes dos eixos traseiros LE e LD gastos (serviço empresa especializada/20390836 (4 unidades))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar regulagem do travamento das portas, motorista relata que as mesmas estão abrindo em movimento (serviço interno Matriz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar recuperação das barras de direção curta e longa (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição da lona de freio terceiro eixo LD avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calibrar e trocar pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBSTITUIR BARRA DE DIREÇÃO PEQUENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar palhetas do climatizador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRIGIR MARCAÇÃO DE NICEL DE COMBUSTIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARLA CONTAMINADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENSOR DE NICEL DE AGUA COM FALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-1064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar e calibrar pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soldar base do paralama dianteiro LD avariada (20453900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor tampa da caixa de fusíveis LD (OS 20352 · 20398773)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir para-sol avariado (82245535)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar válvula de freio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema: Freios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TROCAR PNEUS E FERRAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TROCAR E FERRAR PNEUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRIORIDADE DO KAIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar troca ou calibração dos pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Substituir paralama dianteiro LD avariado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Substituir lente da lanterna traseira LD avariada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Corujinha lateral: Avaria no lado direito (LD).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar faixa refletiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar faixas refletivas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limpeza do climatizador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir acabamento do retrovisor inferior LD (item em aplicação direta ou realizar pedido 21169971)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARCAÇA INTERNA DO FAROL (20453627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir bomba d'água com princípio de vazamento pelo selo lateral (20538820)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Vidros: Revisar a visibilidade dos vidros frontal e laterais.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Grade frontal: Apresenta avaria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Corote: Verificar fixação, pois está batendo no para-lama.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Lameira: Avaria no lado esquerdo (LE).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Para-lama: Parafuso do lado direito (LD) folgado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição lona de freio dianteira LD avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programar substituição da lona de freio dianteiro LE avariada (serviço empresa especializada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alinhar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-1065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar troca de óleo e filtro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir fixação elétrica solta na frente do intercooler (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar limpeza nos bornes das baterias;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reposicionar lanterna corujinha do teto LE e revisar iluminação;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosticar e corrigir falhas: ABS e caixa de marchas (embreagem);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir palhetas do limpador de para-brisas (LD não limpa) 8189631(2 UND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar tubo de escapamento inferior;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar placa dianteira e traseira;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar retrovisor LD e inferior LE;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar extensão da porta e saia lateral LD;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repor quebra-sol do motorista (está dentro da cabine);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir junta da tampa de válvulas com vazamento;20538793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir carcaça do filtro de ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir filtro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar chicote elétrico solto na longarina LD (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixar mangueiras soltas na longarina LE (serviço interno base Mossoró)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar óleo hidráulico da direção;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir lanterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vidro do passageira não aciona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presilha do farol LD e LE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grade do farol LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substituir pneu dianteiro LD com desgaste irregular e verificar demais - instalar indicadores de porca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizar alinhamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alinhar pneus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalar parabrisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terceirizada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferragem de pneus — verificar TAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ VERIFICAR a frota: a mensagem não diz qual · Origem: WhatsApp 02/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frotas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMO USAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acrescente nomes aqui e eles aparecem nas caixinhas da aba Dia a dia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIA A DIA:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  A caixa amarela lá em cima é o DIA. Vem em hoje; troque para ver outro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  Para achar o dia: toque na setinha da coluna Data e filtre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.  Fez? Toque em FEITO e escolha Sim. A linha apaga e o número sobe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.  Abriu a OS no Protheus? Escreva o número em OS PROTHEUS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Enquanto estiver vazia a célula fica laranja — é o que falta lançar lá.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASX (externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARA ACRESCENTAR ATIVIDADE:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Escreva numa linha vazia no fim. Data, frota, atividade, e pronto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eduardo da sticker (externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Sem data ela fica esperando, e entra na conta de “sem data”.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molas Pinheiro (externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não há fórmula nenhuma nas linhas: pode apagar, inserir e arrastar à</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vontade que nada quebra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-871</t>
   </si>
   <si>
     <t xml:space="preserve">MOVIMENTAÇÃO DE FROTAS  ·  o que a operação prometeu e quando entregou</t>
@@ -2808,7 +2802,7 @@
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D4" s="7" t="n">
         <f aca="false">COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;")</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8" t="n">
@@ -2817,11 +2811,11 @@
       </c>
       <c r="G4" s="9" t="n">
         <f aca="false">IF($D$4=0,"",$F$4/$D$4)</f>
-        <v>0.0833333333333333</v>
+        <v>0.0857142857142857</v>
       </c>
       <c r="H4" s="10" t="n">
         <f aca="false">COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;")-COUNTIFS($A$7:$A$706,$B$3,$C$7:$C$706,"&lt;&gt;",$E$7:$E$706,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4499,24 +4493,24 @@
     </row>
     <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B79" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="D79" s="14"/>
+      <c r="E79" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D79" s="14"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="15" t="s">
-        <v>138</v>
-      </c>
+      <c r="F79" s="15"/>
       <c r="G79" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4527,11 +4521,11 @@
         <v>140</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D80" s="14"/>
       <c r="E80" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F80" s="15"/>
       <c r="G80" s="15" t="s">
@@ -4549,11 +4543,11 @@
         <v>140</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D81" s="14"/>
       <c r="E81" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F81" s="15"/>
       <c r="G81" s="15" t="s">
@@ -4571,11 +4565,11 @@
         <v>140</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D82" s="14"/>
       <c r="E82" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F82" s="15"/>
       <c r="G82" s="15" t="s">
@@ -4593,11 +4587,11 @@
         <v>140</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D83" s="14"/>
       <c r="E83" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F83" s="15"/>
       <c r="G83" s="15" t="s">
@@ -4615,11 +4609,11 @@
         <v>140</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D84" s="14"/>
       <c r="E84" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F84" s="15"/>
       <c r="G84" s="15" t="s">
@@ -4630,11 +4624,9 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="13" t="n">
-        <v>46268</v>
-      </c>
+      <c r="A85" s="13"/>
       <c r="B85" s="14" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>197</v>
@@ -4645,196 +4637,196 @@
       </c>
       <c r="F85" s="15"/>
       <c r="G85" s="15" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="13"/>
       <c r="B86" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F86" s="15"/>
       <c r="G86" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="13"/>
       <c r="B87" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D87" s="14"/>
       <c r="E87" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F87" s="15"/>
       <c r="G87" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="13"/>
       <c r="B88" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D88" s="14"/>
       <c r="E88" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F88" s="15"/>
       <c r="G88" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="13"/>
       <c r="B89" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F89" s="15"/>
       <c r="G89" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="13"/>
       <c r="B90" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D90" s="14"/>
       <c r="E90" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F90" s="15"/>
       <c r="G90" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="13"/>
       <c r="B91" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D91" s="14"/>
       <c r="E91" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F91" s="15"/>
       <c r="G91" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="13"/>
       <c r="B92" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F92" s="15"/>
       <c r="G92" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="13"/>
       <c r="B93" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D93" s="14"/>
       <c r="E93" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F93" s="15"/>
       <c r="G93" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H93" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="13"/>
       <c r="B94" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D94" s="14"/>
       <c r="E94" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F94" s="15"/>
       <c r="G94" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="13"/>
       <c r="B95" s="14" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>220</v>
@@ -4845,190 +4837,188 @@
       </c>
       <c r="F95" s="15"/>
       <c r="G95" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H95" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="13"/>
       <c r="B96" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" s="15" t="s">
         <v>222</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>223</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F96" s="15"/>
       <c r="G96" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="13"/>
       <c r="B97" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D97" s="14"/>
       <c r="E97" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" s="15"/>
       <c r="G97" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="13"/>
       <c r="B98" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F98" s="15"/>
       <c r="G98" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H98" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="13"/>
       <c r="B99" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D99" s="14"/>
       <c r="E99" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F99" s="15"/>
       <c r="G99" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H99" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="13"/>
       <c r="B100" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D100" s="14"/>
       <c r="E100" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F100" s="15"/>
       <c r="G100" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="13"/>
       <c r="B101" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D101" s="14"/>
       <c r="E101" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F101" s="15"/>
       <c r="G101" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H101" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="13"/>
       <c r="B102" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F102" s="15"/>
       <c r="G102" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="13"/>
       <c r="B103" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D103" s="14"/>
       <c r="E103" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F103" s="15"/>
       <c r="G103" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H103" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="13"/>
       <c r="B104" s="14" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D104" s="14"/>
-      <c r="E104" s="16" t="s">
-        <v>240</v>
-      </c>
+      <c r="E104" s="16"/>
       <c r="F104" s="15"/>
       <c r="G104" s="15" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5037,7 +5027,7 @@
         <v>15</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D105" s="14"/>
       <c r="E105" s="16"/>
@@ -5046,31 +5036,31 @@
         <v>19</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="13"/>
       <c r="B106" s="14" t="s">
-        <v>15</v>
+        <v>241</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D106" s="14"/>
       <c r="E106" s="16"/>
       <c r="F106" s="15"/>
       <c r="G106" s="15" t="s">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="13"/>
       <c r="B107" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>245</v>
@@ -5079,631 +5069,631 @@
       <c r="E107" s="16"/>
       <c r="F107" s="15"/>
       <c r="G107" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H107" s="15" t="s">
         <v>246</v>
-      </c>
-      <c r="H107" s="15" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="13"/>
       <c r="B108" s="14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="16"/>
       <c r="F108" s="15"/>
       <c r="G108" s="15" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="13"/>
       <c r="B109" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="16"/>
       <c r="F109" s="15"/>
       <c r="G109" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="13"/>
       <c r="B110" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D110" s="14"/>
       <c r="E110" s="16"/>
       <c r="F110" s="15"/>
       <c r="G110" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
       <c r="B111" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D111" s="14"/>
       <c r="E111" s="16"/>
       <c r="F111" s="15"/>
       <c r="G111" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H111" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="13"/>
       <c r="B112" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D112" s="14"/>
+      <c r="E112" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="C112" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="D112" s="14"/>
-      <c r="E112" s="16"/>
       <c r="F112" s="15"/>
       <c r="G112" s="15" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="13"/>
       <c r="B113" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C113" s="15" t="s">
         <v>254</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>255</v>
       </c>
       <c r="D113" s="14"/>
       <c r="E113" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F113" s="15"/>
       <c r="G113" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H113" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="13"/>
       <c r="B114" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D114" s="14"/>
       <c r="E114" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F114" s="15"/>
       <c r="G114" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="13"/>
       <c r="B115" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D115" s="14"/>
       <c r="E115" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F115" s="15"/>
       <c r="G115" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="13"/>
       <c r="B116" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D116" s="14"/>
       <c r="E116" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F116" s="15"/>
       <c r="G116" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="13"/>
       <c r="B117" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D117" s="14"/>
       <c r="E117" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F117" s="15"/>
       <c r="G117" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="13"/>
       <c r="B118" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D118" s="14"/>
       <c r="E118" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F118" s="15"/>
       <c r="G118" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="13"/>
       <c r="B119" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D119" s="14"/>
       <c r="E119" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F119" s="15"/>
       <c r="G119" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="13"/>
       <c r="B120" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D120" s="14"/>
       <c r="E120" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F120" s="15"/>
       <c r="G120" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="13"/>
       <c r="B121" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D121" s="14"/>
       <c r="E121" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F121" s="15"/>
       <c r="G121" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H121" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="13"/>
       <c r="B122" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F122" s="15"/>
       <c r="G122" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="13"/>
       <c r="B123" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D123" s="14"/>
       <c r="E123" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F123" s="15"/>
       <c r="G123" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="13"/>
       <c r="B124" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F124" s="15"/>
       <c r="G124" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="13"/>
       <c r="B125" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D125" s="14"/>
       <c r="E125" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F125" s="15"/>
       <c r="G125" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H125" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="13"/>
       <c r="B126" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D126" s="14"/>
       <c r="E126" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F126" s="15"/>
       <c r="G126" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="13"/>
       <c r="B127" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D127" s="14"/>
       <c r="E127" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F127" s="15"/>
       <c r="G127" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H127" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="13"/>
       <c r="B128" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D128" s="14"/>
       <c r="E128" s="16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F128" s="15"/>
       <c r="G128" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="13"/>
       <c r="B129" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D129" s="14"/>
       <c r="E129" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F129" s="15"/>
       <c r="G129" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H129" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="13"/>
       <c r="B130" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D130" s="14"/>
       <c r="E130" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F130" s="15"/>
       <c r="G130" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H130" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="13"/>
       <c r="B131" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D131" s="14"/>
       <c r="E131" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F131" s="15"/>
       <c r="G131" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="13"/>
       <c r="B132" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D132" s="14"/>
       <c r="E132" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F132" s="15"/>
       <c r="G132" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="13"/>
       <c r="B133" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D133" s="14"/>
       <c r="E133" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F133" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="F133" s="15"/>
       <c r="G133" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H133" s="15" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="13"/>
       <c r="B134" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D134" s="14"/>
       <c r="E134" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="13"/>
       <c r="B135" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D135" s="14"/>
       <c r="E135" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G135" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H135" s="15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="13"/>
       <c r="B136" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D136" s="14"/>
       <c r="E136" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="13"/>
       <c r="B137" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D137" s="14"/>
       <c r="E137" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H137" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="13"/>
       <c r="B138" s="14" t="s">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>304</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="F138" s="15" t="s">
         <v>305</v>
       </c>
+      <c r="F138" s="15"/>
       <c r="G138" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="H138" s="15" t="s">
-        <v>306</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="H138" s="15"/>
     </row>
     <row r="139" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="13"/>
@@ -5711,15 +5701,15 @@
         <v>105</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D139" s="14"/>
       <c r="E139" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F139" s="15"/>
       <c r="G139" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H139" s="15"/>
     </row>
@@ -5729,15 +5719,15 @@
         <v>105</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F140" s="15"/>
       <c r="G140" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H140" s="15"/>
     </row>
@@ -5747,593 +5737,599 @@
         <v>105</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D141" s="14"/>
       <c r="E141" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F141" s="15"/>
       <c r="G141" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H141" s="15"/>
     </row>
     <row r="142" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="13"/>
       <c r="B142" s="14" t="s">
-        <v>105</v>
+        <v>312</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>313</v>
       </c>
       <c r="D142" s="14"/>
-      <c r="E142" s="16" t="s">
-        <v>314</v>
-      </c>
+      <c r="E142" s="16"/>
       <c r="F142" s="15"/>
       <c r="G142" s="15" t="s">
-        <v>202</v>
+        <v>314</v>
       </c>
       <c r="H142" s="15"/>
     </row>
     <row r="143" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="13"/>
       <c r="B143" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C143" s="15" t="s">
         <v>315</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>316</v>
       </c>
       <c r="D143" s="14"/>
       <c r="E143" s="16"/>
       <c r="F143" s="15"/>
       <c r="G143" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H143" s="15"/>
     </row>
     <row r="144" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="13"/>
       <c r="B144" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D144" s="14"/>
       <c r="E144" s="16"/>
       <c r="F144" s="15"/>
       <c r="G144" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H144" s="15"/>
     </row>
     <row r="145" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="13"/>
       <c r="B145" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D145" s="14"/>
       <c r="E145" s="16"/>
       <c r="F145" s="15"/>
       <c r="G145" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H145" s="15"/>
     </row>
     <row r="146" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="13"/>
       <c r="B146" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D146" s="14"/>
       <c r="E146" s="16"/>
       <c r="F146" s="15"/>
       <c r="G146" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="13"/>
       <c r="B147" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D147" s="14"/>
       <c r="E147" s="16"/>
       <c r="F147" s="15"/>
       <c r="G147" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H147" s="15"/>
     </row>
     <row r="148" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="13"/>
       <c r="B148" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D148" s="14"/>
       <c r="E148" s="16"/>
       <c r="F148" s="15"/>
       <c r="G148" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H148" s="15"/>
     </row>
     <row r="149" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="13"/>
       <c r="B149" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D149" s="14"/>
       <c r="E149" s="16"/>
       <c r="F149" s="15"/>
       <c r="G149" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H149" s="15"/>
     </row>
     <row r="150" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="13"/>
       <c r="B150" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D150" s="14"/>
       <c r="E150" s="16"/>
       <c r="F150" s="15"/>
       <c r="G150" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H150" s="15"/>
     </row>
     <row r="151" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="13"/>
       <c r="B151" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D151" s="14"/>
       <c r="E151" s="16"/>
       <c r="F151" s="15"/>
       <c r="G151" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H151" s="15"/>
     </row>
     <row r="152" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="13"/>
       <c r="B152" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D152" s="14"/>
       <c r="E152" s="16"/>
       <c r="F152" s="15"/>
       <c r="G152" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="13"/>
       <c r="B153" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D153" s="14"/>
       <c r="E153" s="16"/>
       <c r="F153" s="15"/>
       <c r="G153" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="13"/>
       <c r="B154" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D154" s="14"/>
       <c r="E154" s="16"/>
       <c r="F154" s="15"/>
       <c r="G154" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="13"/>
       <c r="B155" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D155" s="14"/>
       <c r="E155" s="16"/>
       <c r="F155" s="15"/>
       <c r="G155" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="13"/>
       <c r="B156" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="16"/>
       <c r="F156" s="15"/>
       <c r="G156" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="13"/>
       <c r="B157" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D157" s="14"/>
       <c r="E157" s="16"/>
       <c r="F157" s="15"/>
       <c r="G157" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="13"/>
       <c r="B158" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D158" s="14"/>
       <c r="E158" s="16"/>
       <c r="F158" s="15"/>
       <c r="G158" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="13"/>
       <c r="B159" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D159" s="14"/>
       <c r="E159" s="16"/>
       <c r="F159" s="15"/>
       <c r="G159" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H159" s="15"/>
     </row>
     <row r="160" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="13"/>
       <c r="B160" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D160" s="14"/>
       <c r="E160" s="16"/>
       <c r="F160" s="15"/>
       <c r="G160" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H160" s="15"/>
     </row>
     <row r="161" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="13"/>
       <c r="B161" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D161" s="14"/>
       <c r="E161" s="16"/>
       <c r="F161" s="15"/>
       <c r="G161" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H161" s="15"/>
     </row>
     <row r="162" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="13"/>
       <c r="B162" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D162" s="14"/>
       <c r="E162" s="16"/>
       <c r="F162" s="15"/>
       <c r="G162" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H162" s="15"/>
     </row>
     <row r="163" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="13"/>
       <c r="B163" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D163" s="14"/>
       <c r="E163" s="16"/>
       <c r="F163" s="15"/>
       <c r="G163" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H163" s="15"/>
     </row>
     <row r="164" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="13"/>
       <c r="B164" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D164" s="14"/>
       <c r="E164" s="16"/>
       <c r="F164" s="15"/>
       <c r="G164" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H164" s="15"/>
     </row>
     <row r="165" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="13"/>
       <c r="B165" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D165" s="14"/>
       <c r="E165" s="16"/>
       <c r="F165" s="15"/>
       <c r="G165" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H165" s="15"/>
     </row>
     <row r="166" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="13"/>
       <c r="B166" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D166" s="14"/>
       <c r="E166" s="16"/>
       <c r="F166" s="15"/>
       <c r="G166" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H166" s="15"/>
     </row>
     <row r="167" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="13"/>
       <c r="B167" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D167" s="14"/>
       <c r="E167" s="16"/>
       <c r="F167" s="15"/>
       <c r="G167" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H167" s="15"/>
     </row>
     <row r="168" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="13"/>
       <c r="B168" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D168" s="14"/>
       <c r="E168" s="16"/>
       <c r="F168" s="15"/>
       <c r="G168" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H168" s="15"/>
     </row>
     <row r="169" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="13"/>
       <c r="B169" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D169" s="14"/>
       <c r="E169" s="16"/>
       <c r="F169" s="15"/>
       <c r="G169" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H169" s="15"/>
     </row>
     <row r="170" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="13"/>
       <c r="B170" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D170" s="14"/>
       <c r="E170" s="16"/>
       <c r="F170" s="15"/>
       <c r="G170" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H170" s="15"/>
     </row>
     <row r="171" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="13"/>
       <c r="B171" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D171" s="14"/>
       <c r="E171" s="16"/>
       <c r="F171" s="15"/>
       <c r="G171" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H171" s="15"/>
     </row>
     <row r="172" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="13"/>
       <c r="B172" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D172" s="14"/>
       <c r="E172" s="16"/>
       <c r="F172" s="15"/>
       <c r="G172" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H172" s="15"/>
     </row>
     <row r="173" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="13"/>
       <c r="B173" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D173" s="14"/>
       <c r="E173" s="16"/>
       <c r="F173" s="15"/>
       <c r="G173" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H173" s="15"/>
     </row>
     <row r="174" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="13"/>
       <c r="B174" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D174" s="14"/>
       <c r="E174" s="16"/>
       <c r="F174" s="15"/>
       <c r="G174" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H174" s="15"/>
     </row>
     <row r="175" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="13"/>
       <c r="B175" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D175" s="14"/>
       <c r="E175" s="16"/>
       <c r="F175" s="15"/>
       <c r="G175" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H175" s="15"/>
     </row>
     <row r="176" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="13"/>
       <c r="B176" s="14" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D176" s="14"/>
       <c r="E176" s="16"/>
       <c r="F176" s="15"/>
       <c r="G176" s="15" t="s">
-        <v>317</v>
+        <v>350</v>
       </c>
       <c r="H176" s="15"/>
     </row>
     <row r="177" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="13"/>
+      <c r="A177" s="13" t="n">
+        <v>46258</v>
+      </c>
       <c r="B177" s="14" t="s">
         <v>351</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="D177" s="14"/>
-      <c r="E177" s="16"/>
-      <c r="F177" s="15"/>
+      <c r="D177" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E177" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F177" s="15" t="s">
+        <v>355</v>
+      </c>
       <c r="G177" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H177" s="15"/>
     </row>
@@ -6342,48 +6338,50 @@
         <v>46258</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C178" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="D178" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E178" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="F178" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="D178" s="14" t="s">
+      <c r="G178" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="E178" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="F178" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="G178" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="H178" s="15"/>
     </row>
     <row r="179" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="13" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="C179" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="D179" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E179" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="D179" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E179" s="16" t="s">
+      <c r="F179" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="F179" s="15" t="s">
-        <v>358</v>
-      </c>
       <c r="G179" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="H179" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="H179" s="15" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="13" t="n">
@@ -6393,22 +6391,22 @@
         <v>79</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G180" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6419,22 +6417,20 @@
         <v>79</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E181" s="16" t="s">
-        <v>367</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E181" s="16"/>
       <c r="F181" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G181" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H181" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6445,20 +6441,20 @@
         <v>79</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E182" s="16"/>
       <c r="F182" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G182" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H182" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6469,20 +6465,20 @@
         <v>79</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E183" s="16"/>
       <c r="F183" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G183" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H183" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6490,65 +6486,65 @@
         <v>46259</v>
       </c>
       <c r="B184" s="14" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D184" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E184" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="F184" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G184" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="E184" s="16"/>
-      <c r="F184" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="G184" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H184" s="15" t="s">
-        <v>365</v>
-      </c>
+      <c r="H184" s="15"/>
     </row>
     <row r="185" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="13" t="n">
         <v>46259</v>
       </c>
       <c r="B185" s="14" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="C185" s="15" t="s">
         <v>371</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E185" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E185" s="16"/>
+      <c r="F185" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="F185" s="15" t="s">
-        <v>358</v>
-      </c>
       <c r="G185" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="H185" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="H185" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="13" t="n">
         <v>46259</v>
       </c>
       <c r="B186" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="C186" s="15" t="s">
-        <v>374</v>
-      </c>
       <c r="D186" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E186" s="16"/>
       <c r="F186" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G186" s="15" t="s">
         <v>143</v>
@@ -6559,26 +6555,28 @@
     </row>
     <row r="187" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="13" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C187" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="D187" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E187" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="D187" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E187" s="16"/>
       <c r="F187" s="15" t="s">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="G187" s="15" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="H187" s="15" t="s">
-        <v>25</v>
+        <v>377</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6586,50 +6584,48 @@
         <v>46260</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>377</v>
+        <v>15</v>
       </c>
       <c r="C188" s="15" t="s">
         <v>378</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E188" s="16" t="s">
         <v>379</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H188" s="15" t="s">
         <v>380</v>
       </c>
+      <c r="H188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C189" s="15" t="s">
         <v>381</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E189" s="16" t="s">
-        <v>382</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E189" s="16"/>
       <c r="F189" s="15" t="s">
-        <v>71</v>
+        <v>361</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="H189" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="H189" s="15" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="13" t="n">
@@ -6639,20 +6635,20 @@
         <v>79</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E190" s="16"/>
       <c r="F190" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G190" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6663,20 +6659,20 @@
         <v>79</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E191" s="16"/>
       <c r="F191" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H191" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6687,20 +6683,20 @@
         <v>79</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D192" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E192" s="16"/>
       <c r="F192" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G192" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H192" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6711,20 +6707,20 @@
         <v>79</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E193" s="16"/>
       <c r="F193" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G193" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H193" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6732,65 +6728,65 @@
         <v>46260</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D194" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E194" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="F194" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G194" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="E194" s="16"/>
-      <c r="F194" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="G194" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H194" s="15" t="s">
-        <v>365</v>
-      </c>
+      <c r="H194" s="15"/>
     </row>
     <row r="195" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B195" s="14" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E195" s="16" t="s">
-        <v>390</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E195" s="16"/>
       <c r="F195" s="15" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="G195" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="H195" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="H195" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="13" t="n">
         <v>46260</v>
       </c>
       <c r="B196" s="14" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E196" s="16"/>
       <c r="F196" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G196" s="15" t="s">
         <v>143</v>
@@ -6801,26 +6797,28 @@
     </row>
     <row r="197" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="13" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B197" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E197" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E197" s="16" t="s">
+        <v>376</v>
+      </c>
       <c r="F197" s="15" t="s">
-        <v>375</v>
+        <v>71</v>
       </c>
       <c r="G197" s="15" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="H197" s="15" t="s">
-        <v>25</v>
+        <v>377</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6828,13 +6826,13 @@
         <v>46261</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>377</v>
+        <v>15</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E198" s="16" t="s">
         <v>379</v>
@@ -6843,33 +6841,31 @@
         <v>71</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H198" s="15" t="s">
         <v>380</v>
       </c>
+      <c r="H198" s="15"/>
     </row>
     <row r="199" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B199" s="14" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D199" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E199" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="F199" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G199" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="E199" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="F199" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G199" s="15" t="s">
-        <v>383</v>
       </c>
       <c r="H199" s="15"/>
     </row>
@@ -6878,22 +6874,22 @@
         <v>46261</v>
       </c>
       <c r="B200" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C200" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="D200" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E200" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="D200" s="14" t="s">
+      <c r="F200" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G200" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="E200" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="F200" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="G200" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="H200" s="15"/>
     </row>
@@ -6902,22 +6898,20 @@
         <v>46261</v>
       </c>
       <c r="B201" s="14" t="s">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="C201" s="15" t="s">
         <v>397</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E201" s="16" t="s">
-        <v>398</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E201" s="16"/>
       <c r="F201" s="15" t="s">
-        <v>358</v>
+        <v>183</v>
       </c>
       <c r="G201" s="15" t="s">
-        <v>359</v>
+        <v>176</v>
       </c>
       <c r="H201" s="15"/>
     </row>
@@ -6926,20 +6920,22 @@
         <v>46261</v>
       </c>
       <c r="B202" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C202" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="D202" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E202" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="C202" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="D202" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E202" s="16"/>
       <c r="F202" s="15" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="H202" s="15"/>
     </row>
@@ -6951,19 +6947,19 @@
         <v>105</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="F203" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G203" s="15" t="s">
-        <v>202</v>
+        <v>400</v>
       </c>
       <c r="H203" s="15"/>
     </row>
@@ -6972,41 +6968,41 @@
         <v>46261</v>
       </c>
       <c r="B204" s="14" t="s">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D204" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E204" s="16" t="s">
-        <v>308</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E204" s="16"/>
       <c r="F204" s="15" t="s">
-        <v>71</v>
+        <v>372</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="H204" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="H204" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="13" t="n">
         <v>46261</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E205" s="16"/>
       <c r="F205" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G205" s="15" t="s">
         <v>143</v>
@@ -7020,17 +7016,17 @@
         <v>46261</v>
       </c>
       <c r="B206" s="14" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E206" s="16"/>
       <c r="F206" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G206" s="15" t="s">
         <v>143</v>
@@ -7041,62 +7037,64 @@
     </row>
     <row r="207" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B207" s="14" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E207" s="16"/>
       <c r="F207" s="15" t="s">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="G207" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H207" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="H207" s="15"/>
     </row>
     <row r="208" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B208" s="14" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E208" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E208" s="16" t="s">
+        <v>376</v>
+      </c>
       <c r="F208" s="15" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="G208" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="H208" s="15"/>
+      <c r="H208" s="15" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B209" s="14" t="s">
-        <v>377</v>
+        <v>15</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E209" s="16" t="s">
         <v>379</v>
@@ -7105,11 +7103,9 @@
         <v>71</v>
       </c>
       <c r="G209" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H209" s="15" t="s">
         <v>380</v>
       </c>
+      <c r="H209" s="15"/>
     </row>
     <row r="210" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="13" t="n">
@@ -7119,19 +7115,19 @@
         <v>15</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="F210" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H210" s="15"/>
     </row>
@@ -7140,47 +7136,47 @@
         <v>46262</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>15</v>
+        <v>410</v>
       </c>
       <c r="C211" s="15" t="s">
         <v>411</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E211" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E211" s="16"/>
+      <c r="F211" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="F211" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="G211" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="H211" s="15"/>
+        <v>411</v>
+      </c>
+      <c r="H211" s="15" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B212" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E212" s="16"/>
       <c r="F212" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H212" s="15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7188,23 +7184,23 @@
         <v>46262</v>
       </c>
       <c r="B213" s="14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D213" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E213" s="16"/>
       <c r="F213" s="15" t="s">
-        <v>415</v>
+        <v>183</v>
       </c>
       <c r="G213" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H213" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7212,48 +7208,48 @@
         <v>46262</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>418</v>
+        <v>68</v>
       </c>
       <c r="C214" s="15" t="s">
         <v>419</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E214" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E214" s="16" t="s">
+        <v>420</v>
+      </c>
       <c r="F214" s="15" t="s">
         <v>183</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="H214" s="15" t="s">
-        <v>421</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="H214" s="15"/>
     </row>
     <row r="215" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B215" s="14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D215" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E215" s="16" t="s">
-        <v>423</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E215" s="16"/>
       <c r="F215" s="15" t="s">
-        <v>183</v>
+        <v>361</v>
       </c>
       <c r="G215" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H215" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="H215" s="15" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="216" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="13" t="n">
@@ -7263,20 +7259,20 @@
         <v>79</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D216" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E216" s="16"/>
       <c r="F216" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G216" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7287,20 +7283,20 @@
         <v>79</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E217" s="16"/>
       <c r="F217" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G217" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H217" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7311,20 +7307,20 @@
         <v>79</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E218" s="16"/>
       <c r="F218" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G218" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H218" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7335,20 +7331,20 @@
         <v>79</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E219" s="16"/>
       <c r="F219" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G219" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H219" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7356,84 +7352,86 @@
         <v>46262</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E220" s="16"/>
       <c r="F220" s="15" t="s">
-        <v>364</v>
+        <v>71</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H220" s="15" t="s">
-        <v>365</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="H220" s="15"/>
     </row>
     <row r="221" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="B221" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C221" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="C221" s="15" t="s">
-        <v>430</v>
-      </c>
       <c r="D221" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E221" s="16"/>
       <c r="F221" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G221" s="15" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="H221" s="15"/>
     </row>
     <row r="222" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="13" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>105</v>
+        <v>374</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E222" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E222" s="16" t="s">
+        <v>376</v>
+      </c>
       <c r="F222" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="H222" s="15"/>
+        <v>176</v>
+      </c>
+      <c r="H222" s="15" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="223" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E223" s="16" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F223" s="15" t="s">
         <v>71</v>
@@ -7442,7 +7440,7 @@
         <v>176</v>
       </c>
       <c r="H223" s="15" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7450,25 +7448,25 @@
         <v>46263</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>377</v>
+        <v>26</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E224" s="16" t="s">
-        <v>379</v>
+        <v>28</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="H224" s="15" t="s">
-        <v>380</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7476,25 +7474,23 @@
         <v>46263</v>
       </c>
       <c r="B225" s="14" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D225" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E225" s="16" t="s">
-        <v>28</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E225" s="16"/>
       <c r="F225" s="15" t="s">
-        <v>18</v>
+        <v>361</v>
       </c>
       <c r="G225" s="15" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H225" s="15" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7505,20 +7501,20 @@
         <v>79</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D226" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E226" s="16"/>
       <c r="F226" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G226" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H226" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7529,20 +7525,20 @@
         <v>79</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E227" s="16"/>
       <c r="F227" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G227" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H227" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7553,20 +7549,20 @@
         <v>79</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E228" s="16"/>
       <c r="F228" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G228" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H228" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7577,20 +7573,20 @@
         <v>79</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E229" s="16"/>
       <c r="F229" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G229" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H229" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7598,46 +7594,46 @@
         <v>46263</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D230" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E230" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G230" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="E230" s="16"/>
-      <c r="F230" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="G230" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H230" s="15" t="s">
-        <v>365</v>
-      </c>
+      <c r="H230" s="15"/>
     </row>
     <row r="231" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D231" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E231" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G231" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="E231" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="F231" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="G231" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="H231" s="15"/>
     </row>
@@ -7646,68 +7642,70 @@
         <v>46263</v>
       </c>
       <c r="B232" s="14" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="C232" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E232" s="16" t="s">
-        <v>398</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E232" s="16"/>
       <c r="F232" s="15" t="s">
-        <v>358</v>
+        <v>71</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="H232" s="15"/>
     </row>
     <row r="233" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="13" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B233" s="14" t="s">
-        <v>105</v>
+        <v>441</v>
       </c>
       <c r="C233" s="15" t="s">
-        <v>443</v>
+        <v>405</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E233" s="16"/>
       <c r="F233" s="15" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="G233" s="15" t="s">
-        <v>403</v>
+        <v>176</v>
       </c>
       <c r="H233" s="15"/>
     </row>
     <row r="234" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="13" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B234" s="14" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E234" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E234" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="F234" s="15" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H234" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H234" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="13" t="n">
@@ -7717,10 +7715,10 @@
         <v>26</v>
       </c>
       <c r="C235" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E235" s="16" t="s">
         <v>28</v>
@@ -7740,26 +7738,24 @@
         <v>46265</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C236" s="15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E236" s="16" t="s">
-        <v>28</v>
+        <v>445</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H236" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="H236" s="15"/>
     </row>
     <row r="237" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="13" t="n">
@@ -7769,13 +7765,13 @@
         <v>68</v>
       </c>
       <c r="C237" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E237" s="16" t="s">
         <v>447</v>
-      </c>
-      <c r="D237" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E237" s="16" t="s">
-        <v>448</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>53</v>
@@ -7793,13 +7789,13 @@
         <v>68</v>
       </c>
       <c r="C238" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E238" s="16" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F238" s="15" t="s">
         <v>53</v>
@@ -7817,10 +7813,10 @@
         <v>68</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E239" s="16" t="s">
         <v>450</v>
@@ -7841,16 +7837,16 @@
         <v>68</v>
       </c>
       <c r="C240" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="D240" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E240" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="D240" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E240" s="16" t="s">
-        <v>453</v>
-      </c>
       <c r="F240" s="15" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G240" s="15" t="s">
         <v>72</v>
@@ -7865,13 +7861,13 @@
         <v>68</v>
       </c>
       <c r="C241" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="D241" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E241" s="16" t="s">
         <v>454</v>
-      </c>
-      <c r="D241" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E241" s="16" t="s">
-        <v>455</v>
       </c>
       <c r="F241" s="15" t="s">
         <v>71</v>
@@ -7889,13 +7885,13 @@
         <v>68</v>
       </c>
       <c r="C242" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="D242" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E242" s="16" t="s">
         <v>456</v>
-      </c>
-      <c r="D242" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E242" s="16" t="s">
-        <v>457</v>
       </c>
       <c r="F242" s="15" t="s">
         <v>71</v>
@@ -7913,13 +7909,13 @@
         <v>68</v>
       </c>
       <c r="C243" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D243" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E243" s="16" t="s">
         <v>458</v>
-      </c>
-      <c r="D243" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E243" s="16" t="s">
-        <v>459</v>
       </c>
       <c r="F243" s="15" t="s">
         <v>71</v>
@@ -7937,13 +7933,13 @@
         <v>68</v>
       </c>
       <c r="C244" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D244" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E244" s="16" t="s">
         <v>460</v>
-      </c>
-      <c r="D244" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E244" s="16" t="s">
-        <v>461</v>
       </c>
       <c r="F244" s="15" t="s">
         <v>71</v>
@@ -7961,13 +7957,13 @@
         <v>68</v>
       </c>
       <c r="C245" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="D245" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E245" s="16" t="s">
         <v>462</v>
-      </c>
-      <c r="D245" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E245" s="16" t="s">
-        <v>463</v>
       </c>
       <c r="F245" s="15" t="s">
         <v>71</v>
@@ -7985,13 +7981,13 @@
         <v>68</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E246" s="16" t="s">
-        <v>465</v>
+        <v>70</v>
       </c>
       <c r="F246" s="15" t="s">
         <v>71</v>
@@ -8006,48 +8002,50 @@
         <v>46265</v>
       </c>
       <c r="B247" s="14" t="s">
-        <v>68</v>
+        <v>464</v>
       </c>
       <c r="C247" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="D247" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E247" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="D247" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E247" s="16" t="s">
-        <v>70</v>
-      </c>
       <c r="F247" s="15" t="s">
-        <v>71</v>
+        <v>467</v>
       </c>
       <c r="G247" s="15" t="s">
-        <v>72</v>
+        <v>468</v>
       </c>
       <c r="H247" s="15"/>
     </row>
     <row r="248" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="13" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>467</v>
+        <v>26</v>
       </c>
       <c r="C248" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E248" s="16" t="s">
-        <v>469</v>
+        <v>28</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>470</v>
+        <v>18</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="H248" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="H248" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="249" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="13" t="n">
@@ -8057,10 +8055,10 @@
         <v>26</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E249" s="16" t="s">
         <v>28</v>
@@ -8080,26 +8078,24 @@
         <v>46266</v>
       </c>
       <c r="B250" s="14" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C250" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E250" s="16" t="s">
-        <v>28</v>
+        <v>472</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G250" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H250" s="15" t="s">
-        <v>33</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="H250" s="15"/>
     </row>
     <row r="251" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="13" t="n">
@@ -8109,13 +8105,13 @@
         <v>68</v>
       </c>
       <c r="C251" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="D251" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E251" s="16" t="s">
         <v>474</v>
-      </c>
-      <c r="D251" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E251" s="16" t="s">
-        <v>475</v>
       </c>
       <c r="F251" s="15" t="s">
         <v>71</v>
@@ -8133,16 +8129,16 @@
         <v>68</v>
       </c>
       <c r="C252" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="D252" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E252" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="D252" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E252" s="16" t="s">
-        <v>477</v>
-      </c>
       <c r="F252" s="15" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G252" s="15" t="s">
         <v>72</v>
@@ -8157,13 +8153,13 @@
         <v>68</v>
       </c>
       <c r="C253" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="D253" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E253" s="16" t="s">
         <v>478</v>
-      </c>
-      <c r="D253" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E253" s="16" t="s">
-        <v>479</v>
       </c>
       <c r="F253" s="15" t="s">
         <v>53</v>
@@ -8181,13 +8177,13 @@
         <v>68</v>
       </c>
       <c r="C254" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E254" s="16" t="s">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="F254" s="15" t="s">
         <v>53</v>
@@ -8205,10 +8201,10 @@
         <v>68</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E255" s="16" t="s">
         <v>77</v>
@@ -8229,16 +8225,16 @@
         <v>68</v>
       </c>
       <c r="C256" s="15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D256" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E256" s="16" t="s">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="G256" s="15" t="s">
         <v>72</v>
@@ -8247,27 +8243,27 @@
     </row>
     <row r="257" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="13" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B257" s="14" t="s">
-        <v>68</v>
+        <v>441</v>
       </c>
       <c r="C257" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D257" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E257" s="16" t="s">
-        <v>423</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E257" s="16"/>
       <c r="F257" s="15" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="G257" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H257" s="15"/>
+        <v>139</v>
+      </c>
+      <c r="H257" s="15" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="258" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="13" t="n">
@@ -8277,19 +8273,19 @@
         <v>26</v>
       </c>
       <c r="C258" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="D258" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E258" s="16" t="s">
         <v>485</v>
-      </c>
-      <c r="D258" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E258" s="16" t="s">
-        <v>486</v>
       </c>
       <c r="F258" s="15" t="s">
         <v>183</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H258" s="15"/>
     </row>
@@ -8301,16 +8297,16 @@
         <v>34</v>
       </c>
       <c r="C259" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="D259" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E259" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="D259" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E259" s="16" t="s">
+      <c r="F259" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="F259" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="G259" s="15" t="s">
         <v>143</v>
@@ -8318,28 +8314,14 @@
       <c r="H259" s="15"/>
     </row>
     <row r="260" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="13" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B260" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C260" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="D260" s="14" t="s">
-        <v>356</v>
-      </c>
+      <c r="A260" s="13"/>
+      <c r="B260" s="14"/>
+      <c r="C260" s="15"/>
+      <c r="D260" s="14"/>
       <c r="E260" s="16"/>
-      <c r="F260" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G260" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H260" s="15" t="s">
-        <v>492</v>
-      </c>
+      <c r="F260" s="15"/>
+      <c r="G260" s="15"/>
+      <c r="H260" s="15"/>
     </row>
     <row r="261" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="13"/>
@@ -12874,88 +12856,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>90</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12963,15 +12945,15 @@
         <v>15</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>134</v>
@@ -12983,10 +12965,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12994,55 +12976,55 @@
         <v>125</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B16" s="19"/>
       <c r="D16" s="20" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B17" s="19"/>
     </row>
@@ -13054,13 +13036,13 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B20" s="19"/>
     </row>
@@ -13078,7 +13060,7 @@
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B23" s="19"/>
     </row>
@@ -13090,37 +13072,37 @@
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B30" s="19"/>
     </row>
@@ -13138,13 +13120,13 @@
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B34" s="19"/>
     </row>
@@ -13156,13 +13138,13 @@
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B37" s="19"/>
     </row>
@@ -13174,25 +13156,25 @@
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>184</v>
+        <v>516</v>
       </c>
       <c r="B42" s="19"/>
     </row>
@@ -13387,7 +13369,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13398,7 +13380,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="K1" s="22" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="L1" s="23" t="n">
         <f aca="true">TODAY()</f>
@@ -13407,7 +13389,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13420,25 +13402,25 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>523</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>525</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13472,7 +13454,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
@@ -13488,28 +13470,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="H8" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="I8" s="12" t="s">
         <v>534</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13517,7 +13499,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>46267</v>
@@ -13535,7 +13517,7 @@
         <v>Aguardando</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I9" s="15"/>
     </row>

--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -10,15 +10,11 @@
   <sheets>
     <sheet name="Dia a dia" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Listas" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Movimentações" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Dia a dia'!$A$1:$H$264</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Dia a dia'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Dia a dia'!$A$6:$H$706</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Movimentações!$A$1:$I$37</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Movimentações!$8:$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Movimentações!$A$8:$I$308</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -150,150 +146,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">tudo que foi pedido à operação</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">já chegaram</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">O dia em que você pediu a movimentação à operação.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">chegaram até a data prometida</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">A data que a operação SE COMPROMETEU a entregar. É contra ela que o atraso é medido — sem essa data não há o que cobrar.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">no prazo ÷ entregues. É este o número para levar à reunião</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">O dia em que a frota chegou de verdade. Enquanto estiver vazio, a movimentação está em aberto.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sai sozinho: chegou menos prometida, em dias. Chegar antes conta zero.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">dias, contando só as que atrasaram</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">a soma de todos os atrasos: o tamanho do prejuízo em dias de oficina</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Quem, na operação, deu a data. Sem nome, a cobrança vira conversa.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="530">
   <si>
     <t xml:space="preserve">PROGRAMAÇÃO DIÁRIA  ·  MAKRO TRANSPORTES</t>
   </si>
@@ -1883,78 +1737,20 @@
   </si>
   <si>
     <t xml:space="preserve">Não informada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOVIMENTAÇÃO DE FROTAS  ·  o que a operação prometeu e quando entregou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peça a movimentação, anote a data que a operação prometeu, e marque quando a frota chegou. O atraso e os números saem sozinhos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOVIMENTAÇÕES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENTREGUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO PRAZO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONTUALIDADE DA OPERAÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATRASO MÉDIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAS PERDIDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atraso = quando chegou menos quando foi prometida. Chegar antes conta como zero, não como crédito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destino / fornecedor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedida em</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometida para</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chegou em</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atraso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para quê</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem prometeu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ informar o fornecedor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ informar para que serviço</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$-416]dd/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0%"/>
     <numFmt numFmtId="168" formatCode="@"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2153,22 +1949,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FFB00020"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF4A5464"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -2186,25 +1966,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CF"/>
-        <bgColor rgb="FFFFE9CC"/>
+        <bgColor rgb="FFFDE4E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF1F7"/>
-        <bgColor rgb="FFEDF2FC"/>
+        <bgColor rgb="FFEFF9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A3170"/>
-        <bgColor rgb="FF2C4272"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC97A"/>
-        <bgColor rgb="FFFFE9CC"/>
+        <bgColor rgb="FFFFCC00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2216,13 +1996,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3ECFC"/>
-        <bgColor rgb="FFEDF2FC"/>
+        <bgColor rgb="FFEEF1F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE4E7"/>
-        <bgColor rgb="FFF6E8CE"/>
+        <bgColor rgb="FFEEF1F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -2296,7 +2076,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2421,18 +2201,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2442,7 +2210,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2629,80 +2397,6 @@
         <color rgb="FFA6AEBC"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDF2FC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF2C4272"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF116B3E"/>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFB00020"/>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF9A4C00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE9CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF2C4272"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEDF2FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF8A5A05"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6E8CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF98A1B2"/>
-      </font>
-    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -2717,12 +2411,12 @@
       <rgbColor rgb="FFB00020"/>
       <rgbColor rgb="FF116B3E"/>
       <rgbColor rgb="FF13164E"/>
-      <rgbColor rgb="FF8A5A05"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFA6AEBC"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FFEEF1F7"/>
+      <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF3CF"/>
       <rgbColor rgb="FFE3ECFC"/>
@@ -2741,10 +2435,10 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEFF9F2"/>
       <rgbColor rgb="FFDCF3E4"/>
-      <rgbColor rgb="FFFFE9CC"/>
-      <rgbColor rgb="FFEDF2FC"/>
       <rgbColor rgb="FFFDE4E7"/>
-      <rgbColor rgb="FFF6E8CE"/>
+      <rgbColor rgb="FFEEF1F7"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFC97A"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -2753,7 +2447,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF4A5464"/>
-      <rgbColor rgb="FF98A1B2"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF14181F"/>
@@ -2761,17 +2455,13 @@
       <rgbColor rgb="FF9A4C00"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2A3170"/>
-      <rgbColor rgb="FF2C4272"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -13619,5334 +13309,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF13164E"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:L308"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="K1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="3" t="n">
-        <f aca="true">TODAY()</f>
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
-        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10" t="n">
-        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;",$E$9:$E$308,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <f aca="false">COUNTIFS($A$9:$A$308,"&lt;&gt;",$E$9:$E$308,"&lt;&gt;")-COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="str">
-        <f aca="false">IF($C$4=0,"",$D$4/$C$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="31" t="str">
-        <f aca="false">IF(COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0")=0,"",SUMIFS($F$9:$F$308,$A$9:$A$308,"&lt;&gt;")/COUNTIFS($A$9:$A$308,"&lt;&gt;",$F$9:$F$308,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="32" t="n">
-        <f aca="false">SUMIFS($F$9:$F$308,$A$9:$A$308,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>547</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16" t="str">
-        <f aca="false">IF(OR($A9="",$D9="",$E9=""),"",MAX(0,$E9-$D9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="16" t="str">
-        <f aca="false">IF($A9="","",IF($E9&lt;&gt;"",IF(N($F9)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D9="","Sem data prometida",IF($D9&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v>Aguardando</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>548</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16" t="str">
-        <f aca="false">IF(OR($A10="",$D10="",$E10=""),"",MAX(0,$E10-$D10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="16" t="str">
-        <f aca="false">IF($A10="","",IF($E10&lt;&gt;"",IF(N($F10)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D10="","Sem data prometida",IF($D10&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16" t="str">
-        <f aca="false">IF(OR($A11="",$D11="",$E11=""),"",MAX(0,$E11-$D11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="16" t="str">
-        <f aca="false">IF($A11="","",IF($E11&lt;&gt;"",IF(N($F11)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D11="","Sem data prometida",IF($D11&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16" t="str">
-        <f aca="false">IF(OR($A12="",$D12="",$E12=""),"",MAX(0,$E12-$D12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="16" t="str">
-        <f aca="false">IF($A12="","",IF($E12&lt;&gt;"",IF(N($F12)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D12="","Sem data prometida",IF($D12&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16" t="str">
-        <f aca="false">IF(OR($A13="",$D13="",$E13=""),"",MAX(0,$E13-$D13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="16" t="str">
-        <f aca="false">IF($A13="","",IF($E13&lt;&gt;"",IF(N($F13)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D13="","Sem data prometida",IF($D13&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16" t="str">
-        <f aca="false">IF(OR($A14="",$D14="",$E14=""),"",MAX(0,$E14-$D14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="16" t="str">
-        <f aca="false">IF($A14="","",IF($E14&lt;&gt;"",IF(N($F14)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D14="","Sem data prometida",IF($D14&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16" t="str">
-        <f aca="false">IF(OR($A15="",$D15="",$E15=""),"",MAX(0,$E15-$D15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="16" t="str">
-        <f aca="false">IF($A15="","",IF($E15&lt;&gt;"",IF(N($F15)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D15="","Sem data prometida",IF($D15&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16" t="str">
-        <f aca="false">IF(OR($A16="",$D16="",$E16=""),"",MAX(0,$E16-$D16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="16" t="str">
-        <f aca="false">IF($A16="","",IF($E16&lt;&gt;"",IF(N($F16)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D16="","Sem data prometida",IF($D16&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16" t="str">
-        <f aca="false">IF(OR($A17="",$D17="",$E17=""),"",MAX(0,$E17-$D17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="16" t="str">
-        <f aca="false">IF($A17="","",IF($E17&lt;&gt;"",IF(N($F17)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D17="","Sem data prometida",IF($D17&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16" t="str">
-        <f aca="false">IF(OR($A18="",$D18="",$E18=""),"",MAX(0,$E18-$D18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="16" t="str">
-        <f aca="false">IF($A18="","",IF($E18&lt;&gt;"",IF(N($F18)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D18="","Sem data prometida",IF($D18&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16" t="str">
-        <f aca="false">IF(OR($A19="",$D19="",$E19=""),"",MAX(0,$E19-$D19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF($A19="","",IF($E19&lt;&gt;"",IF(N($F19)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D19="","Sem data prometida",IF($D19&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16" t="str">
-        <f aca="false">IF(OR($A20="",$D20="",$E20=""),"",MAX(0,$E20-$D20))</f>
-        <v/>
-      </c>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF($A20="","",IF($E20&lt;&gt;"",IF(N($F20)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D20="","Sem data prometida",IF($D20&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16" t="str">
-        <f aca="false">IF(OR($A21="",$D21="",$E21=""),"",MAX(0,$E21-$D21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="16" t="str">
-        <f aca="false">IF($A21="","",IF($E21&lt;&gt;"",IF(N($F21)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D21="","Sem data prometida",IF($D21&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16" t="str">
-        <f aca="false">IF(OR($A22="",$D22="",$E22=""),"",MAX(0,$E22-$D22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="16" t="str">
-        <f aca="false">IF($A22="","",IF($E22&lt;&gt;"",IF(N($F22)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D22="","Sem data prometida",IF($D22&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16" t="str">
-        <f aca="false">IF(OR($A23="",$D23="",$E23=""),"",MAX(0,$E23-$D23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="16" t="str">
-        <f aca="false">IF($A23="","",IF($E23&lt;&gt;"",IF(N($F23)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D23="","Sem data prometida",IF($D23&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16" t="str">
-        <f aca="false">IF(OR($A24="",$D24="",$E24=""),"",MAX(0,$E24-$D24))</f>
-        <v/>
-      </c>
-      <c r="G24" s="16" t="str">
-        <f aca="false">IF($A24="","",IF($E24&lt;&gt;"",IF(N($F24)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D24="","Sem data prometida",IF($D24&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="str">
-        <f aca="false">IF(OR($A25="",$D25="",$E25=""),"",MAX(0,$E25-$D25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="16" t="str">
-        <f aca="false">IF($A25="","",IF($E25&lt;&gt;"",IF(N($F25)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D25="","Sem data prometida",IF($D25&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16" t="str">
-        <f aca="false">IF(OR($A26="",$D26="",$E26=""),"",MAX(0,$E26-$D26))</f>
-        <v/>
-      </c>
-      <c r="G26" s="16" t="str">
-        <f aca="false">IF($A26="","",IF($E26&lt;&gt;"",IF(N($F26)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D26="","Sem data prometida",IF($D26&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16" t="str">
-        <f aca="false">IF(OR($A27="",$D27="",$E27=""),"",MAX(0,$E27-$D27))</f>
-        <v/>
-      </c>
-      <c r="G27" s="16" t="str">
-        <f aca="false">IF($A27="","",IF($E27&lt;&gt;"",IF(N($F27)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D27="","Sem data prometida",IF($D27&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16" t="str">
-        <f aca="false">IF(OR($A28="",$D28="",$E28=""),"",MAX(0,$E28-$D28))</f>
-        <v/>
-      </c>
-      <c r="G28" s="16" t="str">
-        <f aca="false">IF($A28="","",IF($E28&lt;&gt;"",IF(N($F28)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D28="","Sem data prometida",IF($D28&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-    </row>
-    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16" t="str">
-        <f aca="false">IF(OR($A29="",$D29="",$E29=""),"",MAX(0,$E29-$D29))</f>
-        <v/>
-      </c>
-      <c r="G29" s="16" t="str">
-        <f aca="false">IF($A29="","",IF($E29&lt;&gt;"",IF(N($F29)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D29="","Sem data prometida",IF($D29&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16" t="str">
-        <f aca="false">IF(OR($A30="",$D30="",$E30=""),"",MAX(0,$E30-$D30))</f>
-        <v/>
-      </c>
-      <c r="G30" s="16" t="str">
-        <f aca="false">IF($A30="","",IF($E30&lt;&gt;"",IF(N($F30)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D30="","Sem data prometida",IF($D30&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-    </row>
-    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16" t="str">
-        <f aca="false">IF(OR($A31="",$D31="",$E31=""),"",MAX(0,$E31-$D31))</f>
-        <v/>
-      </c>
-      <c r="G31" s="16" t="str">
-        <f aca="false">IF($A31="","",IF($E31&lt;&gt;"",IF(N($F31)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D31="","Sem data prometida",IF($D31&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-    </row>
-    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16" t="str">
-        <f aca="false">IF(OR($A32="",$D32="",$E32=""),"",MAX(0,$E32-$D32))</f>
-        <v/>
-      </c>
-      <c r="G32" s="16" t="str">
-        <f aca="false">IF($A32="","",IF($E32&lt;&gt;"",IF(N($F32)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D32="","Sem data prometida",IF($D32&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-    </row>
-    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16" t="str">
-        <f aca="false">IF(OR($A33="",$D33="",$E33=""),"",MAX(0,$E33-$D33))</f>
-        <v/>
-      </c>
-      <c r="G33" s="16" t="str">
-        <f aca="false">IF($A33="","",IF($E33&lt;&gt;"",IF(N($F33)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D33="","Sem data prometida",IF($D33&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-    </row>
-    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16" t="str">
-        <f aca="false">IF(OR($A34="",$D34="",$E34=""),"",MAX(0,$E34-$D34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="16" t="str">
-        <f aca="false">IF($A34="","",IF($E34&lt;&gt;"",IF(N($F34)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D34="","Sem data prometida",IF($D34&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-    </row>
-    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16" t="str">
-        <f aca="false">IF(OR($A35="",$D35="",$E35=""),"",MAX(0,$E35-$D35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="16" t="str">
-        <f aca="false">IF($A35="","",IF($E35&lt;&gt;"",IF(N($F35)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D35="","Sem data prometida",IF($D35&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-    </row>
-    <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16" t="str">
-        <f aca="false">IF(OR($A36="",$D36="",$E36=""),"",MAX(0,$E36-$D36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="16" t="str">
-        <f aca="false">IF($A36="","",IF($E36&lt;&gt;"",IF(N($F36)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D36="","Sem data prometida",IF($D36&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-    </row>
-    <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16" t="str">
-        <f aca="false">IF(OR($A37="",$D37="",$E37=""),"",MAX(0,$E37-$D37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="16" t="str">
-        <f aca="false">IF($A37="","",IF($E37&lt;&gt;"",IF(N($F37)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D37="","Sem data prometida",IF($D37&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-    </row>
-    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16" t="str">
-        <f aca="false">IF(OR($A38="",$D38="",$E38=""),"",MAX(0,$E38-$D38))</f>
-        <v/>
-      </c>
-      <c r="G38" s="16" t="str">
-        <f aca="false">IF($A38="","",IF($E38&lt;&gt;"",IF(N($F38)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D38="","Sem data prometida",IF($D38&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-    </row>
-    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16" t="str">
-        <f aca="false">IF(OR($A39="",$D39="",$E39=""),"",MAX(0,$E39-$D39))</f>
-        <v/>
-      </c>
-      <c r="G39" s="16" t="str">
-        <f aca="false">IF($A39="","",IF($E39&lt;&gt;"",IF(N($F39)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D39="","Sem data prometida",IF($D39&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-    </row>
-    <row r="40" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16" t="str">
-        <f aca="false">IF(OR($A40="",$D40="",$E40=""),"",MAX(0,$E40-$D40))</f>
-        <v/>
-      </c>
-      <c r="G40" s="16" t="str">
-        <f aca="false">IF($A40="","",IF($E40&lt;&gt;"",IF(N($F40)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D40="","Sem data prometida",IF($D40&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-    </row>
-    <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16" t="str">
-        <f aca="false">IF(OR($A41="",$D41="",$E41=""),"",MAX(0,$E41-$D41))</f>
-        <v/>
-      </c>
-      <c r="G41" s="16" t="str">
-        <f aca="false">IF($A41="","",IF($E41&lt;&gt;"",IF(N($F41)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D41="","Sem data prometida",IF($D41&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-    </row>
-    <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16" t="str">
-        <f aca="false">IF(OR($A42="",$D42="",$E42=""),"",MAX(0,$E42-$D42))</f>
-        <v/>
-      </c>
-      <c r="G42" s="16" t="str">
-        <f aca="false">IF($A42="","",IF($E42&lt;&gt;"",IF(N($F42)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D42="","Sem data prometida",IF($D42&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-    </row>
-    <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16" t="str">
-        <f aca="false">IF(OR($A43="",$D43="",$E43=""),"",MAX(0,$E43-$D43))</f>
-        <v/>
-      </c>
-      <c r="G43" s="16" t="str">
-        <f aca="false">IF($A43="","",IF($E43&lt;&gt;"",IF(N($F43)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D43="","Sem data prometida",IF($D43&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-    </row>
-    <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16" t="str">
-        <f aca="false">IF(OR($A44="",$D44="",$E44=""),"",MAX(0,$E44-$D44))</f>
-        <v/>
-      </c>
-      <c r="G44" s="16" t="str">
-        <f aca="false">IF($A44="","",IF($E44&lt;&gt;"",IF(N($F44)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D44="","Sem data prometida",IF($D44&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-    </row>
-    <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16" t="str">
-        <f aca="false">IF(OR($A45="",$D45="",$E45=""),"",MAX(0,$E45-$D45))</f>
-        <v/>
-      </c>
-      <c r="G45" s="16" t="str">
-        <f aca="false">IF($A45="","",IF($E45&lt;&gt;"",IF(N($F45)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D45="","Sem data prometida",IF($D45&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-    </row>
-    <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="16" t="str">
-        <f aca="false">IF(OR($A46="",$D46="",$E46=""),"",MAX(0,$E46-$D46))</f>
-        <v/>
-      </c>
-      <c r="G46" s="16" t="str">
-        <f aca="false">IF($A46="","",IF($E46&lt;&gt;"",IF(N($F46)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D46="","Sem data prometida",IF($D46&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-    </row>
-    <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16" t="str">
-        <f aca="false">IF(OR($A47="",$D47="",$E47=""),"",MAX(0,$E47-$D47))</f>
-        <v/>
-      </c>
-      <c r="G47" s="16" t="str">
-        <f aca="false">IF($A47="","",IF($E47&lt;&gt;"",IF(N($F47)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D47="","Sem data prometida",IF($D47&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-    </row>
-    <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16" t="str">
-        <f aca="false">IF(OR($A48="",$D48="",$E48=""),"",MAX(0,$E48-$D48))</f>
-        <v/>
-      </c>
-      <c r="G48" s="16" t="str">
-        <f aca="false">IF($A48="","",IF($E48&lt;&gt;"",IF(N($F48)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D48="","Sem data prometida",IF($D48&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-    </row>
-    <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16" t="str">
-        <f aca="false">IF(OR($A49="",$D49="",$E49=""),"",MAX(0,$E49-$D49))</f>
-        <v/>
-      </c>
-      <c r="G49" s="16" t="str">
-        <f aca="false">IF($A49="","",IF($E49&lt;&gt;"",IF(N($F49)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D49="","Sem data prometida",IF($D49&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-    </row>
-    <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16" t="str">
-        <f aca="false">IF(OR($A50="",$D50="",$E50=""),"",MAX(0,$E50-$D50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="16" t="str">
-        <f aca="false">IF($A50="","",IF($E50&lt;&gt;"",IF(N($F50)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D50="","Sem data prometida",IF($D50&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-    </row>
-    <row r="51" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="16" t="str">
-        <f aca="false">IF(OR($A51="",$D51="",$E51=""),"",MAX(0,$E51-$D51))</f>
-        <v/>
-      </c>
-      <c r="G51" s="16" t="str">
-        <f aca="false">IF($A51="","",IF($E51&lt;&gt;"",IF(N($F51)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D51="","Sem data prometida",IF($D51&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-    </row>
-    <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16" t="str">
-        <f aca="false">IF(OR($A52="",$D52="",$E52=""),"",MAX(0,$E52-$D52))</f>
-        <v/>
-      </c>
-      <c r="G52" s="16" t="str">
-        <f aca="false">IF($A52="","",IF($E52&lt;&gt;"",IF(N($F52)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D52="","Sem data prometida",IF($D52&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-    </row>
-    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="16" t="str">
-        <f aca="false">IF(OR($A53="",$D53="",$E53=""),"",MAX(0,$E53-$D53))</f>
-        <v/>
-      </c>
-      <c r="G53" s="16" t="str">
-        <f aca="false">IF($A53="","",IF($E53&lt;&gt;"",IF(N($F53)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D53="","Sem data prometida",IF($D53&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-    </row>
-    <row r="54" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="16" t="str">
-        <f aca="false">IF(OR($A54="",$D54="",$E54=""),"",MAX(0,$E54-$D54))</f>
-        <v/>
-      </c>
-      <c r="G54" s="16" t="str">
-        <f aca="false">IF($A54="","",IF($E54&lt;&gt;"",IF(N($F54)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D54="","Sem data prometida",IF($D54&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-    </row>
-    <row r="55" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="16" t="str">
-        <f aca="false">IF(OR($A55="",$D55="",$E55=""),"",MAX(0,$E55-$D55))</f>
-        <v/>
-      </c>
-      <c r="G55" s="16" t="str">
-        <f aca="false">IF($A55="","",IF($E55&lt;&gt;"",IF(N($F55)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D55="","Sem data prometida",IF($D55&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-    </row>
-    <row r="56" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="16" t="str">
-        <f aca="false">IF(OR($A56="",$D56="",$E56=""),"",MAX(0,$E56-$D56))</f>
-        <v/>
-      </c>
-      <c r="G56" s="16" t="str">
-        <f aca="false">IF($A56="","",IF($E56&lt;&gt;"",IF(N($F56)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D56="","Sem data prometida",IF($D56&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-    </row>
-    <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="16" t="str">
-        <f aca="false">IF(OR($A57="",$D57="",$E57=""),"",MAX(0,$E57-$D57))</f>
-        <v/>
-      </c>
-      <c r="G57" s="16" t="str">
-        <f aca="false">IF($A57="","",IF($E57&lt;&gt;"",IF(N($F57)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D57="","Sem data prometida",IF($D57&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-    </row>
-    <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="16" t="str">
-        <f aca="false">IF(OR($A58="",$D58="",$E58=""),"",MAX(0,$E58-$D58))</f>
-        <v/>
-      </c>
-      <c r="G58" s="16" t="str">
-        <f aca="false">IF($A58="","",IF($E58&lt;&gt;"",IF(N($F58)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D58="","Sem data prometida",IF($D58&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-    </row>
-    <row r="59" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="16" t="str">
-        <f aca="false">IF(OR($A59="",$D59="",$E59=""),"",MAX(0,$E59-$D59))</f>
-        <v/>
-      </c>
-      <c r="G59" s="16" t="str">
-        <f aca="false">IF($A59="","",IF($E59&lt;&gt;"",IF(N($F59)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D59="","Sem data prometida",IF($D59&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-    </row>
-    <row r="60" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="16" t="str">
-        <f aca="false">IF(OR($A60="",$D60="",$E60=""),"",MAX(0,$E60-$D60))</f>
-        <v/>
-      </c>
-      <c r="G60" s="16" t="str">
-        <f aca="false">IF($A60="","",IF($E60&lt;&gt;"",IF(N($F60)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D60="","Sem data prometida",IF($D60&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-    </row>
-    <row r="61" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="16" t="str">
-        <f aca="false">IF(OR($A61="",$D61="",$E61=""),"",MAX(0,$E61-$D61))</f>
-        <v/>
-      </c>
-      <c r="G61" s="16" t="str">
-        <f aca="false">IF($A61="","",IF($E61&lt;&gt;"",IF(N($F61)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D61="","Sem data prometida",IF($D61&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-    </row>
-    <row r="62" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="16" t="str">
-        <f aca="false">IF(OR($A62="",$D62="",$E62=""),"",MAX(0,$E62-$D62))</f>
-        <v/>
-      </c>
-      <c r="G62" s="16" t="str">
-        <f aca="false">IF($A62="","",IF($E62&lt;&gt;"",IF(N($F62)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D62="","Sem data prometida",IF($D62&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-    </row>
-    <row r="63" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="16" t="str">
-        <f aca="false">IF(OR($A63="",$D63="",$E63=""),"",MAX(0,$E63-$D63))</f>
-        <v/>
-      </c>
-      <c r="G63" s="16" t="str">
-        <f aca="false">IF($A63="","",IF($E63&lt;&gt;"",IF(N($F63)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D63="","Sem data prometida",IF($D63&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-    </row>
-    <row r="64" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="16" t="str">
-        <f aca="false">IF(OR($A64="",$D64="",$E64=""),"",MAX(0,$E64-$D64))</f>
-        <v/>
-      </c>
-      <c r="G64" s="16" t="str">
-        <f aca="false">IF($A64="","",IF($E64&lt;&gt;"",IF(N($F64)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D64="","Sem data prometida",IF($D64&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-    </row>
-    <row r="65" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="16"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="16" t="str">
-        <f aca="false">IF(OR($A65="",$D65="",$E65=""),"",MAX(0,$E65-$D65))</f>
-        <v/>
-      </c>
-      <c r="G65" s="16" t="str">
-        <f aca="false">IF($A65="","",IF($E65&lt;&gt;"",IF(N($F65)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D65="","Sem data prometida",IF($D65&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-    </row>
-    <row r="66" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="16" t="str">
-        <f aca="false">IF(OR($A66="",$D66="",$E66=""),"",MAX(0,$E66-$D66))</f>
-        <v/>
-      </c>
-      <c r="G66" s="16" t="str">
-        <f aca="false">IF($A66="","",IF($E66&lt;&gt;"",IF(N($F66)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D66="","Sem data prometida",IF($D66&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-    </row>
-    <row r="67" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="16"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="16" t="str">
-        <f aca="false">IF(OR($A67="",$D67="",$E67=""),"",MAX(0,$E67-$D67))</f>
-        <v/>
-      </c>
-      <c r="G67" s="16" t="str">
-        <f aca="false">IF($A67="","",IF($E67&lt;&gt;"",IF(N($F67)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D67="","Sem data prometida",IF($D67&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-    </row>
-    <row r="68" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="16"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="16" t="str">
-        <f aca="false">IF(OR($A68="",$D68="",$E68=""),"",MAX(0,$E68-$D68))</f>
-        <v/>
-      </c>
-      <c r="G68" s="16" t="str">
-        <f aca="false">IF($A68="","",IF($E68&lt;&gt;"",IF(N($F68)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D68="","Sem data prometida",IF($D68&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-    </row>
-    <row r="69" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="16" t="str">
-        <f aca="false">IF(OR($A69="",$D69="",$E69=""),"",MAX(0,$E69-$D69))</f>
-        <v/>
-      </c>
-      <c r="G69" s="16" t="str">
-        <f aca="false">IF($A69="","",IF($E69&lt;&gt;"",IF(N($F69)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D69="","Sem data prometida",IF($D69&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-    </row>
-    <row r="70" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="16" t="str">
-        <f aca="false">IF(OR($A70="",$D70="",$E70=""),"",MAX(0,$E70-$D70))</f>
-        <v/>
-      </c>
-      <c r="G70" s="16" t="str">
-        <f aca="false">IF($A70="","",IF($E70&lt;&gt;"",IF(N($F70)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D70="","Sem data prometida",IF($D70&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-    </row>
-    <row r="71" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="16" t="str">
-        <f aca="false">IF(OR($A71="",$D71="",$E71=""),"",MAX(0,$E71-$D71))</f>
-        <v/>
-      </c>
-      <c r="G71" s="16" t="str">
-        <f aca="false">IF($A71="","",IF($E71&lt;&gt;"",IF(N($F71)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D71="","Sem data prometida",IF($D71&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-    </row>
-    <row r="72" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="16" t="str">
-        <f aca="false">IF(OR($A72="",$D72="",$E72=""),"",MAX(0,$E72-$D72))</f>
-        <v/>
-      </c>
-      <c r="G72" s="16" t="str">
-        <f aca="false">IF($A72="","",IF($E72&lt;&gt;"",IF(N($F72)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D72="","Sem data prometida",IF($D72&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-    </row>
-    <row r="73" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="16" t="str">
-        <f aca="false">IF(OR($A73="",$D73="",$E73=""),"",MAX(0,$E73-$D73))</f>
-        <v/>
-      </c>
-      <c r="G73" s="16" t="str">
-        <f aca="false">IF($A73="","",IF($E73&lt;&gt;"",IF(N($F73)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D73="","Sem data prometida",IF($D73&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-    </row>
-    <row r="74" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="16" t="str">
-        <f aca="false">IF(OR($A74="",$D74="",$E74=""),"",MAX(0,$E74-$D74))</f>
-        <v/>
-      </c>
-      <c r="G74" s="16" t="str">
-        <f aca="false">IF($A74="","",IF($E74&lt;&gt;"",IF(N($F74)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D74="","Sem data prometida",IF($D74&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-    </row>
-    <row r="75" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="16" t="str">
-        <f aca="false">IF(OR($A75="",$D75="",$E75=""),"",MAX(0,$E75-$D75))</f>
-        <v/>
-      </c>
-      <c r="G75" s="16" t="str">
-        <f aca="false">IF($A75="","",IF($E75&lt;&gt;"",IF(N($F75)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D75="","Sem data prometida",IF($D75&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-    </row>
-    <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="16"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="16" t="str">
-        <f aca="false">IF(OR($A76="",$D76="",$E76=""),"",MAX(0,$E76-$D76))</f>
-        <v/>
-      </c>
-      <c r="G76" s="16" t="str">
-        <f aca="false">IF($A76="","",IF($E76&lt;&gt;"",IF(N($F76)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D76="","Sem data prometida",IF($D76&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-    </row>
-    <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="16"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="16" t="str">
-        <f aca="false">IF(OR($A77="",$D77="",$E77=""),"",MAX(0,$E77-$D77))</f>
-        <v/>
-      </c>
-      <c r="G77" s="16" t="str">
-        <f aca="false">IF($A77="","",IF($E77&lt;&gt;"",IF(N($F77)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D77="","Sem data prometida",IF($D77&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-    </row>
-    <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="16" t="str">
-        <f aca="false">IF(OR($A78="",$D78="",$E78=""),"",MAX(0,$E78-$D78))</f>
-        <v/>
-      </c>
-      <c r="G78" s="16" t="str">
-        <f aca="false">IF($A78="","",IF($E78&lt;&gt;"",IF(N($F78)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D78="","Sem data prometida",IF($D78&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-    </row>
-    <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="16" t="str">
-        <f aca="false">IF(OR($A79="",$D79="",$E79=""),"",MAX(0,$E79-$D79))</f>
-        <v/>
-      </c>
-      <c r="G79" s="16" t="str">
-        <f aca="false">IF($A79="","",IF($E79&lt;&gt;"",IF(N($F79)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D79="","Sem data prometida",IF($D79&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-    </row>
-    <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="16" t="str">
-        <f aca="false">IF(OR($A80="",$D80="",$E80=""),"",MAX(0,$E80-$D80))</f>
-        <v/>
-      </c>
-      <c r="G80" s="16" t="str">
-        <f aca="false">IF($A80="","",IF($E80&lt;&gt;"",IF(N($F80)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D80="","Sem data prometida",IF($D80&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-    </row>
-    <row r="81" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="16" t="str">
-        <f aca="false">IF(OR($A81="",$D81="",$E81=""),"",MAX(0,$E81-$D81))</f>
-        <v/>
-      </c>
-      <c r="G81" s="16" t="str">
-        <f aca="false">IF($A81="","",IF($E81&lt;&gt;"",IF(N($F81)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D81="","Sem data prometida",IF($D81&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-    </row>
-    <row r="82" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="16" t="str">
-        <f aca="false">IF(OR($A82="",$D82="",$E82=""),"",MAX(0,$E82-$D82))</f>
-        <v/>
-      </c>
-      <c r="G82" s="16" t="str">
-        <f aca="false">IF($A82="","",IF($E82&lt;&gt;"",IF(N($F82)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D82="","Sem data prometida",IF($D82&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-    </row>
-    <row r="83" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="16"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="16" t="str">
-        <f aca="false">IF(OR($A83="",$D83="",$E83=""),"",MAX(0,$E83-$D83))</f>
-        <v/>
-      </c>
-      <c r="G83" s="16" t="str">
-        <f aca="false">IF($A83="","",IF($E83&lt;&gt;"",IF(N($F83)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D83="","Sem data prometida",IF($D83&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-    </row>
-    <row r="84" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="16" t="str">
-        <f aca="false">IF(OR($A84="",$D84="",$E84=""),"",MAX(0,$E84-$D84))</f>
-        <v/>
-      </c>
-      <c r="G84" s="16" t="str">
-        <f aca="false">IF($A84="","",IF($E84&lt;&gt;"",IF(N($F84)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D84="","Sem data prometida",IF($D84&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-    </row>
-    <row r="85" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="16" t="str">
-        <f aca="false">IF(OR($A85="",$D85="",$E85=""),"",MAX(0,$E85-$D85))</f>
-        <v/>
-      </c>
-      <c r="G85" s="16" t="str">
-        <f aca="false">IF($A85="","",IF($E85&lt;&gt;"",IF(N($F85)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D85="","Sem data prometida",IF($D85&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-    </row>
-    <row r="86" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="16" t="str">
-        <f aca="false">IF(OR($A86="",$D86="",$E86=""),"",MAX(0,$E86-$D86))</f>
-        <v/>
-      </c>
-      <c r="G86" s="16" t="str">
-        <f aca="false">IF($A86="","",IF($E86&lt;&gt;"",IF(N($F86)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D86="","Sem data prometida",IF($D86&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-    </row>
-    <row r="87" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="16" t="str">
-        <f aca="false">IF(OR($A87="",$D87="",$E87=""),"",MAX(0,$E87-$D87))</f>
-        <v/>
-      </c>
-      <c r="G87" s="16" t="str">
-        <f aca="false">IF($A87="","",IF($E87&lt;&gt;"",IF(N($F87)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D87="","Sem data prometida",IF($D87&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-    </row>
-    <row r="88" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="16"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="16" t="str">
-        <f aca="false">IF(OR($A88="",$D88="",$E88=""),"",MAX(0,$E88-$D88))</f>
-        <v/>
-      </c>
-      <c r="G88" s="16" t="str">
-        <f aca="false">IF($A88="","",IF($E88&lt;&gt;"",IF(N($F88)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D88="","Sem data prometida",IF($D88&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-    </row>
-    <row r="89" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="16" t="str">
-        <f aca="false">IF(OR($A89="",$D89="",$E89=""),"",MAX(0,$E89-$D89))</f>
-        <v/>
-      </c>
-      <c r="G89" s="16" t="str">
-        <f aca="false">IF($A89="","",IF($E89&lt;&gt;"",IF(N($F89)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D89="","Sem data prometida",IF($D89&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-    </row>
-    <row r="90" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="16"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="16" t="str">
-        <f aca="false">IF(OR($A90="",$D90="",$E90=""),"",MAX(0,$E90-$D90))</f>
-        <v/>
-      </c>
-      <c r="G90" s="16" t="str">
-        <f aca="false">IF($A90="","",IF($E90&lt;&gt;"",IF(N($F90)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D90="","Sem data prometida",IF($D90&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H90" s="17"/>
-      <c r="I90" s="17"/>
-    </row>
-    <row r="91" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="16" t="str">
-        <f aca="false">IF(OR($A91="",$D91="",$E91=""),"",MAX(0,$E91-$D91))</f>
-        <v/>
-      </c>
-      <c r="G91" s="16" t="str">
-        <f aca="false">IF($A91="","",IF($E91&lt;&gt;"",IF(N($F91)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D91="","Sem data prometida",IF($D91&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-    </row>
-    <row r="92" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="16"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="16" t="str">
-        <f aca="false">IF(OR($A92="",$D92="",$E92=""),"",MAX(0,$E92-$D92))</f>
-        <v/>
-      </c>
-      <c r="G92" s="16" t="str">
-        <f aca="false">IF($A92="","",IF($E92&lt;&gt;"",IF(N($F92)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D92="","Sem data prometida",IF($D92&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-    </row>
-    <row r="93" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="16"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="16" t="str">
-        <f aca="false">IF(OR($A93="",$D93="",$E93=""),"",MAX(0,$E93-$D93))</f>
-        <v/>
-      </c>
-      <c r="G93" s="16" t="str">
-        <f aca="false">IF($A93="","",IF($E93&lt;&gt;"",IF(N($F93)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D93="","Sem data prometida",IF($D93&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-    </row>
-    <row r="94" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="16"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="16" t="str">
-        <f aca="false">IF(OR($A94="",$D94="",$E94=""),"",MAX(0,$E94-$D94))</f>
-        <v/>
-      </c>
-      <c r="G94" s="16" t="str">
-        <f aca="false">IF($A94="","",IF($E94&lt;&gt;"",IF(N($F94)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D94="","Sem data prometida",IF($D94&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H94" s="17"/>
-      <c r="I94" s="17"/>
-    </row>
-    <row r="95" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="16"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="16" t="str">
-        <f aca="false">IF(OR($A95="",$D95="",$E95=""),"",MAX(0,$E95-$D95))</f>
-        <v/>
-      </c>
-      <c r="G95" s="16" t="str">
-        <f aca="false">IF($A95="","",IF($E95&lt;&gt;"",IF(N($F95)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D95="","Sem data prometida",IF($D95&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-    </row>
-    <row r="96" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="16"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="16" t="str">
-        <f aca="false">IF(OR($A96="",$D96="",$E96=""),"",MAX(0,$E96-$D96))</f>
-        <v/>
-      </c>
-      <c r="G96" s="16" t="str">
-        <f aca="false">IF($A96="","",IF($E96&lt;&gt;"",IF(N($F96)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D96="","Sem data prometida",IF($D96&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-    </row>
-    <row r="97" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="16"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="16" t="str">
-        <f aca="false">IF(OR($A97="",$D97="",$E97=""),"",MAX(0,$E97-$D97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="16" t="str">
-        <f aca="false">IF($A97="","",IF($E97&lt;&gt;"",IF(N($F97)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D97="","Sem data prometida",IF($D97&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-    </row>
-    <row r="98" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="16"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="16" t="str">
-        <f aca="false">IF(OR($A98="",$D98="",$E98=""),"",MAX(0,$E98-$D98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="16" t="str">
-        <f aca="false">IF($A98="","",IF($E98&lt;&gt;"",IF(N($F98)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D98="","Sem data prometida",IF($D98&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
-    </row>
-    <row r="99" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="16"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="16" t="str">
-        <f aca="false">IF(OR($A99="",$D99="",$E99=""),"",MAX(0,$E99-$D99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="16" t="str">
-        <f aca="false">IF($A99="","",IF($E99&lt;&gt;"",IF(N($F99)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D99="","Sem data prometida",IF($D99&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-    </row>
-    <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="16"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="16" t="str">
-        <f aca="false">IF(OR($A100="",$D100="",$E100=""),"",MAX(0,$E100-$D100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="16" t="str">
-        <f aca="false">IF($A100="","",IF($E100&lt;&gt;"",IF(N($F100)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D100="","Sem data prometida",IF($D100&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-    </row>
-    <row r="101" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="16"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="16" t="str">
-        <f aca="false">IF(OR($A101="",$D101="",$E101=""),"",MAX(0,$E101-$D101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="16" t="str">
-        <f aca="false">IF($A101="","",IF($E101&lt;&gt;"",IF(N($F101)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D101="","Sem data prometida",IF($D101&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H101" s="17"/>
-      <c r="I101" s="17"/>
-    </row>
-    <row r="102" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="16"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="16" t="str">
-        <f aca="false">IF(OR($A102="",$D102="",$E102=""),"",MAX(0,$E102-$D102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="16" t="str">
-        <f aca="false">IF($A102="","",IF($E102&lt;&gt;"",IF(N($F102)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D102="","Sem data prometida",IF($D102&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H102" s="17"/>
-      <c r="I102" s="17"/>
-    </row>
-    <row r="103" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="16"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="15"/>
-      <c r="D103" s="15"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="16" t="str">
-        <f aca="false">IF(OR($A103="",$D103="",$E103=""),"",MAX(0,$E103-$D103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="16" t="str">
-        <f aca="false">IF($A103="","",IF($E103&lt;&gt;"",IF(N($F103)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D103="","Sem data prometida",IF($D103&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H103" s="17"/>
-      <c r="I103" s="17"/>
-    </row>
-    <row r="104" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="16"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="15"/>
-      <c r="D104" s="15"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="16" t="str">
-        <f aca="false">IF(OR($A104="",$D104="",$E104=""),"",MAX(0,$E104-$D104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="16" t="str">
-        <f aca="false">IF($A104="","",IF($E104&lt;&gt;"",IF(N($F104)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D104="","Sem data prometida",IF($D104&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H104" s="17"/>
-      <c r="I104" s="17"/>
-    </row>
-    <row r="105" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="16"/>
-      <c r="B105" s="17"/>
-      <c r="C105" s="15"/>
-      <c r="D105" s="15"/>
-      <c r="E105" s="15"/>
-      <c r="F105" s="16" t="str">
-        <f aca="false">IF(OR($A105="",$D105="",$E105=""),"",MAX(0,$E105-$D105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="16" t="str">
-        <f aca="false">IF($A105="","",IF($E105&lt;&gt;"",IF(N($F105)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D105="","Sem data prometida",IF($D105&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H105" s="17"/>
-      <c r="I105" s="17"/>
-    </row>
-    <row r="106" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="16"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="15"/>
-      <c r="D106" s="15"/>
-      <c r="E106" s="15"/>
-      <c r="F106" s="16" t="str">
-        <f aca="false">IF(OR($A106="",$D106="",$E106=""),"",MAX(0,$E106-$D106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="16" t="str">
-        <f aca="false">IF($A106="","",IF($E106&lt;&gt;"",IF(N($F106)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D106="","Sem data prometida",IF($D106&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H106" s="17"/>
-      <c r="I106" s="17"/>
-    </row>
-    <row r="107" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="16"/>
-      <c r="B107" s="17"/>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="16" t="str">
-        <f aca="false">IF(OR($A107="",$D107="",$E107=""),"",MAX(0,$E107-$D107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="16" t="str">
-        <f aca="false">IF($A107="","",IF($E107&lt;&gt;"",IF(N($F107)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D107="","Sem data prometida",IF($D107&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H107" s="17"/>
-      <c r="I107" s="17"/>
-    </row>
-    <row r="108" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="16"/>
-      <c r="B108" s="17"/>
-      <c r="C108" s="15"/>
-      <c r="D108" s="15"/>
-      <c r="E108" s="15"/>
-      <c r="F108" s="16" t="str">
-        <f aca="false">IF(OR($A108="",$D108="",$E108=""),"",MAX(0,$E108-$D108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="16" t="str">
-        <f aca="false">IF($A108="","",IF($E108&lt;&gt;"",IF(N($F108)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D108="","Sem data prometida",IF($D108&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H108" s="17"/>
-      <c r="I108" s="17"/>
-    </row>
-    <row r="109" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="16"/>
-      <c r="B109" s="17"/>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="16" t="str">
-        <f aca="false">IF(OR($A109="",$D109="",$E109=""),"",MAX(0,$E109-$D109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="16" t="str">
-        <f aca="false">IF($A109="","",IF($E109&lt;&gt;"",IF(N($F109)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D109="","Sem data prometida",IF($D109&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H109" s="17"/>
-      <c r="I109" s="17"/>
-    </row>
-    <row r="110" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="16"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="15"/>
-      <c r="D110" s="15"/>
-      <c r="E110" s="15"/>
-      <c r="F110" s="16" t="str">
-        <f aca="false">IF(OR($A110="",$D110="",$E110=""),"",MAX(0,$E110-$D110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="16" t="str">
-        <f aca="false">IF($A110="","",IF($E110&lt;&gt;"",IF(N($F110)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D110="","Sem data prometida",IF($D110&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H110" s="17"/>
-      <c r="I110" s="17"/>
-    </row>
-    <row r="111" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="16"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="15"/>
-      <c r="D111" s="15"/>
-      <c r="E111" s="15"/>
-      <c r="F111" s="16" t="str">
-        <f aca="false">IF(OR($A111="",$D111="",$E111=""),"",MAX(0,$E111-$D111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="16" t="str">
-        <f aca="false">IF($A111="","",IF($E111&lt;&gt;"",IF(N($F111)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D111="","Sem data prometida",IF($D111&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H111" s="17"/>
-      <c r="I111" s="17"/>
-    </row>
-    <row r="112" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="16"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="15"/>
-      <c r="F112" s="16" t="str">
-        <f aca="false">IF(OR($A112="",$D112="",$E112=""),"",MAX(0,$E112-$D112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="16" t="str">
-        <f aca="false">IF($A112="","",IF($E112&lt;&gt;"",IF(N($F112)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D112="","Sem data prometida",IF($D112&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H112" s="17"/>
-      <c r="I112" s="17"/>
-    </row>
-    <row r="113" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="16"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="15"/>
-      <c r="D113" s="15"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="16" t="str">
-        <f aca="false">IF(OR($A113="",$D113="",$E113=""),"",MAX(0,$E113-$D113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="16" t="str">
-        <f aca="false">IF($A113="","",IF($E113&lt;&gt;"",IF(N($F113)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D113="","Sem data prometida",IF($D113&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H113" s="17"/>
-      <c r="I113" s="17"/>
-    </row>
-    <row r="114" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="16"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="15"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="16" t="str">
-        <f aca="false">IF(OR($A114="",$D114="",$E114=""),"",MAX(0,$E114-$D114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="16" t="str">
-        <f aca="false">IF($A114="","",IF($E114&lt;&gt;"",IF(N($F114)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D114="","Sem data prometida",IF($D114&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H114" s="17"/>
-      <c r="I114" s="17"/>
-    </row>
-    <row r="115" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="16"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="15"/>
-      <c r="E115" s="15"/>
-      <c r="F115" s="16" t="str">
-        <f aca="false">IF(OR($A115="",$D115="",$E115=""),"",MAX(0,$E115-$D115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="16" t="str">
-        <f aca="false">IF($A115="","",IF($E115&lt;&gt;"",IF(N($F115)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D115="","Sem data prometida",IF($D115&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H115" s="17"/>
-      <c r="I115" s="17"/>
-    </row>
-    <row r="116" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="16"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="15"/>
-      <c r="D116" s="15"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="16" t="str">
-        <f aca="false">IF(OR($A116="",$D116="",$E116=""),"",MAX(0,$E116-$D116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="16" t="str">
-        <f aca="false">IF($A116="","",IF($E116&lt;&gt;"",IF(N($F116)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D116="","Sem data prometida",IF($D116&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H116" s="17"/>
-      <c r="I116" s="17"/>
-    </row>
-    <row r="117" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="16"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="15"/>
-      <c r="D117" s="15"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="16" t="str">
-        <f aca="false">IF(OR($A117="",$D117="",$E117=""),"",MAX(0,$E117-$D117))</f>
-        <v/>
-      </c>
-      <c r="G117" s="16" t="str">
-        <f aca="false">IF($A117="","",IF($E117&lt;&gt;"",IF(N($F117)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D117="","Sem data prometida",IF($D117&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H117" s="17"/>
-      <c r="I117" s="17"/>
-    </row>
-    <row r="118" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="16"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="15"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="16" t="str">
-        <f aca="false">IF(OR($A118="",$D118="",$E118=""),"",MAX(0,$E118-$D118))</f>
-        <v/>
-      </c>
-      <c r="G118" s="16" t="str">
-        <f aca="false">IF($A118="","",IF($E118&lt;&gt;"",IF(N($F118)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D118="","Sem data prometida",IF($D118&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H118" s="17"/>
-      <c r="I118" s="17"/>
-    </row>
-    <row r="119" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="16"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="15"/>
-      <c r="D119" s="15"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="16" t="str">
-        <f aca="false">IF(OR($A119="",$D119="",$E119=""),"",MAX(0,$E119-$D119))</f>
-        <v/>
-      </c>
-      <c r="G119" s="16" t="str">
-        <f aca="false">IF($A119="","",IF($E119&lt;&gt;"",IF(N($F119)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D119="","Sem data prometida",IF($D119&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-    </row>
-    <row r="120" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="16"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="15"/>
-      <c r="D120" s="15"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="16" t="str">
-        <f aca="false">IF(OR($A120="",$D120="",$E120=""),"",MAX(0,$E120-$D120))</f>
-        <v/>
-      </c>
-      <c r="G120" s="16" t="str">
-        <f aca="false">IF($A120="","",IF($E120&lt;&gt;"",IF(N($F120)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D120="","Sem data prometida",IF($D120&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H120" s="17"/>
-      <c r="I120" s="17"/>
-    </row>
-    <row r="121" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="16"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="15"/>
-      <c r="D121" s="15"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="16" t="str">
-        <f aca="false">IF(OR($A121="",$D121="",$E121=""),"",MAX(0,$E121-$D121))</f>
-        <v/>
-      </c>
-      <c r="G121" s="16" t="str">
-        <f aca="false">IF($A121="","",IF($E121&lt;&gt;"",IF(N($F121)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D121="","Sem data prometida",IF($D121&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H121" s="17"/>
-      <c r="I121" s="17"/>
-    </row>
-    <row r="122" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="16"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="15"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="16" t="str">
-        <f aca="false">IF(OR($A122="",$D122="",$E122=""),"",MAX(0,$E122-$D122))</f>
-        <v/>
-      </c>
-      <c r="G122" s="16" t="str">
-        <f aca="false">IF($A122="","",IF($E122&lt;&gt;"",IF(N($F122)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D122="","Sem data prometida",IF($D122&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
-    </row>
-    <row r="123" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="16"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="15"/>
-      <c r="D123" s="15"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="16" t="str">
-        <f aca="false">IF(OR($A123="",$D123="",$E123=""),"",MAX(0,$E123-$D123))</f>
-        <v/>
-      </c>
-      <c r="G123" s="16" t="str">
-        <f aca="false">IF($A123="","",IF($E123&lt;&gt;"",IF(N($F123)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D123="","Sem data prometida",IF($D123&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H123" s="17"/>
-      <c r="I123" s="17"/>
-    </row>
-    <row r="124" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="16"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="15"/>
-      <c r="D124" s="15"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="16" t="str">
-        <f aca="false">IF(OR($A124="",$D124="",$E124=""),"",MAX(0,$E124-$D124))</f>
-        <v/>
-      </c>
-      <c r="G124" s="16" t="str">
-        <f aca="false">IF($A124="","",IF($E124&lt;&gt;"",IF(N($F124)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D124="","Sem data prometida",IF($D124&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H124" s="17"/>
-      <c r="I124" s="17"/>
-    </row>
-    <row r="125" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="16"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="15"/>
-      <c r="D125" s="15"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="16" t="str">
-        <f aca="false">IF(OR($A125="",$D125="",$E125=""),"",MAX(0,$E125-$D125))</f>
-        <v/>
-      </c>
-      <c r="G125" s="16" t="str">
-        <f aca="false">IF($A125="","",IF($E125&lt;&gt;"",IF(N($F125)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D125="","Sem data prometida",IF($D125&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H125" s="17"/>
-      <c r="I125" s="17"/>
-    </row>
-    <row r="126" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="16"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="15"/>
-      <c r="D126" s="15"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="16" t="str">
-        <f aca="false">IF(OR($A126="",$D126="",$E126=""),"",MAX(0,$E126-$D126))</f>
-        <v/>
-      </c>
-      <c r="G126" s="16" t="str">
-        <f aca="false">IF($A126="","",IF($E126&lt;&gt;"",IF(N($F126)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D126="","Sem data prometida",IF($D126&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H126" s="17"/>
-      <c r="I126" s="17"/>
-    </row>
-    <row r="127" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="16"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="16" t="str">
-        <f aca="false">IF(OR($A127="",$D127="",$E127=""),"",MAX(0,$E127-$D127))</f>
-        <v/>
-      </c>
-      <c r="G127" s="16" t="str">
-        <f aca="false">IF($A127="","",IF($E127&lt;&gt;"",IF(N($F127)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D127="","Sem data prometida",IF($D127&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H127" s="17"/>
-      <c r="I127" s="17"/>
-    </row>
-    <row r="128" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="16"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="15"/>
-      <c r="D128" s="15"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="16" t="str">
-        <f aca="false">IF(OR($A128="",$D128="",$E128=""),"",MAX(0,$E128-$D128))</f>
-        <v/>
-      </c>
-      <c r="G128" s="16" t="str">
-        <f aca="false">IF($A128="","",IF($E128&lt;&gt;"",IF(N($F128)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D128="","Sem data prometida",IF($D128&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H128" s="17"/>
-      <c r="I128" s="17"/>
-    </row>
-    <row r="129" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="16"/>
-      <c r="B129" s="17"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="16" t="str">
-        <f aca="false">IF(OR($A129="",$D129="",$E129=""),"",MAX(0,$E129-$D129))</f>
-        <v/>
-      </c>
-      <c r="G129" s="16" t="str">
-        <f aca="false">IF($A129="","",IF($E129&lt;&gt;"",IF(N($F129)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D129="","Sem data prometida",IF($D129&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H129" s="17"/>
-      <c r="I129" s="17"/>
-    </row>
-    <row r="130" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="16"/>
-      <c r="B130" s="17"/>
-      <c r="C130" s="15"/>
-      <c r="D130" s="15"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="16" t="str">
-        <f aca="false">IF(OR($A130="",$D130="",$E130=""),"",MAX(0,$E130-$D130))</f>
-        <v/>
-      </c>
-      <c r="G130" s="16" t="str">
-        <f aca="false">IF($A130="","",IF($E130&lt;&gt;"",IF(N($F130)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D130="","Sem data prometida",IF($D130&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H130" s="17"/>
-      <c r="I130" s="17"/>
-    </row>
-    <row r="131" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="16"/>
-      <c r="B131" s="17"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="16" t="str">
-        <f aca="false">IF(OR($A131="",$D131="",$E131=""),"",MAX(0,$E131-$D131))</f>
-        <v/>
-      </c>
-      <c r="G131" s="16" t="str">
-        <f aca="false">IF($A131="","",IF($E131&lt;&gt;"",IF(N($F131)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D131="","Sem data prometida",IF($D131&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H131" s="17"/>
-      <c r="I131" s="17"/>
-    </row>
-    <row r="132" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="16"/>
-      <c r="B132" s="17"/>
-      <c r="C132" s="15"/>
-      <c r="D132" s="15"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="16" t="str">
-        <f aca="false">IF(OR($A132="",$D132="",$E132=""),"",MAX(0,$E132-$D132))</f>
-        <v/>
-      </c>
-      <c r="G132" s="16" t="str">
-        <f aca="false">IF($A132="","",IF($E132&lt;&gt;"",IF(N($F132)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D132="","Sem data prometida",IF($D132&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H132" s="17"/>
-      <c r="I132" s="17"/>
-    </row>
-    <row r="133" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="16"/>
-      <c r="B133" s="17"/>
-      <c r="C133" s="15"/>
-      <c r="D133" s="15"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="16" t="str">
-        <f aca="false">IF(OR($A133="",$D133="",$E133=""),"",MAX(0,$E133-$D133))</f>
-        <v/>
-      </c>
-      <c r="G133" s="16" t="str">
-        <f aca="false">IF($A133="","",IF($E133&lt;&gt;"",IF(N($F133)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D133="","Sem data prometida",IF($D133&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H133" s="17"/>
-      <c r="I133" s="17"/>
-    </row>
-    <row r="134" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="16"/>
-      <c r="B134" s="17"/>
-      <c r="C134" s="15"/>
-      <c r="D134" s="15"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="16" t="str">
-        <f aca="false">IF(OR($A134="",$D134="",$E134=""),"",MAX(0,$E134-$D134))</f>
-        <v/>
-      </c>
-      <c r="G134" s="16" t="str">
-        <f aca="false">IF($A134="","",IF($E134&lt;&gt;"",IF(N($F134)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D134="","Sem data prometida",IF($D134&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H134" s="17"/>
-      <c r="I134" s="17"/>
-    </row>
-    <row r="135" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="16"/>
-      <c r="B135" s="17"/>
-      <c r="C135" s="15"/>
-      <c r="D135" s="15"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="16" t="str">
-        <f aca="false">IF(OR($A135="",$D135="",$E135=""),"",MAX(0,$E135-$D135))</f>
-        <v/>
-      </c>
-      <c r="G135" s="16" t="str">
-        <f aca="false">IF($A135="","",IF($E135&lt;&gt;"",IF(N($F135)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D135="","Sem data prometida",IF($D135&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H135" s="17"/>
-      <c r="I135" s="17"/>
-    </row>
-    <row r="136" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="16"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="15"/>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="16" t="str">
-        <f aca="false">IF(OR($A136="",$D136="",$E136=""),"",MAX(0,$E136-$D136))</f>
-        <v/>
-      </c>
-      <c r="G136" s="16" t="str">
-        <f aca="false">IF($A136="","",IF($E136&lt;&gt;"",IF(N($F136)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D136="","Sem data prometida",IF($D136&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H136" s="17"/>
-      <c r="I136" s="17"/>
-    </row>
-    <row r="137" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="16"/>
-      <c r="B137" s="17"/>
-      <c r="C137" s="15"/>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="16" t="str">
-        <f aca="false">IF(OR($A137="",$D137="",$E137=""),"",MAX(0,$E137-$D137))</f>
-        <v/>
-      </c>
-      <c r="G137" s="16" t="str">
-        <f aca="false">IF($A137="","",IF($E137&lt;&gt;"",IF(N($F137)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D137="","Sem data prometida",IF($D137&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H137" s="17"/>
-      <c r="I137" s="17"/>
-    </row>
-    <row r="138" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="16"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="15"/>
-      <c r="D138" s="15"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="16" t="str">
-        <f aca="false">IF(OR($A138="",$D138="",$E138=""),"",MAX(0,$E138-$D138))</f>
-        <v/>
-      </c>
-      <c r="G138" s="16" t="str">
-        <f aca="false">IF($A138="","",IF($E138&lt;&gt;"",IF(N($F138)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D138="","Sem data prometida",IF($D138&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H138" s="17"/>
-      <c r="I138" s="17"/>
-    </row>
-    <row r="139" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="16"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="15"/>
-      <c r="D139" s="15"/>
-      <c r="E139" s="15"/>
-      <c r="F139" s="16" t="str">
-        <f aca="false">IF(OR($A139="",$D139="",$E139=""),"",MAX(0,$E139-$D139))</f>
-        <v/>
-      </c>
-      <c r="G139" s="16" t="str">
-        <f aca="false">IF($A139="","",IF($E139&lt;&gt;"",IF(N($F139)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D139="","Sem data prometida",IF($D139&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H139" s="17"/>
-      <c r="I139" s="17"/>
-    </row>
-    <row r="140" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="16"/>
-      <c r="B140" s="17"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15"/>
-      <c r="E140" s="15"/>
-      <c r="F140" s="16" t="str">
-        <f aca="false">IF(OR($A140="",$D140="",$E140=""),"",MAX(0,$E140-$D140))</f>
-        <v/>
-      </c>
-      <c r="G140" s="16" t="str">
-        <f aca="false">IF($A140="","",IF($E140&lt;&gt;"",IF(N($F140)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D140="","Sem data prometida",IF($D140&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H140" s="17"/>
-      <c r="I140" s="17"/>
-    </row>
-    <row r="141" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="16"/>
-      <c r="B141" s="17"/>
-      <c r="C141" s="15"/>
-      <c r="D141" s="15"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="16" t="str">
-        <f aca="false">IF(OR($A141="",$D141="",$E141=""),"",MAX(0,$E141-$D141))</f>
-        <v/>
-      </c>
-      <c r="G141" s="16" t="str">
-        <f aca="false">IF($A141="","",IF($E141&lt;&gt;"",IF(N($F141)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D141="","Sem data prometida",IF($D141&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H141" s="17"/>
-      <c r="I141" s="17"/>
-    </row>
-    <row r="142" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="16"/>
-      <c r="B142" s="17"/>
-      <c r="C142" s="15"/>
-      <c r="D142" s="15"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="16" t="str">
-        <f aca="false">IF(OR($A142="",$D142="",$E142=""),"",MAX(0,$E142-$D142))</f>
-        <v/>
-      </c>
-      <c r="G142" s="16" t="str">
-        <f aca="false">IF($A142="","",IF($E142&lt;&gt;"",IF(N($F142)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D142="","Sem data prometida",IF($D142&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H142" s="17"/>
-      <c r="I142" s="17"/>
-    </row>
-    <row r="143" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="16"/>
-      <c r="B143" s="17"/>
-      <c r="C143" s="15"/>
-      <c r="D143" s="15"/>
-      <c r="E143" s="15"/>
-      <c r="F143" s="16" t="str">
-        <f aca="false">IF(OR($A143="",$D143="",$E143=""),"",MAX(0,$E143-$D143))</f>
-        <v/>
-      </c>
-      <c r="G143" s="16" t="str">
-        <f aca="false">IF($A143="","",IF($E143&lt;&gt;"",IF(N($F143)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D143="","Sem data prometida",IF($D143&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H143" s="17"/>
-      <c r="I143" s="17"/>
-    </row>
-    <row r="144" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="16"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="15"/>
-      <c r="D144" s="15"/>
-      <c r="E144" s="15"/>
-      <c r="F144" s="16" t="str">
-        <f aca="false">IF(OR($A144="",$D144="",$E144=""),"",MAX(0,$E144-$D144))</f>
-        <v/>
-      </c>
-      <c r="G144" s="16" t="str">
-        <f aca="false">IF($A144="","",IF($E144&lt;&gt;"",IF(N($F144)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D144="","Sem data prometida",IF($D144&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H144" s="17"/>
-      <c r="I144" s="17"/>
-    </row>
-    <row r="145" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="16"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="15"/>
-      <c r="D145" s="15"/>
-      <c r="E145" s="15"/>
-      <c r="F145" s="16" t="str">
-        <f aca="false">IF(OR($A145="",$D145="",$E145=""),"",MAX(0,$E145-$D145))</f>
-        <v/>
-      </c>
-      <c r="G145" s="16" t="str">
-        <f aca="false">IF($A145="","",IF($E145&lt;&gt;"",IF(N($F145)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D145="","Sem data prometida",IF($D145&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H145" s="17"/>
-      <c r="I145" s="17"/>
-    </row>
-    <row r="146" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="16"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="15"/>
-      <c r="D146" s="15"/>
-      <c r="E146" s="15"/>
-      <c r="F146" s="16" t="str">
-        <f aca="false">IF(OR($A146="",$D146="",$E146=""),"",MAX(0,$E146-$D146))</f>
-        <v/>
-      </c>
-      <c r="G146" s="16" t="str">
-        <f aca="false">IF($A146="","",IF($E146&lt;&gt;"",IF(N($F146)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D146="","Sem data prometida",IF($D146&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H146" s="17"/>
-      <c r="I146" s="17"/>
-    </row>
-    <row r="147" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="16"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="15"/>
-      <c r="D147" s="15"/>
-      <c r="E147" s="15"/>
-      <c r="F147" s="16" t="str">
-        <f aca="false">IF(OR($A147="",$D147="",$E147=""),"",MAX(0,$E147-$D147))</f>
-        <v/>
-      </c>
-      <c r="G147" s="16" t="str">
-        <f aca="false">IF($A147="","",IF($E147&lt;&gt;"",IF(N($F147)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D147="","Sem data prometida",IF($D147&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H147" s="17"/>
-      <c r="I147" s="17"/>
-    </row>
-    <row r="148" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="16"/>
-      <c r="B148" s="17"/>
-      <c r="C148" s="15"/>
-      <c r="D148" s="15"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="16" t="str">
-        <f aca="false">IF(OR($A148="",$D148="",$E148=""),"",MAX(0,$E148-$D148))</f>
-        <v/>
-      </c>
-      <c r="G148" s="16" t="str">
-        <f aca="false">IF($A148="","",IF($E148&lt;&gt;"",IF(N($F148)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D148="","Sem data prometida",IF($D148&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H148" s="17"/>
-      <c r="I148" s="17"/>
-    </row>
-    <row r="149" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="16"/>
-      <c r="B149" s="17"/>
-      <c r="C149" s="15"/>
-      <c r="D149" s="15"/>
-      <c r="E149" s="15"/>
-      <c r="F149" s="16" t="str">
-        <f aca="false">IF(OR($A149="",$D149="",$E149=""),"",MAX(0,$E149-$D149))</f>
-        <v/>
-      </c>
-      <c r="G149" s="16" t="str">
-        <f aca="false">IF($A149="","",IF($E149&lt;&gt;"",IF(N($F149)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D149="","Sem data prometida",IF($D149&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H149" s="17"/>
-      <c r="I149" s="17"/>
-    </row>
-    <row r="150" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="16"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="15"/>
-      <c r="D150" s="15"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="16" t="str">
-        <f aca="false">IF(OR($A150="",$D150="",$E150=""),"",MAX(0,$E150-$D150))</f>
-        <v/>
-      </c>
-      <c r="G150" s="16" t="str">
-        <f aca="false">IF($A150="","",IF($E150&lt;&gt;"",IF(N($F150)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D150="","Sem data prometida",IF($D150&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H150" s="17"/>
-      <c r="I150" s="17"/>
-    </row>
-    <row r="151" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="16"/>
-      <c r="B151" s="17"/>
-      <c r="C151" s="15"/>
-      <c r="D151" s="15"/>
-      <c r="E151" s="15"/>
-      <c r="F151" s="16" t="str">
-        <f aca="false">IF(OR($A151="",$D151="",$E151=""),"",MAX(0,$E151-$D151))</f>
-        <v/>
-      </c>
-      <c r="G151" s="16" t="str">
-        <f aca="false">IF($A151="","",IF($E151&lt;&gt;"",IF(N($F151)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D151="","Sem data prometida",IF($D151&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H151" s="17"/>
-      <c r="I151" s="17"/>
-    </row>
-    <row r="152" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="16"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="15"/>
-      <c r="D152" s="15"/>
-      <c r="E152" s="15"/>
-      <c r="F152" s="16" t="str">
-        <f aca="false">IF(OR($A152="",$D152="",$E152=""),"",MAX(0,$E152-$D152))</f>
-        <v/>
-      </c>
-      <c r="G152" s="16" t="str">
-        <f aca="false">IF($A152="","",IF($E152&lt;&gt;"",IF(N($F152)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D152="","Sem data prometida",IF($D152&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H152" s="17"/>
-      <c r="I152" s="17"/>
-    </row>
-    <row r="153" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="16"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15"/>
-      <c r="E153" s="15"/>
-      <c r="F153" s="16" t="str">
-        <f aca="false">IF(OR($A153="",$D153="",$E153=""),"",MAX(0,$E153-$D153))</f>
-        <v/>
-      </c>
-      <c r="G153" s="16" t="str">
-        <f aca="false">IF($A153="","",IF($E153&lt;&gt;"",IF(N($F153)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D153="","Sem data prometida",IF($D153&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H153" s="17"/>
-      <c r="I153" s="17"/>
-    </row>
-    <row r="154" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="16"/>
-      <c r="B154" s="17"/>
-      <c r="C154" s="15"/>
-      <c r="D154" s="15"/>
-      <c r="E154" s="15"/>
-      <c r="F154" s="16" t="str">
-        <f aca="false">IF(OR($A154="",$D154="",$E154=""),"",MAX(0,$E154-$D154))</f>
-        <v/>
-      </c>
-      <c r="G154" s="16" t="str">
-        <f aca="false">IF($A154="","",IF($E154&lt;&gt;"",IF(N($F154)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D154="","Sem data prometida",IF($D154&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H154" s="17"/>
-      <c r="I154" s="17"/>
-    </row>
-    <row r="155" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="16"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="15"/>
-      <c r="D155" s="15"/>
-      <c r="E155" s="15"/>
-      <c r="F155" s="16" t="str">
-        <f aca="false">IF(OR($A155="",$D155="",$E155=""),"",MAX(0,$E155-$D155))</f>
-        <v/>
-      </c>
-      <c r="G155" s="16" t="str">
-        <f aca="false">IF($A155="","",IF($E155&lt;&gt;"",IF(N($F155)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D155="","Sem data prometida",IF($D155&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H155" s="17"/>
-      <c r="I155" s="17"/>
-    </row>
-    <row r="156" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="16"/>
-      <c r="B156" s="17"/>
-      <c r="C156" s="15"/>
-      <c r="D156" s="15"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="16" t="str">
-        <f aca="false">IF(OR($A156="",$D156="",$E156=""),"",MAX(0,$E156-$D156))</f>
-        <v/>
-      </c>
-      <c r="G156" s="16" t="str">
-        <f aca="false">IF($A156="","",IF($E156&lt;&gt;"",IF(N($F156)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D156="","Sem data prometida",IF($D156&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H156" s="17"/>
-      <c r="I156" s="17"/>
-    </row>
-    <row r="157" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="16"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="15"/>
-      <c r="D157" s="15"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="16" t="str">
-        <f aca="false">IF(OR($A157="",$D157="",$E157=""),"",MAX(0,$E157-$D157))</f>
-        <v/>
-      </c>
-      <c r="G157" s="16" t="str">
-        <f aca="false">IF($A157="","",IF($E157&lt;&gt;"",IF(N($F157)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D157="","Sem data prometida",IF($D157&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H157" s="17"/>
-      <c r="I157" s="17"/>
-    </row>
-    <row r="158" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="16"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="15"/>
-      <c r="D158" s="15"/>
-      <c r="E158" s="15"/>
-      <c r="F158" s="16" t="str">
-        <f aca="false">IF(OR($A158="",$D158="",$E158=""),"",MAX(0,$E158-$D158))</f>
-        <v/>
-      </c>
-      <c r="G158" s="16" t="str">
-        <f aca="false">IF($A158="","",IF($E158&lt;&gt;"",IF(N($F158)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D158="","Sem data prometida",IF($D158&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H158" s="17"/>
-      <c r="I158" s="17"/>
-    </row>
-    <row r="159" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="16"/>
-      <c r="B159" s="17"/>
-      <c r="C159" s="15"/>
-      <c r="D159" s="15"/>
-      <c r="E159" s="15"/>
-      <c r="F159" s="16" t="str">
-        <f aca="false">IF(OR($A159="",$D159="",$E159=""),"",MAX(0,$E159-$D159))</f>
-        <v/>
-      </c>
-      <c r="G159" s="16" t="str">
-        <f aca="false">IF($A159="","",IF($E159&lt;&gt;"",IF(N($F159)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D159="","Sem data prometida",IF($D159&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-    </row>
-    <row r="160" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="16"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="16" t="str">
-        <f aca="false">IF(OR($A160="",$D160="",$E160=""),"",MAX(0,$E160-$D160))</f>
-        <v/>
-      </c>
-      <c r="G160" s="16" t="str">
-        <f aca="false">IF($A160="","",IF($E160&lt;&gt;"",IF(N($F160)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D160="","Sem data prometida",IF($D160&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H160" s="17"/>
-      <c r="I160" s="17"/>
-    </row>
-    <row r="161" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="16"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="15"/>
-      <c r="D161" s="15"/>
-      <c r="E161" s="15"/>
-      <c r="F161" s="16" t="str">
-        <f aca="false">IF(OR($A161="",$D161="",$E161=""),"",MAX(0,$E161-$D161))</f>
-        <v/>
-      </c>
-      <c r="G161" s="16" t="str">
-        <f aca="false">IF($A161="","",IF($E161&lt;&gt;"",IF(N($F161)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D161="","Sem data prometida",IF($D161&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H161" s="17"/>
-      <c r="I161" s="17"/>
-    </row>
-    <row r="162" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="16"/>
-      <c r="B162" s="17"/>
-      <c r="C162" s="15"/>
-      <c r="D162" s="15"/>
-      <c r="E162" s="15"/>
-      <c r="F162" s="16" t="str">
-        <f aca="false">IF(OR($A162="",$D162="",$E162=""),"",MAX(0,$E162-$D162))</f>
-        <v/>
-      </c>
-      <c r="G162" s="16" t="str">
-        <f aca="false">IF($A162="","",IF($E162&lt;&gt;"",IF(N($F162)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D162="","Sem data prometida",IF($D162&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H162" s="17"/>
-      <c r="I162" s="17"/>
-    </row>
-    <row r="163" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="16"/>
-      <c r="B163" s="17"/>
-      <c r="C163" s="15"/>
-      <c r="D163" s="15"/>
-      <c r="E163" s="15"/>
-      <c r="F163" s="16" t="str">
-        <f aca="false">IF(OR($A163="",$D163="",$E163=""),"",MAX(0,$E163-$D163))</f>
-        <v/>
-      </c>
-      <c r="G163" s="16" t="str">
-        <f aca="false">IF($A163="","",IF($E163&lt;&gt;"",IF(N($F163)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D163="","Sem data prometida",IF($D163&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H163" s="17"/>
-      <c r="I163" s="17"/>
-    </row>
-    <row r="164" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="16"/>
-      <c r="B164" s="17"/>
-      <c r="C164" s="15"/>
-      <c r="D164" s="15"/>
-      <c r="E164" s="15"/>
-      <c r="F164" s="16" t="str">
-        <f aca="false">IF(OR($A164="",$D164="",$E164=""),"",MAX(0,$E164-$D164))</f>
-        <v/>
-      </c>
-      <c r="G164" s="16" t="str">
-        <f aca="false">IF($A164="","",IF($E164&lt;&gt;"",IF(N($F164)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D164="","Sem data prometida",IF($D164&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H164" s="17"/>
-      <c r="I164" s="17"/>
-    </row>
-    <row r="165" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="16"/>
-      <c r="B165" s="17"/>
-      <c r="C165" s="15"/>
-      <c r="D165" s="15"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="16" t="str">
-        <f aca="false">IF(OR($A165="",$D165="",$E165=""),"",MAX(0,$E165-$D165))</f>
-        <v/>
-      </c>
-      <c r="G165" s="16" t="str">
-        <f aca="false">IF($A165="","",IF($E165&lt;&gt;"",IF(N($F165)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D165="","Sem data prometida",IF($D165&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H165" s="17"/>
-      <c r="I165" s="17"/>
-    </row>
-    <row r="166" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="16"/>
-      <c r="B166" s="17"/>
-      <c r="C166" s="15"/>
-      <c r="D166" s="15"/>
-      <c r="E166" s="15"/>
-      <c r="F166" s="16" t="str">
-        <f aca="false">IF(OR($A166="",$D166="",$E166=""),"",MAX(0,$E166-$D166))</f>
-        <v/>
-      </c>
-      <c r="G166" s="16" t="str">
-        <f aca="false">IF($A166="","",IF($E166&lt;&gt;"",IF(N($F166)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D166="","Sem data prometida",IF($D166&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H166" s="17"/>
-      <c r="I166" s="17"/>
-    </row>
-    <row r="167" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="16"/>
-      <c r="B167" s="17"/>
-      <c r="C167" s="15"/>
-      <c r="D167" s="15"/>
-      <c r="E167" s="15"/>
-      <c r="F167" s="16" t="str">
-        <f aca="false">IF(OR($A167="",$D167="",$E167=""),"",MAX(0,$E167-$D167))</f>
-        <v/>
-      </c>
-      <c r="G167" s="16" t="str">
-        <f aca="false">IF($A167="","",IF($E167&lt;&gt;"",IF(N($F167)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D167="","Sem data prometida",IF($D167&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H167" s="17"/>
-      <c r="I167" s="17"/>
-    </row>
-    <row r="168" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="16"/>
-      <c r="B168" s="17"/>
-      <c r="C168" s="15"/>
-      <c r="D168" s="15"/>
-      <c r="E168" s="15"/>
-      <c r="F168" s="16" t="str">
-        <f aca="false">IF(OR($A168="",$D168="",$E168=""),"",MAX(0,$E168-$D168))</f>
-        <v/>
-      </c>
-      <c r="G168" s="16" t="str">
-        <f aca="false">IF($A168="","",IF($E168&lt;&gt;"",IF(N($F168)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D168="","Sem data prometida",IF($D168&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H168" s="17"/>
-      <c r="I168" s="17"/>
-    </row>
-    <row r="169" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="16"/>
-      <c r="B169" s="17"/>
-      <c r="C169" s="15"/>
-      <c r="D169" s="15"/>
-      <c r="E169" s="15"/>
-      <c r="F169" s="16" t="str">
-        <f aca="false">IF(OR($A169="",$D169="",$E169=""),"",MAX(0,$E169-$D169))</f>
-        <v/>
-      </c>
-      <c r="G169" s="16" t="str">
-        <f aca="false">IF($A169="","",IF($E169&lt;&gt;"",IF(N($F169)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D169="","Sem data prometida",IF($D169&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H169" s="17"/>
-      <c r="I169" s="17"/>
-    </row>
-    <row r="170" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="16"/>
-      <c r="B170" s="17"/>
-      <c r="C170" s="15"/>
-      <c r="D170" s="15"/>
-      <c r="E170" s="15"/>
-      <c r="F170" s="16" t="str">
-        <f aca="false">IF(OR($A170="",$D170="",$E170=""),"",MAX(0,$E170-$D170))</f>
-        <v/>
-      </c>
-      <c r="G170" s="16" t="str">
-        <f aca="false">IF($A170="","",IF($E170&lt;&gt;"",IF(N($F170)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D170="","Sem data prometida",IF($D170&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H170" s="17"/>
-      <c r="I170" s="17"/>
-    </row>
-    <row r="171" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="16"/>
-      <c r="B171" s="17"/>
-      <c r="C171" s="15"/>
-      <c r="D171" s="15"/>
-      <c r="E171" s="15"/>
-      <c r="F171" s="16" t="str">
-        <f aca="false">IF(OR($A171="",$D171="",$E171=""),"",MAX(0,$E171-$D171))</f>
-        <v/>
-      </c>
-      <c r="G171" s="16" t="str">
-        <f aca="false">IF($A171="","",IF($E171&lt;&gt;"",IF(N($F171)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D171="","Sem data prometida",IF($D171&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H171" s="17"/>
-      <c r="I171" s="17"/>
-    </row>
-    <row r="172" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="16"/>
-      <c r="B172" s="17"/>
-      <c r="C172" s="15"/>
-      <c r="D172" s="15"/>
-      <c r="E172" s="15"/>
-      <c r="F172" s="16" t="str">
-        <f aca="false">IF(OR($A172="",$D172="",$E172=""),"",MAX(0,$E172-$D172))</f>
-        <v/>
-      </c>
-      <c r="G172" s="16" t="str">
-        <f aca="false">IF($A172="","",IF($E172&lt;&gt;"",IF(N($F172)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D172="","Sem data prometida",IF($D172&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H172" s="17"/>
-      <c r="I172" s="17"/>
-    </row>
-    <row r="173" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="16"/>
-      <c r="B173" s="17"/>
-      <c r="C173" s="15"/>
-      <c r="D173" s="15"/>
-      <c r="E173" s="15"/>
-      <c r="F173" s="16" t="str">
-        <f aca="false">IF(OR($A173="",$D173="",$E173=""),"",MAX(0,$E173-$D173))</f>
-        <v/>
-      </c>
-      <c r="G173" s="16" t="str">
-        <f aca="false">IF($A173="","",IF($E173&lt;&gt;"",IF(N($F173)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D173="","Sem data prometida",IF($D173&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H173" s="17"/>
-      <c r="I173" s="17"/>
-    </row>
-    <row r="174" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="16"/>
-      <c r="B174" s="17"/>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="16" t="str">
-        <f aca="false">IF(OR($A174="",$D174="",$E174=""),"",MAX(0,$E174-$D174))</f>
-        <v/>
-      </c>
-      <c r="G174" s="16" t="str">
-        <f aca="false">IF($A174="","",IF($E174&lt;&gt;"",IF(N($F174)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D174="","Sem data prometida",IF($D174&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H174" s="17"/>
-      <c r="I174" s="17"/>
-    </row>
-    <row r="175" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="16"/>
-      <c r="B175" s="17"/>
-      <c r="C175" s="15"/>
-      <c r="D175" s="15"/>
-      <c r="E175" s="15"/>
-      <c r="F175" s="16" t="str">
-        <f aca="false">IF(OR($A175="",$D175="",$E175=""),"",MAX(0,$E175-$D175))</f>
-        <v/>
-      </c>
-      <c r="G175" s="16" t="str">
-        <f aca="false">IF($A175="","",IF($E175&lt;&gt;"",IF(N($F175)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D175="","Sem data prometida",IF($D175&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H175" s="17"/>
-      <c r="I175" s="17"/>
-    </row>
-    <row r="176" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="16"/>
-      <c r="B176" s="17"/>
-      <c r="C176" s="15"/>
-      <c r="D176" s="15"/>
-      <c r="E176" s="15"/>
-      <c r="F176" s="16" t="str">
-        <f aca="false">IF(OR($A176="",$D176="",$E176=""),"",MAX(0,$E176-$D176))</f>
-        <v/>
-      </c>
-      <c r="G176" s="16" t="str">
-        <f aca="false">IF($A176="","",IF($E176&lt;&gt;"",IF(N($F176)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D176="","Sem data prometida",IF($D176&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H176" s="17"/>
-      <c r="I176" s="17"/>
-    </row>
-    <row r="177" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="16"/>
-      <c r="B177" s="17"/>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="16" t="str">
-        <f aca="false">IF(OR($A177="",$D177="",$E177=""),"",MAX(0,$E177-$D177))</f>
-        <v/>
-      </c>
-      <c r="G177" s="16" t="str">
-        <f aca="false">IF($A177="","",IF($E177&lt;&gt;"",IF(N($F177)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D177="","Sem data prometida",IF($D177&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H177" s="17"/>
-      <c r="I177" s="17"/>
-    </row>
-    <row r="178" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="16"/>
-      <c r="B178" s="17"/>
-      <c r="C178" s="15"/>
-      <c r="D178" s="15"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="16" t="str">
-        <f aca="false">IF(OR($A178="",$D178="",$E178=""),"",MAX(0,$E178-$D178))</f>
-        <v/>
-      </c>
-      <c r="G178" s="16" t="str">
-        <f aca="false">IF($A178="","",IF($E178&lt;&gt;"",IF(N($F178)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D178="","Sem data prometida",IF($D178&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H178" s="17"/>
-      <c r="I178" s="17"/>
-    </row>
-    <row r="179" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="16"/>
-      <c r="B179" s="17"/>
-      <c r="C179" s="15"/>
-      <c r="D179" s="15"/>
-      <c r="E179" s="15"/>
-      <c r="F179" s="16" t="str">
-        <f aca="false">IF(OR($A179="",$D179="",$E179=""),"",MAX(0,$E179-$D179))</f>
-        <v/>
-      </c>
-      <c r="G179" s="16" t="str">
-        <f aca="false">IF($A179="","",IF($E179&lt;&gt;"",IF(N($F179)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D179="","Sem data prometida",IF($D179&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H179" s="17"/>
-      <c r="I179" s="17"/>
-    </row>
-    <row r="180" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="16"/>
-      <c r="B180" s="17"/>
-      <c r="C180" s="15"/>
-      <c r="D180" s="15"/>
-      <c r="E180" s="15"/>
-      <c r="F180" s="16" t="str">
-        <f aca="false">IF(OR($A180="",$D180="",$E180=""),"",MAX(0,$E180-$D180))</f>
-        <v/>
-      </c>
-      <c r="G180" s="16" t="str">
-        <f aca="false">IF($A180="","",IF($E180&lt;&gt;"",IF(N($F180)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D180="","Sem data prometida",IF($D180&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H180" s="17"/>
-      <c r="I180" s="17"/>
-    </row>
-    <row r="181" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="16"/>
-      <c r="B181" s="17"/>
-      <c r="C181" s="15"/>
-      <c r="D181" s="15"/>
-      <c r="E181" s="15"/>
-      <c r="F181" s="16" t="str">
-        <f aca="false">IF(OR($A181="",$D181="",$E181=""),"",MAX(0,$E181-$D181))</f>
-        <v/>
-      </c>
-      <c r="G181" s="16" t="str">
-        <f aca="false">IF($A181="","",IF($E181&lt;&gt;"",IF(N($F181)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D181="","Sem data prometida",IF($D181&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H181" s="17"/>
-      <c r="I181" s="17"/>
-    </row>
-    <row r="182" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="16"/>
-      <c r="B182" s="17"/>
-      <c r="C182" s="15"/>
-      <c r="D182" s="15"/>
-      <c r="E182" s="15"/>
-      <c r="F182" s="16" t="str">
-        <f aca="false">IF(OR($A182="",$D182="",$E182=""),"",MAX(0,$E182-$D182))</f>
-        <v/>
-      </c>
-      <c r="G182" s="16" t="str">
-        <f aca="false">IF($A182="","",IF($E182&lt;&gt;"",IF(N($F182)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D182="","Sem data prometida",IF($D182&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H182" s="17"/>
-      <c r="I182" s="17"/>
-    </row>
-    <row r="183" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="16"/>
-      <c r="B183" s="17"/>
-      <c r="C183" s="15"/>
-      <c r="D183" s="15"/>
-      <c r="E183" s="15"/>
-      <c r="F183" s="16" t="str">
-        <f aca="false">IF(OR($A183="",$D183="",$E183=""),"",MAX(0,$E183-$D183))</f>
-        <v/>
-      </c>
-      <c r="G183" s="16" t="str">
-        <f aca="false">IF($A183="","",IF($E183&lt;&gt;"",IF(N($F183)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D183="","Sem data prometida",IF($D183&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H183" s="17"/>
-      <c r="I183" s="17"/>
-    </row>
-    <row r="184" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="16"/>
-      <c r="B184" s="17"/>
-      <c r="C184" s="15"/>
-      <c r="D184" s="15"/>
-      <c r="E184" s="15"/>
-      <c r="F184" s="16" t="str">
-        <f aca="false">IF(OR($A184="",$D184="",$E184=""),"",MAX(0,$E184-$D184))</f>
-        <v/>
-      </c>
-      <c r="G184" s="16" t="str">
-        <f aca="false">IF($A184="","",IF($E184&lt;&gt;"",IF(N($F184)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D184="","Sem data prometida",IF($D184&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H184" s="17"/>
-      <c r="I184" s="17"/>
-    </row>
-    <row r="185" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="16"/>
-      <c r="B185" s="17"/>
-      <c r="C185" s="15"/>
-      <c r="D185" s="15"/>
-      <c r="E185" s="15"/>
-      <c r="F185" s="16" t="str">
-        <f aca="false">IF(OR($A185="",$D185="",$E185=""),"",MAX(0,$E185-$D185))</f>
-        <v/>
-      </c>
-      <c r="G185" s="16" t="str">
-        <f aca="false">IF($A185="","",IF($E185&lt;&gt;"",IF(N($F185)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D185="","Sem data prometida",IF($D185&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H185" s="17"/>
-      <c r="I185" s="17"/>
-    </row>
-    <row r="186" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="16"/>
-      <c r="B186" s="17"/>
-      <c r="C186" s="15"/>
-      <c r="D186" s="15"/>
-      <c r="E186" s="15"/>
-      <c r="F186" s="16" t="str">
-        <f aca="false">IF(OR($A186="",$D186="",$E186=""),"",MAX(0,$E186-$D186))</f>
-        <v/>
-      </c>
-      <c r="G186" s="16" t="str">
-        <f aca="false">IF($A186="","",IF($E186&lt;&gt;"",IF(N($F186)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D186="","Sem data prometida",IF($D186&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H186" s="17"/>
-      <c r="I186" s="17"/>
-    </row>
-    <row r="187" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="16"/>
-      <c r="B187" s="17"/>
-      <c r="C187" s="15"/>
-      <c r="D187" s="15"/>
-      <c r="E187" s="15"/>
-      <c r="F187" s="16" t="str">
-        <f aca="false">IF(OR($A187="",$D187="",$E187=""),"",MAX(0,$E187-$D187))</f>
-        <v/>
-      </c>
-      <c r="G187" s="16" t="str">
-        <f aca="false">IF($A187="","",IF($E187&lt;&gt;"",IF(N($F187)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D187="","Sem data prometida",IF($D187&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H187" s="17"/>
-      <c r="I187" s="17"/>
-    </row>
-    <row r="188" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="16"/>
-      <c r="B188" s="17"/>
-      <c r="C188" s="15"/>
-      <c r="D188" s="15"/>
-      <c r="E188" s="15"/>
-      <c r="F188" s="16" t="str">
-        <f aca="false">IF(OR($A188="",$D188="",$E188=""),"",MAX(0,$E188-$D188))</f>
-        <v/>
-      </c>
-      <c r="G188" s="16" t="str">
-        <f aca="false">IF($A188="","",IF($E188&lt;&gt;"",IF(N($F188)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D188="","Sem data prometida",IF($D188&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H188" s="17"/>
-      <c r="I188" s="17"/>
-    </row>
-    <row r="189" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="16"/>
-      <c r="B189" s="17"/>
-      <c r="C189" s="15"/>
-      <c r="D189" s="15"/>
-      <c r="E189" s="15"/>
-      <c r="F189" s="16" t="str">
-        <f aca="false">IF(OR($A189="",$D189="",$E189=""),"",MAX(0,$E189-$D189))</f>
-        <v/>
-      </c>
-      <c r="G189" s="16" t="str">
-        <f aca="false">IF($A189="","",IF($E189&lt;&gt;"",IF(N($F189)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D189="","Sem data prometida",IF($D189&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H189" s="17"/>
-      <c r="I189" s="17"/>
-    </row>
-    <row r="190" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="16"/>
-      <c r="B190" s="17"/>
-      <c r="C190" s="15"/>
-      <c r="D190" s="15"/>
-      <c r="E190" s="15"/>
-      <c r="F190" s="16" t="str">
-        <f aca="false">IF(OR($A190="",$D190="",$E190=""),"",MAX(0,$E190-$D190))</f>
-        <v/>
-      </c>
-      <c r="G190" s="16" t="str">
-        <f aca="false">IF($A190="","",IF($E190&lt;&gt;"",IF(N($F190)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D190="","Sem data prometida",IF($D190&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H190" s="17"/>
-      <c r="I190" s="17"/>
-    </row>
-    <row r="191" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="16"/>
-      <c r="B191" s="17"/>
-      <c r="C191" s="15"/>
-      <c r="D191" s="15"/>
-      <c r="E191" s="15"/>
-      <c r="F191" s="16" t="str">
-        <f aca="false">IF(OR($A191="",$D191="",$E191=""),"",MAX(0,$E191-$D191))</f>
-        <v/>
-      </c>
-      <c r="G191" s="16" t="str">
-        <f aca="false">IF($A191="","",IF($E191&lt;&gt;"",IF(N($F191)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D191="","Sem data prometida",IF($D191&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H191" s="17"/>
-      <c r="I191" s="17"/>
-    </row>
-    <row r="192" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="16"/>
-      <c r="B192" s="17"/>
-      <c r="C192" s="15"/>
-      <c r="D192" s="15"/>
-      <c r="E192" s="15"/>
-      <c r="F192" s="16" t="str">
-        <f aca="false">IF(OR($A192="",$D192="",$E192=""),"",MAX(0,$E192-$D192))</f>
-        <v/>
-      </c>
-      <c r="G192" s="16" t="str">
-        <f aca="false">IF($A192="","",IF($E192&lt;&gt;"",IF(N($F192)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D192="","Sem data prometida",IF($D192&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H192" s="17"/>
-      <c r="I192" s="17"/>
-    </row>
-    <row r="193" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="16"/>
-      <c r="B193" s="17"/>
-      <c r="C193" s="15"/>
-      <c r="D193" s="15"/>
-      <c r="E193" s="15"/>
-      <c r="F193" s="16" t="str">
-        <f aca="false">IF(OR($A193="",$D193="",$E193=""),"",MAX(0,$E193-$D193))</f>
-        <v/>
-      </c>
-      <c r="G193" s="16" t="str">
-        <f aca="false">IF($A193="","",IF($E193&lt;&gt;"",IF(N($F193)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D193="","Sem data prometida",IF($D193&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H193" s="17"/>
-      <c r="I193" s="17"/>
-    </row>
-    <row r="194" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="16"/>
-      <c r="B194" s="17"/>
-      <c r="C194" s="15"/>
-      <c r="D194" s="15"/>
-      <c r="E194" s="15"/>
-      <c r="F194" s="16" t="str">
-        <f aca="false">IF(OR($A194="",$D194="",$E194=""),"",MAX(0,$E194-$D194))</f>
-        <v/>
-      </c>
-      <c r="G194" s="16" t="str">
-        <f aca="false">IF($A194="","",IF($E194&lt;&gt;"",IF(N($F194)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D194="","Sem data prometida",IF($D194&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H194" s="17"/>
-      <c r="I194" s="17"/>
-    </row>
-    <row r="195" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="16"/>
-      <c r="B195" s="17"/>
-      <c r="C195" s="15"/>
-      <c r="D195" s="15"/>
-      <c r="E195" s="15"/>
-      <c r="F195" s="16" t="str">
-        <f aca="false">IF(OR($A195="",$D195="",$E195=""),"",MAX(0,$E195-$D195))</f>
-        <v/>
-      </c>
-      <c r="G195" s="16" t="str">
-        <f aca="false">IF($A195="","",IF($E195&lt;&gt;"",IF(N($F195)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D195="","Sem data prometida",IF($D195&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H195" s="17"/>
-      <c r="I195" s="17"/>
-    </row>
-    <row r="196" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="16"/>
-      <c r="B196" s="17"/>
-      <c r="C196" s="15"/>
-      <c r="D196" s="15"/>
-      <c r="E196" s="15"/>
-      <c r="F196" s="16" t="str">
-        <f aca="false">IF(OR($A196="",$D196="",$E196=""),"",MAX(0,$E196-$D196))</f>
-        <v/>
-      </c>
-      <c r="G196" s="16" t="str">
-        <f aca="false">IF($A196="","",IF($E196&lt;&gt;"",IF(N($F196)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D196="","Sem data prometida",IF($D196&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H196" s="17"/>
-      <c r="I196" s="17"/>
-    </row>
-    <row r="197" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="16"/>
-      <c r="B197" s="17"/>
-      <c r="C197" s="15"/>
-      <c r="D197" s="15"/>
-      <c r="E197" s="15"/>
-      <c r="F197" s="16" t="str">
-        <f aca="false">IF(OR($A197="",$D197="",$E197=""),"",MAX(0,$E197-$D197))</f>
-        <v/>
-      </c>
-      <c r="G197" s="16" t="str">
-        <f aca="false">IF($A197="","",IF($E197&lt;&gt;"",IF(N($F197)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D197="","Sem data prometida",IF($D197&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H197" s="17"/>
-      <c r="I197" s="17"/>
-    </row>
-    <row r="198" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="16"/>
-      <c r="B198" s="17"/>
-      <c r="C198" s="15"/>
-      <c r="D198" s="15"/>
-      <c r="E198" s="15"/>
-      <c r="F198" s="16" t="str">
-        <f aca="false">IF(OR($A198="",$D198="",$E198=""),"",MAX(0,$E198-$D198))</f>
-        <v/>
-      </c>
-      <c r="G198" s="16" t="str">
-        <f aca="false">IF($A198="","",IF($E198&lt;&gt;"",IF(N($F198)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D198="","Sem data prometida",IF($D198&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H198" s="17"/>
-      <c r="I198" s="17"/>
-    </row>
-    <row r="199" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="16"/>
-      <c r="B199" s="17"/>
-      <c r="C199" s="15"/>
-      <c r="D199" s="15"/>
-      <c r="E199" s="15"/>
-      <c r="F199" s="16" t="str">
-        <f aca="false">IF(OR($A199="",$D199="",$E199=""),"",MAX(0,$E199-$D199))</f>
-        <v/>
-      </c>
-      <c r="G199" s="16" t="str">
-        <f aca="false">IF($A199="","",IF($E199&lt;&gt;"",IF(N($F199)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D199="","Sem data prometida",IF($D199&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H199" s="17"/>
-      <c r="I199" s="17"/>
-    </row>
-    <row r="200" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="16"/>
-      <c r="B200" s="17"/>
-      <c r="C200" s="15"/>
-      <c r="D200" s="15"/>
-      <c r="E200" s="15"/>
-      <c r="F200" s="16" t="str">
-        <f aca="false">IF(OR($A200="",$D200="",$E200=""),"",MAX(0,$E200-$D200))</f>
-        <v/>
-      </c>
-      <c r="G200" s="16" t="str">
-        <f aca="false">IF($A200="","",IF($E200&lt;&gt;"",IF(N($F200)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D200="","Sem data prometida",IF($D200&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H200" s="17"/>
-      <c r="I200" s="17"/>
-    </row>
-    <row r="201" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="16"/>
-      <c r="B201" s="17"/>
-      <c r="C201" s="15"/>
-      <c r="D201" s="15"/>
-      <c r="E201" s="15"/>
-      <c r="F201" s="16" t="str">
-        <f aca="false">IF(OR($A201="",$D201="",$E201=""),"",MAX(0,$E201-$D201))</f>
-        <v/>
-      </c>
-      <c r="G201" s="16" t="str">
-        <f aca="false">IF($A201="","",IF($E201&lt;&gt;"",IF(N($F201)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D201="","Sem data prometida",IF($D201&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H201" s="17"/>
-      <c r="I201" s="17"/>
-    </row>
-    <row r="202" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="16"/>
-      <c r="B202" s="17"/>
-      <c r="C202" s="15"/>
-      <c r="D202" s="15"/>
-      <c r="E202" s="15"/>
-      <c r="F202" s="16" t="str">
-        <f aca="false">IF(OR($A202="",$D202="",$E202=""),"",MAX(0,$E202-$D202))</f>
-        <v/>
-      </c>
-      <c r="G202" s="16" t="str">
-        <f aca="false">IF($A202="","",IF($E202&lt;&gt;"",IF(N($F202)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D202="","Sem data prometida",IF($D202&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H202" s="17"/>
-      <c r="I202" s="17"/>
-    </row>
-    <row r="203" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="16"/>
-      <c r="B203" s="17"/>
-      <c r="C203" s="15"/>
-      <c r="D203" s="15"/>
-      <c r="E203" s="15"/>
-      <c r="F203" s="16" t="str">
-        <f aca="false">IF(OR($A203="",$D203="",$E203=""),"",MAX(0,$E203-$D203))</f>
-        <v/>
-      </c>
-      <c r="G203" s="16" t="str">
-        <f aca="false">IF($A203="","",IF($E203&lt;&gt;"",IF(N($F203)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D203="","Sem data prometida",IF($D203&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H203" s="17"/>
-      <c r="I203" s="17"/>
-    </row>
-    <row r="204" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="16"/>
-      <c r="B204" s="17"/>
-      <c r="C204" s="15"/>
-      <c r="D204" s="15"/>
-      <c r="E204" s="15"/>
-      <c r="F204" s="16" t="str">
-        <f aca="false">IF(OR($A204="",$D204="",$E204=""),"",MAX(0,$E204-$D204))</f>
-        <v/>
-      </c>
-      <c r="G204" s="16" t="str">
-        <f aca="false">IF($A204="","",IF($E204&lt;&gt;"",IF(N($F204)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D204="","Sem data prometida",IF($D204&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H204" s="17"/>
-      <c r="I204" s="17"/>
-    </row>
-    <row r="205" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="16"/>
-      <c r="B205" s="17"/>
-      <c r="C205" s="15"/>
-      <c r="D205" s="15"/>
-      <c r="E205" s="15"/>
-      <c r="F205" s="16" t="str">
-        <f aca="false">IF(OR($A205="",$D205="",$E205=""),"",MAX(0,$E205-$D205))</f>
-        <v/>
-      </c>
-      <c r="G205" s="16" t="str">
-        <f aca="false">IF($A205="","",IF($E205&lt;&gt;"",IF(N($F205)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D205="","Sem data prometida",IF($D205&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H205" s="17"/>
-      <c r="I205" s="17"/>
-    </row>
-    <row r="206" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="16"/>
-      <c r="B206" s="17"/>
-      <c r="C206" s="15"/>
-      <c r="D206" s="15"/>
-      <c r="E206" s="15"/>
-      <c r="F206" s="16" t="str">
-        <f aca="false">IF(OR($A206="",$D206="",$E206=""),"",MAX(0,$E206-$D206))</f>
-        <v/>
-      </c>
-      <c r="G206" s="16" t="str">
-        <f aca="false">IF($A206="","",IF($E206&lt;&gt;"",IF(N($F206)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D206="","Sem data prometida",IF($D206&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H206" s="17"/>
-      <c r="I206" s="17"/>
-    </row>
-    <row r="207" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="16"/>
-      <c r="B207" s="17"/>
-      <c r="C207" s="15"/>
-      <c r="D207" s="15"/>
-      <c r="E207" s="15"/>
-      <c r="F207" s="16" t="str">
-        <f aca="false">IF(OR($A207="",$D207="",$E207=""),"",MAX(0,$E207-$D207))</f>
-        <v/>
-      </c>
-      <c r="G207" s="16" t="str">
-        <f aca="false">IF($A207="","",IF($E207&lt;&gt;"",IF(N($F207)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D207="","Sem data prometida",IF($D207&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H207" s="17"/>
-      <c r="I207" s="17"/>
-    </row>
-    <row r="208" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="16"/>
-      <c r="B208" s="17"/>
-      <c r="C208" s="15"/>
-      <c r="D208" s="15"/>
-      <c r="E208" s="15"/>
-      <c r="F208" s="16" t="str">
-        <f aca="false">IF(OR($A208="",$D208="",$E208=""),"",MAX(0,$E208-$D208))</f>
-        <v/>
-      </c>
-      <c r="G208" s="16" t="str">
-        <f aca="false">IF($A208="","",IF($E208&lt;&gt;"",IF(N($F208)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D208="","Sem data prometida",IF($D208&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H208" s="17"/>
-      <c r="I208" s="17"/>
-    </row>
-    <row r="209" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="16"/>
-      <c r="B209" s="17"/>
-      <c r="C209" s="15"/>
-      <c r="D209" s="15"/>
-      <c r="E209" s="15"/>
-      <c r="F209" s="16" t="str">
-        <f aca="false">IF(OR($A209="",$D209="",$E209=""),"",MAX(0,$E209-$D209))</f>
-        <v/>
-      </c>
-      <c r="G209" s="16" t="str">
-        <f aca="false">IF($A209="","",IF($E209&lt;&gt;"",IF(N($F209)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D209="","Sem data prometida",IF($D209&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H209" s="17"/>
-      <c r="I209" s="17"/>
-    </row>
-    <row r="210" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="16"/>
-      <c r="B210" s="17"/>
-      <c r="C210" s="15"/>
-      <c r="D210" s="15"/>
-      <c r="E210" s="15"/>
-      <c r="F210" s="16" t="str">
-        <f aca="false">IF(OR($A210="",$D210="",$E210=""),"",MAX(0,$E210-$D210))</f>
-        <v/>
-      </c>
-      <c r="G210" s="16" t="str">
-        <f aca="false">IF($A210="","",IF($E210&lt;&gt;"",IF(N($F210)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D210="","Sem data prometida",IF($D210&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H210" s="17"/>
-      <c r="I210" s="17"/>
-    </row>
-    <row r="211" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="16"/>
-      <c r="B211" s="17"/>
-      <c r="C211" s="15"/>
-      <c r="D211" s="15"/>
-      <c r="E211" s="15"/>
-      <c r="F211" s="16" t="str">
-        <f aca="false">IF(OR($A211="",$D211="",$E211=""),"",MAX(0,$E211-$D211))</f>
-        <v/>
-      </c>
-      <c r="G211" s="16" t="str">
-        <f aca="false">IF($A211="","",IF($E211&lt;&gt;"",IF(N($F211)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D211="","Sem data prometida",IF($D211&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H211" s="17"/>
-      <c r="I211" s="17"/>
-    </row>
-    <row r="212" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="16"/>
-      <c r="B212" s="17"/>
-      <c r="C212" s="15"/>
-      <c r="D212" s="15"/>
-      <c r="E212" s="15"/>
-      <c r="F212" s="16" t="str">
-        <f aca="false">IF(OR($A212="",$D212="",$E212=""),"",MAX(0,$E212-$D212))</f>
-        <v/>
-      </c>
-      <c r="G212" s="16" t="str">
-        <f aca="false">IF($A212="","",IF($E212&lt;&gt;"",IF(N($F212)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D212="","Sem data prometida",IF($D212&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H212" s="17"/>
-      <c r="I212" s="17"/>
-    </row>
-    <row r="213" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="16"/>
-      <c r="B213" s="17"/>
-      <c r="C213" s="15"/>
-      <c r="D213" s="15"/>
-      <c r="E213" s="15"/>
-      <c r="F213" s="16" t="str">
-        <f aca="false">IF(OR($A213="",$D213="",$E213=""),"",MAX(0,$E213-$D213))</f>
-        <v/>
-      </c>
-      <c r="G213" s="16" t="str">
-        <f aca="false">IF($A213="","",IF($E213&lt;&gt;"",IF(N($F213)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D213="","Sem data prometida",IF($D213&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H213" s="17"/>
-      <c r="I213" s="17"/>
-    </row>
-    <row r="214" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="16"/>
-      <c r="B214" s="17"/>
-      <c r="C214" s="15"/>
-      <c r="D214" s="15"/>
-      <c r="E214" s="15"/>
-      <c r="F214" s="16" t="str">
-        <f aca="false">IF(OR($A214="",$D214="",$E214=""),"",MAX(0,$E214-$D214))</f>
-        <v/>
-      </c>
-      <c r="G214" s="16" t="str">
-        <f aca="false">IF($A214="","",IF($E214&lt;&gt;"",IF(N($F214)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D214="","Sem data prometida",IF($D214&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H214" s="17"/>
-      <c r="I214" s="17"/>
-    </row>
-    <row r="215" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="16"/>
-      <c r="B215" s="17"/>
-      <c r="C215" s="15"/>
-      <c r="D215" s="15"/>
-      <c r="E215" s="15"/>
-      <c r="F215" s="16" t="str">
-        <f aca="false">IF(OR($A215="",$D215="",$E215=""),"",MAX(0,$E215-$D215))</f>
-        <v/>
-      </c>
-      <c r="G215" s="16" t="str">
-        <f aca="false">IF($A215="","",IF($E215&lt;&gt;"",IF(N($F215)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D215="","Sem data prometida",IF($D215&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H215" s="17"/>
-      <c r="I215" s="17"/>
-    </row>
-    <row r="216" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="16"/>
-      <c r="B216" s="17"/>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="16" t="str">
-        <f aca="false">IF(OR($A216="",$D216="",$E216=""),"",MAX(0,$E216-$D216))</f>
-        <v/>
-      </c>
-      <c r="G216" s="16" t="str">
-        <f aca="false">IF($A216="","",IF($E216&lt;&gt;"",IF(N($F216)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D216="","Sem data prometida",IF($D216&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H216" s="17"/>
-      <c r="I216" s="17"/>
-    </row>
-    <row r="217" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="16"/>
-      <c r="B217" s="17"/>
-      <c r="C217" s="15"/>
-      <c r="D217" s="15"/>
-      <c r="E217" s="15"/>
-      <c r="F217" s="16" t="str">
-        <f aca="false">IF(OR($A217="",$D217="",$E217=""),"",MAX(0,$E217-$D217))</f>
-        <v/>
-      </c>
-      <c r="G217" s="16" t="str">
-        <f aca="false">IF($A217="","",IF($E217&lt;&gt;"",IF(N($F217)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D217="","Sem data prometida",IF($D217&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H217" s="17"/>
-      <c r="I217" s="17"/>
-    </row>
-    <row r="218" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="16"/>
-      <c r="B218" s="17"/>
-      <c r="C218" s="15"/>
-      <c r="D218" s="15"/>
-      <c r="E218" s="15"/>
-      <c r="F218" s="16" t="str">
-        <f aca="false">IF(OR($A218="",$D218="",$E218=""),"",MAX(0,$E218-$D218))</f>
-        <v/>
-      </c>
-      <c r="G218" s="16" t="str">
-        <f aca="false">IF($A218="","",IF($E218&lt;&gt;"",IF(N($F218)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D218="","Sem data prometida",IF($D218&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H218" s="17"/>
-      <c r="I218" s="17"/>
-    </row>
-    <row r="219" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="16"/>
-      <c r="B219" s="17"/>
-      <c r="C219" s="15"/>
-      <c r="D219" s="15"/>
-      <c r="E219" s="15"/>
-      <c r="F219" s="16" t="str">
-        <f aca="false">IF(OR($A219="",$D219="",$E219=""),"",MAX(0,$E219-$D219))</f>
-        <v/>
-      </c>
-      <c r="G219" s="16" t="str">
-        <f aca="false">IF($A219="","",IF($E219&lt;&gt;"",IF(N($F219)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D219="","Sem data prometida",IF($D219&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H219" s="17"/>
-      <c r="I219" s="17"/>
-    </row>
-    <row r="220" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="16"/>
-      <c r="B220" s="17"/>
-      <c r="C220" s="15"/>
-      <c r="D220" s="15"/>
-      <c r="E220" s="15"/>
-      <c r="F220" s="16" t="str">
-        <f aca="false">IF(OR($A220="",$D220="",$E220=""),"",MAX(0,$E220-$D220))</f>
-        <v/>
-      </c>
-      <c r="G220" s="16" t="str">
-        <f aca="false">IF($A220="","",IF($E220&lt;&gt;"",IF(N($F220)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D220="","Sem data prometida",IF($D220&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H220" s="17"/>
-      <c r="I220" s="17"/>
-    </row>
-    <row r="221" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="16"/>
-      <c r="B221" s="17"/>
-      <c r="C221" s="15"/>
-      <c r="D221" s="15"/>
-      <c r="E221" s="15"/>
-      <c r="F221" s="16" t="str">
-        <f aca="false">IF(OR($A221="",$D221="",$E221=""),"",MAX(0,$E221-$D221))</f>
-        <v/>
-      </c>
-      <c r="G221" s="16" t="str">
-        <f aca="false">IF($A221="","",IF($E221&lt;&gt;"",IF(N($F221)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D221="","Sem data prometida",IF($D221&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H221" s="17"/>
-      <c r="I221" s="17"/>
-    </row>
-    <row r="222" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="16"/>
-      <c r="B222" s="17"/>
-      <c r="C222" s="15"/>
-      <c r="D222" s="15"/>
-      <c r="E222" s="15"/>
-      <c r="F222" s="16" t="str">
-        <f aca="false">IF(OR($A222="",$D222="",$E222=""),"",MAX(0,$E222-$D222))</f>
-        <v/>
-      </c>
-      <c r="G222" s="16" t="str">
-        <f aca="false">IF($A222="","",IF($E222&lt;&gt;"",IF(N($F222)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D222="","Sem data prometida",IF($D222&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H222" s="17"/>
-      <c r="I222" s="17"/>
-    </row>
-    <row r="223" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="16"/>
-      <c r="B223" s="17"/>
-      <c r="C223" s="15"/>
-      <c r="D223" s="15"/>
-      <c r="E223" s="15"/>
-      <c r="F223" s="16" t="str">
-        <f aca="false">IF(OR($A223="",$D223="",$E223=""),"",MAX(0,$E223-$D223))</f>
-        <v/>
-      </c>
-      <c r="G223" s="16" t="str">
-        <f aca="false">IF($A223="","",IF($E223&lt;&gt;"",IF(N($F223)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D223="","Sem data prometida",IF($D223&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H223" s="17"/>
-      <c r="I223" s="17"/>
-    </row>
-    <row r="224" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="16"/>
-      <c r="B224" s="17"/>
-      <c r="C224" s="15"/>
-      <c r="D224" s="15"/>
-      <c r="E224" s="15"/>
-      <c r="F224" s="16" t="str">
-        <f aca="false">IF(OR($A224="",$D224="",$E224=""),"",MAX(0,$E224-$D224))</f>
-        <v/>
-      </c>
-      <c r="G224" s="16" t="str">
-        <f aca="false">IF($A224="","",IF($E224&lt;&gt;"",IF(N($F224)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D224="","Sem data prometida",IF($D224&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H224" s="17"/>
-      <c r="I224" s="17"/>
-    </row>
-    <row r="225" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="16"/>
-      <c r="B225" s="17"/>
-      <c r="C225" s="15"/>
-      <c r="D225" s="15"/>
-      <c r="E225" s="15"/>
-      <c r="F225" s="16" t="str">
-        <f aca="false">IF(OR($A225="",$D225="",$E225=""),"",MAX(0,$E225-$D225))</f>
-        <v/>
-      </c>
-      <c r="G225" s="16" t="str">
-        <f aca="false">IF($A225="","",IF($E225&lt;&gt;"",IF(N($F225)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D225="","Sem data prometida",IF($D225&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H225" s="17"/>
-      <c r="I225" s="17"/>
-    </row>
-    <row r="226" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="16"/>
-      <c r="B226" s="17"/>
-      <c r="C226" s="15"/>
-      <c r="D226" s="15"/>
-      <c r="E226" s="15"/>
-      <c r="F226" s="16" t="str">
-        <f aca="false">IF(OR($A226="",$D226="",$E226=""),"",MAX(0,$E226-$D226))</f>
-        <v/>
-      </c>
-      <c r="G226" s="16" t="str">
-        <f aca="false">IF($A226="","",IF($E226&lt;&gt;"",IF(N($F226)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D226="","Sem data prometida",IF($D226&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H226" s="17"/>
-      <c r="I226" s="17"/>
-    </row>
-    <row r="227" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="16"/>
-      <c r="B227" s="17"/>
-      <c r="C227" s="15"/>
-      <c r="D227" s="15"/>
-      <c r="E227" s="15"/>
-      <c r="F227" s="16" t="str">
-        <f aca="false">IF(OR($A227="",$D227="",$E227=""),"",MAX(0,$E227-$D227))</f>
-        <v/>
-      </c>
-      <c r="G227" s="16" t="str">
-        <f aca="false">IF($A227="","",IF($E227&lt;&gt;"",IF(N($F227)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D227="","Sem data prometida",IF($D227&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H227" s="17"/>
-      <c r="I227" s="17"/>
-    </row>
-    <row r="228" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="16"/>
-      <c r="B228" s="17"/>
-      <c r="C228" s="15"/>
-      <c r="D228" s="15"/>
-      <c r="E228" s="15"/>
-      <c r="F228" s="16" t="str">
-        <f aca="false">IF(OR($A228="",$D228="",$E228=""),"",MAX(0,$E228-$D228))</f>
-        <v/>
-      </c>
-      <c r="G228" s="16" t="str">
-        <f aca="false">IF($A228="","",IF($E228&lt;&gt;"",IF(N($F228)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D228="","Sem data prometida",IF($D228&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H228" s="17"/>
-      <c r="I228" s="17"/>
-    </row>
-    <row r="229" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="16"/>
-      <c r="B229" s="17"/>
-      <c r="C229" s="15"/>
-      <c r="D229" s="15"/>
-      <c r="E229" s="15"/>
-      <c r="F229" s="16" t="str">
-        <f aca="false">IF(OR($A229="",$D229="",$E229=""),"",MAX(0,$E229-$D229))</f>
-        <v/>
-      </c>
-      <c r="G229" s="16" t="str">
-        <f aca="false">IF($A229="","",IF($E229&lt;&gt;"",IF(N($F229)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D229="","Sem data prometida",IF($D229&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H229" s="17"/>
-      <c r="I229" s="17"/>
-    </row>
-    <row r="230" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="16"/>
-      <c r="B230" s="17"/>
-      <c r="C230" s="15"/>
-      <c r="D230" s="15"/>
-      <c r="E230" s="15"/>
-      <c r="F230" s="16" t="str">
-        <f aca="false">IF(OR($A230="",$D230="",$E230=""),"",MAX(0,$E230-$D230))</f>
-        <v/>
-      </c>
-      <c r="G230" s="16" t="str">
-        <f aca="false">IF($A230="","",IF($E230&lt;&gt;"",IF(N($F230)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D230="","Sem data prometida",IF($D230&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H230" s="17"/>
-      <c r="I230" s="17"/>
-    </row>
-    <row r="231" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="16"/>
-      <c r="B231" s="17"/>
-      <c r="C231" s="15"/>
-      <c r="D231" s="15"/>
-      <c r="E231" s="15"/>
-      <c r="F231" s="16" t="str">
-        <f aca="false">IF(OR($A231="",$D231="",$E231=""),"",MAX(0,$E231-$D231))</f>
-        <v/>
-      </c>
-      <c r="G231" s="16" t="str">
-        <f aca="false">IF($A231="","",IF($E231&lt;&gt;"",IF(N($F231)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D231="","Sem data prometida",IF($D231&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H231" s="17"/>
-      <c r="I231" s="17"/>
-    </row>
-    <row r="232" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="16"/>
-      <c r="B232" s="17"/>
-      <c r="C232" s="15"/>
-      <c r="D232" s="15"/>
-      <c r="E232" s="15"/>
-      <c r="F232" s="16" t="str">
-        <f aca="false">IF(OR($A232="",$D232="",$E232=""),"",MAX(0,$E232-$D232))</f>
-        <v/>
-      </c>
-      <c r="G232" s="16" t="str">
-        <f aca="false">IF($A232="","",IF($E232&lt;&gt;"",IF(N($F232)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D232="","Sem data prometida",IF($D232&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H232" s="17"/>
-      <c r="I232" s="17"/>
-    </row>
-    <row r="233" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="16"/>
-      <c r="B233" s="17"/>
-      <c r="C233" s="15"/>
-      <c r="D233" s="15"/>
-      <c r="E233" s="15"/>
-      <c r="F233" s="16" t="str">
-        <f aca="false">IF(OR($A233="",$D233="",$E233=""),"",MAX(0,$E233-$D233))</f>
-        <v/>
-      </c>
-      <c r="G233" s="16" t="str">
-        <f aca="false">IF($A233="","",IF($E233&lt;&gt;"",IF(N($F233)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D233="","Sem data prometida",IF($D233&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H233" s="17"/>
-      <c r="I233" s="17"/>
-    </row>
-    <row r="234" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="16"/>
-      <c r="B234" s="17"/>
-      <c r="C234" s="15"/>
-      <c r="D234" s="15"/>
-      <c r="E234" s="15"/>
-      <c r="F234" s="16" t="str">
-        <f aca="false">IF(OR($A234="",$D234="",$E234=""),"",MAX(0,$E234-$D234))</f>
-        <v/>
-      </c>
-      <c r="G234" s="16" t="str">
-        <f aca="false">IF($A234="","",IF($E234&lt;&gt;"",IF(N($F234)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D234="","Sem data prometida",IF($D234&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H234" s="17"/>
-      <c r="I234" s="17"/>
-    </row>
-    <row r="235" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="16"/>
-      <c r="B235" s="17"/>
-      <c r="C235" s="15"/>
-      <c r="D235" s="15"/>
-      <c r="E235" s="15"/>
-      <c r="F235" s="16" t="str">
-        <f aca="false">IF(OR($A235="",$D235="",$E235=""),"",MAX(0,$E235-$D235))</f>
-        <v/>
-      </c>
-      <c r="G235" s="16" t="str">
-        <f aca="false">IF($A235="","",IF($E235&lt;&gt;"",IF(N($F235)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D235="","Sem data prometida",IF($D235&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H235" s="17"/>
-      <c r="I235" s="17"/>
-    </row>
-    <row r="236" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="16"/>
-      <c r="B236" s="17"/>
-      <c r="C236" s="15"/>
-      <c r="D236" s="15"/>
-      <c r="E236" s="15"/>
-      <c r="F236" s="16" t="str">
-        <f aca="false">IF(OR($A236="",$D236="",$E236=""),"",MAX(0,$E236-$D236))</f>
-        <v/>
-      </c>
-      <c r="G236" s="16" t="str">
-        <f aca="false">IF($A236="","",IF($E236&lt;&gt;"",IF(N($F236)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D236="","Sem data prometida",IF($D236&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H236" s="17"/>
-      <c r="I236" s="17"/>
-    </row>
-    <row r="237" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="16"/>
-      <c r="B237" s="17"/>
-      <c r="C237" s="15"/>
-      <c r="D237" s="15"/>
-      <c r="E237" s="15"/>
-      <c r="F237" s="16" t="str">
-        <f aca="false">IF(OR($A237="",$D237="",$E237=""),"",MAX(0,$E237-$D237))</f>
-        <v/>
-      </c>
-      <c r="G237" s="16" t="str">
-        <f aca="false">IF($A237="","",IF($E237&lt;&gt;"",IF(N($F237)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D237="","Sem data prometida",IF($D237&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H237" s="17"/>
-      <c r="I237" s="17"/>
-    </row>
-    <row r="238" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="16"/>
-      <c r="B238" s="17"/>
-      <c r="C238" s="15"/>
-      <c r="D238" s="15"/>
-      <c r="E238" s="15"/>
-      <c r="F238" s="16" t="str">
-        <f aca="false">IF(OR($A238="",$D238="",$E238=""),"",MAX(0,$E238-$D238))</f>
-        <v/>
-      </c>
-      <c r="G238" s="16" t="str">
-        <f aca="false">IF($A238="","",IF($E238&lt;&gt;"",IF(N($F238)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D238="","Sem data prometida",IF($D238&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H238" s="17"/>
-      <c r="I238" s="17"/>
-    </row>
-    <row r="239" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="16"/>
-      <c r="B239" s="17"/>
-      <c r="C239" s="15"/>
-      <c r="D239" s="15"/>
-      <c r="E239" s="15"/>
-      <c r="F239" s="16" t="str">
-        <f aca="false">IF(OR($A239="",$D239="",$E239=""),"",MAX(0,$E239-$D239))</f>
-        <v/>
-      </c>
-      <c r="G239" s="16" t="str">
-        <f aca="false">IF($A239="","",IF($E239&lt;&gt;"",IF(N($F239)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D239="","Sem data prometida",IF($D239&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H239" s="17"/>
-      <c r="I239" s="17"/>
-    </row>
-    <row r="240" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="16"/>
-      <c r="B240" s="17"/>
-      <c r="C240" s="15"/>
-      <c r="D240" s="15"/>
-      <c r="E240" s="15"/>
-      <c r="F240" s="16" t="str">
-        <f aca="false">IF(OR($A240="",$D240="",$E240=""),"",MAX(0,$E240-$D240))</f>
-        <v/>
-      </c>
-      <c r="G240" s="16" t="str">
-        <f aca="false">IF($A240="","",IF($E240&lt;&gt;"",IF(N($F240)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D240="","Sem data prometida",IF($D240&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H240" s="17"/>
-      <c r="I240" s="17"/>
-    </row>
-    <row r="241" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="16"/>
-      <c r="B241" s="17"/>
-      <c r="C241" s="15"/>
-      <c r="D241" s="15"/>
-      <c r="E241" s="15"/>
-      <c r="F241" s="16" t="str">
-        <f aca="false">IF(OR($A241="",$D241="",$E241=""),"",MAX(0,$E241-$D241))</f>
-        <v/>
-      </c>
-      <c r="G241" s="16" t="str">
-        <f aca="false">IF($A241="","",IF($E241&lt;&gt;"",IF(N($F241)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D241="","Sem data prometida",IF($D241&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H241" s="17"/>
-      <c r="I241" s="17"/>
-    </row>
-    <row r="242" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="16"/>
-      <c r="B242" s="17"/>
-      <c r="C242" s="15"/>
-      <c r="D242" s="15"/>
-      <c r="E242" s="15"/>
-      <c r="F242" s="16" t="str">
-        <f aca="false">IF(OR($A242="",$D242="",$E242=""),"",MAX(0,$E242-$D242))</f>
-        <v/>
-      </c>
-      <c r="G242" s="16" t="str">
-        <f aca="false">IF($A242="","",IF($E242&lt;&gt;"",IF(N($F242)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D242="","Sem data prometida",IF($D242&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H242" s="17"/>
-      <c r="I242" s="17"/>
-    </row>
-    <row r="243" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="16"/>
-      <c r="B243" s="17"/>
-      <c r="C243" s="15"/>
-      <c r="D243" s="15"/>
-      <c r="E243" s="15"/>
-      <c r="F243" s="16" t="str">
-        <f aca="false">IF(OR($A243="",$D243="",$E243=""),"",MAX(0,$E243-$D243))</f>
-        <v/>
-      </c>
-      <c r="G243" s="16" t="str">
-        <f aca="false">IF($A243="","",IF($E243&lt;&gt;"",IF(N($F243)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D243="","Sem data prometida",IF($D243&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H243" s="17"/>
-      <c r="I243" s="17"/>
-    </row>
-    <row r="244" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="16"/>
-      <c r="B244" s="17"/>
-      <c r="C244" s="15"/>
-      <c r="D244" s="15"/>
-      <c r="E244" s="15"/>
-      <c r="F244" s="16" t="str">
-        <f aca="false">IF(OR($A244="",$D244="",$E244=""),"",MAX(0,$E244-$D244))</f>
-        <v/>
-      </c>
-      <c r="G244" s="16" t="str">
-        <f aca="false">IF($A244="","",IF($E244&lt;&gt;"",IF(N($F244)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D244="","Sem data prometida",IF($D244&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H244" s="17"/>
-      <c r="I244" s="17"/>
-    </row>
-    <row r="245" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="16"/>
-      <c r="B245" s="17"/>
-      <c r="C245" s="15"/>
-      <c r="D245" s="15"/>
-      <c r="E245" s="15"/>
-      <c r="F245" s="16" t="str">
-        <f aca="false">IF(OR($A245="",$D245="",$E245=""),"",MAX(0,$E245-$D245))</f>
-        <v/>
-      </c>
-      <c r="G245" s="16" t="str">
-        <f aca="false">IF($A245="","",IF($E245&lt;&gt;"",IF(N($F245)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D245="","Sem data prometida",IF($D245&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H245" s="17"/>
-      <c r="I245" s="17"/>
-    </row>
-    <row r="246" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="16"/>
-      <c r="B246" s="17"/>
-      <c r="C246" s="15"/>
-      <c r="D246" s="15"/>
-      <c r="E246" s="15"/>
-      <c r="F246" s="16" t="str">
-        <f aca="false">IF(OR($A246="",$D246="",$E246=""),"",MAX(0,$E246-$D246))</f>
-        <v/>
-      </c>
-      <c r="G246" s="16" t="str">
-        <f aca="false">IF($A246="","",IF($E246&lt;&gt;"",IF(N($F246)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D246="","Sem data prometida",IF($D246&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H246" s="17"/>
-      <c r="I246" s="17"/>
-    </row>
-    <row r="247" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="16"/>
-      <c r="B247" s="17"/>
-      <c r="C247" s="15"/>
-      <c r="D247" s="15"/>
-      <c r="E247" s="15"/>
-      <c r="F247" s="16" t="str">
-        <f aca="false">IF(OR($A247="",$D247="",$E247=""),"",MAX(0,$E247-$D247))</f>
-        <v/>
-      </c>
-      <c r="G247" s="16" t="str">
-        <f aca="false">IF($A247="","",IF($E247&lt;&gt;"",IF(N($F247)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D247="","Sem data prometida",IF($D247&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H247" s="17"/>
-      <c r="I247" s="17"/>
-    </row>
-    <row r="248" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="16"/>
-      <c r="B248" s="17"/>
-      <c r="C248" s="15"/>
-      <c r="D248" s="15"/>
-      <c r="E248" s="15"/>
-      <c r="F248" s="16" t="str">
-        <f aca="false">IF(OR($A248="",$D248="",$E248=""),"",MAX(0,$E248-$D248))</f>
-        <v/>
-      </c>
-      <c r="G248" s="16" t="str">
-        <f aca="false">IF($A248="","",IF($E248&lt;&gt;"",IF(N($F248)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D248="","Sem data prometida",IF($D248&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H248" s="17"/>
-      <c r="I248" s="17"/>
-    </row>
-    <row r="249" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="16"/>
-      <c r="B249" s="17"/>
-      <c r="C249" s="15"/>
-      <c r="D249" s="15"/>
-      <c r="E249" s="15"/>
-      <c r="F249" s="16" t="str">
-        <f aca="false">IF(OR($A249="",$D249="",$E249=""),"",MAX(0,$E249-$D249))</f>
-        <v/>
-      </c>
-      <c r="G249" s="16" t="str">
-        <f aca="false">IF($A249="","",IF($E249&lt;&gt;"",IF(N($F249)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D249="","Sem data prometida",IF($D249&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H249" s="17"/>
-      <c r="I249" s="17"/>
-    </row>
-    <row r="250" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="16"/>
-      <c r="B250" s="17"/>
-      <c r="C250" s="15"/>
-      <c r="D250" s="15"/>
-      <c r="E250" s="15"/>
-      <c r="F250" s="16" t="str">
-        <f aca="false">IF(OR($A250="",$D250="",$E250=""),"",MAX(0,$E250-$D250))</f>
-        <v/>
-      </c>
-      <c r="G250" s="16" t="str">
-        <f aca="false">IF($A250="","",IF($E250&lt;&gt;"",IF(N($F250)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D250="","Sem data prometida",IF($D250&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H250" s="17"/>
-      <c r="I250" s="17"/>
-    </row>
-    <row r="251" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="16"/>
-      <c r="B251" s="17"/>
-      <c r="C251" s="15"/>
-      <c r="D251" s="15"/>
-      <c r="E251" s="15"/>
-      <c r="F251" s="16" t="str">
-        <f aca="false">IF(OR($A251="",$D251="",$E251=""),"",MAX(0,$E251-$D251))</f>
-        <v/>
-      </c>
-      <c r="G251" s="16" t="str">
-        <f aca="false">IF($A251="","",IF($E251&lt;&gt;"",IF(N($F251)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D251="","Sem data prometida",IF($D251&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H251" s="17"/>
-      <c r="I251" s="17"/>
-    </row>
-    <row r="252" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="16"/>
-      <c r="B252" s="17"/>
-      <c r="C252" s="15"/>
-      <c r="D252" s="15"/>
-      <c r="E252" s="15"/>
-      <c r="F252" s="16" t="str">
-        <f aca="false">IF(OR($A252="",$D252="",$E252=""),"",MAX(0,$E252-$D252))</f>
-        <v/>
-      </c>
-      <c r="G252" s="16" t="str">
-        <f aca="false">IF($A252="","",IF($E252&lt;&gt;"",IF(N($F252)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D252="","Sem data prometida",IF($D252&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H252" s="17"/>
-      <c r="I252" s="17"/>
-    </row>
-    <row r="253" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="16"/>
-      <c r="B253" s="17"/>
-      <c r="C253" s="15"/>
-      <c r="D253" s="15"/>
-      <c r="E253" s="15"/>
-      <c r="F253" s="16" t="str">
-        <f aca="false">IF(OR($A253="",$D253="",$E253=""),"",MAX(0,$E253-$D253))</f>
-        <v/>
-      </c>
-      <c r="G253" s="16" t="str">
-        <f aca="false">IF($A253="","",IF($E253&lt;&gt;"",IF(N($F253)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D253="","Sem data prometida",IF($D253&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H253" s="17"/>
-      <c r="I253" s="17"/>
-    </row>
-    <row r="254" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="16"/>
-      <c r="B254" s="17"/>
-      <c r="C254" s="15"/>
-      <c r="D254" s="15"/>
-      <c r="E254" s="15"/>
-      <c r="F254" s="16" t="str">
-        <f aca="false">IF(OR($A254="",$D254="",$E254=""),"",MAX(0,$E254-$D254))</f>
-        <v/>
-      </c>
-      <c r="G254" s="16" t="str">
-        <f aca="false">IF($A254="","",IF($E254&lt;&gt;"",IF(N($F254)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D254="","Sem data prometida",IF($D254&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H254" s="17"/>
-      <c r="I254" s="17"/>
-    </row>
-    <row r="255" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="16"/>
-      <c r="B255" s="17"/>
-      <c r="C255" s="15"/>
-      <c r="D255" s="15"/>
-      <c r="E255" s="15"/>
-      <c r="F255" s="16" t="str">
-        <f aca="false">IF(OR($A255="",$D255="",$E255=""),"",MAX(0,$E255-$D255))</f>
-        <v/>
-      </c>
-      <c r="G255" s="16" t="str">
-        <f aca="false">IF($A255="","",IF($E255&lt;&gt;"",IF(N($F255)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D255="","Sem data prometida",IF($D255&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H255" s="17"/>
-      <c r="I255" s="17"/>
-    </row>
-    <row r="256" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="16"/>
-      <c r="B256" s="17"/>
-      <c r="C256" s="15"/>
-      <c r="D256" s="15"/>
-      <c r="E256" s="15"/>
-      <c r="F256" s="16" t="str">
-        <f aca="false">IF(OR($A256="",$D256="",$E256=""),"",MAX(0,$E256-$D256))</f>
-        <v/>
-      </c>
-      <c r="G256" s="16" t="str">
-        <f aca="false">IF($A256="","",IF($E256&lt;&gt;"",IF(N($F256)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D256="","Sem data prometida",IF($D256&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H256" s="17"/>
-      <c r="I256" s="17"/>
-    </row>
-    <row r="257" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A257" s="16"/>
-      <c r="B257" s="17"/>
-      <c r="C257" s="15"/>
-      <c r="D257" s="15"/>
-      <c r="E257" s="15"/>
-      <c r="F257" s="16" t="str">
-        <f aca="false">IF(OR($A257="",$D257="",$E257=""),"",MAX(0,$E257-$D257))</f>
-        <v/>
-      </c>
-      <c r="G257" s="16" t="str">
-        <f aca="false">IF($A257="","",IF($E257&lt;&gt;"",IF(N($F257)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D257="","Sem data prometida",IF($D257&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H257" s="17"/>
-      <c r="I257" s="17"/>
-    </row>
-    <row r="258" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="16"/>
-      <c r="B258" s="17"/>
-      <c r="C258" s="15"/>
-      <c r="D258" s="15"/>
-      <c r="E258" s="15"/>
-      <c r="F258" s="16" t="str">
-        <f aca="false">IF(OR($A258="",$D258="",$E258=""),"",MAX(0,$E258-$D258))</f>
-        <v/>
-      </c>
-      <c r="G258" s="16" t="str">
-        <f aca="false">IF($A258="","",IF($E258&lt;&gt;"",IF(N($F258)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D258="","Sem data prometida",IF($D258&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H258" s="17"/>
-      <c r="I258" s="17"/>
-    </row>
-    <row r="259" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="16"/>
-      <c r="B259" s="17"/>
-      <c r="C259" s="15"/>
-      <c r="D259" s="15"/>
-      <c r="E259" s="15"/>
-      <c r="F259" s="16" t="str">
-        <f aca="false">IF(OR($A259="",$D259="",$E259=""),"",MAX(0,$E259-$D259))</f>
-        <v/>
-      </c>
-      <c r="G259" s="16" t="str">
-        <f aca="false">IF($A259="","",IF($E259&lt;&gt;"",IF(N($F259)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D259="","Sem data prometida",IF($D259&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H259" s="17"/>
-      <c r="I259" s="17"/>
-    </row>
-    <row r="260" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="16"/>
-      <c r="B260" s="17"/>
-      <c r="C260" s="15"/>
-      <c r="D260" s="15"/>
-      <c r="E260" s="15"/>
-      <c r="F260" s="16" t="str">
-        <f aca="false">IF(OR($A260="",$D260="",$E260=""),"",MAX(0,$E260-$D260))</f>
-        <v/>
-      </c>
-      <c r="G260" s="16" t="str">
-        <f aca="false">IF($A260="","",IF($E260&lt;&gt;"",IF(N($F260)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D260="","Sem data prometida",IF($D260&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H260" s="17"/>
-      <c r="I260" s="17"/>
-    </row>
-    <row r="261" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="16"/>
-      <c r="B261" s="17"/>
-      <c r="C261" s="15"/>
-      <c r="D261" s="15"/>
-      <c r="E261" s="15"/>
-      <c r="F261" s="16" t="str">
-        <f aca="false">IF(OR($A261="",$D261="",$E261=""),"",MAX(0,$E261-$D261))</f>
-        <v/>
-      </c>
-      <c r="G261" s="16" t="str">
-        <f aca="false">IF($A261="","",IF($E261&lt;&gt;"",IF(N($F261)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D261="","Sem data prometida",IF($D261&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H261" s="17"/>
-      <c r="I261" s="17"/>
-    </row>
-    <row r="262" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="16"/>
-      <c r="B262" s="17"/>
-      <c r="C262" s="15"/>
-      <c r="D262" s="15"/>
-      <c r="E262" s="15"/>
-      <c r="F262" s="16" t="str">
-        <f aca="false">IF(OR($A262="",$D262="",$E262=""),"",MAX(0,$E262-$D262))</f>
-        <v/>
-      </c>
-      <c r="G262" s="16" t="str">
-        <f aca="false">IF($A262="","",IF($E262&lt;&gt;"",IF(N($F262)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D262="","Sem data prometida",IF($D262&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H262" s="17"/>
-      <c r="I262" s="17"/>
-    </row>
-    <row r="263" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="16"/>
-      <c r="B263" s="17"/>
-      <c r="C263" s="15"/>
-      <c r="D263" s="15"/>
-      <c r="E263" s="15"/>
-      <c r="F263" s="16" t="str">
-        <f aca="false">IF(OR($A263="",$D263="",$E263=""),"",MAX(0,$E263-$D263))</f>
-        <v/>
-      </c>
-      <c r="G263" s="16" t="str">
-        <f aca="false">IF($A263="","",IF($E263&lt;&gt;"",IF(N($F263)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D263="","Sem data prometida",IF($D263&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H263" s="17"/>
-      <c r="I263" s="17"/>
-    </row>
-    <row r="264" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A264" s="16"/>
-      <c r="B264" s="17"/>
-      <c r="C264" s="15"/>
-      <c r="D264" s="15"/>
-      <c r="E264" s="15"/>
-      <c r="F264" s="16" t="str">
-        <f aca="false">IF(OR($A264="",$D264="",$E264=""),"",MAX(0,$E264-$D264))</f>
-        <v/>
-      </c>
-      <c r="G264" s="16" t="str">
-        <f aca="false">IF($A264="","",IF($E264&lt;&gt;"",IF(N($F264)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D264="","Sem data prometida",IF($D264&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H264" s="17"/>
-      <c r="I264" s="17"/>
-    </row>
-    <row r="265" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="16"/>
-      <c r="B265" s="17"/>
-      <c r="C265" s="15"/>
-      <c r="D265" s="15"/>
-      <c r="E265" s="15"/>
-      <c r="F265" s="16" t="str">
-        <f aca="false">IF(OR($A265="",$D265="",$E265=""),"",MAX(0,$E265-$D265))</f>
-        <v/>
-      </c>
-      <c r="G265" s="16" t="str">
-        <f aca="false">IF($A265="","",IF($E265&lt;&gt;"",IF(N($F265)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D265="","Sem data prometida",IF($D265&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H265" s="17"/>
-      <c r="I265" s="17"/>
-    </row>
-    <row r="266" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="16"/>
-      <c r="B266" s="17"/>
-      <c r="C266" s="15"/>
-      <c r="D266" s="15"/>
-      <c r="E266" s="15"/>
-      <c r="F266" s="16" t="str">
-        <f aca="false">IF(OR($A266="",$D266="",$E266=""),"",MAX(0,$E266-$D266))</f>
-        <v/>
-      </c>
-      <c r="G266" s="16" t="str">
-        <f aca="false">IF($A266="","",IF($E266&lt;&gt;"",IF(N($F266)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D266="","Sem data prometida",IF($D266&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H266" s="17"/>
-      <c r="I266" s="17"/>
-    </row>
-    <row r="267" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="16"/>
-      <c r="B267" s="17"/>
-      <c r="C267" s="15"/>
-      <c r="D267" s="15"/>
-      <c r="E267" s="15"/>
-      <c r="F267" s="16" t="str">
-        <f aca="false">IF(OR($A267="",$D267="",$E267=""),"",MAX(0,$E267-$D267))</f>
-        <v/>
-      </c>
-      <c r="G267" s="16" t="str">
-        <f aca="false">IF($A267="","",IF($E267&lt;&gt;"",IF(N($F267)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D267="","Sem data prometida",IF($D267&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H267" s="17"/>
-      <c r="I267" s="17"/>
-    </row>
-    <row r="268" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="16"/>
-      <c r="B268" s="17"/>
-      <c r="C268" s="15"/>
-      <c r="D268" s="15"/>
-      <c r="E268" s="15"/>
-      <c r="F268" s="16" t="str">
-        <f aca="false">IF(OR($A268="",$D268="",$E268=""),"",MAX(0,$E268-$D268))</f>
-        <v/>
-      </c>
-      <c r="G268" s="16" t="str">
-        <f aca="false">IF($A268="","",IF($E268&lt;&gt;"",IF(N($F268)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D268="","Sem data prometida",IF($D268&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H268" s="17"/>
-      <c r="I268" s="17"/>
-    </row>
-    <row r="269" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="16"/>
-      <c r="B269" s="17"/>
-      <c r="C269" s="15"/>
-      <c r="D269" s="15"/>
-      <c r="E269" s="15"/>
-      <c r="F269" s="16" t="str">
-        <f aca="false">IF(OR($A269="",$D269="",$E269=""),"",MAX(0,$E269-$D269))</f>
-        <v/>
-      </c>
-      <c r="G269" s="16" t="str">
-        <f aca="false">IF($A269="","",IF($E269&lt;&gt;"",IF(N($F269)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D269="","Sem data prometida",IF($D269&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H269" s="17"/>
-      <c r="I269" s="17"/>
-    </row>
-    <row r="270" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="16"/>
-      <c r="B270" s="17"/>
-      <c r="C270" s="15"/>
-      <c r="D270" s="15"/>
-      <c r="E270" s="15"/>
-      <c r="F270" s="16" t="str">
-        <f aca="false">IF(OR($A270="",$D270="",$E270=""),"",MAX(0,$E270-$D270))</f>
-        <v/>
-      </c>
-      <c r="G270" s="16" t="str">
-        <f aca="false">IF($A270="","",IF($E270&lt;&gt;"",IF(N($F270)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D270="","Sem data prometida",IF($D270&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H270" s="17"/>
-      <c r="I270" s="17"/>
-    </row>
-    <row r="271" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="16"/>
-      <c r="B271" s="17"/>
-      <c r="C271" s="15"/>
-      <c r="D271" s="15"/>
-      <c r="E271" s="15"/>
-      <c r="F271" s="16" t="str">
-        <f aca="false">IF(OR($A271="",$D271="",$E271=""),"",MAX(0,$E271-$D271))</f>
-        <v/>
-      </c>
-      <c r="G271" s="16" t="str">
-        <f aca="false">IF($A271="","",IF($E271&lt;&gt;"",IF(N($F271)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D271="","Sem data prometida",IF($D271&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H271" s="17"/>
-      <c r="I271" s="17"/>
-    </row>
-    <row r="272" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A272" s="16"/>
-      <c r="B272" s="17"/>
-      <c r="C272" s="15"/>
-      <c r="D272" s="15"/>
-      <c r="E272" s="15"/>
-      <c r="F272" s="16" t="str">
-        <f aca="false">IF(OR($A272="",$D272="",$E272=""),"",MAX(0,$E272-$D272))</f>
-        <v/>
-      </c>
-      <c r="G272" s="16" t="str">
-        <f aca="false">IF($A272="","",IF($E272&lt;&gt;"",IF(N($F272)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D272="","Sem data prometida",IF($D272&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H272" s="17"/>
-      <c r="I272" s="17"/>
-    </row>
-    <row r="273" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="16"/>
-      <c r="B273" s="17"/>
-      <c r="C273" s="15"/>
-      <c r="D273" s="15"/>
-      <c r="E273" s="15"/>
-      <c r="F273" s="16" t="str">
-        <f aca="false">IF(OR($A273="",$D273="",$E273=""),"",MAX(0,$E273-$D273))</f>
-        <v/>
-      </c>
-      <c r="G273" s="16" t="str">
-        <f aca="false">IF($A273="","",IF($E273&lt;&gt;"",IF(N($F273)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D273="","Sem data prometida",IF($D273&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H273" s="17"/>
-      <c r="I273" s="17"/>
-    </row>
-    <row r="274" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="16"/>
-      <c r="B274" s="17"/>
-      <c r="C274" s="15"/>
-      <c r="D274" s="15"/>
-      <c r="E274" s="15"/>
-      <c r="F274" s="16" t="str">
-        <f aca="false">IF(OR($A274="",$D274="",$E274=""),"",MAX(0,$E274-$D274))</f>
-        <v/>
-      </c>
-      <c r="G274" s="16" t="str">
-        <f aca="false">IF($A274="","",IF($E274&lt;&gt;"",IF(N($F274)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D274="","Sem data prometida",IF($D274&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H274" s="17"/>
-      <c r="I274" s="17"/>
-    </row>
-    <row r="275" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="16"/>
-      <c r="B275" s="17"/>
-      <c r="C275" s="15"/>
-      <c r="D275" s="15"/>
-      <c r="E275" s="15"/>
-      <c r="F275" s="16" t="str">
-        <f aca="false">IF(OR($A275="",$D275="",$E275=""),"",MAX(0,$E275-$D275))</f>
-        <v/>
-      </c>
-      <c r="G275" s="16" t="str">
-        <f aca="false">IF($A275="","",IF($E275&lt;&gt;"",IF(N($F275)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D275="","Sem data prometida",IF($D275&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H275" s="17"/>
-      <c r="I275" s="17"/>
-    </row>
-    <row r="276" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="16"/>
-      <c r="B276" s="17"/>
-      <c r="C276" s="15"/>
-      <c r="D276" s="15"/>
-      <c r="E276" s="15"/>
-      <c r="F276" s="16" t="str">
-        <f aca="false">IF(OR($A276="",$D276="",$E276=""),"",MAX(0,$E276-$D276))</f>
-        <v/>
-      </c>
-      <c r="G276" s="16" t="str">
-        <f aca="false">IF($A276="","",IF($E276&lt;&gt;"",IF(N($F276)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D276="","Sem data prometida",IF($D276&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H276" s="17"/>
-      <c r="I276" s="17"/>
-    </row>
-    <row r="277" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="16"/>
-      <c r="B277" s="17"/>
-      <c r="C277" s="15"/>
-      <c r="D277" s="15"/>
-      <c r="E277" s="15"/>
-      <c r="F277" s="16" t="str">
-        <f aca="false">IF(OR($A277="",$D277="",$E277=""),"",MAX(0,$E277-$D277))</f>
-        <v/>
-      </c>
-      <c r="G277" s="16" t="str">
-        <f aca="false">IF($A277="","",IF($E277&lt;&gt;"",IF(N($F277)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D277="","Sem data prometida",IF($D277&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H277" s="17"/>
-      <c r="I277" s="17"/>
-    </row>
-    <row r="278" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="16"/>
-      <c r="B278" s="17"/>
-      <c r="C278" s="15"/>
-      <c r="D278" s="15"/>
-      <c r="E278" s="15"/>
-      <c r="F278" s="16" t="str">
-        <f aca="false">IF(OR($A278="",$D278="",$E278=""),"",MAX(0,$E278-$D278))</f>
-        <v/>
-      </c>
-      <c r="G278" s="16" t="str">
-        <f aca="false">IF($A278="","",IF($E278&lt;&gt;"",IF(N($F278)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D278="","Sem data prometida",IF($D278&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H278" s="17"/>
-      <c r="I278" s="17"/>
-    </row>
-    <row r="279" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="16"/>
-      <c r="B279" s="17"/>
-      <c r="C279" s="15"/>
-      <c r="D279" s="15"/>
-      <c r="E279" s="15"/>
-      <c r="F279" s="16" t="str">
-        <f aca="false">IF(OR($A279="",$D279="",$E279=""),"",MAX(0,$E279-$D279))</f>
-        <v/>
-      </c>
-      <c r="G279" s="16" t="str">
-        <f aca="false">IF($A279="","",IF($E279&lt;&gt;"",IF(N($F279)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D279="","Sem data prometida",IF($D279&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H279" s="17"/>
-      <c r="I279" s="17"/>
-    </row>
-    <row r="280" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="16"/>
-      <c r="B280" s="17"/>
-      <c r="C280" s="15"/>
-      <c r="D280" s="15"/>
-      <c r="E280" s="15"/>
-      <c r="F280" s="16" t="str">
-        <f aca="false">IF(OR($A280="",$D280="",$E280=""),"",MAX(0,$E280-$D280))</f>
-        <v/>
-      </c>
-      <c r="G280" s="16" t="str">
-        <f aca="false">IF($A280="","",IF($E280&lt;&gt;"",IF(N($F280)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D280="","Sem data prometida",IF($D280&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H280" s="17"/>
-      <c r="I280" s="17"/>
-    </row>
-    <row r="281" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="16"/>
-      <c r="B281" s="17"/>
-      <c r="C281" s="15"/>
-      <c r="D281" s="15"/>
-      <c r="E281" s="15"/>
-      <c r="F281" s="16" t="str">
-        <f aca="false">IF(OR($A281="",$D281="",$E281=""),"",MAX(0,$E281-$D281))</f>
-        <v/>
-      </c>
-      <c r="G281" s="16" t="str">
-        <f aca="false">IF($A281="","",IF($E281&lt;&gt;"",IF(N($F281)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D281="","Sem data prometida",IF($D281&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H281" s="17"/>
-      <c r="I281" s="17"/>
-    </row>
-    <row r="282" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="16"/>
-      <c r="B282" s="17"/>
-      <c r="C282" s="15"/>
-      <c r="D282" s="15"/>
-      <c r="E282" s="15"/>
-      <c r="F282" s="16" t="str">
-        <f aca="false">IF(OR($A282="",$D282="",$E282=""),"",MAX(0,$E282-$D282))</f>
-        <v/>
-      </c>
-      <c r="G282" s="16" t="str">
-        <f aca="false">IF($A282="","",IF($E282&lt;&gt;"",IF(N($F282)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D282="","Sem data prometida",IF($D282&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H282" s="17"/>
-      <c r="I282" s="17"/>
-    </row>
-    <row r="283" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="16"/>
-      <c r="B283" s="17"/>
-      <c r="C283" s="15"/>
-      <c r="D283" s="15"/>
-      <c r="E283" s="15"/>
-      <c r="F283" s="16" t="str">
-        <f aca="false">IF(OR($A283="",$D283="",$E283=""),"",MAX(0,$E283-$D283))</f>
-        <v/>
-      </c>
-      <c r="G283" s="16" t="str">
-        <f aca="false">IF($A283="","",IF($E283&lt;&gt;"",IF(N($F283)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D283="","Sem data prometida",IF($D283&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H283" s="17"/>
-      <c r="I283" s="17"/>
-    </row>
-    <row r="284" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="16"/>
-      <c r="B284" s="17"/>
-      <c r="C284" s="15"/>
-      <c r="D284" s="15"/>
-      <c r="E284" s="15"/>
-      <c r="F284" s="16" t="str">
-        <f aca="false">IF(OR($A284="",$D284="",$E284=""),"",MAX(0,$E284-$D284))</f>
-        <v/>
-      </c>
-      <c r="G284" s="16" t="str">
-        <f aca="false">IF($A284="","",IF($E284&lt;&gt;"",IF(N($F284)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D284="","Sem data prometida",IF($D284&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H284" s="17"/>
-      <c r="I284" s="17"/>
-    </row>
-    <row r="285" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="16"/>
-      <c r="B285" s="17"/>
-      <c r="C285" s="15"/>
-      <c r="D285" s="15"/>
-      <c r="E285" s="15"/>
-      <c r="F285" s="16" t="str">
-        <f aca="false">IF(OR($A285="",$D285="",$E285=""),"",MAX(0,$E285-$D285))</f>
-        <v/>
-      </c>
-      <c r="G285" s="16" t="str">
-        <f aca="false">IF($A285="","",IF($E285&lt;&gt;"",IF(N($F285)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D285="","Sem data prometida",IF($D285&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H285" s="17"/>
-      <c r="I285" s="17"/>
-    </row>
-    <row r="286" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A286" s="16"/>
-      <c r="B286" s="17"/>
-      <c r="C286" s="15"/>
-      <c r="D286" s="15"/>
-      <c r="E286" s="15"/>
-      <c r="F286" s="16" t="str">
-        <f aca="false">IF(OR($A286="",$D286="",$E286=""),"",MAX(0,$E286-$D286))</f>
-        <v/>
-      </c>
-      <c r="G286" s="16" t="str">
-        <f aca="false">IF($A286="","",IF($E286&lt;&gt;"",IF(N($F286)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D286="","Sem data prometida",IF($D286&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H286" s="17"/>
-      <c r="I286" s="17"/>
-    </row>
-    <row r="287" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="16"/>
-      <c r="B287" s="17"/>
-      <c r="C287" s="15"/>
-      <c r="D287" s="15"/>
-      <c r="E287" s="15"/>
-      <c r="F287" s="16" t="str">
-        <f aca="false">IF(OR($A287="",$D287="",$E287=""),"",MAX(0,$E287-$D287))</f>
-        <v/>
-      </c>
-      <c r="G287" s="16" t="str">
-        <f aca="false">IF($A287="","",IF($E287&lt;&gt;"",IF(N($F287)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D287="","Sem data prometida",IF($D287&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H287" s="17"/>
-      <c r="I287" s="17"/>
-    </row>
-    <row r="288" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="16"/>
-      <c r="B288" s="17"/>
-      <c r="C288" s="15"/>
-      <c r="D288" s="15"/>
-      <c r="E288" s="15"/>
-      <c r="F288" s="16" t="str">
-        <f aca="false">IF(OR($A288="",$D288="",$E288=""),"",MAX(0,$E288-$D288))</f>
-        <v/>
-      </c>
-      <c r="G288" s="16" t="str">
-        <f aca="false">IF($A288="","",IF($E288&lt;&gt;"",IF(N($F288)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D288="","Sem data prometida",IF($D288&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H288" s="17"/>
-      <c r="I288" s="17"/>
-    </row>
-    <row r="289" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="16"/>
-      <c r="B289" s="17"/>
-      <c r="C289" s="15"/>
-      <c r="D289" s="15"/>
-      <c r="E289" s="15"/>
-      <c r="F289" s="16" t="str">
-        <f aca="false">IF(OR($A289="",$D289="",$E289=""),"",MAX(0,$E289-$D289))</f>
-        <v/>
-      </c>
-      <c r="G289" s="16" t="str">
-        <f aca="false">IF($A289="","",IF($E289&lt;&gt;"",IF(N($F289)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D289="","Sem data prometida",IF($D289&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H289" s="17"/>
-      <c r="I289" s="17"/>
-    </row>
-    <row r="290" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="16"/>
-      <c r="B290" s="17"/>
-      <c r="C290" s="15"/>
-      <c r="D290" s="15"/>
-      <c r="E290" s="15"/>
-      <c r="F290" s="16" t="str">
-        <f aca="false">IF(OR($A290="",$D290="",$E290=""),"",MAX(0,$E290-$D290))</f>
-        <v/>
-      </c>
-      <c r="G290" s="16" t="str">
-        <f aca="false">IF($A290="","",IF($E290&lt;&gt;"",IF(N($F290)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D290="","Sem data prometida",IF($D290&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H290" s="17"/>
-      <c r="I290" s="17"/>
-    </row>
-    <row r="291" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="16"/>
-      <c r="B291" s="17"/>
-      <c r="C291" s="15"/>
-      <c r="D291" s="15"/>
-      <c r="E291" s="15"/>
-      <c r="F291" s="16" t="str">
-        <f aca="false">IF(OR($A291="",$D291="",$E291=""),"",MAX(0,$E291-$D291))</f>
-        <v/>
-      </c>
-      <c r="G291" s="16" t="str">
-        <f aca="false">IF($A291="","",IF($E291&lt;&gt;"",IF(N($F291)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D291="","Sem data prometida",IF($D291&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H291" s="17"/>
-      <c r="I291" s="17"/>
-    </row>
-    <row r="292" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="16"/>
-      <c r="B292" s="17"/>
-      <c r="C292" s="15"/>
-      <c r="D292" s="15"/>
-      <c r="E292" s="15"/>
-      <c r="F292" s="16" t="str">
-        <f aca="false">IF(OR($A292="",$D292="",$E292=""),"",MAX(0,$E292-$D292))</f>
-        <v/>
-      </c>
-      <c r="G292" s="16" t="str">
-        <f aca="false">IF($A292="","",IF($E292&lt;&gt;"",IF(N($F292)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D292="","Sem data prometida",IF($D292&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H292" s="17"/>
-      <c r="I292" s="17"/>
-    </row>
-    <row r="293" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A293" s="16"/>
-      <c r="B293" s="17"/>
-      <c r="C293" s="15"/>
-      <c r="D293" s="15"/>
-      <c r="E293" s="15"/>
-      <c r="F293" s="16" t="str">
-        <f aca="false">IF(OR($A293="",$D293="",$E293=""),"",MAX(0,$E293-$D293))</f>
-        <v/>
-      </c>
-      <c r="G293" s="16" t="str">
-        <f aca="false">IF($A293="","",IF($E293&lt;&gt;"",IF(N($F293)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D293="","Sem data prometida",IF($D293&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H293" s="17"/>
-      <c r="I293" s="17"/>
-    </row>
-    <row r="294" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A294" s="16"/>
-      <c r="B294" s="17"/>
-      <c r="C294" s="15"/>
-      <c r="D294" s="15"/>
-      <c r="E294" s="15"/>
-      <c r="F294" s="16" t="str">
-        <f aca="false">IF(OR($A294="",$D294="",$E294=""),"",MAX(0,$E294-$D294))</f>
-        <v/>
-      </c>
-      <c r="G294" s="16" t="str">
-        <f aca="false">IF($A294="","",IF($E294&lt;&gt;"",IF(N($F294)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D294="","Sem data prometida",IF($D294&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H294" s="17"/>
-      <c r="I294" s="17"/>
-    </row>
-    <row r="295" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="16"/>
-      <c r="B295" s="17"/>
-      <c r="C295" s="15"/>
-      <c r="D295" s="15"/>
-      <c r="E295" s="15"/>
-      <c r="F295" s="16" t="str">
-        <f aca="false">IF(OR($A295="",$D295="",$E295=""),"",MAX(0,$E295-$D295))</f>
-        <v/>
-      </c>
-      <c r="G295" s="16" t="str">
-        <f aca="false">IF($A295="","",IF($E295&lt;&gt;"",IF(N($F295)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D295="","Sem data prometida",IF($D295&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H295" s="17"/>
-      <c r="I295" s="17"/>
-    </row>
-    <row r="296" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="16"/>
-      <c r="B296" s="17"/>
-      <c r="C296" s="15"/>
-      <c r="D296" s="15"/>
-      <c r="E296" s="15"/>
-      <c r="F296" s="16" t="str">
-        <f aca="false">IF(OR($A296="",$D296="",$E296=""),"",MAX(0,$E296-$D296))</f>
-        <v/>
-      </c>
-      <c r="G296" s="16" t="str">
-        <f aca="false">IF($A296="","",IF($E296&lt;&gt;"",IF(N($F296)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D296="","Sem data prometida",IF($D296&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H296" s="17"/>
-      <c r="I296" s="17"/>
-    </row>
-    <row r="297" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="16"/>
-      <c r="B297" s="17"/>
-      <c r="C297" s="15"/>
-      <c r="D297" s="15"/>
-      <c r="E297" s="15"/>
-      <c r="F297" s="16" t="str">
-        <f aca="false">IF(OR($A297="",$D297="",$E297=""),"",MAX(0,$E297-$D297))</f>
-        <v/>
-      </c>
-      <c r="G297" s="16" t="str">
-        <f aca="false">IF($A297="","",IF($E297&lt;&gt;"",IF(N($F297)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D297="","Sem data prometida",IF($D297&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H297" s="17"/>
-      <c r="I297" s="17"/>
-    </row>
-    <row r="298" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="16"/>
-      <c r="B298" s="17"/>
-      <c r="C298" s="15"/>
-      <c r="D298" s="15"/>
-      <c r="E298" s="15"/>
-      <c r="F298" s="16" t="str">
-        <f aca="false">IF(OR($A298="",$D298="",$E298=""),"",MAX(0,$E298-$D298))</f>
-        <v/>
-      </c>
-      <c r="G298" s="16" t="str">
-        <f aca="false">IF($A298="","",IF($E298&lt;&gt;"",IF(N($F298)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D298="","Sem data prometida",IF($D298&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H298" s="17"/>
-      <c r="I298" s="17"/>
-    </row>
-    <row r="299" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A299" s="16"/>
-      <c r="B299" s="17"/>
-      <c r="C299" s="15"/>
-      <c r="D299" s="15"/>
-      <c r="E299" s="15"/>
-      <c r="F299" s="16" t="str">
-        <f aca="false">IF(OR($A299="",$D299="",$E299=""),"",MAX(0,$E299-$D299))</f>
-        <v/>
-      </c>
-      <c r="G299" s="16" t="str">
-        <f aca="false">IF($A299="","",IF($E299&lt;&gt;"",IF(N($F299)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D299="","Sem data prometida",IF($D299&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H299" s="17"/>
-      <c r="I299" s="17"/>
-    </row>
-    <row r="300" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="16"/>
-      <c r="B300" s="17"/>
-      <c r="C300" s="15"/>
-      <c r="D300" s="15"/>
-      <c r="E300" s="15"/>
-      <c r="F300" s="16" t="str">
-        <f aca="false">IF(OR($A300="",$D300="",$E300=""),"",MAX(0,$E300-$D300))</f>
-        <v/>
-      </c>
-      <c r="G300" s="16" t="str">
-        <f aca="false">IF($A300="","",IF($E300&lt;&gt;"",IF(N($F300)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D300="","Sem data prometida",IF($D300&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H300" s="17"/>
-      <c r="I300" s="17"/>
-    </row>
-    <row r="301" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="16"/>
-      <c r="B301" s="17"/>
-      <c r="C301" s="15"/>
-      <c r="D301" s="15"/>
-      <c r="E301" s="15"/>
-      <c r="F301" s="16" t="str">
-        <f aca="false">IF(OR($A301="",$D301="",$E301=""),"",MAX(0,$E301-$D301))</f>
-        <v/>
-      </c>
-      <c r="G301" s="16" t="str">
-        <f aca="false">IF($A301="","",IF($E301&lt;&gt;"",IF(N($F301)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D301="","Sem data prometida",IF($D301&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H301" s="17"/>
-      <c r="I301" s="17"/>
-    </row>
-    <row r="302" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A302" s="16"/>
-      <c r="B302" s="17"/>
-      <c r="C302" s="15"/>
-      <c r="D302" s="15"/>
-      <c r="E302" s="15"/>
-      <c r="F302" s="16" t="str">
-        <f aca="false">IF(OR($A302="",$D302="",$E302=""),"",MAX(0,$E302-$D302))</f>
-        <v/>
-      </c>
-      <c r="G302" s="16" t="str">
-        <f aca="false">IF($A302="","",IF($E302&lt;&gt;"",IF(N($F302)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D302="","Sem data prometida",IF($D302&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H302" s="17"/>
-      <c r="I302" s="17"/>
-    </row>
-    <row r="303" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A303" s="16"/>
-      <c r="B303" s="17"/>
-      <c r="C303" s="15"/>
-      <c r="D303" s="15"/>
-      <c r="E303" s="15"/>
-      <c r="F303" s="16" t="str">
-        <f aca="false">IF(OR($A303="",$D303="",$E303=""),"",MAX(0,$E303-$D303))</f>
-        <v/>
-      </c>
-      <c r="G303" s="16" t="str">
-        <f aca="false">IF($A303="","",IF($E303&lt;&gt;"",IF(N($F303)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D303="","Sem data prometida",IF($D303&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H303" s="17"/>
-      <c r="I303" s="17"/>
-    </row>
-    <row r="304" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A304" s="16"/>
-      <c r="B304" s="17"/>
-      <c r="C304" s="15"/>
-      <c r="D304" s="15"/>
-      <c r="E304" s="15"/>
-      <c r="F304" s="16" t="str">
-        <f aca="false">IF(OR($A304="",$D304="",$E304=""),"",MAX(0,$E304-$D304))</f>
-        <v/>
-      </c>
-      <c r="G304" s="16" t="str">
-        <f aca="false">IF($A304="","",IF($E304&lt;&gt;"",IF(N($F304)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D304="","Sem data prometida",IF($D304&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H304" s="17"/>
-      <c r="I304" s="17"/>
-    </row>
-    <row r="305" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A305" s="16"/>
-      <c r="B305" s="17"/>
-      <c r="C305" s="15"/>
-      <c r="D305" s="15"/>
-      <c r="E305" s="15"/>
-      <c r="F305" s="16" t="str">
-        <f aca="false">IF(OR($A305="",$D305="",$E305=""),"",MAX(0,$E305-$D305))</f>
-        <v/>
-      </c>
-      <c r="G305" s="16" t="str">
-        <f aca="false">IF($A305="","",IF($E305&lt;&gt;"",IF(N($F305)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D305="","Sem data prometida",IF($D305&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H305" s="17"/>
-      <c r="I305" s="17"/>
-    </row>
-    <row r="306" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A306" s="16"/>
-      <c r="B306" s="17"/>
-      <c r="C306" s="15"/>
-      <c r="D306" s="15"/>
-      <c r="E306" s="15"/>
-      <c r="F306" s="16" t="str">
-        <f aca="false">IF(OR($A306="",$D306="",$E306=""),"",MAX(0,$E306-$D306))</f>
-        <v/>
-      </c>
-      <c r="G306" s="16" t="str">
-        <f aca="false">IF($A306="","",IF($E306&lt;&gt;"",IF(N($F306)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D306="","Sem data prometida",IF($D306&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H306" s="17"/>
-      <c r="I306" s="17"/>
-    </row>
-    <row r="307" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A307" s="16"/>
-      <c r="B307" s="17"/>
-      <c r="C307" s="15"/>
-      <c r="D307" s="15"/>
-      <c r="E307" s="15"/>
-      <c r="F307" s="16" t="str">
-        <f aca="false">IF(OR($A307="",$D307="",$E307=""),"",MAX(0,$E307-$D307))</f>
-        <v/>
-      </c>
-      <c r="G307" s="16" t="str">
-        <f aca="false">IF($A307="","",IF($E307&lt;&gt;"",IF(N($F307)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D307="","Sem data prometida",IF($D307&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H307" s="17"/>
-      <c r="I307" s="17"/>
-    </row>
-    <row r="308" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="16"/>
-      <c r="B308" s="17"/>
-      <c r="C308" s="15"/>
-      <c r="D308" s="15"/>
-      <c r="E308" s="15"/>
-      <c r="F308" s="16" t="str">
-        <f aca="false">IF(OR($A308="",$D308="",$E308=""),"",MAX(0,$E308-$D308))</f>
-        <v/>
-      </c>
-      <c r="G308" s="16" t="str">
-        <f aca="false">IF($A308="","",IF($E308&lt;&gt;"",IF(N($F308)&gt;0,"Entregue com atraso","Entregue no prazo"),IF($D308="","Sem data prometida",IF($D308&lt;$L$1,"ATRASADA","Aguardando"))))</f>
-        <v/>
-      </c>
-      <c r="H308" s="17"/>
-      <c r="I308" s="17"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A8:I308"/>
-  <mergeCells count="9">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A6:I6"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
-      <formula>0.85</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9:G308">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>$G9="Entregue no prazo"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
-      <formula>$G9="Entregue com atraso"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>$G9="ATRASADA"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
-      <formula>$G9="Aguardando"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
-      <formula>$G9="Sem data prometida"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F308">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>N($F9)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D308">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>AND($A9&lt;&gt;"",$D9&lt;&gt;"",$E9="",$D9&lt;$L$1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:I308">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
-      <formula>$E9&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Frota fora da lista — pode continuar." errorStyle="warning" errorTitle="Frota" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A9:A308" type="list">
-      <formula1>Listas!$A$2:$A$81</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
 </file>
--- a/planilha/Programacao_Diaria_Makro.xlsx
+++ b/planilha/Programacao_Diaria_Makro.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dia a dia'!$A$6:$H$706</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dia a dia'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dia a dia'!$A$1:$H$269</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dia a dia'!$A$1:$H$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2366,107 +2366,107 @@
       <c r="A49" s="16" t="n"/>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>F-425</t>
+          <t>F-1064</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Verificar pendências na rota de inspeção de setembro</t>
+          <t>Instalar indicadores de porca</t>
         </is>
       </c>
       <c r="D49" s="17" t="n"/>
       <c r="E49" s="19" t="n"/>
-      <c r="F49" s="18" t="n"/>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Luiz Paulo · Airton</t>
+        </is>
+      </c>
       <c r="G49" s="18" t="inlineStr">
         <is>
-          <t>Inspeção de setembro</t>
-        </is>
-      </c>
-      <c r="H49" s="18" t="inlineStr">
-        <is>
-          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="16" t="n"/>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>F-425</t>
+          <t>F-1064</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>Realizar preventiva da frota F-425</t>
+          <t>Substituir estepe</t>
         </is>
       </c>
       <c r="D50" s="17" t="n"/>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>007011</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Luiz Paulo · Airton</t>
+        </is>
+      </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
-        <is>
-          <t>Local: Matriz · Para programar · OS informadas: 007011, 007012, 007013 · ⚠️ Aguardando identificação da OS correspondente · Origem: WhatsApp 02/09</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="n"/>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="16" t="n"/>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>F-433</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>Verificar pendências na rota de inspeção de setembro</t>
+          <t>Realizar lubrificação geral</t>
         </is>
       </c>
       <c r="D51" s="17" t="n"/>
       <c r="E51" s="19" t="n"/>
-      <c r="F51" s="18" t="n"/>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
       <c r="G51" s="18" t="inlineStr">
         <is>
-          <t>Inspeção de setembro</t>
-        </is>
-      </c>
-      <c r="H51" s="18" t="inlineStr">
-        <is>
-          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="16" t="n"/>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>F-621</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>Verificar pendências na rota de inspeção de setembro</t>
+          <t>Montar ar condicionado</t>
         </is>
       </c>
       <c r="D52" s="17" t="n"/>
       <c r="E52" s="19" t="n"/>
-      <c r="F52" s="18" t="n"/>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Adilton</t>
+        </is>
+      </c>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>Inspeção de setembro</t>
+          <t>Programação 04/09</t>
         </is>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
+          <t>já existe "Trocar peças do ar condicionado" (OS 021570) em aberto nesta frota, esta é a montagem depois da troca</t>
         </is>
       </c>
     </row>
@@ -2474,25 +2474,29 @@
       <c r="A53" s="16" t="n"/>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>F-745</t>
+          <t>F-332</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>Verificar pendências na rota de inspeção de setembro</t>
+          <t>Verificar falha de ABD</t>
         </is>
       </c>
       <c r="D53" s="17" t="n"/>
       <c r="E53" s="19" t="n"/>
-      <c r="F53" s="18" t="n"/>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Thawan</t>
+        </is>
+      </c>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>Inspeção de setembro</t>
+          <t>Programação 04/09</t>
         </is>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
+          <t>⚠️ VERIFICAR a frota, F-332 não existia na lista</t>
         </is>
       </c>
     </row>
@@ -2500,29 +2504,25 @@
       <c r="A54" s="16" t="n"/>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-425</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>Corrigir iluminação da luz de freio traseira LE e revisar demais luzes</t>
+          <t>Verificar pendências na rota de inspeção de setembro</t>
         </is>
       </c>
       <c r="D54" s="17" t="n"/>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>007348</t>
-        </is>
-      </c>
+      <c r="E54" s="19" t="n"/>
       <c r="F54" s="18" t="n"/>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Inspeção de setembro</t>
         </is>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2530,29 @@
       <c r="A55" s="16" t="n"/>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-425</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>Substituir farol LE avariado</t>
+          <t>Realizar preventiva da frota F-425</t>
         </is>
       </c>
       <c r="D55" s="17" t="n"/>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>007355</t>
+          <t>007011</t>
         </is>
       </c>
       <c r="F55" s="18" t="n"/>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Preventiva</t>
         </is>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Peça 21035645 · realizar acompanhamento</t>
+          <t>Local: Matriz · Para programar · OS informadas: 007011, 007012, 007013 · ⚠️ Aguardando identificação da OS correspondente · Origem: WhatsApp 02/09</t>
         </is>
       </c>
     </row>
@@ -2560,29 +2560,25 @@
       <c r="A56" s="16" t="n"/>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-433</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>Fixar farol LD</t>
+          <t>Verificar pendências na rota de inspeção de setembro</t>
         </is>
       </c>
       <c r="D56" s="17" t="n"/>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>007357</t>
-        </is>
-      </c>
+      <c r="E56" s="19" t="n"/>
       <c r="F56" s="18" t="n"/>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Inspeção de setembro</t>
         </is>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
         </is>
       </c>
     </row>
@@ -2590,119 +2586,107 @@
       <c r="A57" s="16" t="n"/>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>Substituir farol de neblina LE avariado</t>
+          <t>Realizar lubrificação geral</t>
         </is>
       </c>
       <c r="D57" s="17" t="n"/>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>007358</t>
-        </is>
-      </c>
-      <c r="F57" s="18" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
       <c r="G57" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
-        <is>
-          <t>Peça 21297918 · realizar acompanhamento</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="16" t="n"/>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>Substituir paralama traseiro LE avariado</t>
+          <t>Reparar acabamento do teto</t>
         </is>
       </c>
       <c r="D58" s="17" t="n"/>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>007359</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Júnior</t>
+        </is>
+      </c>
       <c r="G58" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H58" s="18" t="inlineStr">
-        <is>
-          <t>Peça 812975614 · realizar acompanhamento</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="16" t="n"/>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-618</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>Corrigir e isolar fiação de iluminação do reboque exposta</t>
+          <t>Realizar lubrificação geral</t>
         </is>
       </c>
       <c r="D59" s="17" t="n"/>
-      <c r="E59" s="19" t="inlineStr">
-        <is>
-          <t>007362</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
       <c r="G59" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="n"/>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="16" t="n"/>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-618</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Corrigir iluminação interna das portas LE e LD</t>
+          <t>Continuar diagnóstico</t>
         </is>
       </c>
       <c r="D60" s="17" t="n"/>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>007363</t>
-        </is>
-      </c>
-      <c r="F60" s="18" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Thawan</t>
+        </is>
+      </c>
       <c r="G60" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Programação 04/09</t>
         </is>
       </c>
       <c r="H60" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>⚠️ VERIFICAR qual diagnóstico, não há nenhum em aberto na F-618 para continuar</t>
         </is>
       </c>
     </row>
@@ -2710,55 +2694,51 @@
       <c r="A61" s="16" t="n"/>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>F-817</t>
+          <t>F-618</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>Verificar pendências na rota de inspeção de setembro</t>
+          <t>Reparar carenagens</t>
         </is>
       </c>
       <c r="D61" s="17" t="n"/>
       <c r="E61" s="19" t="n"/>
-      <c r="F61" s="18" t="n"/>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Júnior</t>
+        </is>
+      </c>
       <c r="G61" s="18" t="inlineStr">
         <is>
-          <t>Inspeção de setembro</t>
-        </is>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="n"/>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="16" t="n"/>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-621</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Substituir vareta de nível de óleo avariada</t>
+          <t>Verificar pendências na rota de inspeção de setembro</t>
         </is>
       </c>
       <c r="D62" s="17" t="n"/>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>021400</t>
-        </is>
-      </c>
+      <c r="E62" s="19" t="n"/>
       <c r="F62" s="18" t="n"/>
       <c r="G62" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Inspeção de setembro</t>
         </is>
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
         </is>
       </c>
     </row>
@@ -2766,29 +2746,25 @@
       <c r="A63" s="16" t="n"/>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-745</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>Substituir junta da tampa de válvulas</t>
+          <t>Verificar pendências na rota de inspeção de setembro</t>
         </is>
       </c>
       <c r="D63" s="17" t="n"/>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>021402</t>
-        </is>
-      </c>
+      <c r="E63" s="19" t="n"/>
       <c r="F63" s="18" t="n"/>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Inspeção de setembro</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH · devido vazamento</t>
+          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
         </is>
       </c>
     </row>
@@ -2796,89 +2772,81 @@
       <c r="A64" s="16" t="n"/>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-814</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>Substituir válvula termostática e tampa do reservatório contaminado</t>
+          <t>Realizar lubrificação geral</t>
         </is>
       </c>
       <c r="D64" s="17" t="n"/>
-      <c r="E64" s="19" t="inlineStr">
-        <is>
-          <t>021403</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>Apenas HH</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="n"/>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="16" t="n"/>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-814</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>Substituir amortecedores do 3º eixo LE</t>
+          <t>Trocar retrovisor LD</t>
         </is>
       </c>
       <c r="D65" s="17" t="n"/>
-      <c r="E65" s="19" t="inlineStr">
-        <is>
-          <t>021404</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Júnior</t>
+        </is>
+      </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
-        </is>
-      </c>
-      <c r="H65" s="18" t="inlineStr">
-        <is>
-          <t>Apenas HH</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="n"/>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="16" t="n"/>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>Substituir amortecedores da cabine</t>
+          <t>Corrigir iluminação da luz de freio traseira LE e revisar demais luzes</t>
         </is>
       </c>
       <c r="D66" s="17" t="n"/>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>021405</t>
+          <t>007348</t>
         </is>
       </c>
       <c r="F66" s="18" t="n"/>
       <c r="G66" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H66" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH · horizontais traseiros e verticais dianteiros</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2854,29 @@
       <c r="A67" s="16" t="n"/>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>Substituir joystick de mudanças</t>
+          <t>Substituir farol LE avariado</t>
         </is>
       </c>
       <c r="D67" s="17" t="n"/>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>021406</t>
+          <t>007355</t>
         </is>
       </c>
       <c r="F67" s="18" t="n"/>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Peça 21035645 · realizar acompanhamento</t>
         </is>
       </c>
     </row>
@@ -2916,29 +2884,29 @@
       <c r="A68" s="16" t="n"/>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Sanar vazamento no tubo de enchimento / vedação do cárter</t>
+          <t>Fixar farol LD</t>
         </is>
       </c>
       <c r="D68" s="17" t="n"/>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>021407</t>
+          <t>007357</t>
         </is>
       </c>
       <c r="F68" s="18" t="n"/>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H68" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -2946,29 +2914,29 @@
       <c r="A69" s="16" t="n"/>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
+          <t>Substituir farol de neblina LE avariado</t>
         </is>
       </c>
       <c r="D69" s="17" t="n"/>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>021408</t>
+          <t>007358</t>
         </is>
       </c>
       <c r="F69" s="18" t="n"/>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Peça 21297918 · realizar acompanhamento</t>
         </is>
       </c>
     </row>
@@ -2976,29 +2944,29 @@
       <c r="A70" s="16" t="n"/>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>Fixar retrovisor inferior LD</t>
+          <t>Substituir paralama traseiro LE avariado</t>
         </is>
       </c>
       <c r="D70" s="17" t="n"/>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>021409</t>
+          <t>007359</t>
         </is>
       </c>
       <c r="F70" s="18" t="n"/>
       <c r="G70" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H70" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Peça 812975614 · realizar acompanhamento</t>
         </is>
       </c>
     </row>
@@ -3006,29 +2974,29 @@
       <c r="A71" s="16" t="n"/>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>Isolar fiação exposta do sensor de temperatura</t>
+          <t>Corrigir e isolar fiação de iluminação do reboque exposta</t>
         </is>
       </c>
       <c r="D71" s="17" t="n"/>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>021410</t>
+          <t>007362</t>
         </is>
       </c>
       <c r="F71" s="18" t="n"/>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -3036,29 +3004,29 @@
       <c r="A72" s="16" t="n"/>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Fixar caixa do chicote das unidades</t>
+          <t>Corrigir iluminação interna das portas LE e LD</t>
         </is>
       </c>
       <c r="D72" s="17" t="n"/>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>021412</t>
+          <t>007363</t>
         </is>
       </c>
       <c r="F72" s="18" t="n"/>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -3066,59 +3034,51 @@
       <c r="A73" s="16" t="n"/>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>Fixar módulo do motor</t>
+          <t>Realizar lubrificação geral</t>
         </is>
       </c>
       <c r="D73" s="17" t="n"/>
-      <c r="E73" s="19" t="inlineStr">
-        <is>
-          <t>021417</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
-        </is>
-      </c>
-      <c r="H73" s="18" t="inlineStr">
-        <is>
-          <t>Apenas HH</t>
-        </is>
-      </c>
+          <t>Programação 04/09</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="n"/>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="16" t="n"/>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-817</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
+          <t>Verificar pendências na rota de inspeção de setembro</t>
         </is>
       </c>
       <c r="D74" s="17" t="n"/>
-      <c r="E74" s="19" t="inlineStr">
-        <is>
-          <t>021416</t>
-        </is>
-      </c>
+      <c r="E74" s="19" t="n"/>
       <c r="F74" s="18" t="n"/>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
+          <t>Inspeção de setembro</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Verificar na rota de inspeção de setembro — sem pendências mapeadas</t>
         </is>
       </c>
     </row>
@@ -3131,13 +3091,13 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>Regular freios 3º eixo</t>
+          <t>Substituir vareta de nível de óleo avariada</t>
         </is>
       </c>
       <c r="D75" s="17" t="n"/>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>021420</t>
+          <t>021400</t>
         </is>
       </c>
       <c r="F75" s="18" t="n"/>
@@ -3161,13 +3121,13 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>Regular freios 1º eixo</t>
+          <t>Substituir junta da tampa de válvulas</t>
         </is>
       </c>
       <c r="D76" s="17" t="n"/>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>021430</t>
+          <t>021402</t>
         </is>
       </c>
       <c r="F76" s="18" t="n"/>
@@ -3178,7 +3138,7 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Apenas HH · devido vazamento</t>
         </is>
       </c>
     </row>
@@ -3191,13 +3151,13 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>Corrigir fixação da lameira traseira LE</t>
+          <t>Substituir válvula termostática e tampa do reservatório contaminado</t>
         </is>
       </c>
       <c r="D77" s="17" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>021431</t>
+          <t>021403</t>
         </is>
       </c>
       <c r="F77" s="18" t="n"/>
@@ -3221,13 +3181,13 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Reposicionar cabo do varão da válvula sensível à carga</t>
+          <t>Substituir amortecedores do 3º eixo LE</t>
         </is>
       </c>
       <c r="D78" s="17" t="n"/>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>021433</t>
+          <t>021404</t>
         </is>
       </c>
       <c r="F78" s="18" t="n"/>
@@ -3251,13 +3211,13 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>Fixar tampa superior do catalisador</t>
+          <t>Substituir amortecedores da cabine</t>
         </is>
       </c>
       <c r="D79" s="17" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>021435</t>
+          <t>021405</t>
         </is>
       </c>
       <c r="F79" s="18" t="n"/>
@@ -3268,7 +3228,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>Apenas HH</t>
+          <t>Apenas HH · horizontais traseiros e verticais dianteiros</t>
         </is>
       </c>
     </row>
@@ -3281,13 +3241,13 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>Reposicionar mangueira do dreno do AC</t>
+          <t>Substituir joystick de mudanças</t>
         </is>
       </c>
       <c r="D80" s="17" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>021436</t>
+          <t>021406</t>
         </is>
       </c>
       <c r="F80" s="18" t="n"/>
@@ -3311,13 +3271,13 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>Corrigir iluminação interna da cabine</t>
+          <t>Sanar vazamento no tubo de enchimento / vedação do cárter</t>
         </is>
       </c>
       <c r="D81" s="17" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>021438</t>
+          <t>021407</t>
         </is>
       </c>
       <c r="F81" s="18" t="n"/>
@@ -3341,13 +3301,13 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>Substituir faixa refletiva do para-choque traseiro</t>
+          <t>Completar óleo da direção hidráulica e sanar vazamento do reservatório</t>
         </is>
       </c>
       <c r="D82" s="17" t="n"/>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>021442</t>
+          <t>021408</t>
         </is>
       </c>
       <c r="F82" s="18" t="n"/>
@@ -3371,20 +3331,16 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>Recuperar barra V dianteira e traseira</t>
+          <t>Fixar retrovisor inferior LD</t>
         </is>
       </c>
       <c r="D83" s="17" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>21378</t>
-        </is>
-      </c>
-      <c r="F83" s="18" t="inlineStr">
-        <is>
-          <t>Cardan Nordeste (externo)</t>
-        </is>
-      </c>
+          <t>021409</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="n"/>
       <c r="G83" s="18" t="inlineStr">
         <is>
           <t>Pendências de inspeção</t>
@@ -3392,7 +3348,7 @@
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>Terceirizada — Cardan Nordeste · devido folga</t>
+          <t>Apenas HH</t>
         </is>
       </c>
     </row>
@@ -3405,20 +3361,16 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>Recuperar barra de direção longa</t>
+          <t>Isolar fiação exposta do sensor de temperatura</t>
         </is>
       </c>
       <c r="D84" s="17" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>21378</t>
-        </is>
-      </c>
-      <c r="F84" s="18" t="inlineStr">
-        <is>
-          <t>Cardan Nordeste (externo)</t>
-        </is>
-      </c>
+          <t>021410</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="n"/>
       <c r="G84" s="18" t="inlineStr">
         <is>
           <t>Pendências de inspeção</t>
@@ -3426,7 +3378,7 @@
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>Terceirizada — Cardan Nordeste · coifa rasgada</t>
+          <t>Apenas HH</t>
         </is>
       </c>
     </row>
@@ -3439,20 +3391,16 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>Substituir espelho contrapoeira 2º eixo LE</t>
+          <t>Fixar caixa do chicote das unidades</t>
         </is>
       </c>
       <c r="D85" s="17" t="n"/>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>21378</t>
-        </is>
-      </c>
-      <c r="F85" s="18" t="inlineStr">
-        <is>
-          <t>Cardan Nordeste (externo)</t>
-        </is>
-      </c>
+          <t>021412</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="n"/>
       <c r="G85" s="18" t="inlineStr">
         <is>
           <t>Pendências de inspeção</t>
@@ -3460,7 +3408,7 @@
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>Terceirizada — Cardan Nordeste</t>
+          <t>Apenas HH</t>
         </is>
       </c>
     </row>
@@ -3473,20 +3421,16 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Substituir lonas de freio 1º eixo LD e LE</t>
+          <t>Fixar módulo do motor</t>
         </is>
       </c>
       <c r="D86" s="17" t="n"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>21378</t>
-        </is>
-      </c>
-      <c r="F86" s="18" t="inlineStr">
-        <is>
-          <t>Cardan Nordeste (externo)</t>
-        </is>
-      </c>
+          <t>021417</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="n"/>
       <c r="G86" s="18" t="inlineStr">
         <is>
           <t>Pendências de inspeção</t>
@@ -3494,7 +3438,7 @@
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>Terceirizada — Cardan Nordeste</t>
+          <t>Apenas HH</t>
         </is>
       </c>
     </row>
@@ -3507,20 +3451,16 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>Recuperar banco do motorista</t>
+          <t>Recuperar / fabricar base de proteção das conexões da bomba de ARLA</t>
         </is>
       </c>
       <c r="D87" s="17" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>21378</t>
-        </is>
-      </c>
-      <c r="F87" s="18" t="inlineStr">
-        <is>
-          <t>Rodo Ceará (externo)</t>
-        </is>
-      </c>
+          <t>021416</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="n"/>
       <c r="G87" s="18" t="inlineStr">
         <is>
           <t>Pendências de inspeção</t>
@@ -3528,7 +3468,7 @@
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>Terceirizada — Rodo Ceará · fixação do assento e tapeçaria</t>
+          <t>Apenas HH</t>
         </is>
       </c>
     </row>
@@ -3536,18 +3476,18 @@
       <c r="A88" s="16" t="n"/>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>Desobstruir esguichos dos limpadores de para-brisas</t>
+          <t>Regular freios 3º eixo</t>
         </is>
       </c>
       <c r="D88" s="17" t="n"/>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>021390</t>
+          <t>021420</t>
         </is>
       </c>
       <c r="F88" s="18" t="n"/>
@@ -3556,24 +3496,28 @@
           <t>Pendências de inspeção</t>
         </is>
       </c>
-      <c r="H88" s="18" t="n"/>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="16" t="n"/>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>Instalar lameiras dianteiras</t>
+          <t>Regular freios 1º eixo</t>
         </is>
       </c>
       <c r="D89" s="17" t="n"/>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>021394</t>
+          <t>021430</t>
         </is>
       </c>
       <c r="F89" s="18" t="n"/>
@@ -3582,24 +3526,28 @@
           <t>Pendências de inspeção</t>
         </is>
       </c>
-      <c r="H89" s="18" t="n"/>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="16" t="n"/>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>Instalar indicadores de porcas folgadas nas rodas</t>
+          <t>Corrigir fixação da lameira traseira LE</t>
         </is>
       </c>
       <c r="D90" s="17" t="n"/>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>021396</t>
+          <t>021431</t>
         </is>
       </c>
       <c r="F90" s="18" t="n"/>
@@ -3608,24 +3556,28 @@
           <t>Pendências de inspeção</t>
         </is>
       </c>
-      <c r="H90" s="18" t="n"/>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="16" t="n"/>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>Regular freios do terceiro eixo LE e LD</t>
+          <t>Reposicionar cabo do varão da válvula sensível à carga</t>
         </is>
       </c>
       <c r="D91" s="17" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>021397</t>
+          <t>021433</t>
         </is>
       </c>
       <c r="F91" s="18" t="n"/>
@@ -3634,250 +3586,350 @@
           <t>Pendências de inspeção</t>
         </is>
       </c>
-      <c r="H91" s="18" t="n"/>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="16" t="n"/>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>Verificado vestígio de óleo no reservatório de ar, ficando em observação recuperar o compressor pneumático</t>
+          <t>Fixar tampa superior do catalisador</t>
         </is>
       </c>
       <c r="D92" s="17" t="n"/>
-      <c r="E92" s="19" t="n"/>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>021435</t>
+        </is>
+      </c>
       <c r="F92" s="18" t="n"/>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H92" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="16" t="n"/>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C93" s="18" t="inlineStr">
         <is>
-          <t>Realizar lavagem para verificação de vazamento de óleo diesel na dianteira do motor LE</t>
+          <t>Reposicionar mangueira do dreno do AC</t>
         </is>
       </c>
       <c r="D93" s="17" t="n"/>
-      <c r="E93" s="19" t="n"/>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>021436</t>
+        </is>
+      </c>
       <c r="F93" s="18" t="n"/>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H93" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="16" t="n"/>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>Realizar lavagem e verificar vazamento nas juntas das tampas de válvulas, se é escorrido do vazamento de óleo diesel</t>
+          <t>Corrigir iluminação interna da cabine</t>
         </is>
       </c>
       <c r="D94" s="17" t="n"/>
-      <c r="E94" s="19" t="n"/>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>021438</t>
+        </is>
+      </c>
       <c r="F94" s="18" t="n"/>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H94" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="16" t="n"/>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>Corrigir engate das marchas: substituir pino de bloqueio de marcha, realizar testes e concluir diagnóstico</t>
+          <t>Substituir faixa refletiva do para-choque traseiro</t>
         </is>
       </c>
       <c r="D95" s="17" t="n"/>
-      <c r="E95" s="19" t="n"/>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>021442</t>
+        </is>
+      </c>
       <c r="F95" s="18" t="n"/>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H95" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>Apenas HH</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="16" t="n"/>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>Substituir mangote superior do radiador ressecado</t>
+          <t>Recuperar barra V dianteira e traseira</t>
         </is>
       </c>
       <c r="D96" s="17" t="n"/>
-      <c r="E96" s="19" t="n"/>
-      <c r="F96" s="18" t="n"/>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>21378</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Cardan Nordeste (externo)</t>
+        </is>
+      </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H96" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>Terceirizada — Cardan Nordeste · devido folga</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="16" t="n"/>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>Substituir farol LE avariado</t>
+          <t>Recuperar barra de direção longa</t>
         </is>
       </c>
       <c r="D97" s="17" t="n"/>
-      <c r="E97" s="19" t="n"/>
-      <c r="F97" s="18" t="n"/>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>21378</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Cardan Nordeste (externo)</t>
+        </is>
+      </c>
       <c r="G97" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H97" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>Terceirizada — Cardan Nordeste · coifa rasgada</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="16" t="n"/>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>Fixar lanterna do pisca LE</t>
+          <t>Substituir espelho contrapoeira 2º eixo LE</t>
         </is>
       </c>
       <c r="D98" s="17" t="n"/>
-      <c r="E98" s="19" t="n"/>
-      <c r="F98" s="18" t="n"/>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>21378</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Cardan Nordeste (externo)</t>
+        </is>
+      </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H98" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>Terceirizada — Cardan Nordeste</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="16" t="n"/>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>Instalar lanternas traseiras e placa de trânsito</t>
+          <t>Substituir lonas de freio 1º eixo LD e LE</t>
         </is>
       </c>
       <c r="D99" s="17" t="n"/>
-      <c r="E99" s="19" t="n"/>
-      <c r="F99" s="18" t="n"/>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>21378</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>Cardan Nordeste (externo)</t>
+        </is>
+      </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H99" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>Terceirizada — Cardan Nordeste</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="16" t="n"/>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>Fixar base do chicote elétrico e das mangueiras da carreta</t>
+          <t>Recuperar banco do motorista</t>
         </is>
       </c>
       <c r="D100" s="17" t="n"/>
-      <c r="E100" s="19" t="n"/>
-      <c r="F100" s="18" t="n"/>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>21378</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Rodo Ceará (externo)</t>
+        </is>
+      </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H100" s="18" t="n"/>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>Terceirizada — Rodo Ceará · fixação do assento e tapeçaria</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="16" t="n"/>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>Fixar tubo de enchimento frontal</t>
+          <t>Desobstruir esguichos dos limpadores de para-brisas</t>
         </is>
       </c>
       <c r="D101" s="17" t="n"/>
-      <c r="E101" s="19" t="n"/>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>021390</t>
+        </is>
+      </c>
       <c r="F101" s="18" t="n"/>
       <c r="G101" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H101" s="18" t="inlineStr">
-        <is>
-          <t>evitando danificar o mesmo com atrito da ventoinha</t>
-        </is>
-      </c>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="n"/>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="16" t="n"/>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>Reposicionar e instalar cardan do veículo</t>
+          <t>Instalar lameiras dianteiras</t>
         </is>
       </c>
       <c r="D102" s="17" t="n"/>
-      <c r="E102" s="19" t="n"/>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>021394</t>
+        </is>
+      </c>
       <c r="F102" s="18" t="n"/>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
+          <t>Pendências de inspeção</t>
         </is>
       </c>
       <c r="H102" s="18" t="n"/>
@@ -3886,57 +3938,53 @@
       <c r="A103" s="16" t="n"/>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C103" s="18" t="inlineStr">
         <is>
-          <t>Substituir anéis de vedação das unidades</t>
+          <t>Instalar indicadores de porcas folgadas nas rodas</t>
         </is>
       </c>
       <c r="D103" s="17" t="n"/>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>021396</t>
         </is>
       </c>
       <c r="F103" s="18" t="n"/>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H103" s="18" t="inlineStr">
-        <is>
-          <t>OS 7166 · devido vazamento nas unidades · peças A 023 997 64 48 (6 unidades) e A 023 997 65 48 · ⚠️ texto veio cortado do PDF de inspeção</t>
-        </is>
-      </c>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="n"/>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="16" t="n"/>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>Lavar conjunto do filtro racor e verificar vazamento</t>
+          <t>Regular freios do terceiro eixo LE e LD</t>
         </is>
       </c>
       <c r="D104" s="17" t="n"/>
-      <c r="E104" s="19" t="n"/>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>021397</t>
+        </is>
+      </c>
       <c r="F104" s="18" t="n"/>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE CARTEIRA</t>
-        </is>
-      </c>
-      <c r="H104" s="18" t="inlineStr">
-        <is>
-          <t>Peça A 000 470 24 90 · realizar acompanhamento</t>
-        </is>
-      </c>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="n"/>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="16" t="n"/>
@@ -3947,26 +3995,18 @@
       </c>
       <c r="C105" s="18" t="inlineStr">
         <is>
-          <t>Recuperar barra de direção curta com desgaste</t>
+          <t>Verificado vestígio de óleo no reservatório de ar, ficando em observação recuperar o compressor pneumático</t>
         </is>
       </c>
       <c r="D105" s="17" t="n"/>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>7185</t>
-        </is>
-      </c>
+      <c r="E105" s="19" t="n"/>
       <c r="F105" s="18" t="n"/>
       <c r="G105" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H105" s="18" t="inlineStr">
-        <is>
-          <t>OS 7185 · serviço empresa especializada</t>
-        </is>
-      </c>
+      <c r="H105" s="18" t="n"/>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="16" t="n"/>
@@ -3977,26 +4017,18 @@
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>Recuperar barra de direção longa com desgaste</t>
+          <t>Realizar lavagem para verificação de vazamento de óleo diesel na dianteira do motor LE</t>
         </is>
       </c>
       <c r="D106" s="17" t="n"/>
-      <c r="E106" s="19" t="inlineStr">
-        <is>
-          <t>7185</t>
-        </is>
-      </c>
+      <c r="E106" s="19" t="n"/>
       <c r="F106" s="18" t="n"/>
       <c r="G106" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H106" s="18" t="inlineStr">
-        <is>
-          <t>OS 7185 · serviço empresa especializada</t>
-        </is>
-      </c>
+      <c r="H106" s="18" t="n"/>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="16" t="n"/>
@@ -4007,26 +4039,18 @@
       </c>
       <c r="C107" s="18" t="inlineStr">
         <is>
-          <t>Repor espelho retrovisor inferior LE</t>
+          <t>Realizar lavagem e verificar vazamento nas juntas das tampas de válvulas, se é escorrido do vazamento de óleo diesel</t>
         </is>
       </c>
       <c r="D107" s="17" t="n"/>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>7168</t>
-        </is>
-      </c>
+      <c r="E107" s="19" t="n"/>
       <c r="F107" s="18" t="n"/>
       <c r="G107" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H107" s="18" t="inlineStr">
-        <is>
-          <t>OS 7168 · peças A 000 810 24 79 e A 002 811 31 33 (retrovisor auxiliar completo)</t>
-        </is>
-      </c>
+      <c r="H107" s="18" t="n"/>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="16" t="n"/>
@@ -4037,26 +4061,18 @@
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>Repor parafuso de fixação do painel frontal</t>
+          <t>Corrigir engate das marchas: substituir pino de bloqueio de marcha, realizar testes e concluir diagnóstico</t>
         </is>
       </c>
       <c r="D108" s="17" t="n"/>
-      <c r="E108" s="19" t="inlineStr">
-        <is>
-          <t>7189</t>
-        </is>
-      </c>
+      <c r="E108" s="19" t="n"/>
       <c r="F108" s="18" t="n"/>
       <c r="G108" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H108" s="18" t="inlineStr">
-        <is>
-          <t>OS 7189 · serviço interno Matriz</t>
-        </is>
-      </c>
+      <c r="H108" s="18" t="n"/>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="16" t="n"/>
@@ -4067,26 +4083,18 @@
       </c>
       <c r="C109" s="18" t="inlineStr">
         <is>
-          <t>Corrigir instalação elétrica da tomada 12V e do acendedor de cigarros</t>
+          <t>Substituir mangote superior do radiador ressecado</t>
         </is>
       </c>
       <c r="D109" s="17" t="n"/>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>7171</t>
-        </is>
-      </c>
+      <c r="E109" s="19" t="n"/>
       <c r="F109" s="18" t="n"/>
       <c r="G109" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H109" s="18" t="inlineStr">
-        <is>
-          <t>OS 7171 · serviço interno Matriz/A 694 820 01 53/A 696 825 01 54</t>
-        </is>
-      </c>
+      <c r="H109" s="18" t="n"/>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="16" t="n"/>
@@ -4097,26 +4105,18 @@
       </c>
       <c r="C110" s="18" t="inlineStr">
         <is>
-          <t>Retirar borracha inferior da cabine</t>
+          <t>Substituir farol LE avariado</t>
         </is>
       </c>
       <c r="D110" s="17" t="n"/>
-      <c r="E110" s="19" t="inlineStr">
-        <is>
-          <t>7193</t>
-        </is>
-      </c>
+      <c r="E110" s="19" t="n"/>
       <c r="F110" s="18" t="n"/>
       <c r="G110" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H110" s="18" t="inlineStr">
-        <is>
-          <t>OS 7193 · devido atrito com o reservatório de arrefecimento · serviço interno Matriz · ⚠️ texto veio cortado do PDF de inspeção</t>
-        </is>
-      </c>
+      <c r="H110" s="18" t="n"/>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="16" t="n"/>
@@ -4127,26 +4127,18 @@
       </c>
       <c r="C111" s="18" t="inlineStr">
         <is>
-          <t>Corrigir feixes de molas dianteiros: LE com mais molas</t>
+          <t>Fixar lanterna do pisca LE</t>
         </is>
       </c>
       <c r="D111" s="17" t="n"/>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>7185</t>
-        </is>
-      </c>
+      <c r="E111" s="19" t="n"/>
       <c r="F111" s="18" t="n"/>
       <c r="G111" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H111" s="18" t="inlineStr">
-        <is>
-          <t>OS 7185 · serviço empresa especializada · devido transporte da lança do munck</t>
-        </is>
-      </c>
+      <c r="H111" s="18" t="n"/>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="16" t="n"/>
@@ -4157,26 +4149,18 @@
       </c>
       <c r="C112" s="18" t="inlineStr">
         <is>
-          <t>Retirar espelhos das rodas traseiras</t>
+          <t>Instalar lanternas traseiras e placa de trânsito</t>
         </is>
       </c>
       <c r="D112" s="17" t="n"/>
-      <c r="E112" s="19" t="inlineStr">
-        <is>
-          <t>7190</t>
-        </is>
-      </c>
+      <c r="E112" s="19" t="n"/>
       <c r="F112" s="18" t="n"/>
       <c r="G112" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H112" s="18" t="inlineStr">
-        <is>
-          <t>OS 7190 · especialmente o LE · para melhor visualização do desgaste das lonas de freio · serviço interno Matriz · ⚠️ texto veio cortado do PDF de inspeção</t>
-        </is>
-      </c>
+      <c r="H112" s="18" t="n"/>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="16" t="n"/>
@@ -4187,26 +4171,18 @@
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>Regular freios segundo eixo LD</t>
+          <t>Fixar base do chicote elétrico e das mangueiras da carreta</t>
         </is>
       </c>
       <c r="D113" s="17" t="n"/>
-      <c r="E113" s="19" t="inlineStr">
-        <is>
-          <t>7205</t>
-        </is>
-      </c>
+      <c r="E113" s="19" t="n"/>
       <c r="F113" s="18" t="n"/>
       <c r="G113" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H113" s="18" t="inlineStr">
-        <is>
-          <t>OS 7205 · serviço interno Matriz</t>
-        </is>
-      </c>
+      <c r="H113" s="18" t="n"/>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="16" t="n"/>
@@ -4217,15 +4193,11 @@
       </c>
       <c r="C114" s="18" t="inlineStr">
         <is>
-          <t>Repor parafuso da bieleta traseira LE</t>
+          <t>Fixar tubo de enchimento frontal</t>
         </is>
       </c>
       <c r="D114" s="17" t="n"/>
-      <c r="E114" s="19" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
+      <c r="E114" s="19" t="n"/>
       <c r="F114" s="18" t="n"/>
       <c r="G114" s="18" t="inlineStr">
         <is>
@@ -4234,7 +4206,7 @@
       </c>
       <c r="H114" s="18" t="inlineStr">
         <is>
-          <t>fixação com a barra estabilizadora · OS 7192 · serviço interno Matriz</t>
+          <t>evitando danificar o mesmo com atrito da ventoinha</t>
         </is>
       </c>
     </row>
@@ -4247,26 +4219,18 @@
       </c>
       <c r="C115" s="18" t="inlineStr">
         <is>
-          <t>Repor acabamento das abraçadeiras do retrovisor LD</t>
+          <t>Reposicionar e instalar cardan do veículo</t>
         </is>
       </c>
       <c r="D115" s="17" t="n"/>
-      <c r="E115" s="19" t="inlineStr">
-        <is>
-          <t>7168</t>
-        </is>
-      </c>
+      <c r="E115" s="19" t="n"/>
       <c r="F115" s="18" t="n"/>
       <c r="G115" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE CARTEIRA</t>
         </is>
       </c>
-      <c r="H115" s="18" t="inlineStr">
-        <is>
-          <t>OS 7168 · A 000 811 36 07</t>
-        </is>
-      </c>
+      <c r="H115" s="18" t="n"/>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="16" t="n"/>
@@ -4277,11 +4241,15 @@
       </c>
       <c r="C116" s="18" t="inlineStr">
         <is>
-          <t>Substituir janela de inspeção frontal</t>
+          <t>Substituir anéis de vedação das unidades</t>
         </is>
       </c>
       <c r="D116" s="17" t="n"/>
-      <c r="E116" s="19" t="n"/>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>7166</t>
+        </is>
+      </c>
       <c r="F116" s="18" t="n"/>
       <c r="G116" s="18" t="inlineStr">
         <is>
@@ -4290,7 +4258,7 @@
       </c>
       <c r="H116" s="18" t="inlineStr">
         <is>
-          <t>A 940 888 11 23</t>
+          <t>OS 7166 · devido vazamento nas unidades · peças A 023 997 64 48 (6 unidades) e A 023 997 65 48 · ⚠️ texto veio cortado do PDF de inspeção</t>
         </is>
       </c>
     </row>
@@ -4303,15 +4271,11 @@
       </c>
       <c r="C117" s="18" t="inlineStr">
         <is>
-          <t>Repor acabamento inferior do braço do retrovisor LD</t>
+          <t>Lavar conjunto do filtro racor e verificar vazamento</t>
         </is>
       </c>
       <c r="D117" s="17" t="n"/>
-      <c r="E117" s="19" t="inlineStr">
-        <is>
-          <t>7168</t>
-        </is>
-      </c>
+      <c r="E117" s="19" t="n"/>
       <c r="F117" s="18" t="n"/>
       <c r="G117" s="18" t="inlineStr">
         <is>
@@ -4320,7 +4284,7 @@
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>OS 7168 · A 000 811 04 61</t>
+          <t>Peça A 000 470 24 90 · realizar acompanhamento</t>
         </is>
       </c>
     </row>
@@ -4333,13 +4297,13 @@
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>Reapertar parafusos de fixação do paralama dianteiro LD</t>
+          <t>Recuperar barra de direção curta com desgaste</t>
         </is>
       </c>
       <c r="D118" s="17" t="n"/>
       <c r="E118" s="19" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="F118" s="18" t="n"/>
@@ -4350,7 +4314,7 @@
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>OS 7195 · serviço interno Matriz</t>
+          <t>OS 7185 · serviço empresa especializada</t>
         </is>
       </c>
     </row>
@@ -4363,13 +4327,13 @@
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>Repor borracha de vedação da porta LD</t>
+          <t>Recuperar barra de direção longa com desgaste</t>
         </is>
       </c>
       <c r="D119" s="17" t="n"/>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="F119" s="18" t="n"/>
@@ -4380,7 +4344,7 @@
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>OS 7168 · peça A 958 721 00 80 (2 unidades)</t>
+          <t>OS 7185 · serviço empresa especializada</t>
         </is>
       </c>
     </row>
@@ -4393,13 +4357,13 @@
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>Fixar acabamento da tomada OBD</t>
+          <t>Repor espelho retrovisor inferior LE</t>
         </is>
       </c>
       <c r="D120" s="17" t="n"/>
       <c r="E120" s="19" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F120" s="18" t="n"/>
@@ -4410,7 +4374,7 @@
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>OS 7196 · serviço interno Matriz</t>
+          <t>OS 7168 · peças A 000 810 24 79 e A 002 811 31 33 (retrovisor auxiliar completo)</t>
         </is>
       </c>
     </row>
@@ -4423,13 +4387,13 @@
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>Retirar manta inferior da cabine</t>
+          <t>Repor parafuso de fixação do painel frontal</t>
         </is>
       </c>
       <c r="D121" s="17" t="n"/>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="F121" s="18" t="n"/>
@@ -4440,7 +4404,7 @@
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>OS 7197 · serviço interno Matriz</t>
+          <t>OS 7189 · serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -4453,13 +4417,13 @@
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>Substituir buchas da barra estabilizadora dianteira</t>
+          <t>Corrigir instalação elétrica da tomada 12V e do acendedor de cigarros</t>
         </is>
       </c>
       <c r="D122" s="17" t="n"/>
       <c r="E122" s="19" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="F122" s="18" t="n"/>
@@ -4470,7 +4434,7 @@
       </c>
       <c r="H122" s="18" t="inlineStr">
         <is>
-          <t>OS 7185 · serviço empresa especializada</t>
+          <t>OS 7171 · serviço interno Matriz/A 694 820 01 53/A 696 825 01 54</t>
         </is>
       </c>
     </row>
@@ -4483,11 +4447,15 @@
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>Substituir letreiro do modelo Axor "3344"</t>
+          <t>Retirar borracha inferior da cabine</t>
         </is>
       </c>
       <c r="D123" s="17" t="n"/>
-      <c r="E123" s="19" t="n"/>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>7193</t>
+        </is>
+      </c>
       <c r="F123" s="18" t="n"/>
       <c r="G123" s="18" t="inlineStr">
         <is>
@@ -4496,7 +4464,7 @@
       </c>
       <c r="H123" s="18" t="inlineStr">
         <is>
-          <t>Peça A 943 817 13 14 · certificar com fornecedor</t>
+          <t>OS 7193 · devido atrito com o reservatório de arrefecimento · serviço interno Matriz · ⚠️ texto veio cortado do PDF de inspeção</t>
         </is>
       </c>
     </row>
@@ -4509,11 +4477,15 @@
       </c>
       <c r="C124" s="18" t="inlineStr">
         <is>
-          <t>Recuperar pisante do estribo LD avariado</t>
+          <t>Corrigir feixes de molas dianteiros: LE com mais molas</t>
         </is>
       </c>
       <c r="D124" s="17" t="n"/>
-      <c r="E124" s="19" t="n"/>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>7185</t>
+        </is>
+      </c>
       <c r="F124" s="18" t="n"/>
       <c r="G124" s="18" t="inlineStr">
         <is>
@@ -4522,7 +4494,7 @@
       </c>
       <c r="H124" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>OS 7185 · serviço empresa especializada · devido transporte da lança do munck</t>
         </is>
       </c>
     </row>
@@ -4530,806 +4502,700 @@
       <c r="A125" s="16" t="n"/>
       <c r="B125" s="17" t="inlineStr">
         <is>
-          <t>F-968</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C125" s="18" t="inlineStr">
         <is>
-          <t>Bater e validar as pendências da inspeção realizada em Mossoró</t>
+          <t>Retirar espelhos das rodas traseiras</t>
         </is>
       </c>
       <c r="D125" s="17" t="n"/>
-      <c r="E125" s="19" t="n"/>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>7190</t>
+        </is>
+      </c>
       <c r="F125" s="18" t="n"/>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t>Inspeção Mossoró</t>
-        </is>
-      </c>
-      <c r="H125" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>OS 7190 · especialmente o LE · para melhor visualização do desgaste das lonas de freio · serviço interno Matriz · ⚠️ texto veio cortado do PDF de inspeção</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="21" customHeight="1">
       <c r="A126" s="16" t="n"/>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR JUNTA DAS TAMPAS DE VALVULA COM VAZAMENTO</t>
+          <t>Regular freios segundo eixo LD</t>
         </is>
       </c>
       <c r="D126" s="17" t="n"/>
       <c r="E126" s="19" t="inlineStr">
         <is>
-          <t>007397</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="F126" s="18" t="n"/>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H126" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
+          <t>OS 7205 · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="21" customHeight="1">
       <c r="A127" s="16" t="n"/>
       <c r="B127" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR MANGUEIRA DO TUBO DO RADIADOR COM VAZAMENTO</t>
+          <t>Repor parafuso da bieleta traseira LE</t>
         </is>
       </c>
       <c r="D127" s="17" t="n"/>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t>007400</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="F127" s="18" t="n"/>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H127" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="inlineStr">
+        <is>
+          <t>fixação com a barra estabilizadora · OS 7192 · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="21" customHeight="1">
       <c r="A128" s="16" t="n"/>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR MANGOTE INFERIOR DO RADIADOR RESSECADO E COM VAZAMENTO</t>
+          <t>Repor acabamento das abraçadeiras do retrovisor LD</t>
         </is>
       </c>
       <c r="D128" s="17" t="n"/>
       <c r="E128" s="19" t="inlineStr">
         <is>
-          <t>007400</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F128" s="18" t="n"/>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H128" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="inlineStr">
+        <is>
+          <t>OS 7168 · A 000 811 36 07</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="21" customHeight="1">
       <c r="A129" s="16" t="n"/>
       <c r="B129" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR JUNTA DA TAMPA DO CUBO DE RODA DIANTEIRO LD COM VAZAMENTO</t>
+          <t>Substituir janela de inspeção frontal</t>
         </is>
       </c>
       <c r="D129" s="17" t="n"/>
-      <c r="E129" s="19" t="inlineStr">
-        <is>
-          <t>007401</t>
-        </is>
-      </c>
+      <c r="E129" s="19" t="n"/>
       <c r="F129" s="18" t="n"/>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H129" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H129" s="18" t="inlineStr">
+        <is>
+          <t>A 940 888 11 23</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="21" customHeight="1">
       <c r="A130" s="16" t="n"/>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR LANTERNA LATERAL LD</t>
+          <t>Repor acabamento inferior do braço do retrovisor LD</t>
         </is>
       </c>
       <c r="D130" s="17" t="n"/>
       <c r="E130" s="19" t="inlineStr">
         <is>
-          <t>007402</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F130" s="18" t="n"/>
       <c r="G130" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H130" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr">
+        <is>
+          <t>OS 7168 · A 000 811 04 61</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="21" customHeight="1">
       <c r="A131" s="16" t="n"/>
       <c r="B131" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR TAMPA DE ABASTECIMENTO DE OLÉO COM VEDAÇÃO GASTA</t>
+          <t>Reapertar parafusos de fixação do paralama dianteiro LD</t>
         </is>
       </c>
       <c r="D131" s="17" t="n"/>
       <c r="E131" s="19" t="inlineStr">
         <is>
-          <t>007403</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="F131" s="18" t="n"/>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H131" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>OS 7195 · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="21" customHeight="1">
       <c r="A132" s="16" t="n"/>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR BUCHAS DA BARRA ESTABILIZADORA DIANTEIRA GASTAS</t>
+          <t>Repor borracha de vedação da porta LD</t>
         </is>
       </c>
       <c r="D132" s="17" t="n"/>
       <c r="E132" s="19" t="inlineStr">
         <is>
-          <t>007404</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F132" s="18" t="n"/>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H132" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr">
+        <is>
+          <t>OS 7168 · peça A 958 721 00 80 (2 unidades)</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="21" customHeight="1">
       <c r="A133" s="16" t="n"/>
       <c r="B133" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR PALHETAS DO LIMPADOR DE PARABRISA</t>
+          <t>Fixar acabamento da tomada OBD</t>
         </is>
       </c>
       <c r="D133" s="17" t="n"/>
       <c r="E133" s="19" t="inlineStr">
         <is>
-          <t>007405</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="F133" s="18" t="n"/>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H133" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>OS 7196 · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="21" customHeight="1">
       <c r="A134" s="16" t="n"/>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR BORRACHA DE VEDAÇÃO DA PORTA</t>
+          <t>Retirar manta inferior da cabine</t>
         </is>
       </c>
       <c r="D134" s="17" t="n"/>
       <c r="E134" s="19" t="inlineStr">
         <is>
-          <t>007406</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F134" s="18" t="n"/>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H134" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="inlineStr">
+        <is>
+          <t>OS 7197 · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="21" customHeight="1">
       <c r="A135" s="16" t="n"/>
       <c r="B135" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR JANELA DE INSPEÇÃO FRONTAL</t>
+          <t>Substituir buchas da barra estabilizadora dianteira</t>
         </is>
       </c>
       <c r="D135" s="17" t="n"/>
       <c r="E135" s="19" t="inlineStr">
         <is>
-          <t>007407</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="F135" s="18" t="n"/>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
-        </is>
-      </c>
-      <c r="H135" s="18" t="n"/>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>OS 7185 · serviço empresa especializada</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="21" customHeight="1">
       <c r="A136" s="16" t="n"/>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>REPOR ACABAMENTO DO PUXADOR DA PORTA LE</t>
+          <t>Substituir letreiro do modelo Axor "3344"</t>
         </is>
       </c>
       <c r="D136" s="17" t="n"/>
-      <c r="E136" s="19" t="inlineStr">
-        <is>
-          <t>007408</t>
-        </is>
-      </c>
+      <c r="E136" s="19" t="n"/>
       <c r="F136" s="18" t="n"/>
       <c r="G136" s="18" t="inlineStr">
         <is>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr">
+        <is>
+          <t>Peça A 943 817 13 14 · certificar com fornecedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="21" customHeight="1">
+      <c r="A137" s="16" t="n"/>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>F-964</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>Recuperar pisante do estribo LD avariado</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="n"/>
+      <c r="E137" s="19" t="n"/>
+      <c r="F137" s="18" t="n"/>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>BAIXA DE CARTEIRA</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="21" customHeight="1">
+      <c r="A138" s="16" t="n"/>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>F-968</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Bater e validar as pendências da inspeção realizada em Mossoró</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="18" t="n"/>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>Inspeção Mossoró</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="n"/>
+    </row>
+    <row r="139" ht="21" customHeight="1">
+      <c r="A139" s="16" t="n"/>
+      <c r="B139" s="17" t="inlineStr">
+        <is>
+          <t>F-972</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>SUBSTITUIR JUNTA DAS TAMPAS DE VALVULA COM VAZAMENTO</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="n"/>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
+          <t>007397</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="n"/>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
           <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
-      <c r="H136" s="18" t="n"/>
-    </row>
-    <row r="137" ht="21" customHeight="1">
-      <c r="A137" s="16" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B137" s="17" t="inlineStr">
-        <is>
-          <t>F-626</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
-        <is>
-          <t>Trocar cabeçote de combustível</t>
-        </is>
-      </c>
-      <c r="D137" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E137" s="19" t="inlineStr">
-        <is>
-          <t>21318</t>
-        </is>
-      </c>
-      <c r="F137" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Alexandre</t>
-        </is>
-      </c>
-      <c r="G137" s="18" t="inlineStr">
-        <is>
-          <t>Trocar o cabeçote</t>
-        </is>
-      </c>
-      <c r="H137" s="18" t="n"/>
-    </row>
-    <row r="138" ht="21" customHeight="1">
-      <c r="A138" s="16" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B138" s="17" t="inlineStr">
-        <is>
-          <t>F-626</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>Bomba de combustível</t>
-        </is>
-      </c>
-      <c r="D138" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E138" s="19" t="inlineStr">
-        <is>
-          <t>21129</t>
-        </is>
-      </c>
-      <c r="F138" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Alexandre</t>
-        </is>
-      </c>
-      <c r="G138" s="18" t="inlineStr">
-        <is>
-          <t>Trocar o cabeçote</t>
-        </is>
-      </c>
-      <c r="H138" s="18" t="n"/>
-    </row>
-    <row r="139" ht="21" customHeight="1">
-      <c r="A139" s="16" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B139" s="17" t="inlineStr">
-        <is>
-          <t>F-624</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>1. Substituir reservatório do líquido de arrefecimento contaminado</t>
-        </is>
-      </c>
-      <c r="D139" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E139" s="19" t="inlineStr">
-        <is>
-          <t>21072</t>
-        </is>
-      </c>
-      <c r="F139" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
-      <c r="G139" s="18" t="inlineStr">
-        <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H139" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+      <c r="H139" s="18" t="n"/>
     </row>
     <row r="140" ht="21" customHeight="1">
-      <c r="A140" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A140" s="16" t="n"/>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>2. Realizar lavagem e corrigir vazamento na bomba de direção hidráulica</t>
-        </is>
-      </c>
-      <c r="D140" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR MANGUEIRA DO TUBO DO RADIADOR COM VAZAMENTO</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="n"/>
       <c r="E140" s="19" t="inlineStr">
         <is>
-          <t>21177</t>
-        </is>
-      </c>
-      <c r="F140" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
+          <t>007400</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="n"/>
       <c r="G140" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H140" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="n"/>
     </row>
     <row r="141" ht="21" customHeight="1">
-      <c r="A141" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A141" s="16" t="n"/>
       <c r="B141" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C141" s="18" t="inlineStr">
         <is>
-          <t>3. Substituir tirante V traseiro empenado</t>
-        </is>
-      </c>
-      <c r="D141" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E141" s="19" t="n"/>
-      <c r="F141" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR MANGOTE INFERIOR DO RADIADOR RESSECADO E COM VAZAMENTO</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="n"/>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>007400</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="n"/>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H141" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="n"/>
     </row>
     <row r="142" ht="21" customHeight="1">
-      <c r="A142" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A142" s="16" t="n"/>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C142" s="18" t="inlineStr">
         <is>
-          <t>4. Corrigir vazamento de ar no freio de estacionamento</t>
-        </is>
-      </c>
-      <c r="D142" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E142" s="19" t="n"/>
-      <c r="F142" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR JUNTA DA TAMPA DO CUBO DE RODA DIANTEIRO LD COM VAZAMENTO</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="n"/>
+      <c r="E142" s="19" t="inlineStr">
+        <is>
+          <t>007401</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="n"/>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H142" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas · maneco</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="n"/>
     </row>
     <row r="143" ht="21" customHeight="1">
-      <c r="A143" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A143" s="16" t="n"/>
       <c r="B143" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>5. Repor batedores dianteiros da cabine</t>
-        </is>
-      </c>
-      <c r="D143" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E143" s="19" t="n"/>
-      <c r="F143" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR LANTERNA LATERAL LD</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="n"/>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>007402</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="n"/>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H143" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="n"/>
     </row>
     <row r="144" ht="21" customHeight="1">
-      <c r="A144" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A144" s="16" t="n"/>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>Realizar ajuste no velocímetro</t>
-        </is>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR TAMPA DE ABASTECIMENTO DE OLÉO COM VEDAÇÃO GASTA</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="n"/>
       <c r="E144" s="19" t="inlineStr">
         <is>
-          <t>21340</t>
-        </is>
-      </c>
-      <c r="F144" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Alexandre</t>
-        </is>
-      </c>
+          <t>007403</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="n"/>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H144" s="18" t="n"/>
     </row>
     <row r="145" ht="21" customHeight="1">
-      <c r="A145" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A145" s="16" t="n"/>
       <c r="B145" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>REPOR PARAFUSO DE FIXAÇÃO DA GRADE DO FAROL LE</t>
-        </is>
-      </c>
-      <c r="D145" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E145" s="19" t="n"/>
-      <c r="F145" s="18" t="inlineStr">
-        <is>
-          <t>Alexandre · Heliton</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR BUCHAS DA BARRA ESTABILIZADORA DIANTEIRA GASTAS</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="n"/>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>007404</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="n"/>
       <c r="G145" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
-      <c r="H145" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou</t>
-        </is>
-      </c>
+      <c r="H145" s="18" t="n"/>
     </row>
     <row r="146" ht="21" customHeight="1">
-      <c r="A146" s="16" t="n">
-        <v>46259</v>
-      </c>
+      <c r="A146" s="16" t="n"/>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>FIXAR CHICOTE ELETRICO SOLTO</t>
-        </is>
-      </c>
-      <c r="D146" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E146" s="19" t="n"/>
-      <c r="F146" s="18" t="inlineStr">
-        <is>
-          <t>Alexandre · Heliton</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR PALHETAS DO LIMPADOR DE PARABRISA</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="n"/>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>007405</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="n"/>
       <c r="G146" s="18" t="inlineStr">
         <is>
           <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
-      <c r="H146" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou</t>
-        </is>
-      </c>
+      <c r="H146" s="18" t="n"/>
     </row>
     <row r="147" ht="21" customHeight="1">
-      <c r="A147" s="16" t="n">
-        <v>46260</v>
-      </c>
+      <c r="A147" s="16" t="n"/>
       <c r="B147" s="17" t="inlineStr">
         <is>
-          <t>F-326</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>Trocar pneus</t>
-        </is>
-      </c>
-      <c r="D147" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR BORRACHA DE VEDAÇÃO DA PORTA</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="n"/>
       <c r="E147" s="19" t="inlineStr">
         <is>
-          <t>021188</t>
-        </is>
-      </c>
-      <c r="F147" s="18" t="inlineStr">
-        <is>
-          <t>Airton · Luiz Paulo</t>
-        </is>
-      </c>
+          <t>007406</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="n"/>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
-        </is>
-      </c>
-      <c r="H147" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Pneus</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="n"/>
     </row>
     <row r="148" ht="21" customHeight="1">
-      <c r="A148" s="16" t="n">
-        <v>46260</v>
-      </c>
+      <c r="A148" s="16" t="n"/>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>Realizar lavagem e corrigir vazamento na bomba de direção</t>
-        </is>
-      </c>
-      <c r="D148" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>SUBSTITUIR JANELA DE INSPEÇÃO FRONTAL</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="n"/>
       <c r="E148" s="19" t="inlineStr">
         <is>
-          <t>19784</t>
-        </is>
-      </c>
-      <c r="F148" s="18" t="inlineStr">
-        <is>
-          <t>Júnior</t>
-        </is>
-      </c>
+          <t>007407</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="n"/>
       <c r="G148" s="18" t="inlineStr">
         <is>
-          <t>Montar adesivos e baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H148" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="n"/>
     </row>
     <row r="149" ht="21" customHeight="1">
-      <c r="A149" s="16" t="n">
-        <v>46260</v>
-      </c>
+      <c r="A149" s="16" t="n"/>
       <c r="B149" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-972</t>
         </is>
       </c>
       <c r="C149" s="18" t="inlineStr">
         <is>
-          <t>6. Substituir lanterna do pisca dianteiro LD avariada</t>
-        </is>
-      </c>
-      <c r="D149" s="17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E149" s="19" t="n"/>
-      <c r="F149" s="18" t="inlineStr">
-        <is>
-          <t>Adilton · Gabriel · Júnior</t>
-        </is>
-      </c>
+          <t>REPOR ACABAMENTO DO PUXADOR DA PORTA LE</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="n"/>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>007408</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="n"/>
       <c r="G149" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H149" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>BAIXA DE PENDENCIAS</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="n"/>
     </row>
     <row r="150" ht="21" customHeight="1">
       <c r="A150" s="16" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
         <is>
-          <t>7. Substituir extensão da porta LE avariada</t>
+          <t>Trocar cabeçote de combustível</t>
         </is>
       </c>
       <c r="D150" s="17" t="inlineStr">
@@ -5337,35 +5203,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E150" s="19" t="n"/>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>21318</t>
+        </is>
+      </c>
       <c r="F150" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G150" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H150" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="n"/>
     </row>
     <row r="151" ht="21" customHeight="1">
       <c r="A151" s="16" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B151" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C151" s="18" t="inlineStr">
         <is>
-          <t>8. Substituir saia lateral da cabine LD</t>
+          <t>Bomba de combustível</t>
         </is>
       </c>
       <c r="D151" s="17" t="inlineStr">
@@ -5373,26 +5239,26 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E151" s="19" t="n"/>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>21129</t>
+        </is>
+      </c>
       <c r="F151" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G151" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H151" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="n"/>
     </row>
     <row r="152" ht="21" customHeight="1">
       <c r="A152" s="16" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
@@ -5401,7 +5267,7 @@
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>9. Programar recuperação da barra de direção curta com início de folga</t>
+          <t>1. Substituir reservatório do líquido de arrefecimento contaminado</t>
         </is>
       </c>
       <c r="D152" s="17" t="inlineStr">
@@ -5409,7 +5275,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E152" s="19" t="n"/>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>21072</t>
+        </is>
+      </c>
       <c r="F152" s="18" t="inlineStr">
         <is>
           <t>Adilton · Gabriel · Júnior</t>
@@ -5428,7 +5298,7 @@
     </row>
     <row r="153" ht="21" customHeight="1">
       <c r="A153" s="16" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B153" s="17" t="inlineStr">
         <is>
@@ -5437,7 +5307,7 @@
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
+          <t>2. Realizar lavagem e corrigir vazamento na bomba de direção hidráulica</t>
         </is>
       </c>
       <c r="D153" s="17" t="inlineStr">
@@ -5445,7 +5315,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E153" s="19" t="n"/>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>21177</t>
+        </is>
+      </c>
       <c r="F153" s="18" t="inlineStr">
         <is>
           <t>Adilton · Gabriel · Júnior</t>
@@ -5464,16 +5338,16 @@
     </row>
     <row r="154" ht="21" customHeight="1">
       <c r="A154" s="16" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
         <is>
-          <t>Substituir juntas do coletor de escapamento</t>
+          <t>3. Substituir tirante V traseiro empenado</t>
         </is>
       </c>
       <c r="D154" s="17" t="inlineStr">
@@ -5481,39 +5355,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E154" s="19" t="inlineStr">
-        <is>
-          <t>21341</t>
-        </is>
-      </c>
+      <c r="E154" s="19" t="n"/>
       <c r="F154" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Alexandre</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H154" s="18" t="inlineStr">
         <is>
-          <t>Peça 20855371 (6 unidades)</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
       <c r="A155" s="16" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B155" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
         <is>
-          <t>FICAR CHICOTE ELETRICO SOLTO NO BLOCO DE COMANDO</t>
+          <t>4. Corrigir vazamento de ar no freio de estacionamento</t>
         </is>
       </c>
       <c r="D155" s="17" t="inlineStr">
@@ -5524,32 +5394,32 @@
       <c r="E155" s="19" t="n"/>
       <c r="F155" s="18" t="inlineStr">
         <is>
-          <t>Alexandre · Heliton</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G155" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H155" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Sistema: Estruturas · maneco</t>
         </is>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
       <c r="A156" s="16" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
         <is>
-          <t>FIXAR GRADE FRONTAL SOLTA</t>
+          <t>5. Repor batedores dianteiros da cabine</t>
         </is>
       </c>
       <c r="D156" s="17" t="inlineStr">
@@ -5560,32 +5430,32 @@
       <c r="E156" s="19" t="n"/>
       <c r="F156" s="18" t="inlineStr">
         <is>
-          <t>Alexandre · Heliton</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G156" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H156" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
       <c r="A157" s="16" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B157" s="17" t="inlineStr">
         <is>
-          <t>F-326</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>Substituir batentes dos eixos traseiros LE e LD gastos</t>
+          <t>Realizar ajuste no velocímetro</t>
         </is>
       </c>
       <c r="D157" s="17" t="inlineStr">
@@ -5595,37 +5465,33 @@
       </c>
       <c r="E157" s="19" t="inlineStr">
         <is>
-          <t>021188</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="F157" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G157" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
-        </is>
-      </c>
-      <c r="H157" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Pneus · Serviço empresa especializada · peça 20390836 (4 unidades)</t>
-        </is>
-      </c>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="n"/>
     </row>
     <row r="158" ht="21" customHeight="1">
       <c r="A158" s="16" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">
         <is>
-          <t>Regular travamento das portas, motorista relata que as mesmas estão abrindo em movimento</t>
+          <t>REPOR PARAFUSO DE FIXAÇÃO DA GRADE DO FAROL LE</t>
         </is>
       </c>
       <c r="D158" s="17" t="inlineStr">
@@ -5633,39 +5499,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E158" s="19" t="inlineStr">
-        <is>
-          <t>19784</t>
-        </is>
-      </c>
+      <c r="E158" s="19" t="n"/>
       <c r="F158" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G158" s="18" t="inlineStr">
         <is>
-          <t>Montar adesivos e baixa de carteira</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H158" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1">
       <c r="A159" s="16" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B159" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>Recuperar barras de direção curta e longa</t>
+          <t>FIXAR CHICOTE ELETRICO SOLTO</t>
         </is>
       </c>
       <c r="D159" s="17" t="inlineStr">
@@ -5673,39 +5535,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E159" s="19" t="inlineStr">
-        <is>
-          <t>21342</t>
-        </is>
-      </c>
+      <c r="E159" s="19" t="n"/>
       <c r="F159" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Alexandre</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G159" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H159" s="18" t="inlineStr">
         <is>
-          <t>serviço empresa especializada</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
       <c r="A160" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-326</t>
         </is>
       </c>
       <c r="C160" s="18" t="inlineStr">
         <is>
-          <t>Substituir lona de freio terceiro eixo LD avariada</t>
+          <t>Trocar pneus</t>
         </is>
       </c>
       <c r="D160" s="17" t="inlineStr">
@@ -5715,37 +5573,37 @@
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>021188</t>
         </is>
       </c>
       <c r="F160" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Alexandre</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G160" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>Calibração e troca de pneus</t>
         </is>
       </c>
       <c r="H160" s="18" t="inlineStr">
         <is>
-          <t>serviço empresa especializada</t>
+          <t>Sistema: Pneus</t>
         </is>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
       <c r="A161" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B161" s="17" t="inlineStr">
         <is>
-          <t>F-789</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>Calibrar e trocar pneus</t>
+          <t>Realizar lavagem e corrigir vazamento na bomba de direção</t>
         </is>
       </c>
       <c r="D161" s="17" t="inlineStr">
@@ -5753,31 +5611,39 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E161" s="19" t="n"/>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>19784</t>
+        </is>
+      </c>
       <c r="F161" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G161" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
-        </is>
-      </c>
-      <c r="H161" s="18" t="n"/>
+          <t>Montar adesivos e baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="21" customHeight="1">
       <c r="A162" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C162" s="18" t="inlineStr">
         <is>
-          <t>SUBSTITUIR BARRA DE DIREÇÃO PEQUENA</t>
+          <t>6. Substituir lanterna do pisca dianteiro LD avariada</t>
         </is>
       </c>
       <c r="D162" s="17" t="inlineStr">
@@ -5785,35 +5651,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E162" s="19" t="inlineStr">
-        <is>
-          <t>021314</t>
-        </is>
-      </c>
+      <c r="E162" s="19" t="n"/>
       <c r="F162" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G162" s="18" t="inlineStr">
         <is>
-          <t>Pendências de inspeção</t>
-        </is>
-      </c>
-      <c r="H162" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="inlineStr">
+        <is>
+          <t>Sistema: Estruturas</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="21" customHeight="1">
       <c r="A163" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B163" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>Trocar palhetas do climatizador</t>
+          <t>7. Substituir extensão da porta LE avariada</t>
         </is>
       </c>
       <c r="D163" s="17" t="inlineStr">
@@ -5821,35 +5687,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E163" s="19" t="inlineStr">
-        <is>
-          <t>021390</t>
-        </is>
-      </c>
+      <c r="E163" s="19" t="n"/>
       <c r="F163" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G163" s="18" t="inlineStr">
         <is>
-          <t>Trocar palhetas do climatizador</t>
-        </is>
-      </c>
-      <c r="H163" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H163" s="18" t="inlineStr">
+        <is>
+          <t>Sistema: Estruturas</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C164" s="18" t="inlineStr">
         <is>
-          <t>CORRIGIR MARCAÇÃO DE NICEL DE COMBUSTIVEL</t>
+          <t>8. Substituir saia lateral da cabine LD</t>
         </is>
       </c>
       <c r="D164" s="17" t="inlineStr">
@@ -5860,32 +5726,32 @@
       <c r="E164" s="19" t="n"/>
       <c r="F164" s="18" t="inlineStr">
         <is>
-          <t>Alexandre · Heliton</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G164" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H164" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B165" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>ARLA CONTAMINADO</t>
+          <t>9. Programar recuperação da barra de direção curta com início de folga</t>
         </is>
       </c>
       <c r="D165" s="17" t="inlineStr">
@@ -5896,32 +5762,32 @@
       <c r="E165" s="19" t="n"/>
       <c r="F165" s="18" t="inlineStr">
         <is>
-          <t>Alexandre · Heliton</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G165" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H165" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
       <c r="A166" s="16" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C166" s="18" t="inlineStr">
         <is>
-          <t>SENSOR DE NICEL DE AGUA COM FALHA</t>
+          <t>10. Substituir junta da tampa do módulo i-shift, apresentando princípio de vazamento</t>
         </is>
       </c>
       <c r="D166" s="17" t="inlineStr">
@@ -5932,32 +5798,32 @@
       <c r="E166" s="19" t="n"/>
       <c r="F166" s="18" t="inlineStr">
         <is>
-          <t>Alexandre · Heliton</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G166" s="18" t="inlineStr">
         <is>
-          <t>BAIXA DE PENDENCIAS</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H166" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
       <c r="A167" s="16" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B167" s="17" t="inlineStr">
         <is>
-          <t>F-1064</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>Trocar e calibrar pneus</t>
+          <t>Substituir juntas do coletor de escapamento</t>
         </is>
       </c>
       <c r="D167" s="17" t="inlineStr">
@@ -5965,31 +5831,39 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E167" s="19" t="n"/>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>21341</t>
+        </is>
+      </c>
       <c r="F167" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G167" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
-        </is>
-      </c>
-      <c r="H167" s="18" t="n"/>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="inlineStr">
+        <is>
+          <t>Peça 20855371 (6 unidades)</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="21" customHeight="1">
       <c r="A168" s="16" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>F-326</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C168" s="18" t="inlineStr">
         <is>
-          <t>Soldar base do paralama dianteiro LD avariada</t>
+          <t>FICAR CHICOTE ELETRICO SOLTO NO BLOCO DE COMANDO</t>
         </is>
       </c>
       <c r="D168" s="17" t="inlineStr">
@@ -5997,39 +5871,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E168" s="19" t="inlineStr">
-        <is>
-          <t>021188</t>
-        </is>
-      </c>
+      <c r="E168" s="19" t="n"/>
       <c r="F168" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G168" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H168" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Pneus · 20453900</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="16" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B169" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>Repor tampa da caixa de fusíveis LD</t>
+          <t>FIXAR GRADE FRONTAL SOLTA</t>
         </is>
       </c>
       <c r="D169" s="17" t="inlineStr">
@@ -6037,39 +5907,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E169" s="19" t="inlineStr">
-        <is>
-          <t>19784</t>
-        </is>
-      </c>
+      <c r="E169" s="19" t="n"/>
       <c r="F169" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G169" s="18" t="inlineStr">
         <is>
-          <t>Montar adesivos e baixa de carteira</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H169" s="18" t="inlineStr">
         <is>
-          <t>OS 20352 · 20398773</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
       <c r="A170" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-326</t>
         </is>
       </c>
       <c r="C170" s="18" t="inlineStr">
         <is>
-          <t>Substituir para-sol avariado</t>
+          <t>Substituir batentes dos eixos traseiros LE e LD gastos</t>
         </is>
       </c>
       <c r="D170" s="17" t="inlineStr">
@@ -6079,7 +5945,7 @@
       </c>
       <c r="E170" s="19" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>021188</t>
         </is>
       </c>
       <c r="F170" s="18" t="inlineStr">
@@ -6089,27 +5955,27 @@
       </c>
       <c r="G170" s="18" t="inlineStr">
         <is>
-          <t>Montar adesivos e baixa de carteira</t>
+          <t>Calibração e troca de pneus</t>
         </is>
       </c>
       <c r="H170" s="18" t="inlineStr">
         <is>
-          <t>82245535</t>
+          <t>Sistema: Pneus · Serviço empresa especializada · peça 20390836 (4 unidades)</t>
         </is>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
       <c r="A171" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B171" s="17" t="inlineStr">
         <is>
-          <t>F-457</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C171" s="18" t="inlineStr">
         <is>
-          <t>Verificar válvula de freio</t>
+          <t>Regular travamento das portas, motorista relata que as mesmas estão abrindo em movimento</t>
         </is>
       </c>
       <c r="D171" s="17" t="inlineStr">
@@ -6117,35 +5983,39 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E171" s="19" t="n"/>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>19784</t>
+        </is>
+      </c>
       <c r="F171" s="18" t="inlineStr">
         <is>
-          <t>Adilton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G171" s="18" t="inlineStr">
         <is>
-          <t>Verificar válvula de freio</t>
+          <t>Montar adesivos e baixa de carteira</t>
         </is>
       </c>
       <c r="H171" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Freios</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1">
       <c r="A172" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>F-458</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C172" s="18" t="inlineStr">
         <is>
-          <t>Verificar válvula de freio</t>
+          <t>Recuperar barras de direção curta e longa</t>
         </is>
       </c>
       <c r="D172" s="17" t="inlineStr">
@@ -6153,35 +6023,39 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E172" s="19" t="n"/>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>21342</t>
+        </is>
+      </c>
       <c r="F172" s="18" t="inlineStr">
         <is>
-          <t>Adilton</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G172" s="18" t="inlineStr">
         <is>
-          <t>Verificar válvula de freio</t>
+          <t>Trocar o cabeçote</t>
         </is>
       </c>
       <c r="H172" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Freios</t>
+          <t>serviço empresa especializada</t>
         </is>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1">
       <c r="A173" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B173" s="17" t="inlineStr">
         <is>
-          <t>F-616</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C173" s="18" t="inlineStr">
         <is>
-          <t>TROCAR PNEUS E FERRAR</t>
+          <t>Substituir lona de freio terceiro eixo LD avariada</t>
         </is>
       </c>
       <c r="D173" s="17" t="inlineStr">
@@ -6189,35 +6063,39 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E173" s="19" t="n"/>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>21343</t>
+        </is>
+      </c>
       <c r="F173" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G173" s="18" t="inlineStr">
         <is>
-          <t>TROCAR E FERRAR PNEUS</t>
+          <t>Trocar o cabeçote</t>
         </is>
       </c>
       <c r="H173" s="18" t="inlineStr">
         <is>
-          <t>PRIORIDADE DO KAIRO</t>
+          <t>serviço empresa especializada</t>
         </is>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
       <c r="A174" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-789</t>
         </is>
       </c>
       <c r="C174" s="18" t="inlineStr">
         <is>
-          <t>Realizar troca ou calibração dos pneus</t>
+          <t>Calibrar e trocar pneus</t>
         </is>
       </c>
       <c r="D174" s="17" t="inlineStr">
@@ -6225,11 +6103,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E174" s="19" t="inlineStr">
-        <is>
-          <t>21330</t>
-        </is>
-      </c>
+      <c r="E174" s="19" t="n"/>
       <c r="F174" s="18" t="inlineStr">
         <is>
           <t>Airton · Luiz Paulo</t>
@@ -6244,16 +6118,16 @@
     </row>
     <row r="175" ht="21" customHeight="1">
       <c r="A175" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B175" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C175" s="18" t="inlineStr">
         <is>
-          <t>11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
+          <t>SUBSTITUIR BARRA DE DIREÇÃO PEQUENA</t>
         </is>
       </c>
       <c r="D175" s="17" t="inlineStr">
@@ -6261,35 +6135,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E175" s="19" t="n"/>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>021314</t>
+        </is>
+      </c>
       <c r="F175" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G175" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H175" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>Pendências de inspeção</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="n"/>
     </row>
     <row r="176" ht="21" customHeight="1">
       <c r="A176" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>13. Substituir paralama dianteiro LD avariado</t>
+          <t>Trocar palhetas do climatizador</t>
         </is>
       </c>
       <c r="D176" s="17" t="inlineStr">
@@ -6297,35 +6171,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E176" s="19" t="n"/>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>021390</t>
+        </is>
+      </c>
       <c r="F176" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G176" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H176" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas</t>
-        </is>
-      </c>
+          <t>Trocar palhetas do climatizador</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="n"/>
     </row>
     <row r="177" ht="21" customHeight="1">
       <c r="A177" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B177" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C177" s="18" t="inlineStr">
         <is>
-          <t>14. Substituir lente da lanterna traseira LD avariada</t>
+          <t>CORRIGIR MARCAÇÃO DE NICEL DE COMBUSTIVEL</t>
         </is>
       </c>
       <c r="D177" s="17" t="inlineStr">
@@ -6336,32 +6210,32 @@
       <c r="E177" s="19" t="n"/>
       <c r="F177" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G177" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H177" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="178" ht="21" customHeight="1">
       <c r="A178" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento</t>
+          <t>ARLA CONTAMINADO</t>
         </is>
       </c>
       <c r="D178" s="17" t="inlineStr">
@@ -6372,32 +6246,32 @@
       <c r="E178" s="19" t="n"/>
       <c r="F178" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G178" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H178" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
     <row r="179" ht="21" customHeight="1">
       <c r="A179" s="16" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B179" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>Corujinha lateral: Avaria no lado direito</t>
+          <t>SENSOR DE NICEL DE AGUA COM FALHA</t>
         </is>
       </c>
       <c r="D179" s="17" t="inlineStr">
@@ -6408,17 +6282,17 @@
       <c r="E179" s="19" t="n"/>
       <c r="F179" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Alexandre · Heliton</t>
         </is>
       </c>
       <c r="G179" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>BAIXA DE PENDENCIAS</t>
         </is>
       </c>
       <c r="H179" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas · LD</t>
+          <t>Peça não chegou</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6302,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>F-696</t>
+          <t>F-1064</t>
         </is>
       </c>
       <c r="C180" s="18" t="inlineStr">
         <is>
-          <t>Aplicar faixa refletiva</t>
+          <t>Trocar e calibrar pneus</t>
         </is>
       </c>
       <c r="D180" s="17" t="inlineStr">
@@ -6444,12 +6318,12 @@
       <c r="E180" s="19" t="n"/>
       <c r="F180" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G180" s="18" t="inlineStr">
         <is>
-          <t>Aplicar faixas refletivas</t>
+          <t>Calibração e troca de pneus</t>
         </is>
       </c>
       <c r="H180" s="18" t="n"/>
@@ -6460,12 +6334,12 @@
       </c>
       <c r="B181" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-326</t>
         </is>
       </c>
       <c r="C181" s="18" t="inlineStr">
         <is>
-          <t>Limpeza do climatizador</t>
+          <t>Soldar base do paralama dianteiro LD avariada</t>
         </is>
       </c>
       <c r="D181" s="17" t="inlineStr">
@@ -6473,7 +6347,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E181" s="19" t="n"/>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>021188</t>
+        </is>
+      </c>
       <c r="F181" s="18" t="inlineStr">
         <is>
           <t>Júnior</t>
@@ -6481,23 +6359,27 @@
       </c>
       <c r="G181" s="18" t="inlineStr">
         <is>
-          <t>Trocar palhetas do climatizador</t>
-        </is>
-      </c>
-      <c r="H181" s="18" t="n"/>
+          <t>Calibração e troca de pneus</t>
+        </is>
+      </c>
+      <c r="H181" s="18" t="inlineStr">
+        <is>
+          <t>Sistema: Pneus · 20453900</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="21" customHeight="1">
       <c r="A182" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>F-326</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C182" s="18" t="inlineStr">
         <is>
-          <t>Substituir acabamento do retrovisor inferior LD</t>
+          <t>Repor tampa da caixa de fusíveis LD</t>
         </is>
       </c>
       <c r="D182" s="17" t="inlineStr">
@@ -6507,7 +6389,7 @@
       </c>
       <c r="E182" s="19" t="inlineStr">
         <is>
-          <t>021188</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="F182" s="18" t="inlineStr">
@@ -6517,27 +6399,27 @@
       </c>
       <c r="G182" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
+          <t>Montar adesivos e baixa de carteira</t>
         </is>
       </c>
       <c r="H182" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Pneus · item em aplicação direta ou realizar pedido 21169971</t>
+          <t>OS 20352 · 20398773</t>
         </is>
       </c>
     </row>
     <row r="183" ht="21" customHeight="1">
       <c r="A183" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B183" s="17" t="inlineStr">
         <is>
-          <t>F-326</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C183" s="18" t="inlineStr">
         <is>
-          <t>CARCAÇA INTERNA DO FAROL</t>
+          <t>Substituir para-sol avariado</t>
         </is>
       </c>
       <c r="D183" s="17" t="inlineStr">
@@ -6547,7 +6429,7 @@
       </c>
       <c r="E183" s="19" t="inlineStr">
         <is>
-          <t>021188</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="F183" s="18" t="inlineStr">
@@ -6557,27 +6439,27 @@
       </c>
       <c r="G183" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
+          <t>Montar adesivos e baixa de carteira</t>
         </is>
       </c>
       <c r="H183" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Pneus · 20453627</t>
+          <t>82245535</t>
         </is>
       </c>
     </row>
     <row r="184" ht="21" customHeight="1">
       <c r="A184" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-457</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>Substituir bomba d'água com princípio de vazamento pelo selo lateral</t>
+          <t>Verificar válvula de freio</t>
         </is>
       </c>
       <c r="D184" s="17" t="inlineStr">
@@ -6585,39 +6467,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E184" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E184" s="19" t="n"/>
       <c r="F184" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton</t>
         </is>
       </c>
       <c r="G184" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Verificar válvula de freio</t>
         </is>
       </c>
       <c r="H184" s="18" t="inlineStr">
         <is>
-          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 20538820</t>
+          <t>Sistema: Freios</t>
         </is>
       </c>
     </row>
     <row r="185" ht="21" customHeight="1">
       <c r="A185" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B185" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-458</t>
         </is>
       </c>
       <c r="C185" s="18" t="inlineStr">
         <is>
-          <t>Vidros: Revisar a visibilidade dos vidros frontal e laterais</t>
+          <t>Verificar válvula de freio</t>
         </is>
       </c>
       <c r="D185" s="17" t="inlineStr">
@@ -6628,32 +6506,32 @@
       <c r="E185" s="19" t="n"/>
       <c r="F185" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Adilton</t>
         </is>
       </c>
       <c r="G185" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Verificar válvula de freio</t>
         </is>
       </c>
       <c r="H185" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas</t>
+          <t>Sistema: Freios</t>
         </is>
       </c>
     </row>
     <row r="186" ht="21" customHeight="1">
       <c r="A186" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-616</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
         <is>
-          <t>Grade frontal: Apresenta avaria</t>
+          <t>TROCAR PNEUS E FERRAR</t>
         </is>
       </c>
       <c r="D186" s="17" t="inlineStr">
@@ -6664,32 +6542,32 @@
       <c r="E186" s="19" t="n"/>
       <c r="F186" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G186" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>TROCAR E FERRAR PNEUS</t>
         </is>
       </c>
       <c r="H186" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas</t>
+          <t>PRIORIDADE DO KAIRO</t>
         </is>
       </c>
     </row>
     <row r="187" ht="21" customHeight="1">
       <c r="A187" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B187" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
         <is>
-          <t>Corote: Verificar fixação</t>
+          <t>Realizar troca ou calibração dos pneus</t>
         </is>
       </c>
       <c r="D187" s="17" t="inlineStr">
@@ -6697,26 +6575,26 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E187" s="19" t="n"/>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>21330</t>
+        </is>
+      </c>
       <c r="F187" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel · Júnior</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G187" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H187" s="18" t="inlineStr">
-        <is>
-          <t>Sistema: Estruturas · pois está batendo no para-lama.</t>
-        </is>
-      </c>
+          <t>Calibração e troca de pneus</t>
+        </is>
+      </c>
+      <c r="H187" s="18" t="n"/>
     </row>
     <row r="188" ht="21" customHeight="1">
       <c r="A188" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
@@ -6725,7 +6603,7 @@
       </c>
       <c r="C188" s="18" t="inlineStr">
         <is>
-          <t>Lameira: Avaria no lado esquerdo</t>
+          <t>11. Substituir amortecedores dianteiros estourados, apresentando início de vazamento</t>
         </is>
       </c>
       <c r="D188" s="17" t="inlineStr">
@@ -6746,13 +6624,13 @@
       </c>
       <c r="H188" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas · LE</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="189" ht="21" customHeight="1">
       <c r="A189" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B189" s="17" t="inlineStr">
         <is>
@@ -6761,7 +6639,7 @@
       </c>
       <c r="C189" s="18" t="inlineStr">
         <is>
-          <t>Para-lama: Parafuso do lado direito folgado</t>
+          <t>13. Substituir paralama dianteiro LD avariado</t>
         </is>
       </c>
       <c r="D189" s="17" t="inlineStr">
@@ -6782,22 +6660,22 @@
       </c>
       <c r="H189" s="18" t="inlineStr">
         <is>
-          <t>Sistema: Estruturas · LD</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="190" ht="21" customHeight="1">
       <c r="A190" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C190" s="18" t="inlineStr">
         <is>
-          <t>Substituir lona de freio dianteira LD avariada</t>
+          <t>14. Substituir lente da lanterna traseira LD avariada</t>
         </is>
       </c>
       <c r="D190" s="17" t="inlineStr">
@@ -6805,39 +6683,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E190" s="19" t="inlineStr">
-        <is>
-          <t>21343</t>
-        </is>
-      </c>
+      <c r="E190" s="19" t="n"/>
       <c r="F190" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Alexandre</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G190" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H190" s="18" t="inlineStr">
         <is>
-          <t>serviço empresa especializada</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="191" ht="21" customHeight="1">
       <c r="A191" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B191" s="17" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C191" s="18" t="inlineStr">
         <is>
-          <t>Substituir lona de freio dianteiro LE avariada</t>
+          <t>Vazamento: Conjunto de mangueiras dianteiras LE — realizar lavagem para identificar a origem do vazamento</t>
         </is>
       </c>
       <c r="D191" s="17" t="inlineStr">
@@ -6845,39 +6719,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E191" s="19" t="inlineStr">
-        <is>
-          <t>21343</t>
-        </is>
-      </c>
+      <c r="E191" s="19" t="n"/>
       <c r="F191" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Alexandre</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G191" s="18" t="inlineStr">
         <is>
-          <t>Trocar o cabeçote</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H191" s="18" t="inlineStr">
         <is>
-          <t>serviço empresa especializada</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="192" ht="21" customHeight="1">
       <c r="A192" s="16" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C192" s="18" t="inlineStr">
         <is>
-          <t>Alinhar</t>
+          <t>Corujinha lateral: Avaria no lado direito</t>
         </is>
       </c>
       <c r="D192" s="17" t="inlineStr">
@@ -6888,28 +6758,32 @@
       <c r="E192" s="19" t="n"/>
       <c r="F192" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G192" s="18" t="inlineStr">
         <is>
-          <t>Trocar palhetas do climatizador</t>
-        </is>
-      </c>
-      <c r="H192" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H192" s="18" t="inlineStr">
+        <is>
+          <t>Sistema: Estruturas · LD</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="21" customHeight="1">
       <c r="A193" s="16" t="n">
-        <v>46264</v>
+        <v>46262</v>
       </c>
       <c r="B193" s="17" t="inlineStr">
         <is>
-          <t>F-1065</t>
+          <t>F-696</t>
         </is>
       </c>
       <c r="C193" s="18" t="inlineStr">
         <is>
-          <t>Trocar e calibrar pneus</t>
+          <t>Aplicar faixa refletiva</t>
         </is>
       </c>
       <c r="D193" s="17" t="inlineStr">
@@ -6920,28 +6794,28 @@
       <c r="E193" s="19" t="n"/>
       <c r="F193" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G193" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
+          <t>Aplicar faixas refletivas</t>
         </is>
       </c>
       <c r="H193" s="18" t="n"/>
     </row>
     <row r="194" ht="21" customHeight="1">
       <c r="A194" s="16" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C194" s="18" t="inlineStr">
         <is>
-          <t>Corrigir ligação da chave geral</t>
+          <t>Limpeza do climatizador</t>
         </is>
       </c>
       <c r="D194" s="17" t="inlineStr">
@@ -6949,39 +6823,31 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E194" s="19" t="inlineStr">
-        <is>
-          <t>21437</t>
-        </is>
-      </c>
+      <c r="E194" s="19" t="n"/>
       <c r="F194" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G194" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H194" s="18" t="inlineStr">
-        <is>
-          <t>Mudou a prioridade · serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Trocar palhetas do climatizador</t>
+        </is>
+      </c>
+      <c r="H194" s="18" t="n"/>
     </row>
     <row r="195" ht="21" customHeight="1">
       <c r="A195" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B195" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-326</t>
         </is>
       </c>
       <c r="C195" s="18" t="inlineStr">
         <is>
-          <t>Verificado intercooler com reparos, ficando apenas em observação de substituição</t>
+          <t>Substituir acabamento do retrovisor inferior LD</t>
         </is>
       </c>
       <c r="D195" s="17" t="inlineStr">
@@ -6991,37 +6857,37 @@
       </c>
       <c r="E195" s="19" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>021188</t>
         </is>
       </c>
       <c r="F195" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G195" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
+          <t>Calibração e troca de pneus</t>
         </is>
       </c>
       <c r="H195" s="18" t="inlineStr">
         <is>
-          <t>Mudou a prioridade · serviço interno Matriz</t>
+          <t>Sistema: Pneus · item em aplicação direta ou realizar pedido 21169971</t>
         </is>
       </c>
     </row>
     <row r="196" ht="21" customHeight="1">
       <c r="A196" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-326</t>
         </is>
       </c>
       <c r="C196" s="18" t="inlineStr">
         <is>
-          <t>Substituir buchas das abraçadeiras do tanque LD gastas e corrigir/substituir tanque amassado</t>
+          <t>CARCAÇA INTERNA DO FAROL</t>
         </is>
       </c>
       <c r="D196" s="17" t="inlineStr">
@@ -7031,37 +6897,37 @@
       </c>
       <c r="E196" s="19" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>021188</t>
         </is>
       </c>
       <c r="F196" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G196" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
+          <t>Calibração e troca de pneus</t>
         </is>
       </c>
       <c r="H196" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou · serviço interno Matriz</t>
+          <t>Sistema: Pneus · 20453627</t>
         </is>
       </c>
     </row>
     <row r="197" ht="21" customHeight="1">
       <c r="A197" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B197" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>Fixar banco do passageiro LD</t>
+          <t>Substituir bomba d'água com princípio de vazamento pelo selo lateral</t>
         </is>
       </c>
       <c r="D197" s="17" t="inlineStr">
@@ -7071,7 +6937,7 @@
       </c>
       <c r="E197" s="19" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F197" s="18" t="inlineStr">
@@ -7081,27 +6947,27 @@
       </c>
       <c r="G197" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
+          <t>Preventiva</t>
         </is>
       </c>
       <c r="H197" s="18" t="inlineStr">
         <is>
-          <t>Mudou a prioridade · serviço interno Matriz</t>
+          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 20538820</t>
         </is>
       </c>
     </row>
     <row r="198" ht="21" customHeight="1">
       <c r="A198" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C198" s="18" t="inlineStr">
         <is>
-          <t>Trocar óleo e filtro</t>
+          <t>Vidros: Revisar a visibilidade dos vidros frontal e laterais</t>
         </is>
       </c>
       <c r="D198" s="17" t="inlineStr">
@@ -7109,39 +6975,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E198" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E198" s="19" t="n"/>
       <c r="F198" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G198" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H198" s="18" t="inlineStr">
         <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="199" ht="21" customHeight="1">
       <c r="A199" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B199" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C199" s="18" t="inlineStr">
         <is>
-          <t>Diagnosticar e corrigir falha no sistema do motor: temperatura dos gases de escape</t>
+          <t>Grade frontal: Apresenta avaria</t>
         </is>
       </c>
       <c r="D199" s="17" t="inlineStr">
@@ -7149,39 +7011,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E199" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E199" s="19" t="n"/>
       <c r="F199" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G199" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H199" s="18" t="inlineStr">
         <is>
-          <t>Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+          <t>Sistema: Estruturas</t>
         </is>
       </c>
     </row>
     <row r="200" ht="21" customHeight="1">
       <c r="A200" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C200" s="18" t="inlineStr">
         <is>
-          <t>Realizar lavagem e sanar vazamento na bomba de direção hidráulica</t>
+          <t>Corote: Verificar fixação</t>
         </is>
       </c>
       <c r="D200" s="17" t="inlineStr">
@@ -7189,39 +7047,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E200" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E200" s="19" t="n"/>
       <c r="F200" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G200" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H200" s="18" t="inlineStr">
         <is>
-          <t>Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+          <t>Sistema: Estruturas · pois está batendo no para-lama.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="21" customHeight="1">
       <c r="A201" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B201" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C201" s="18" t="inlineStr">
         <is>
-          <t>Sanar vazamento na mangueira da bomba de direção</t>
+          <t>Lameira: Avaria no lado esquerdo</t>
         </is>
       </c>
       <c r="D201" s="17" t="inlineStr">
@@ -7229,39 +7083,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E201" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E201" s="19" t="n"/>
       <c r="F201" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G201" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H201" s="18" t="inlineStr">
         <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró solicitar codigo do tubo original</t>
+          <t>Sistema: Estruturas · LE</t>
         </is>
       </c>
     </row>
     <row r="202" ht="21" customHeight="1">
       <c r="A202" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C202" s="18" t="inlineStr">
         <is>
-          <t>Corrigir fixação elétrica solta na frente do intercooler</t>
+          <t>Para-lama: Parafuso do lado direito folgado</t>
         </is>
       </c>
       <c r="D202" s="17" t="inlineStr">
@@ -7269,39 +7119,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E202" s="19" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
+      <c r="E202" s="19" t="n"/>
       <c r="F202" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Adilton · Gabriel · Júnior</t>
         </is>
       </c>
       <c r="G202" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H202" s="18" t="inlineStr">
         <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+          <t>Sistema: Estruturas · LD</t>
         </is>
       </c>
     </row>
     <row r="203" ht="21" customHeight="1">
       <c r="A203" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B203" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C203" s="18" t="inlineStr">
         <is>
-          <t>Realizar limpeza nos bornes das baterias</t>
+          <t>Substituir lona de freio dianteira LD avariada</t>
         </is>
       </c>
       <c r="D203" s="17" t="inlineStr">
@@ -7311,33 +7157,37 @@
       </c>
       <c r="E203" s="19" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="F203" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G203" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H203" s="18" t="n"/>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H203" s="18" t="inlineStr">
+        <is>
+          <t>serviço empresa especializada</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="21" customHeight="1">
       <c r="A204" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="C204" s="18" t="inlineStr">
         <is>
-          <t>Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
+          <t>Substituir lona de freio dianteiro LE avariada</t>
         </is>
       </c>
       <c r="D204" s="17" t="inlineStr">
@@ -7347,33 +7197,37 @@
       </c>
       <c r="E204" s="19" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Alexandre</t>
         </is>
       </c>
       <c r="G204" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H204" s="18" t="n"/>
+          <t>Trocar o cabeçote</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="inlineStr">
+        <is>
+          <t>serviço empresa especializada</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="21" customHeight="1">
       <c r="A205" s="16" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B205" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C205" s="18" t="inlineStr">
         <is>
-          <t>Reposicionar lanterna corujinha do teto LE e revisar iluminação</t>
+          <t>Alinhar</t>
         </is>
       </c>
       <c r="D205" s="17" t="inlineStr">
@@ -7381,35 +7235,31 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E205" s="19" t="inlineStr">
-        <is>
-          <t>21325</t>
-        </is>
-      </c>
+      <c r="E205" s="19" t="n"/>
       <c r="F205" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G205" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
+          <t>Trocar palhetas do climatizador</t>
         </is>
       </c>
       <c r="H205" s="18" t="n"/>
     </row>
     <row r="206" ht="21" customHeight="1">
       <c r="A206" s="16" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-1065</t>
         </is>
       </c>
       <c r="C206" s="18" t="inlineStr">
         <is>
-          <t>Diagnosticar e corrigir falhas: ABS e caixa de marchas</t>
+          <t>Trocar e calibrar pneus</t>
         </is>
       </c>
       <c r="D206" s="17" t="inlineStr">
@@ -7417,26 +7267,18 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E206" s="19" t="inlineStr">
-        <is>
-          <t>21317</t>
-        </is>
-      </c>
+      <c r="E206" s="19" t="n"/>
       <c r="F206" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G206" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H206" s="18" t="inlineStr">
-        <is>
-          <t>embreagem</t>
-        </is>
-      </c>
+          <t>Calibração e troca de pneus</t>
+        </is>
+      </c>
+      <c r="H206" s="18" t="n"/>
     </row>
     <row r="207" ht="21" customHeight="1">
       <c r="A207" s="16" t="n">
@@ -7444,12 +7286,12 @@
       </c>
       <c r="B207" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C207" s="18" t="inlineStr">
         <is>
-          <t>Substituir palhetas do limpador de para-brisas 8189631</t>
+          <t>Corrigir ligação da chave geral</t>
         </is>
       </c>
       <c r="D207" s="17" t="inlineStr">
@@ -7459,22 +7301,22 @@
       </c>
       <c r="E207" s="19" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="F207" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G207" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
+          <t>baixa de carteira</t>
         </is>
       </c>
       <c r="H207" s="18" t="inlineStr">
         <is>
-          <t>LD não limpa · 2 UND</t>
+          <t>Mudou a prioridade · serviço interno Matriz</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7326,12 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C208" s="18" t="inlineStr">
         <is>
-          <t>Fixar tubo de escapamento inferior</t>
+          <t>Verificado intercooler com reparos, ficando apenas em observação de substituição</t>
         </is>
       </c>
       <c r="D208" s="17" t="inlineStr">
@@ -7499,20 +7341,24 @@
       </c>
       <c r="E208" s="19" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="F208" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G208" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H208" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H208" s="18" t="inlineStr">
+        <is>
+          <t>Mudou a prioridade · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="21" customHeight="1">
       <c r="A209" s="16" t="n">
@@ -7520,12 +7366,12 @@
       </c>
       <c r="B209" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C209" s="18" t="inlineStr">
         <is>
-          <t>Fixar placa dianteira e traseira</t>
+          <t>Substituir buchas das abraçadeiras do tanque LD gastas e corrigir/substituir tanque amassado</t>
         </is>
       </c>
       <c r="D209" s="17" t="inlineStr">
@@ -7535,20 +7381,24 @@
       </c>
       <c r="E209" s="19" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="F209" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G209" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H209" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H209" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="21" customHeight="1">
       <c r="A210" s="16" t="n">
@@ -7556,12 +7406,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C210" s="18" t="inlineStr">
         <is>
-          <t>Fixar retrovisor LD e inferior LE</t>
+          <t>Fixar banco do passageiro LD</t>
         </is>
       </c>
       <c r="D210" s="17" t="inlineStr">
@@ -7571,20 +7421,24 @@
       </c>
       <c r="E210" s="19" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="F210" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G210" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H210" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H210" s="18" t="inlineStr">
+        <is>
+          <t>Mudou a prioridade · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="21" customHeight="1">
       <c r="A211" s="16" t="n">
@@ -7592,12 +7446,12 @@
       </c>
       <c r="B211" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C211" s="18" t="inlineStr">
         <is>
-          <t>Fixar extensão da porta e saia lateral LD</t>
+          <t>Trocar óleo e filtro</t>
         </is>
       </c>
       <c r="D211" s="17" t="inlineStr">
@@ -7607,20 +7461,24 @@
       </c>
       <c r="E211" s="19" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F211" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G211" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H211" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H211" s="18" t="inlineStr">
+        <is>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="21" customHeight="1">
       <c r="A212" s="16" t="n">
@@ -7628,12 +7486,12 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C212" s="18" t="inlineStr">
         <is>
-          <t>Repor quebra-sol do motorista</t>
+          <t>Diagnosticar e corrigir falha no sistema do motor: temperatura dos gases de escape</t>
         </is>
       </c>
       <c r="D212" s="17" t="inlineStr">
@@ -7643,22 +7501,22 @@
       </c>
       <c r="E212" s="19" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F212" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G212" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
+          <t>Preventiva</t>
         </is>
       </c>
       <c r="H212" s="18" t="inlineStr">
         <is>
-          <t>está dentro da cabine</t>
+          <t>Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7526,12 @@
       </c>
       <c r="B213" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C213" s="18" t="inlineStr">
         <is>
-          <t>Substituir junta da tampa de válvulas com vazamento;20538793</t>
+          <t>Realizar lavagem e sanar vazamento na bomba de direção hidráulica</t>
         </is>
       </c>
       <c r="D213" s="17" t="inlineStr">
@@ -7683,20 +7541,24 @@
       </c>
       <c r="E213" s="19" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F213" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G213" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H213" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H213" s="18" t="inlineStr">
+        <is>
+          <t>Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="21" customHeight="1">
       <c r="A214" s="16" t="n">
@@ -7704,12 +7566,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>F-711</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C214" s="18" t="inlineStr">
         <is>
-          <t>Substituir carcaça do filtro de ar</t>
+          <t>Sanar vazamento na mangueira da bomba de direção</t>
         </is>
       </c>
       <c r="D214" s="17" t="inlineStr">
@@ -7719,20 +7581,24 @@
       </c>
       <c r="E214" s="19" t="inlineStr">
         <is>
-          <t>021470</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F214" s="18" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G214" s="18" t="inlineStr">
         <is>
-          <t>Substituir filtro</t>
-        </is>
-      </c>
-      <c r="H214" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H214" s="18" t="inlineStr">
+        <is>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró solicitar codigo do tubo original</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="21" customHeight="1">
       <c r="A215" s="16" t="n">
@@ -7740,12 +7606,12 @@
       </c>
       <c r="B215" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C215" s="18" t="inlineStr">
         <is>
-          <t>Substituir junta da tampa de válvulas com vazamento</t>
+          <t>Corrigir fixação elétrica solta na frente do intercooler</t>
         </is>
       </c>
       <c r="D215" s="17" t="inlineStr">
@@ -7755,22 +7621,22 @@
       </c>
       <c r="E215" s="19" t="inlineStr">
         <is>
-          <t>007157</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F215" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G215" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Preventiva</t>
         </is>
       </c>
       <c r="H215" s="18" t="inlineStr">
         <is>
-          <t>Frota não chegou na oficina · Peça 20804638 (junta motor D11)</t>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7646,12 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C216" s="18" t="inlineStr">
         <is>
-          <t>Recuperar mangueira de lubrificação do compressor com vazamento</t>
+          <t>Realizar limpeza nos bornes das baterias</t>
         </is>
       </c>
       <c r="D216" s="17" t="inlineStr">
@@ -7795,24 +7661,20 @@
       </c>
       <c r="E216" s="19" t="inlineStr">
         <is>
-          <t>007334</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="F216" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G216" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H216" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H216" s="18" t="n"/>
     </row>
     <row r="217" ht="21" customHeight="1">
       <c r="A217" s="16" t="n">
@@ -7820,12 +7682,12 @@
       </c>
       <c r="B217" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
         <is>
-          <t>Corrigir vazamento nas mangueiras do reservatório de óleo hidráulico</t>
+          <t>Fixar farol dianteiro LD, substituir bojo do mesmo avariado e repor acabamento da bomba de bascular;82209849/82056991</t>
         </is>
       </c>
       <c r="D217" s="17" t="inlineStr">
@@ -7835,24 +7697,20 @@
       </c>
       <c r="E217" s="19" t="inlineStr">
         <is>
-          <t>007302</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="F217" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G217" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H217" s="18" t="inlineStr">
-        <is>
-          <t>Recuperar as mangueiras e substituir abraçadeiras · ⚠️ texto veio cortado do PDF de inspeção</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H217" s="18" t="n"/>
     </row>
     <row r="218" ht="21" customHeight="1">
       <c r="A218" s="16" t="n">
@@ -7860,12 +7718,12 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">
         <is>
-          <t>Completar nível do líquido de arrefecimento</t>
+          <t>Reposicionar lanterna corujinha do teto LE e revisar iluminação</t>
         </is>
       </c>
       <c r="D218" s="17" t="inlineStr">
@@ -7875,24 +7733,20 @@
       </c>
       <c r="E218" s="19" t="inlineStr">
         <is>
-          <t>007343</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="F218" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G218" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H218" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H218" s="18" t="n"/>
     </row>
     <row r="219" ht="21" customHeight="1">
       <c r="A219" s="16" t="n">
@@ -7900,12 +7754,12 @@
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C219" s="18" t="inlineStr">
         <is>
-          <t>Corrigir vazamento no diferencial do segundo eixo</t>
+          <t>Diagnosticar e corrigir falhas: ABS e caixa de marchas</t>
         </is>
       </c>
       <c r="D219" s="17" t="inlineStr">
@@ -7915,37 +7769,37 @@
       </c>
       <c r="E219" s="19" t="inlineStr">
         <is>
-          <t>007344</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="F219" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G219" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Baixa de carteira</t>
         </is>
       </c>
       <c r="H219" s="18" t="inlineStr">
         <is>
-          <t>serviço interno Matriz</t>
+          <t>embreagem</t>
         </is>
       </c>
     </row>
     <row r="220" ht="21" customHeight="1">
       <c r="A220" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C220" s="18" t="inlineStr">
         <is>
-          <t>Corrigir empeno do aro segundo eixo LD</t>
+          <t>Substituir palhetas do limpador de para-brisas 8189631</t>
         </is>
       </c>
       <c r="D220" s="17" t="inlineStr">
@@ -7955,37 +7809,37 @@
       </c>
       <c r="E220" s="19" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G220" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
+          <t>Baixa de carteira</t>
         </is>
       </c>
       <c r="H220" s="18" t="inlineStr">
         <is>
-          <t>Mudou a prioridade · serviço interno Matriz</t>
+          <t>LD não limpa · 2 UND</t>
         </is>
       </c>
     </row>
     <row r="221" ht="21" customHeight="1">
       <c r="A221" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C221" s="18" t="inlineStr">
         <is>
-          <t>Substituir juntas do escapamento gastas</t>
+          <t>Fixar tubo de escapamento inferior</t>
         </is>
       </c>
       <c r="D221" s="17" t="inlineStr">
@@ -7995,37 +7849,33 @@
       </c>
       <c r="E221" s="19" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="F221" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G221" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H221" s="18" t="inlineStr">
-        <is>
-          <t>Mudou a prioridade · Serviço interno Matriz · peça 20855371 (6 unidades) · realizar acompanhamento</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H221" s="18" t="n"/>
     </row>
     <row r="222" ht="21" customHeight="1">
       <c r="A222" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C222" s="18" t="inlineStr">
         <is>
-          <t>Substituir estribo da cabine LD</t>
+          <t>Fixar placa dianteira e traseira</t>
         </is>
       </c>
       <c r="D222" s="17" t="inlineStr">
@@ -8035,37 +7885,33 @@
       </c>
       <c r="E222" s="19" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="F222" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G222" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H222" s="18" t="inlineStr">
-        <is>
-          <t>Mudou a prioridade · 3175928/realizar acompanhamento</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H222" s="18" t="n"/>
     </row>
     <row r="223" ht="21" customHeight="1">
       <c r="A223" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
         <is>
-          <t>Fixar chicote elétrico solto na longarina LD</t>
+          <t>Fixar retrovisor LD e inferior LE</t>
         </is>
       </c>
       <c r="D223" s="17" t="inlineStr">
@@ -8075,37 +7921,33 @@
       </c>
       <c r="E223" s="19" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="F223" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G223" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H223" s="18" t="inlineStr">
-        <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H223" s="18" t="n"/>
     </row>
     <row r="224" ht="21" customHeight="1">
       <c r="A224" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C224" s="18" t="inlineStr">
         <is>
-          <t>Repor acabamento inferior frontal do parachoque</t>
+          <t>Fixar extensão da porta e saia lateral LD</t>
         </is>
       </c>
       <c r="D224" s="17" t="inlineStr">
@@ -8115,37 +7957,33 @@
       </c>
       <c r="E224" s="19" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F224" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G224" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H224" s="18" t="inlineStr">
-        <is>
-          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 20711859</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H224" s="18" t="n"/>
     </row>
     <row r="225" ht="21" customHeight="1">
       <c r="A225" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C225" s="18" t="inlineStr">
         <is>
-          <t>Repor vidrala sanefa/carga e corrigir empeno no varão</t>
+          <t>Repor quebra-sol do motorista</t>
         </is>
       </c>
       <c r="D225" s="17" t="inlineStr">
@@ -8155,37 +7993,37 @@
       </c>
       <c r="E225" s="19" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="F225" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G225" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de carteira</t>
         </is>
       </c>
       <c r="H225" s="18" t="inlineStr">
         <is>
-          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 1628953 peça adaptada</t>
+          <t>está dentro da cabine</t>
         </is>
       </c>
     </row>
     <row r="226" ht="21" customHeight="1">
       <c r="A226" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C226" s="18" t="inlineStr">
         <is>
-          <t>Corrigir iluminação interna da cabine</t>
+          <t>Substituir junta da tampa de válvulas com vazamento;20538793</t>
         </is>
       </c>
       <c r="D226" s="17" t="inlineStr">
@@ -8195,37 +8033,33 @@
       </c>
       <c r="E226" s="19" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="F226" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G226" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H226" s="18" t="inlineStr">
-        <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H226" s="18" t="n"/>
     </row>
     <row r="227" ht="21" customHeight="1">
       <c r="A227" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-711</t>
         </is>
       </c>
       <c r="C227" s="18" t="inlineStr">
         <is>
-          <t>Fixar mangueiras soltas na longarina LE</t>
+          <t>Substituir carcaça do filtro de ar</t>
         </is>
       </c>
       <c r="D227" s="17" t="inlineStr">
@@ -8235,37 +8069,33 @@
       </c>
       <c r="E227" s="19" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>021470</t>
         </is>
       </c>
       <c r="F227" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G227" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H227" s="18" t="inlineStr">
-        <is>
-          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
-        </is>
-      </c>
+          <t>Substituir filtro</t>
+        </is>
+      </c>
+      <c r="H227" s="18" t="n"/>
     </row>
     <row r="228" ht="21" customHeight="1">
       <c r="A228" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C228" s="18" t="inlineStr">
         <is>
-          <t>Corrigir vazamento na mangueira de arrefecimento do compressor</t>
+          <t>Substituir junta da tampa de válvulas com vazamento</t>
         </is>
       </c>
       <c r="D228" s="17" t="inlineStr">
@@ -8275,33 +8105,37 @@
       </c>
       <c r="E228" s="19" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>007157</t>
         </is>
       </c>
       <c r="F228" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G228" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H228" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H228" s="18" t="inlineStr">
+        <is>
+          <t>Frota não chegou na oficina · Peça 20804638 (junta motor D11)</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="21" customHeight="1">
       <c r="A229" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
         <is>
-          <t>Completar óleo hidráulico da direção</t>
+          <t>Recuperar mangueira de lubrificação do compressor com vazamento</t>
         </is>
       </c>
       <c r="D229" s="17" t="inlineStr">
@@ -8311,33 +8145,37 @@
       </c>
       <c r="E229" s="19" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>007334</t>
         </is>
       </c>
       <c r="F229" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G229" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H229" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H229" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="21" customHeight="1">
       <c r="A230" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C230" s="18" t="inlineStr">
         <is>
-          <t>Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
+          <t>Corrigir vazamento nas mangueiras do reservatório de óleo hidráulico</t>
         </is>
       </c>
       <c r="D230" s="17" t="inlineStr">
@@ -8347,33 +8185,37 @@
       </c>
       <c r="E230" s="19" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>007302</t>
         </is>
       </c>
       <c r="F230" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G230" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H230" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H230" s="18" t="inlineStr">
+        <is>
+          <t>Recuperar as mangueiras e substituir abraçadeiras · ⚠️ texto veio cortado do PDF de inspeção</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="21" customHeight="1">
       <c r="A231" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C231" s="18" t="inlineStr">
         <is>
-          <t>Substituir lanterna</t>
+          <t>Completar nível do líquido de arrefecimento</t>
         </is>
       </c>
       <c r="D231" s="17" t="inlineStr">
@@ -8383,33 +8225,37 @@
       </c>
       <c r="E231" s="19" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>007343</t>
         </is>
       </c>
       <c r="F231" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G231" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H231" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H231" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="21" customHeight="1">
       <c r="A232" s="16" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C232" s="18" t="inlineStr">
         <is>
-          <t>Vidro do passageira não aciona</t>
+          <t>Corrigir vazamento no diferencial do segundo eixo</t>
         </is>
       </c>
       <c r="D232" s="17" t="inlineStr">
@@ -8419,20 +8265,24 @@
       </c>
       <c r="E232" s="19" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>007344</t>
         </is>
       </c>
       <c r="F232" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G232" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H232" s="18" t="n"/>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H232" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="21" customHeight="1">
       <c r="A233" s="16" t="n">
@@ -8440,12 +8290,12 @@
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C233" s="18" t="inlineStr">
         <is>
-          <t>Substituir batentes das cabines</t>
+          <t>Corrigir empeno do aro segundo eixo LD</t>
         </is>
       </c>
       <c r="D233" s="17" t="inlineStr">
@@ -8455,20 +8305,24 @@
       </c>
       <c r="E233" s="19" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="F233" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G233" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H233" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H233" s="18" t="inlineStr">
+        <is>
+          <t>Mudou a prioridade · serviço interno Matriz</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="21" customHeight="1">
       <c r="A234" s="16" t="n">
@@ -8476,12 +8330,12 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C234" s="18" t="inlineStr">
         <is>
-          <t>Substituir mangueira do do tubo de ar quente com vazamento</t>
+          <t>Substituir juntas do escapamento gastas</t>
         </is>
       </c>
       <c r="D234" s="17" t="inlineStr">
@@ -8491,20 +8345,24 @@
       </c>
       <c r="E234" s="19" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="F234" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G234" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H234" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H234" s="18" t="inlineStr">
+        <is>
+          <t>Mudou a prioridade · Serviço interno Matriz · peça 20855371 (6 unidades) · realizar acompanhamento</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="21" customHeight="1">
       <c r="A235" s="16" t="n">
@@ -8512,12 +8370,12 @@
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C235" s="18" t="inlineStr">
         <is>
-          <t>Presilha do farol LD e LE</t>
+          <t>Substituir estribo da cabine LD</t>
         </is>
       </c>
       <c r="D235" s="17" t="inlineStr">
@@ -8527,20 +8385,24 @@
       </c>
       <c r="E235" s="19" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="F235" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G235" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H235" s="18" t="n"/>
+          <t>baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H235" s="18" t="inlineStr">
+        <is>
+          <t>Mudou a prioridade · 3175928/realizar acompanhamento</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="21" customHeight="1">
       <c r="A236" s="16" t="n">
@@ -8548,12 +8410,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C236" s="18" t="inlineStr">
         <is>
-          <t>Chave de luz</t>
+          <t>Fixar chicote elétrico solto na longarina LD</t>
         </is>
       </c>
       <c r="D236" s="17" t="inlineStr">
@@ -8563,20 +8425,24 @@
       </c>
       <c r="E236" s="19" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F236" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G236" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H236" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H236" s="18" t="inlineStr">
+        <is>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="21" customHeight="1">
       <c r="A237" s="16" t="n">
@@ -8584,12 +8450,12 @@
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C237" s="18" t="inlineStr">
         <is>
-          <t>Grade do farol LD</t>
+          <t>Repor acabamento inferior frontal do parachoque</t>
         </is>
       </c>
       <c r="D237" s="17" t="inlineStr">
@@ -8599,20 +8465,24 @@
       </c>
       <c r="E237" s="19" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="F237" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G237" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H237" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H237" s="18" t="inlineStr">
+        <is>
+          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 20711859</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="21" customHeight="1">
       <c r="A238" s="16" t="n">
@@ -8620,12 +8490,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C238" s="18" t="inlineStr">
         <is>
-          <t>Substituir pneu dianteiro LD com desgaste irregular e verificar demais - instalar indicadores de porca</t>
+          <t>Repor vidrala sanefa/carga e corrigir empeno no varão</t>
         </is>
       </c>
       <c r="D238" s="17" t="inlineStr">
@@ -8635,20 +8505,24 @@
       </c>
       <c r="E238" s="19" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="F238" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G238" s="18" t="inlineStr">
         <is>
-          <t>Baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H238" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H238" s="18" t="inlineStr">
+        <is>
+          <t>Reprogramada por conta de box bloqueado por conta de guindaste · 1628953 peça adaptada</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="21" customHeight="1">
       <c r="A239" s="16" t="n">
@@ -8656,12 +8530,12 @@
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C239" s="18" t="inlineStr">
         <is>
-          <t>Completar liquido de arrefecimento</t>
+          <t>Corrigir iluminação interna da cabine</t>
         </is>
       </c>
       <c r="D239" s="17" t="inlineStr">
@@ -8671,20 +8545,24 @@
       </c>
       <c r="E239" s="19" t="inlineStr">
         <is>
-          <t>021487</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="F239" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G239" s="18" t="inlineStr">
         <is>
-          <t>Completar liquido de arrefecimento</t>
-        </is>
-      </c>
-      <c r="H239" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H239" s="18" t="inlineStr">
+        <is>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="21" customHeight="1">
       <c r="A240" s="16" t="n">
@@ -8692,12 +8570,12 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C240" s="18" t="inlineStr">
         <is>
-          <t>Substituir chave geral avariada</t>
+          <t>Fixar mangueiras soltas na longarina LE</t>
         </is>
       </c>
       <c r="D240" s="17" t="inlineStr">
@@ -8707,22 +8585,22 @@
       </c>
       <c r="E240" s="19" t="inlineStr">
         <is>
-          <t>007158</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F240" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G240" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Preventiva</t>
         </is>
       </c>
       <c r="H240" s="18" t="inlineStr">
         <is>
-          <t>Frota não chegou na oficina · OS 7158 · 21243844</t>
+          <t>Serviço maior que o previsto · Reprogramada por conta de box bloqueado por conta de guindaste · serviço interno base Mossoró</t>
         </is>
       </c>
     </row>
@@ -8732,12 +8610,12 @@
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C241" s="18" t="inlineStr">
         <is>
-          <t>Repor tampa de proteção das tomadas frontais LD</t>
+          <t>Corrigir vazamento na mangueira de arrefecimento do compressor</t>
         </is>
       </c>
       <c r="D241" s="17" t="inlineStr">
@@ -8747,24 +8625,20 @@
       </c>
       <c r="E241" s="19" t="inlineStr">
         <is>
-          <t>007159</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="F241" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G241" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H241" s="18" t="inlineStr">
-        <is>
-          <t>Frota não chegou na oficina · erraque · OS 7159 · 20410141</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H241" s="18" t="n"/>
     </row>
     <row r="242" ht="21" customHeight="1">
       <c r="A242" s="16" t="n">
@@ -8772,12 +8646,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C242" s="18" t="inlineStr">
         <is>
-          <t>Fixar módulo do motor</t>
+          <t>Completar óleo hidráulico da direção</t>
         </is>
       </c>
       <c r="D242" s="17" t="inlineStr">
@@ -8787,24 +8661,20 @@
       </c>
       <c r="E242" s="19" t="inlineStr">
         <is>
-          <t>007349</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="F242" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G242" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H242" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz · evitando excesso de vibração no mesmo</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H242" s="18" t="n"/>
     </row>
     <row r="243" ht="21" customHeight="1">
       <c r="A243" s="16" t="n">
@@ -8812,12 +8682,12 @@
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
         <is>
-          <t>Substituir estepe furado</t>
+          <t>Substituir copo do filtro racor com vazamento; verificar item em estoque ou realizar pedido 20869391</t>
         </is>
       </c>
       <c r="D243" s="17" t="inlineStr">
@@ -8827,24 +8697,20 @@
       </c>
       <c r="E243" s="19" t="inlineStr">
         <is>
-          <t>007351</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="F243" s="18" t="inlineStr">
         <is>
-          <t>Luiz Paulo</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G243" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H243" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H243" s="18" t="n"/>
     </row>
     <row r="244" ht="21" customHeight="1">
       <c r="A244" s="16" t="n">
@@ -8852,12 +8718,12 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C244" s="18" t="inlineStr">
         <is>
-          <t>Substituir amortecedor dianteiro da cabine LD</t>
+          <t>Substituir lanterna</t>
         </is>
       </c>
       <c r="D244" s="17" t="inlineStr">
@@ -8867,24 +8733,20 @@
       </c>
       <c r="E244" s="19" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G244" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H244" s="18" t="inlineStr">
-        <is>
-          <t>Frota não chegou na oficina · Desgaste nas buchas, com ruído "ferro com ferro" ao movimentar · ⚠️ texto veio cortado do PDF de inspeção</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H244" s="18" t="n"/>
     </row>
     <row r="245" ht="21" customHeight="1">
       <c r="A245" s="16" t="n">
@@ -8892,12 +8754,12 @@
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
         <is>
-          <t>Substituir reservatório do limpador de parabrisas avariado</t>
+          <t>Vidro do passageira não aciona</t>
         </is>
       </c>
       <c r="D245" s="17" t="inlineStr">
@@ -8907,24 +8769,20 @@
       </c>
       <c r="E245" s="19" t="inlineStr">
         <is>
-          <t>007352</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="F245" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G245" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H245" s="18" t="inlineStr">
-        <is>
-          <t>verificar possível correção ou realizar pedido 20360593</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H245" s="18" t="n"/>
     </row>
     <row r="246" ht="21" customHeight="1">
       <c r="A246" s="16" t="n">
@@ -8932,12 +8790,12 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C246" s="18" t="inlineStr">
         <is>
-          <t>Trocar bateria</t>
+          <t>Substituir batentes das cabines</t>
         </is>
       </c>
       <c r="D246" s="17" t="inlineStr">
@@ -8947,7 +8805,7 @@
       </c>
       <c r="E246" s="19" t="inlineStr">
         <is>
-          <t>021496</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="F246" s="18" t="inlineStr">
@@ -8957,23 +8815,23 @@
       </c>
       <c r="G246" s="18" t="inlineStr">
         <is>
-          <t>Realizar troca de baterias</t>
+          <t>Baixa de carteira</t>
         </is>
       </c>
       <c r="H246" s="18" t="n"/>
     </row>
     <row r="247" ht="21" customHeight="1">
       <c r="A247" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>F-1065</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
         <is>
-          <t>Ferragem de pneus do bitrem</t>
+          <t>Substituir mangueira do do tubo de ar quente com vazamento</t>
         </is>
       </c>
       <c r="D247" s="17" t="inlineStr">
@@ -8983,37 +8841,33 @@
       </c>
       <c r="E247" s="19" t="inlineStr">
         <is>
-          <t>007384</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="F247" s="18" t="inlineStr">
         <is>
-          <t>Luiz Paulo · Airton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G247" s="18" t="inlineStr">
         <is>
-          <t>Borracharia 02/09</t>
-        </is>
-      </c>
-      <c r="H247" s="18" t="inlineStr">
-        <is>
-          <t>Verificar TAG · Bitrem identificado pelo PCM como F-1065 (mensagem das 10:03) · Origem: WhatsApp 02/09</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H247" s="18" t="n"/>
     </row>
     <row r="248" ht="21" customHeight="1">
       <c r="A248" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>F-327</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C248" s="18" t="inlineStr">
         <is>
-          <t>Repor acabamento do cinto do banco do motorista</t>
+          <t>Presilha do farol LD e LE</t>
         </is>
       </c>
       <c r="D248" s="17" t="inlineStr">
@@ -9021,35 +8875,35 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E248" s="19" t="n"/>
+      <c r="E248" s="19" t="inlineStr">
+        <is>
+          <t>21359</t>
+        </is>
+      </c>
       <c r="F248" s="18" t="inlineStr">
         <is>
-          <t>Júnior</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G248" s="18" t="inlineStr">
         <is>
-          <t>baixa de carteira</t>
-        </is>
-      </c>
-      <c r="H248" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou · Aguardando material · 0586501</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H248" s="18" t="n"/>
     </row>
     <row r="249" ht="21" customHeight="1">
       <c r="A249" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C249" s="18" t="inlineStr">
         <is>
-          <t>Realizar alinhamento</t>
+          <t>Chave de luz</t>
         </is>
       </c>
       <c r="D249" s="17" t="inlineStr">
@@ -9059,33 +8913,33 @@
       </c>
       <c r="E249" s="19" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="F249" s="18" t="inlineStr">
         <is>
-          <t>Airton · Luiz Paulo</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G249" s="18" t="inlineStr">
         <is>
-          <t>Alinhar pneus</t>
+          <t>Baixa de carteira</t>
         </is>
       </c>
       <c r="H249" s="18" t="n"/>
     </row>
     <row r="250" ht="21" customHeight="1">
       <c r="A250" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C250" s="18" t="inlineStr">
         <is>
-          <t>Motor esguicho</t>
+          <t>Grade do farol LD</t>
         </is>
       </c>
       <c r="D250" s="17" t="inlineStr">
@@ -9095,37 +8949,33 @@
       </c>
       <c r="E250" s="19" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="F250" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G250" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H250" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H250" s="18" t="n"/>
     </row>
     <row r="251" ht="21" customHeight="1">
       <c r="A251" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="C251" s="18" t="inlineStr">
         <is>
-          <t>Mola gás</t>
+          <t>Substituir pneu dianteiro LD com desgaste irregular e verificar demais - instalar indicadores de porca</t>
         </is>
       </c>
       <c r="D251" s="17" t="inlineStr">
@@ -9135,37 +8985,33 @@
       </c>
       <c r="E251" s="19" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="F251" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G251" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H251" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou</t>
-        </is>
-      </c>
+          <t>Baixa de carteira</t>
+        </is>
+      </c>
+      <c r="H251" s="18" t="n"/>
     </row>
     <row r="252" ht="21" customHeight="1">
       <c r="A252" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="C252" s="18" t="inlineStr">
         <is>
-          <t>Lamina d'agua</t>
+          <t>Completar liquido de arrefecimento</t>
         </is>
       </c>
       <c r="D252" s="17" t="inlineStr">
@@ -9175,37 +9021,33 @@
       </c>
       <c r="E252" s="19" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>021487</t>
         </is>
       </c>
       <c r="F252" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G252" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="H252" s="18" t="inlineStr">
-        <is>
-          <t>Peça não chegou</t>
-        </is>
-      </c>
+          <t>Completar liquido de arrefecimento</t>
+        </is>
+      </c>
+      <c r="H252" s="18" t="n"/>
     </row>
     <row r="253" ht="21" customHeight="1">
       <c r="A253" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C253" s="18" t="inlineStr">
         <is>
-          <t>Mola do pedal</t>
+          <t>Substituir chave geral avariada</t>
         </is>
       </c>
       <c r="D253" s="17" t="inlineStr">
@@ -9215,37 +9057,37 @@
       </c>
       <c r="E253" s="19" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>007158</t>
         </is>
       </c>
       <c r="F253" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="G253" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H253" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Frota não chegou na oficina · OS 7158 · 21243844</t>
         </is>
       </c>
     </row>
     <row r="254" ht="21" customHeight="1">
       <c r="A254" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C254" s="18" t="inlineStr">
         <is>
-          <t>Interruptor</t>
+          <t>Repor tampa de proteção das tomadas frontais LD</t>
         </is>
       </c>
       <c r="D254" s="17" t="inlineStr">
@@ -9255,37 +9097,37 @@
       </c>
       <c r="E254" s="19" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>007159</t>
         </is>
       </c>
       <c r="F254" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Gabriel</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G254" s="18" t="inlineStr">
         <is>
-          <t>Preventiva</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H254" s="18" t="inlineStr">
         <is>
-          <t>Peça não chegou</t>
+          <t>Frota não chegou na oficina · erraque · OS 7159 · 20410141</t>
         </is>
       </c>
     </row>
     <row r="255" ht="21" customHeight="1">
       <c r="A255" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>F-331</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C255" s="18" t="inlineStr">
         <is>
-          <t>Verificar fechamento das portas LD e LE</t>
+          <t>Fixar módulo do motor</t>
         </is>
       </c>
       <c r="D255" s="17" t="inlineStr">
@@ -9295,37 +9137,37 @@
       </c>
       <c r="E255" s="19" t="inlineStr">
         <is>
-          <t>021569</t>
+          <t>007349</t>
         </is>
       </c>
       <c r="F255" s="18" t="inlineStr">
         <is>
-          <t>Adilton · Júnior · Gabriel</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G255" s="18" t="inlineStr">
         <is>
-          <t>Programação 02/09</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H255" s="18" t="inlineStr">
         <is>
-          <t>Origem: WhatsApp 02/09</t>
+          <t>serviço interno Matriz · evitando excesso de vibração no mesmo</t>
         </is>
       </c>
     </row>
     <row r="256" ht="21" customHeight="1">
       <c r="A256" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>F-580</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C256" s="18" t="inlineStr">
         <is>
-          <t>Atuação / manutenção na frota F-580</t>
+          <t>Substituir estepe furado</t>
         </is>
       </c>
       <c r="D256" s="17" t="inlineStr">
@@ -9335,37 +9177,37 @@
       </c>
       <c r="E256" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>007351</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Luiz Paulo</t>
         </is>
       </c>
       <c r="G256" s="18" t="inlineStr">
         <is>
-          <t>Rentaf</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H256" s="18" t="inlineStr">
         <is>
-          <t>Local: Externo / Rentaf · Origem: WhatsApp 02/09</t>
+          <t>serviço interno Matriz</t>
         </is>
       </c>
     </row>
     <row r="257" ht="21" customHeight="1">
       <c r="A257" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C257" s="18" t="inlineStr">
         <is>
-          <t>Verificar falha na embreagem ativa</t>
+          <t>Substituir amortecedor dianteiro da cabine LD</t>
         </is>
       </c>
       <c r="D257" s="17" t="inlineStr">
@@ -9375,37 +9217,37 @@
       </c>
       <c r="E257" s="19" t="inlineStr">
         <is>
-          <t>021571</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="F257" s="18" t="inlineStr">
         <is>
-          <t>Thawan</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G257" s="18" t="inlineStr">
         <is>
-          <t>Extra 02/09</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H257" s="18" t="inlineStr">
         <is>
-          <t>EXTRA PROGRAMADO · Origem: WhatsApp 02/09</t>
+          <t>Frota não chegou na oficina · Desgaste nas buchas, com ruído "ferro com ferro" ao movimentar · ⚠️ texto veio cortado do PDF de inspeção</t>
         </is>
       </c>
     </row>
     <row r="258" ht="21" customHeight="1">
       <c r="A258" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>F-814</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="C258" s="18" t="inlineStr">
         <is>
-          <t>Trocar pneus da inspeção</t>
+          <t>Substituir reservatório do limpador de parabrisas avariado</t>
         </is>
       </c>
       <c r="D258" s="17" t="inlineStr">
@@ -9415,37 +9257,37 @@
       </c>
       <c r="E258" s="19" t="inlineStr">
         <is>
-          <t>007288</t>
+          <t>007352</t>
         </is>
       </c>
       <c r="F258" s="18" t="inlineStr">
         <is>
-          <t>Luiz Paulo · Airton</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="G258" s="18" t="inlineStr">
         <is>
-          <t>Borracharia 02/09</t>
+          <t>Baixa de pendências backlog</t>
         </is>
       </c>
       <c r="H258" s="18" t="inlineStr">
         <is>
-          <t>⚠️ VERIFICAR se é a mesma da linha 'revisar pneus dianteiros' (OS 7288), que já está na semana 36 · Origem: WhatsApp 02/09</t>
+          <t>verificar possível correção ou realizar pedido 20360593</t>
         </is>
       </c>
     </row>
     <row r="259" ht="21" customHeight="1">
       <c r="A259" s="16" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="C259" s="18" t="inlineStr">
         <is>
-          <t>Substituir flexível do escapamento avariado</t>
+          <t>Trocar bateria</t>
         </is>
       </c>
       <c r="D259" s="17" t="inlineStr">
@@ -9455,24 +9297,20 @@
       </c>
       <c r="E259" s="19" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>021496</t>
         </is>
       </c>
       <c r="F259" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G259" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H259" s="18" t="inlineStr">
-        <is>
-          <t>Frota não chegou na oficina · OS 7162 · 20442244 · evitando danificar mangueiras e chicotes</t>
-        </is>
-      </c>
+          <t>Realizar troca de baterias</t>
+        </is>
+      </c>
+      <c r="H259" s="18" t="n"/>
     </row>
     <row r="260" ht="21" customHeight="1">
       <c r="A260" s="16" t="n">
@@ -9480,12 +9318,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-1065</t>
         </is>
       </c>
       <c r="C260" s="18" t="inlineStr">
         <is>
-          <t>Substituir vedação dos pescadores do tanque LD e LE</t>
+          <t>Ferragem de pneus do bitrem</t>
         </is>
       </c>
       <c r="D260" s="17" t="inlineStr">
@@ -9495,22 +9333,22 @@
       </c>
       <c r="E260" s="19" t="inlineStr">
         <is>
-          <t>007356</t>
+          <t>007384</t>
         </is>
       </c>
       <c r="F260" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Luiz Paulo · Airton</t>
         </is>
       </c>
       <c r="G260" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>Borracharia 02/09</t>
         </is>
       </c>
       <c r="H260" s="18" t="inlineStr">
         <is>
-          <t>Devido vazamento · peça 20732301 (2 unidades) · realizar acompanhamento</t>
+          <t>Verificar TAG · Bitrem identificado pelo PCM como F-1065 (mensagem das 10:03) · Origem: WhatsApp 02/09</t>
         </is>
       </c>
     </row>
@@ -9520,12 +9358,12 @@
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-327</t>
         </is>
       </c>
       <c r="C261" s="18" t="inlineStr">
         <is>
-          <t>Repor tampa do reservatório do limpador de parabrisas</t>
+          <t>Repor acabamento do cinto do banco do motorista</t>
         </is>
       </c>
       <c r="D261" s="17" t="inlineStr">
@@ -9533,24 +9371,20 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E261" s="19" t="inlineStr">
-        <is>
-          <t>7164</t>
-        </is>
-      </c>
+      <c r="E261" s="19" t="n"/>
       <c r="F261" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Júnior</t>
         </is>
       </c>
       <c r="G261" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
+          <t>baixa de carteira</t>
         </is>
       </c>
       <c r="H261" s="18" t="inlineStr">
         <is>
-          <t>Frota não chegou na oficina · OS 7164 · 24425399</t>
+          <t>Peça não chegou · Aguardando material · 0586501</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9394,12 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C262" s="18" t="inlineStr">
         <is>
-          <t>Retirar mangueiras não utilizadas do rodoar</t>
+          <t>Realizar alinhamento</t>
         </is>
       </c>
       <c r="D262" s="17" t="inlineStr">
@@ -9575,24 +9409,20 @@
       </c>
       <c r="E262" s="19" t="inlineStr">
         <is>
-          <t>007360</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="F262" s="18" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Airton · Luiz Paulo</t>
         </is>
       </c>
       <c r="G262" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H262" s="18" t="inlineStr">
-        <is>
-          <t>serviço interno Matriz</t>
-        </is>
-      </c>
+          <t>Alinhar pneus</t>
+        </is>
+      </c>
+      <c r="H262" s="18" t="n"/>
     </row>
     <row r="263" ht="21" customHeight="1">
       <c r="A263" s="16" t="n">
@@ -9600,12 +9430,12 @@
       </c>
       <c r="B263" s="17" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-331</t>
         </is>
       </c>
       <c r="C263" s="18" t="inlineStr">
         <is>
-          <t>Calibração e troca de pneus</t>
+          <t>Motor esguicho</t>
         </is>
       </c>
       <c r="D263" s="17" t="inlineStr">
@@ -9615,20 +9445,24 @@
       </c>
       <c r="E263" s="19" t="inlineStr">
         <is>
-          <t>007351</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="F263" s="18" t="inlineStr">
         <is>
-          <t>Luiz Paulo</t>
+          <t>Adilton · Gabriel</t>
         </is>
       </c>
       <c r="G263" s="18" t="inlineStr">
         <is>
-          <t>Baixa de pendências backlog</t>
-        </is>
-      </c>
-      <c r="H263" s="18" t="n"/>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H263" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="21" customHeight="1">
       <c r="A264" s="16" t="n">
@@ -9636,169 +9470,555 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="C264" s="18" t="inlineStr">
+        <is>
+          <t>Mola gás</t>
+        </is>
+      </c>
+      <c r="D264" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E264" s="19" t="inlineStr">
+        <is>
+          <t>21297</t>
+        </is>
+      </c>
+      <c r="F264" s="18" t="inlineStr">
+        <is>
+          <t>Adilton · Gabriel</t>
+        </is>
+      </c>
+      <c r="G264" s="18" t="inlineStr">
+        <is>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H264" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="21" customHeight="1">
+      <c r="A265" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B265" s="17" t="inlineStr">
+        <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="C265" s="18" t="inlineStr">
+        <is>
+          <t>Lamina d'agua</t>
+        </is>
+      </c>
+      <c r="D265" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E265" s="19" t="inlineStr">
+        <is>
+          <t>21298</t>
+        </is>
+      </c>
+      <c r="F265" s="18" t="inlineStr">
+        <is>
+          <t>Adilton · Gabriel</t>
+        </is>
+      </c>
+      <c r="G265" s="18" t="inlineStr">
+        <is>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H265" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="21" customHeight="1">
+      <c r="A266" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B266" s="17" t="inlineStr">
+        <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="C266" s="18" t="inlineStr">
+        <is>
+          <t>Mola do pedal</t>
+        </is>
+      </c>
+      <c r="D266" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E266" s="19" t="inlineStr">
+        <is>
+          <t>21299</t>
+        </is>
+      </c>
+      <c r="F266" s="18" t="inlineStr">
+        <is>
+          <t>Adilton · Gabriel</t>
+        </is>
+      </c>
+      <c r="G266" s="18" t="inlineStr">
+        <is>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H266" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="21" customHeight="1">
+      <c r="A267" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B267" s="17" t="inlineStr">
+        <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="C267" s="18" t="inlineStr">
+        <is>
+          <t>Interruptor</t>
+        </is>
+      </c>
+      <c r="D267" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E267" s="19" t="inlineStr">
+        <is>
+          <t>21300</t>
+        </is>
+      </c>
+      <c r="F267" s="18" t="inlineStr">
+        <is>
+          <t>Adilton · Gabriel</t>
+        </is>
+      </c>
+      <c r="G267" s="18" t="inlineStr">
+        <is>
+          <t>Preventiva</t>
+        </is>
+      </c>
+      <c r="H267" s="18" t="inlineStr">
+        <is>
+          <t>Peça não chegou</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="21" customHeight="1">
+      <c r="A268" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B268" s="17" t="inlineStr">
+        <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="C268" s="18" t="inlineStr">
+        <is>
+          <t>Verificar fechamento das portas LD e LE</t>
+        </is>
+      </c>
+      <c r="D268" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E268" s="19" t="inlineStr">
+        <is>
+          <t>021569</t>
+        </is>
+      </c>
+      <c r="F268" s="18" t="inlineStr">
+        <is>
+          <t>Adilton · Júnior · Gabriel</t>
+        </is>
+      </c>
+      <c r="G268" s="18" t="inlineStr">
+        <is>
+          <t>Programação 02/09</t>
+        </is>
+      </c>
+      <c r="H268" s="18" t="inlineStr">
+        <is>
+          <t>Origem: WhatsApp 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="21" customHeight="1">
+      <c r="A269" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B269" s="17" t="inlineStr">
+        <is>
+          <t>F-580</t>
+        </is>
+      </c>
+      <c r="C269" s="18" t="inlineStr">
+        <is>
+          <t>Atuação / manutenção na frota F-580</t>
+        </is>
+      </c>
+      <c r="D269" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E269" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" s="18" t="inlineStr">
+        <is>
+          <t>Alexandre</t>
+        </is>
+      </c>
+      <c r="G269" s="18" t="inlineStr">
+        <is>
+          <t>Rentaf</t>
+        </is>
+      </c>
+      <c r="H269" s="18" t="inlineStr">
+        <is>
+          <t>Local: Externo / Rentaf · Origem: WhatsApp 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="21" customHeight="1">
+      <c r="A270" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B270" s="17" t="inlineStr">
+        <is>
+          <t>F-617</t>
+        </is>
+      </c>
+      <c r="C270" s="18" t="inlineStr">
+        <is>
+          <t>Verificar falha na embreagem ativa</t>
+        </is>
+      </c>
+      <c r="D270" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E270" s="19" t="inlineStr">
+        <is>
+          <t>021571</t>
+        </is>
+      </c>
+      <c r="F270" s="18" t="inlineStr">
+        <is>
+          <t>Thawan</t>
+        </is>
+      </c>
+      <c r="G270" s="18" t="inlineStr">
+        <is>
+          <t>Extra 02/09</t>
+        </is>
+      </c>
+      <c r="H270" s="18" t="inlineStr">
+        <is>
+          <t>EXTRA PROGRAMADO · Origem: WhatsApp 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="21" customHeight="1">
+      <c r="A271" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B271" s="17" t="inlineStr">
+        <is>
+          <t>F-814</t>
+        </is>
+      </c>
+      <c r="C271" s="18" t="inlineStr">
+        <is>
+          <t>Trocar pneus da inspeção</t>
+        </is>
+      </c>
+      <c r="D271" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E271" s="19" t="inlineStr">
+        <is>
+          <t>007288</t>
+        </is>
+      </c>
+      <c r="F271" s="18" t="inlineStr">
+        <is>
+          <t>Luiz Paulo · Airton</t>
+        </is>
+      </c>
+      <c r="G271" s="18" t="inlineStr">
+        <is>
+          <t>Borracharia 02/09</t>
+        </is>
+      </c>
+      <c r="H271" s="18" t="inlineStr">
+        <is>
+          <t>⚠️ VERIFICAR se é a mesma da linha 'revisar pneus dianteiros' (OS 7288), que já está na semana 36 · Origem: WhatsApp 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="21" customHeight="1">
+      <c r="A272" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B272" s="17" t="inlineStr">
+        <is>
+          <t>F-815</t>
+        </is>
+      </c>
+      <c r="C272" s="18" t="inlineStr">
+        <is>
+          <t>Substituir flexível do escapamento avariado</t>
+        </is>
+      </c>
+      <c r="D272" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E272" s="19" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="F272" s="18" t="inlineStr">
+        <is>
+          <t>Heliton</t>
+        </is>
+      </c>
+      <c r="G272" s="18" t="inlineStr">
+        <is>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H272" s="18" t="inlineStr">
+        <is>
+          <t>Frota não chegou na oficina · OS 7162 · 20442244 · evitando danificar mangueiras e chicotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="21" customHeight="1">
+      <c r="A273" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B273" s="17" t="inlineStr">
+        <is>
+          <t>F-815</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>Substituir vedação dos pescadores do tanque LD e LE</t>
+        </is>
+      </c>
+      <c r="D273" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E273" s="19" t="inlineStr">
+        <is>
+          <t>007356</t>
+        </is>
+      </c>
+      <c r="F273" s="18" t="inlineStr">
+        <is>
+          <t>Heliton</t>
+        </is>
+      </c>
+      <c r="G273" s="18" t="inlineStr">
+        <is>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H273" s="18" t="inlineStr">
+        <is>
+          <t>Devido vazamento · peça 20732301 (2 unidades) · realizar acompanhamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="21" customHeight="1">
+      <c r="A274" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B274" s="17" t="inlineStr">
+        <is>
+          <t>F-815</t>
+        </is>
+      </c>
+      <c r="C274" s="18" t="inlineStr">
+        <is>
+          <t>Repor tampa do reservatório do limpador de parabrisas</t>
+        </is>
+      </c>
+      <c r="D274" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E274" s="19" t="inlineStr">
+        <is>
+          <t>7164</t>
+        </is>
+      </c>
+      <c r="F274" s="18" t="inlineStr">
+        <is>
+          <t>Heliton</t>
+        </is>
+      </c>
+      <c r="G274" s="18" t="inlineStr">
+        <is>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H274" s="18" t="inlineStr">
+        <is>
+          <t>Frota não chegou na oficina · OS 7164 · 24425399</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="21" customHeight="1">
+      <c r="A275" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B275" s="17" t="inlineStr">
+        <is>
+          <t>F-815</t>
+        </is>
+      </c>
+      <c r="C275" s="18" t="inlineStr">
+        <is>
+          <t>Retirar mangueiras não utilizadas do rodoar</t>
+        </is>
+      </c>
+      <c r="D275" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E275" s="19" t="inlineStr">
+        <is>
+          <t>007360</t>
+        </is>
+      </c>
+      <c r="F275" s="18" t="inlineStr">
+        <is>
+          <t>Heliton</t>
+        </is>
+      </c>
+      <c r="G275" s="18" t="inlineStr">
+        <is>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H275" s="18" t="inlineStr">
+        <is>
+          <t>serviço interno Matriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="21" customHeight="1">
+      <c r="A276" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B276" s="17" t="inlineStr">
+        <is>
+          <t>F-815</t>
+        </is>
+      </c>
+      <c r="C276" s="18" t="inlineStr">
+        <is>
+          <t>Calibração e troca de pneus</t>
+        </is>
+      </c>
+      <c r="D276" s="17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E276" s="19" t="inlineStr">
+        <is>
+          <t>007351</t>
+        </is>
+      </c>
+      <c r="F276" s="18" t="inlineStr">
+        <is>
+          <t>Luiz Paulo</t>
+        </is>
+      </c>
+      <c r="G276" s="18" t="inlineStr">
+        <is>
+          <t>Baixa de pendências backlog</t>
+        </is>
+      </c>
+      <c r="H276" s="18" t="n"/>
+    </row>
+    <row r="277" ht="21" customHeight="1">
+      <c r="A277" s="16" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B277" s="17" t="inlineStr">
+        <is>
           <t>F-848</t>
         </is>
       </c>
-      <c r="C264" s="18" t="inlineStr">
+      <c r="C277" s="18" t="inlineStr">
         <is>
           <t>Trocar pneus</t>
         </is>
       </c>
-      <c r="D264" s="17" t="inlineStr">
+      <c r="D277" s="17" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E264" s="19" t="inlineStr">
+      <c r="E277" s="19" t="inlineStr">
         <is>
           <t>007386</t>
         </is>
       </c>
-      <c r="F264" s="18" t="inlineStr">
+      <c r="F277" s="18" t="inlineStr">
         <is>
           <t>Airton · Luiz Paulo</t>
         </is>
       </c>
-      <c r="G264" s="18" t="inlineStr">
+      <c r="G277" s="18" t="inlineStr">
         <is>
           <t>Borracharia 02/09</t>
         </is>
       </c>
-      <c r="H264" s="18" t="inlineStr">
+      <c r="H277" s="18" t="inlineStr">
         <is>
           <t>Origem: WhatsApp 02/09</t>
         </is>
       </c>
-    </row>
-    <row r="265" ht="21" customHeight="1">
-      <c r="A265" s="16" t="n"/>
-      <c r="B265" s="17" t="n"/>
-      <c r="C265" s="18" t="n"/>
-      <c r="D265" s="17" t="n"/>
-      <c r="E265" s="19" t="n"/>
-      <c r="F265" s="18" t="n"/>
-      <c r="G265" s="18" t="n"/>
-      <c r="H265" s="18" t="n"/>
-    </row>
-    <row r="266" ht="21" customHeight="1">
-      <c r="A266" s="16" t="n"/>
-      <c r="B266" s="17" t="n"/>
-      <c r="C266" s="18" t="n"/>
-      <c r="D266" s="17" t="n"/>
-      <c r="E266" s="19" t="n"/>
-      <c r="F266" s="18" t="n"/>
-      <c r="G266" s="18" t="n"/>
-      <c r="H266" s="18" t="n"/>
-    </row>
-    <row r="267" ht="21" customHeight="1">
-      <c r="A267" s="16" t="n"/>
-      <c r="B267" s="17" t="n"/>
-      <c r="C267" s="18" t="n"/>
-      <c r="D267" s="17" t="n"/>
-      <c r="E267" s="19" t="n"/>
-      <c r="F267" s="18" t="n"/>
-      <c r="G267" s="18" t="n"/>
-      <c r="H267" s="18" t="n"/>
-    </row>
-    <row r="268" ht="21" customHeight="1">
-      <c r="A268" s="16" t="n"/>
-      <c r="B268" s="17" t="n"/>
-      <c r="C268" s="18" t="n"/>
-      <c r="D268" s="17" t="n"/>
-      <c r="E268" s="19" t="n"/>
-      <c r="F268" s="18" t="n"/>
-      <c r="G268" s="18" t="n"/>
-      <c r="H268" s="18" t="n"/>
-    </row>
-    <row r="269" ht="21" customHeight="1">
-      <c r="A269" s="16" t="n"/>
-      <c r="B269" s="17" t="n"/>
-      <c r="C269" s="18" t="n"/>
-      <c r="D269" s="17" t="n"/>
-      <c r="E269" s="19" t="n"/>
-      <c r="F269" s="18" t="n"/>
-      <c r="G269" s="18" t="n"/>
-      <c r="H269" s="18" t="n"/>
-    </row>
-    <row r="270" ht="21" customHeight="1">
-      <c r="A270" s="16" t="n"/>
-      <c r="B270" s="17" t="n"/>
-      <c r="C270" s="18" t="n"/>
-      <c r="D270" s="17" t="n"/>
-      <c r="E270" s="19" t="n"/>
-      <c r="F270" s="18" t="n"/>
-      <c r="G270" s="18" t="n"/>
-      <c r="H270" s="18" t="n"/>
-    </row>
-    <row r="271" ht="21" customHeight="1">
-      <c r="A271" s="16" t="n"/>
-      <c r="B271" s="17" t="n"/>
-      <c r="C271" s="18" t="n"/>
-      <c r="D271" s="17" t="n"/>
-      <c r="E271" s="19" t="n"/>
-      <c r="F271" s="18" t="n"/>
-      <c r="G271" s="18" t="n"/>
-      <c r="H271" s="18" t="n"/>
-    </row>
-    <row r="272" ht="21" customHeight="1">
-      <c r="A272" s="16" t="n"/>
-      <c r="B272" s="17" t="n"/>
-      <c r="C272" s="18" t="n"/>
-      <c r="D272" s="17" t="n"/>
-      <c r="E272" s="19" t="n"/>
-      <c r="F272" s="18" t="n"/>
-      <c r="G272" s="18" t="n"/>
-      <c r="H272" s="18" t="n"/>
-    </row>
-    <row r="273" ht="21" customHeight="1">
-      <c r="A273" s="16" t="n"/>
-      <c r="B273" s="17" t="n"/>
-      <c r="C273" s="18" t="n"/>
-      <c r="D273" s="17" t="n"/>
-      <c r="E273" s="19" t="n"/>
-      <c r="F273" s="18" t="n"/>
-      <c r="G273" s="18" t="n"/>
-      <c r="H273" s="18" t="n"/>
-    </row>
-    <row r="274" ht="21" customHeight="1">
-      <c r="A274" s="16" t="n"/>
-      <c r="B274" s="17" t="n"/>
-      <c r="C274" s="18" t="n"/>
-      <c r="D274" s="17" t="n"/>
-      <c r="E274" s="19" t="n"/>
-      <c r="F274" s="18" t="n"/>
-      <c r="G274" s="18" t="n"/>
-      <c r="H274" s="18" t="n"/>
-    </row>
-    <row r="275" ht="21" customHeight="1">
-      <c r="A275" s="16" t="n"/>
-      <c r="B275" s="17" t="n"/>
-      <c r="C275" s="18" t="n"/>
-      <c r="D275" s="17" t="n"/>
-      <c r="E275" s="19" t="n"/>
-      <c r="F275" s="18" t="n"/>
-      <c r="G275" s="18" t="n"/>
-      <c r="H275" s="18" t="n"/>
-    </row>
-    <row r="276" ht="21" customHeight="1">
-      <c r="A276" s="16" t="n"/>
-      <c r="B276" s="17" t="n"/>
-      <c r="C276" s="18" t="n"/>
-      <c r="D276" s="17" t="n"/>
-      <c r="E276" s="19" t="n"/>
-      <c r="F276" s="18" t="n"/>
-      <c r="G276" s="18" t="n"/>
-      <c r="H276" s="18" t="n"/>
-    </row>
-    <row r="277" ht="21" customHeight="1">
-      <c r="A277" s="16" t="n"/>
-      <c r="B277" s="17" t="n"/>
-      <c r="C277" s="18" t="n"/>
-      <c r="D277" s="17" t="n"/>
-      <c r="E277" s="19" t="n"/>
-      <c r="F277" s="18" t="n"/>
-      <c r="G277" s="18" t="n"/>
-      <c r="H277" s="18" t="n"/>
     </row>
     <row r="278" ht="21" customHeight="1">
       <c r="A278" s="16" t="n"/>
@@ -14130,10 +14350,10 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="B7:B706" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Frota" error="Frota fora da lista. Pode continuar — depois acrescente na aba Listas." type="list" errorStyle="warning">
-      <formula1>=Listas!$A$2:$A$83</formula1>
+      <formula1>=Listas!$A$2:$A$84</formula1>
     </dataValidation>
     <dataValidation sqref="F7:F706" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Quem faz" error="Nome fora da lista. Pode continuar — depois acrescente na aba Listas." type="list" errorStyle="warning">
-      <formula1>=Listas!$B$2:$B$83</formula1>
+      <formula1>=Listas!$B$2:$B$84</formula1>
     </dataValidation>
     <dataValidation sqref="D7:D706" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Feito" error="Escolha Sim ou Não, ou deixe vazio." type="list">
       <formula1>"Sim,Não"</formula1>
@@ -14152,7 +14372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14344,7 +14564,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>F-424</t>
+          <t>F-332</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
@@ -14361,7 +14581,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>F-425</t>
+          <t>F-424</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -14378,7 +14598,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>F-433</t>
+          <t>F-425</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
@@ -14391,7 +14611,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>F-457</t>
+          <t>F-433</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -14408,7 +14628,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>F-458</t>
+          <t>F-457</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -14421,7 +14641,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>F-485</t>
+          <t>F-458</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
@@ -14429,7 +14649,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>F-580</t>
+          <t>F-485</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -14437,7 +14657,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>F-614</t>
+          <t>F-580</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -14450,7 +14670,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>F-616</t>
+          <t>F-614</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -14468,7 +14688,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>F-617</t>
+          <t>F-616</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -14486,7 +14706,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>F-618</t>
+          <t>F-617</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -14504,7 +14724,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>F-621</t>
+          <t>F-618</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -14522,7 +14742,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>F-624</t>
+          <t>F-621</t>
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
@@ -14540,7 +14760,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>F-626</t>
+          <t>F-624</t>
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
@@ -14558,7 +14778,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>F-627</t>
+          <t>F-626</t>
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
@@ -14566,7 +14786,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>F-696</t>
+          <t>F-627</t>
         </is>
       </c>
       <c r="B27" s="22" t="n"/>
@@ -14574,7 +14794,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>F-711</t>
+          <t>F-696</t>
         </is>
       </c>
       <c r="B28" s="22" t="n"/>
@@ -14582,7 +14802,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>F-745</t>
+          <t>F-711</t>
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
@@ -14590,7 +14810,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>F-763</t>
+          <t>F-745</t>
         </is>
       </c>
       <c r="B30" s="22" t="n"/>
@@ -14598,7 +14818,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>F-789</t>
+          <t>F-763</t>
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
@@ -14606,7 +14826,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>F-814</t>
+          <t>F-789</t>
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
@@ -14614,7 +14834,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>F-815</t>
+          <t>F-814</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
@@ -14622,7 +14842,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>F-817</t>
+          <t>F-815</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -14630,7 +14850,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>F-818</t>
+          <t>F-817</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -14638,7 +14858,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>F-848</t>
+          <t>F-818</t>
         </is>
       </c>
       <c r="B36" s="22" t="n"/>
@@ -14646,7 +14866,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>F-856</t>
+          <t>F-848</t>
         </is>
       </c>
       <c r="B37" s="22" t="n"/>
@@ -14654,7 +14874,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>F-871</t>
+          <t>F-856</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -14662,7 +14882,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>F-938</t>
+          <t>F-871</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -14670,7 +14890,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>F-964</t>
+          <t>F-938</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -14678,7 +14898,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>F-966</t>
+          <t>F-964</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -14686,7 +14906,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>F-968</t>
+          <t>F-966</t>
         </is>
       </c>
       <c r="B42" s="22" t="n"/>
@@ -14694,7 +14914,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>F-972</t>
+          <t>F-968</t>
         </is>
       </c>
       <c r="B43" s="22" t="n"/>
@@ -14702,13 +14922,17 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
+          <t>F-972</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
           <t>Não informada</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="22" t="n"/>
       <c r="B45" s="22" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -14862,6 +15086,10 @@
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="22" t="n"/>
       <c r="B83" s="22" t="n"/>
+    </row>
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="22" t="n"/>
+      <c r="B84" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
